--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="1163">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288782119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099271774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
+    <t xml:space="preserve">7.90288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099319458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910047531128</t>
   </si>
   <si>
     <t xml:space="preserve">7.68969249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87348031997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67407035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44433641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30282020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206869125366</t>
+    <t xml:space="preserve">7.87347984313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721410751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67406988143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97640228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46639108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">7.4434175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52612113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54450130462646</t>
+    <t xml:space="preserve">7.52612161636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54450035095215</t>
   </si>
   <si>
     <t xml:space="preserve">7.64742231369019</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">7.8018045425415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85694122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92218446731567</t>
+    <t xml:space="preserve">7.85693883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92218494415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.00397205352783</t>
@@ -113,64 +113,64 @@
     <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81466865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7650465965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142755508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336843490601</t>
+    <t xml:space="preserve">7.81466817855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76504707336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336891174316</t>
   </si>
   <si>
     <t xml:space="preserve">7.79261445999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74666690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910341262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56379890441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67315149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7852635383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74850463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478054046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002712249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11424350738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30354690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46343994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48641395568848</t>
+    <t xml:space="preserve">7.74666833877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56379842758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67315196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78526401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74850606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11424255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46344089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48641490936279</t>
   </si>
   <si>
     <t xml:space="preserve">8.75382518768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95966911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60128116607666</t>
+    <t xml:space="preserve">8.95966815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60128021240234</t>
   </si>
   <si>
     <t xml:space="preserve">8.28884220123291</t>
@@ -179,34 +179,34 @@
     <t xml:space="preserve">8.25208473205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46987152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36235618591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45425128936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71155548095703</t>
+    <t xml:space="preserve">8.46987342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36235809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45425033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7115535736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61598587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66560745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7942590713501</t>
+    <t xml:space="preserve">8.6159839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66560935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79426002502441</t>
   </si>
   <si>
     <t xml:space="preserve">9.00561618804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86869525909424</t>
+    <t xml:space="preserve">8.86869430541992</t>
   </si>
   <si>
     <t xml:space="preserve">9.11588859558105</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">9.14345645904541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33643436431885</t>
+    <t xml:space="preserve">9.33643341064453</t>
   </si>
   <si>
     <t xml:space="preserve">9.09751033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11680889129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091053009033</t>
+    <t xml:space="preserve">9.11680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091243743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.18572902679443</t>
@@ -236,34 +236,34 @@
     <t xml:space="preserve">9.02399349212646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76577281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99366855621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04237270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90177631378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67112159729004</t>
+    <t xml:space="preserve">8.76577091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9936695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04237461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90177536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67112064361572</t>
   </si>
   <si>
     <t xml:space="preserve">8.50755023956299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98191499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30630207061768</t>
+    <t xml:space="preserve">7.9819164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30630302429199</t>
   </si>
   <si>
     <t xml:space="preserve">8.40830421447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54614448547363</t>
+    <t xml:space="preserve">8.54614639282227</t>
   </si>
   <si>
     <t xml:space="preserve">8.5920934677124</t>
@@ -272,28 +272,28 @@
     <t xml:space="preserve">8.63803958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126560211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34214115142822</t>
+    <t xml:space="preserve">8.80804443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7512640953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126512527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34214210510254</t>
   </si>
   <si>
     <t xml:space="preserve">8.77496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77771854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75474452972412</t>
+    <t xml:space="preserve">8.77771949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7547435760498</t>
   </si>
   <si>
     <t xml:space="preserve">8.50571155548096</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">8.59944343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70144748687744</t>
+    <t xml:space="preserve">8.70144653320312</t>
   </si>
   <si>
     <t xml:space="preserve">8.57739067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39268207550049</t>
+    <t xml:space="preserve">8.39268112182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.34122180938721</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">8.56084823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71982574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05451393127441</t>
+    <t xml:space="preserve">8.71982479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
     <t xml:space="preserve">8.04164695739746</t>
@@ -329,52 +329,52 @@
     <t xml:space="preserve">8.0866756439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18867874145508</t>
+    <t xml:space="preserve">8.18867778778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.54890251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33478832244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50938892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03869819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437191009521</t>
+    <t xml:space="preserve">8.33478927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9210729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9743709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.01664352416992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1526460647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84939670562744</t>
+    <t xml:space="preserve">9.15264797210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84939575195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.07913017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85582828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27046394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33754634857178</t>
+    <t xml:space="preserve">8.8558292388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23370361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27046298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33754539489746</t>
   </si>
   <si>
     <t xml:space="preserve">8.20062351226807</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">8.50019836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43587207794189</t>
+    <t xml:space="preserve">8.43587112426758</t>
   </si>
   <si>
     <t xml:space="preserve">8.22451686859131</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">8.35408687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22083950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1528377532959</t>
+    <t xml:space="preserve">8.22084045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15283870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.39911556243896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42668437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48365592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.709716796875</t>
+    <t xml:space="preserve">8.42668342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48365688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70971775054932</t>
   </si>
   <si>
     <t xml:space="preserve">8.77128505706787</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">9.06534671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89809989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469390869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97712802886963</t>
+    <t xml:space="preserve">8.89809894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97712898254395</t>
   </si>
   <si>
     <t xml:space="preserve">9.05156135559082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23534965515137</t>
+    <t xml:space="preserve">9.2353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.20594501495361</t>
@@ -452,49 +452,49 @@
     <t xml:space="preserve">9.36216354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3952465057373</t>
+    <t xml:space="preserve">9.39524555206299</t>
   </si>
   <si>
     <t xml:space="preserve">9.61027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64887523651123</t>
+    <t xml:space="preserve">9.6488733291626</t>
   </si>
   <si>
     <t xml:space="preserve">9.69482231140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59373760223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64336204528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989288330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61763000488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265384674072</t>
+    <t xml:space="preserve">9.59373664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64336013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3198938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61763095855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">9.5110330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28497409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46324729919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33091831207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12875366210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26291847229004</t>
+    <t xml:space="preserve">9.28497314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46324825286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33092021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12875461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26291751861572</t>
   </si>
   <si>
     <t xml:space="preserve">9.14713287353516</t>
@@ -503,37 +503,37 @@
     <t xml:space="preserve">9.06075191497803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94128894805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37797927856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76025676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00653457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18940448760986</t>
+    <t xml:space="preserve">8.94128799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37798023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76025772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00653553009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18940544128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.96885776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1067008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44670677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39157009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46508598327637</t>
+    <t xml:space="preserve">9.10669994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44670581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39157104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7407693862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46508502960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.53860092163086</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">9.90617752075195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807262420654</t>
+    <t xml:space="preserve">9.99807167053223</t>
   </si>
   <si>
     <t xml:space="preserve">10.0532073974609</t>
@@ -560,16 +560,16 @@
     <t xml:space="preserve">9.92455673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81428241729736</t>
+    <t xml:space="preserve">9.81428337097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.94293594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0715856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083421707153</t>
+    <t xml:space="preserve">10.0715866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083431243896</t>
   </si>
   <si>
     <t xml:space="preserve">9.6672534942627</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">9.77752590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86941719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.163480758667</t>
+    <t xml:space="preserve">9.83266258239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86941814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1634798049927</t>
   </si>
   <si>
     <t xml:space="preserve">10.310510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0348310470581</t>
+    <t xml:space="preserve">10.0348281860352</t>
   </si>
   <si>
     <t xml:space="preserve">10.016450881958</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">10.1267213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5126791000366</t>
+    <t xml:space="preserve">10.5126781463623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6045722961426</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">10.7332239151001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4207830429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4759197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288898468018</t>
+    <t xml:space="preserve">10.420783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4759206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288888931274</t>
   </si>
   <si>
     <t xml:space="preserve">9.97969436645508</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">9.85104084014893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.941086769104</t>
+    <t xml:space="preserve">10.1821956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94108581542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.88544654846191</t>
@@ -644,58 +644,58 @@
     <t xml:space="preserve">9.92253971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1451015472412</t>
+    <t xml:space="preserve">10.1451005935669</t>
   </si>
   <si>
     <t xml:space="preserve">9.99672698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2007398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2192869186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0894622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73707294464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86689949035645</t>
+    <t xml:space="preserve">10.2007417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2192888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0894613265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523672103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73707103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86690044403076</t>
   </si>
   <si>
     <t xml:space="preserve">10.1636476516724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5531301498413</t>
+    <t xml:space="preserve">10.5531311035156</t>
   </si>
   <si>
     <t xml:space="preserve">10.4047565460205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.423303604126</t>
+    <t xml:space="preserve">10.4233045578003</t>
   </si>
   <si>
     <t xml:space="preserve">10.3862104415894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3676633834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82980632781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3120241165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338220596313</t>
+    <t xml:space="preserve">10.3676624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3120231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338201522827</t>
   </si>
   <si>
     <t xml:space="preserve">9.81125926971436</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">10.8498802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789447784424</t>
+    <t xml:space="preserve">10.4789428710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651763916016</t>
+    <t xml:space="preserve">11.1651754379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.6102991104126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062852859497</t>
+    <t xml:space="preserve">11.4062843322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.536111831665</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">12.2408905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4449052810669</t>
+    <t xml:space="preserve">12.4449043273926</t>
   </si>
   <si>
     <t xml:space="preserve">12.5932807922363</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">12.1852502822876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.573205947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5917530059814</t>
+    <t xml:space="preserve">11.5732049942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5917510986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401266098022</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">13.5020723342896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0584783554077</t>
+    <t xml:space="preserve">14.0584774017334</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649791717529</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">13.1125907897949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3892641067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3521718978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2965307235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4078102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2037982940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779836654663</t>
+    <t xml:space="preserve">12.3892650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3521728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2965297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.407811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2037954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779846191406</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963354110718</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">13.168231010437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8529348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7045583724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3707180023193</t>
+    <t xml:space="preserve">12.852933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7045593261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561857223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3707189559937</t>
   </si>
   <si>
     <t xml:space="preserve">12.7787485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8158407211304</t>
+    <t xml:space="preserve">12.8158416748047</t>
   </si>
   <si>
     <t xml:space="preserve">12.8900289535522</t>
@@ -869,37 +869,37 @@
     <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3351526260376</t>
+    <t xml:space="preserve">13.335150718689</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569486618042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6489200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3150787353516</t>
+    <t xml:space="preserve">12.6489191055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3150777816772</t>
   </si>
   <si>
     <t xml:space="preserve">12.463451385498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4263572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514070510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2950029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0168008804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909881591797</t>
+    <t xml:space="preserve">12.4263582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2950048446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0167999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090989112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353479385376</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">10.7571449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3135499954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280813217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2764558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.220817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3691902160645</t>
+    <t xml:space="preserve">11.3135509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2764568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2208156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3691892623901</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095342636108</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40322971343994</t>
+    <t xml:space="preserve">9.40322780609131</t>
   </si>
   <si>
     <t xml:space="preserve">8.88391780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55160427093506</t>
+    <t xml:space="preserve">9.55160331726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.71699810028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80973148345947</t>
+    <t xml:space="preserve">8.80973243713379</t>
   </si>
   <si>
     <t xml:space="preserve">8.20696067810059</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">8.53152942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43879413604736</t>
+    <t xml:space="preserve">8.438796043396</t>
   </si>
   <si>
     <t xml:space="preserve">9.64433860778809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7200527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77416515350342</t>
+    <t xml:space="preserve">10.7200536727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77416610717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2934770584106</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">10.2378358840942</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71852493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152740478516</t>
+    <t xml:space="preserve">9.71852397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152759552002</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015056610107</t>
@@ -986,31 +986,31 @@
     <t xml:space="preserve">11.6844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8699531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4819984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6118259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7586736679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7246360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4835262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.650447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930826187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0414590835571</t>
+    <t xml:space="preserve">11.8699541091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6118268966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7586727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7246341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4835271835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6504487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0414571762085</t>
   </si>
   <si>
     <t xml:space="preserve">14.9301767349243</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">15.2825660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462377548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687967300415</t>
+    <t xml:space="preserve">15.7462368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687995910645</t>
   </si>
   <si>
     <t xml:space="preserve">15.3938465118408</t>
@@ -1034,40 +1034,40 @@
     <t xml:space="preserve">14.9487228393555</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6148824691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4665069580078</t>
+    <t xml:space="preserve">14.6148815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4665060043335</t>
   </si>
   <si>
     <t xml:space="preserve">14.0399303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1326627731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7988214492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8173685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6689949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0770244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.318133354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076148986816</t>
+    <t xml:space="preserve">14.1326637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7988233566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8173675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6689939498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0770235061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3181324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076139450073</t>
   </si>
   <si>
     <t xml:space="preserve">14.9858169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560493469238</t>
+    <t xml:space="preserve">14.5560503005981</t>
   </si>
   <si>
     <t xml:space="preserve">14.79896068573</t>
@@ -1082,25 +1082,28 @@
     <t xml:space="preserve">14.7615909576416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2660999298096</t>
+    <t xml:space="preserve">14.9858179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2661008834839</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4155855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221578598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0045022964478</t>
+    <t xml:space="preserve">15.4155864715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221559524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0045032501221</t>
   </si>
   <si>
     <t xml:space="preserve">14.6121063232422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0792446136475</t>
+    <t xml:space="preserve">15.0792455673218</t>
   </si>
   <si>
     <t xml:space="preserve">14.911075592041</t>
@@ -1109,43 +1112,43 @@
     <t xml:space="preserve">14.6494770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0231885910034</t>
+    <t xml:space="preserve">15.1353015899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.929759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9484462738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5650682449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1630077362061</t>
+    <t xml:space="preserve">14.9484453201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813070297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5650672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1630058288574</t>
   </si>
   <si>
     <t xml:space="preserve">16.9664878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6765384674072</t>
+    <t xml:space="preserve">17.6765403747559</t>
   </si>
   <si>
     <t xml:space="preserve">16.723575592041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8730583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336242675781</t>
+    <t xml:space="preserve">16.8730564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336261749268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4149398803711</t>
@@ -1154,25 +1157,25 @@
     <t xml:space="preserve">17.3962554931641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7886524200439</t>
+    <t xml:space="preserve">17.7886505126953</t>
   </si>
   <si>
     <t xml:space="preserve">18.0128765106201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8820781707764</t>
+    <t xml:space="preserve">17.882080078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6578540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5270519256592</t>
+    <t xml:space="preserve">18.3118457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6578502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
     <t xml:space="preserve">17.9941940307617</t>
@@ -1181,10 +1184,10 @@
     <t xml:space="preserve">18.6855602264404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3305339813232</t>
+    <t xml:space="preserve">19.1526966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3305320739746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2184181213379</t>
@@ -1202,7 +1205,7 @@
     <t xml:space="preserve">17.4709968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.807336807251</t>
+    <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9291152954102</t>
@@ -1214,43 +1217,43 @@
     <t xml:space="preserve">15.8266668319702</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4619770050049</t>
+    <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
     <t xml:space="preserve">15.9574661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3782138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706108093262</t>
+    <t xml:space="preserve">15.378212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706089019775</t>
   </si>
   <si>
     <t xml:space="preserve">16.5367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927772521973</t>
+    <t xml:space="preserve">16.5927753448486</t>
   </si>
   <si>
     <t xml:space="preserve">16.2938060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4246082305908</t>
+    <t xml:space="preserve">16.4246044158936</t>
   </si>
   <si>
     <t xml:space="preserve">16.2751235961914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8543720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7048892974854</t>
+    <t xml:space="preserve">16.8543739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7048873901367</t>
   </si>
   <si>
     <t xml:space="preserve">16.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4993495941162</t>
+    <t xml:space="preserve">16.4993457794189</t>
   </si>
   <si>
     <t xml:space="preserve">16.3685474395752</t>
@@ -1262,109 +1265,109 @@
     <t xml:space="preserve">16.6862049102783</t>
   </si>
   <si>
-    <t xml:space="preserve">16.63014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114616394043</t>
+    <t xml:space="preserve">16.6301460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114597320557</t>
   </si>
   <si>
     <t xml:space="preserve">16.7609462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170013427734</t>
+    <t xml:space="preserve">16.8170032501221</t>
   </si>
   <si>
     <t xml:space="preserve">16.7983169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4342708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671316146851</t>
+    <t xml:space="preserve">15.7892951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4342727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671325683594</t>
   </si>
   <si>
     <t xml:space="preserve">14.6868476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5373640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.32151222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5180339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6211252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8827238082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377490997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4806632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4432907104492</t>
+    <t xml:space="preserve">14.5373649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3215103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5180320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6211261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8827228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4806613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4432926177979</t>
   </si>
   <si>
     <t xml:space="preserve">16.9478015899658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0785999298096</t>
+    <t xml:space="preserve">17.0785980224609</t>
   </si>
   <si>
     <t xml:space="preserve">16.648832321167</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9104290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8917446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.900764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0876178741455</t>
+    <t xml:space="preserve">16.9104270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8917465209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9007625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0876197814941</t>
   </si>
   <si>
     <t xml:space="preserve">18.5360736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9194507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0502471923828</t>
+    <t xml:space="preserve">17.9194488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0502490997314</t>
   </si>
   <si>
     <t xml:space="preserve">16.5740909576416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.742259979248</t>
+    <t xml:space="preserve">16.7422580718994</t>
   </si>
   <si>
     <t xml:space="preserve">16.5554046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3124942779541</t>
+    <t xml:space="preserve">16.3124923706055</t>
   </si>
   <si>
     <t xml:space="preserve">17.0225448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0695819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8453540802002</t>
+    <t xml:space="preserve">16.069580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8453531265259</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519245147705</t>
@@ -1373,16 +1376,16 @@
     <t xml:space="preserve">15.6024398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0135250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9014120101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3595285415649</t>
+    <t xml:space="preserve">16.0135231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9014091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9761505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3595275878906</t>
   </si>
   <si>
     <t xml:space="preserve">14.5186777114868</t>
@@ -1391,34 +1394,34 @@
     <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8550186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5090112686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6398105621338</t>
+    <t xml:space="preserve">14.855019569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.50901222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6398115158081</t>
   </si>
   <si>
     <t xml:space="preserve">15.6771802902222</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5276985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145519256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716415405273</t>
+    <t xml:space="preserve">15.5276975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145547866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716424942017</t>
   </si>
   <si>
     <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8640403747559</t>
+    <t xml:space="preserve">15.6584978103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8640394210815</t>
   </si>
   <si>
     <t xml:space="preserve">16.2190628051758</t>
@@ -1436,58 +1439,58 @@
     <t xml:space="preserve">17.5831108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7699661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1249904632568</t>
+    <t xml:space="preserve">17.7699642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1249923706055</t>
   </si>
   <si>
     <t xml:space="preserve">17.6391658782959</t>
   </si>
   <si>
-    <t xml:space="preserve">18.480016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0689334869385</t>
+    <t xml:space="preserve">18.4800186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0689315795898</t>
   </si>
   <si>
     <t xml:space="preserve">17.1720294952393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5644226074219</t>
+    <t xml:space="preserve">17.5644245147705</t>
   </si>
   <si>
     <t xml:space="preserve">17.6017932891846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.713264465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8066921234131</t>
+    <t xml:space="preserve">17.7512817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7132663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8066902160645</t>
   </si>
   <si>
     <t xml:space="preserve">19.4329814910889</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5264072418213</t>
+    <t xml:space="preserve">19.5264053344727</t>
   </si>
   <si>
     <t xml:space="preserve">19.9935455322266</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5541133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4606857299805</t>
+    <t xml:space="preserve">20.5541152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4606876373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.2738304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1336860656738</t>
+    <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
     <t xml:space="preserve">19.9468326568604</t>
@@ -1496,31 +1499,31 @@
     <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6475391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2081050872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5818195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9555282592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.30153465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8343982696533</t>
+    <t xml:space="preserve">20.6008262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6475410461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2081069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5818214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9555320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3015365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8343963623047</t>
   </si>
   <si>
     <t xml:space="preserve">20.0869750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7599754333496</t>
+    <t xml:space="preserve">19.7599773406982</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796924591064</t>
@@ -1529,7 +1532,7 @@
     <t xml:space="preserve">19.1994113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7350769042969</t>
+    <t xml:space="preserve">19.7350749969482</t>
   </si>
   <si>
     <t xml:space="preserve">19.9700183868408</t>
@@ -1589,7 +1592,7 @@
     <t xml:space="preserve">18.4757900238037</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7765140533447</t>
+    <t xml:space="preserve">18.7765159606934</t>
   </si>
   <si>
     <t xml:space="preserve">18.5133819580078</t>
@@ -1598,7 +1601,7 @@
     <t xml:space="preserve">18.7953128814697</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6449508666992</t>
+    <t xml:space="preserve">18.6449489593506</t>
   </si>
   <si>
     <t xml:space="preserve">20.0639953613281</t>
@@ -1610,7 +1613,7 @@
     <t xml:space="preserve">20.8158054351807</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2856922149658</t>
+    <t xml:space="preserve">21.2856903076172</t>
   </si>
   <si>
     <t xml:space="preserve">22.0844917297363</t>
@@ -1619,19 +1622,19 @@
     <t xml:space="preserve">22.4603977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9772682189941</t>
+    <t xml:space="preserve">22.9772663116455</t>
   </si>
   <si>
     <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.494140625</t>
+    <t xml:space="preserve">23.4941387176514</t>
   </si>
   <si>
     <t xml:space="preserve">23.1652221679688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0712432861328</t>
+    <t xml:space="preserve">23.0712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">23.5881156921387</t>
@@ -1658,16 +1661,16 @@
     <t xml:space="preserve">23.5411281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.447151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.870044708252</t>
+    <t xml:space="preserve">22.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8700466156006</t>
   </si>
   <si>
     <t xml:space="preserve">21.7555732727051</t>
@@ -1685,19 +1688,19 @@
     <t xml:space="preserve">21.5676212310791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1447257995605</t>
+    <t xml:space="preserve">21.1447238922119</t>
   </si>
   <si>
     <t xml:space="preserve">20.9097843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.76881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5808658599854</t>
+    <t xml:space="preserve">20.9567718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7688179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.580867767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.2387008666992</t>
@@ -1709,7 +1712,7 @@
     <t xml:space="preserve">24.8098106384277</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6688461303711</t>
+    <t xml:space="preserve">24.6688442230225</t>
   </si>
   <si>
     <t xml:space="preserve">24.9977626800537</t>
@@ -1718,19 +1721,19 @@
     <t xml:space="preserve">24.4339046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3869152069092</t>
+    <t xml:space="preserve">24.3869171142578</t>
   </si>
   <si>
     <t xml:space="preserve">23.4001617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6351051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230571746826</t>
+    <t xml:space="preserve">23.635103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230590820312</t>
   </si>
   <si>
     <t xml:space="preserve">24.2929382324219</t>
@@ -1742,10 +1745,10 @@
     <t xml:space="preserve">24.4808921813965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5616226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206581115723</t>
+    <t xml:space="preserve">25.5616245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.6556015014648</t>
@@ -1754,31 +1757,31 @@
     <t xml:space="preserve">25.3736705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">25.279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061847686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.554370880127</t>
+    <t xml:space="preserve">25.2796936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543727874756</t>
   </si>
   <si>
     <t xml:space="preserve">22.2724456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1182346343994</t>
+    <t xml:space="preserve">23.1182327270508</t>
   </si>
   <si>
     <t xml:space="preserve">24.2459526062012</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7158355712891</t>
+    <t xml:space="preserve">24.7158336639404</t>
   </si>
   <si>
     <t xml:space="preserve">24.5278816223145</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7628211975098</t>
+    <t xml:space="preserve">24.7628231048584</t>
   </si>
   <si>
     <t xml:space="preserve">23.9170341491699</t>
@@ -1808,7 +1811,7 @@
     <t xml:space="preserve">21.4266548156738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4398994445801</t>
+    <t xml:space="preserve">20.4399013519287</t>
   </si>
   <si>
     <t xml:space="preserve">21.8025608062744</t>
@@ -1817,7 +1820,7 @@
     <t xml:space="preserve">20.8627967834473</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3326759338379</t>
+    <t xml:space="preserve">21.3326778411865</t>
   </si>
   <si>
     <t xml:space="preserve">21.6146087646484</t>
@@ -1826,16 +1829,16 @@
     <t xml:space="preserve">21.3796653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2519493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3459243774414</t>
+    <t xml:space="preserve">20.2519474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.34592628479</t>
   </si>
   <si>
     <t xml:space="preserve">19.218204498291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5697650909424</t>
+    <t xml:space="preserve">18.569766998291</t>
   </si>
   <si>
     <t xml:space="preserve">19.8760414123535</t>
@@ -1868,10 +1871,10 @@
     <t xml:space="preserve">18.6637439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9230270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615962982178</t>
+    <t xml:space="preserve">19.9230289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615943908691</t>
   </si>
   <si>
     <t xml:space="preserve">21.990514755249</t>
@@ -1898,7 +1901,7 @@
     <t xml:space="preserve">18.7013339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8965358734131</t>
+    <t xml:space="preserve">21.8965377807617</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049598693848</t>
@@ -1910,7 +1913,7 @@
     <t xml:space="preserve">18.3254280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9683170318604</t>
+    <t xml:space="preserve">17.9683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">17.8931350708008</t>
@@ -2159,9 +2162,6 @@
     <t xml:space="preserve">23.4040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302806854248</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.6883068084717</t>
   </si>
   <si>
@@ -3498,6 +3498,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -17322,7 +17325,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17348,7 +17351,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17400,7 +17403,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17426,7 +17429,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17452,7 +17455,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17478,7 +17481,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17504,7 +17507,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17530,7 +17533,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17556,7 +17559,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17582,7 +17585,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17608,7 +17611,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17634,7 +17637,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17660,7 +17663,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17686,7 +17689,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17712,7 +17715,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17738,7 +17741,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17764,7 +17767,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17790,7 +17793,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17816,7 +17819,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17842,7 +17845,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17868,7 +17871,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17894,7 +17897,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17946,7 +17949,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17972,7 +17975,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17998,7 +18001,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18024,7 +18027,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -18050,7 +18053,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18076,7 +18079,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18102,7 +18105,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18128,7 +18131,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18154,7 +18157,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18180,7 +18183,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18206,7 +18209,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18232,7 +18235,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18258,7 +18261,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18284,7 +18287,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18310,7 +18313,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18336,7 +18339,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18362,7 +18365,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18388,7 +18391,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18414,7 +18417,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18440,7 +18443,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18466,7 +18469,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18492,7 +18495,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18518,7 +18521,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18544,7 +18547,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18570,7 +18573,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18596,7 +18599,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18622,7 +18625,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18648,7 +18651,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18674,7 +18677,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18700,7 +18703,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18726,7 +18729,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18752,7 +18755,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18778,7 +18781,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18804,7 +18807,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18830,7 +18833,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18856,7 +18859,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18882,7 +18885,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18908,7 +18911,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18934,7 +18937,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18960,7 +18963,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18986,7 +18989,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19012,7 +19015,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -19038,7 +19041,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -19064,7 +19067,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19090,7 +19093,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19116,7 +19119,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19142,7 +19145,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19168,7 +19171,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19194,7 +19197,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19220,7 +19223,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19246,7 +19249,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19272,7 +19275,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19298,7 +19301,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19324,7 +19327,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19350,7 +19353,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19376,7 +19379,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19402,7 +19405,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19428,7 +19431,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19454,7 +19457,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19480,7 +19483,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19506,7 +19509,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19532,7 +19535,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19558,7 +19561,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19584,7 +19587,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19610,7 +19613,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19636,7 +19639,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19662,7 +19665,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19688,7 +19691,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19714,7 +19717,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19740,7 +19743,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19766,7 +19769,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19792,7 +19795,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19818,7 +19821,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19844,7 +19847,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19870,7 +19873,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19896,7 +19899,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19922,7 +19925,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19948,7 +19951,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19974,7 +19977,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20000,7 +20003,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -20026,7 +20029,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20052,7 +20055,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20078,7 +20081,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20104,7 +20107,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20130,7 +20133,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20156,7 +20159,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20182,7 +20185,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20208,7 +20211,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20234,7 +20237,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20260,7 +20263,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20286,7 +20289,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20312,7 +20315,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20338,7 +20341,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20364,7 +20367,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20390,7 +20393,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20416,7 +20419,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20442,7 +20445,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20468,7 +20471,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20494,7 +20497,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20520,7 +20523,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20546,7 +20549,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20572,7 +20575,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20598,7 +20601,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20624,7 +20627,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20650,7 +20653,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20676,7 +20679,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20702,7 +20705,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20728,7 +20731,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20754,7 +20757,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20780,7 +20783,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20806,7 +20809,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20832,7 +20835,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20858,7 +20861,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20884,7 +20887,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20910,7 +20913,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20936,7 +20939,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20962,7 +20965,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20988,7 +20991,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -21014,7 +21017,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21040,7 +21043,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21066,7 +21069,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21092,7 +21095,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21118,7 +21121,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21144,7 +21147,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21170,7 +21173,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21196,7 +21199,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21222,7 +21225,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21248,7 +21251,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21274,7 +21277,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21300,7 +21303,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21326,7 +21329,7 @@
         <v>17.6916809082031</v>
       </c>
       <c r="G673" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21352,7 +21355,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21378,7 +21381,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21404,7 +21407,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21430,7 +21433,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21456,7 +21459,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21482,7 +21485,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21508,7 +21511,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21534,7 +21537,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21560,7 +21563,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21586,7 +21589,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21612,7 +21615,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21638,7 +21641,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21664,7 +21667,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21690,7 +21693,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21716,7 +21719,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21742,7 +21745,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21768,7 +21771,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21794,7 +21797,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21820,7 +21823,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21846,7 +21849,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21872,7 +21875,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21898,7 +21901,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21950,7 +21953,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21976,7 +21979,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22002,7 +22005,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22028,7 +22031,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22054,7 +22057,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22080,7 +22083,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22106,7 +22109,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22132,7 +22135,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22158,7 +22161,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22184,7 +22187,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22210,7 +22213,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22236,7 +22239,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22262,7 +22265,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22288,7 +22291,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22314,7 +22317,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22340,7 +22343,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22366,7 +22369,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22392,7 +22395,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22418,7 +22421,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22444,7 +22447,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22470,7 +22473,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22496,7 +22499,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22522,7 +22525,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22548,7 +22551,7 @@
         <v>18.2742824554443</v>
       </c>
       <c r="G720" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22574,7 +22577,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22600,7 +22603,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22626,7 +22629,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22652,7 +22655,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22678,7 +22681,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22704,7 +22707,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22730,7 +22733,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22756,7 +22759,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22782,7 +22785,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22808,7 +22811,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22834,7 +22837,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22860,7 +22863,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22886,7 +22889,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22912,7 +22915,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22938,7 +22941,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22964,7 +22967,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22990,7 +22993,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23016,7 +23019,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23042,7 +23045,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23068,7 +23071,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23094,7 +23097,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G741" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23120,7 +23123,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23146,7 +23149,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23172,7 +23175,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23198,7 +23201,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23224,7 +23227,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23250,7 +23253,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23276,7 +23279,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23302,7 +23305,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23328,7 +23331,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23354,7 +23357,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23380,7 +23383,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23406,7 +23409,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23432,7 +23435,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23458,7 +23461,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23484,7 +23487,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23510,7 +23513,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23536,7 +23539,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23562,7 +23565,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23588,7 +23591,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23614,7 +23617,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23640,7 +23643,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23666,7 +23669,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G763" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23692,7 +23695,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23718,7 +23721,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23744,7 +23747,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23770,7 +23773,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23796,7 +23799,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G768" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23822,7 +23825,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23848,7 +23851,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23874,7 +23877,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23900,7 +23903,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23926,7 +23929,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23952,7 +23955,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23978,7 +23981,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24004,7 +24007,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24030,7 +24033,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24056,7 +24059,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24082,7 +24085,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24108,7 +24111,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24134,7 +24137,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24160,7 +24163,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24186,7 +24189,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24212,7 +24215,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24238,7 +24241,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24264,7 +24267,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24290,7 +24293,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24316,7 +24319,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24342,7 +24345,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24368,7 +24371,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24394,7 +24397,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24420,7 +24423,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24446,7 +24449,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24472,7 +24475,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24498,7 +24501,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24524,7 +24527,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24550,7 +24553,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24576,7 +24579,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24602,7 +24605,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G799" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24628,7 +24631,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24654,7 +24657,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24680,7 +24683,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24706,7 +24709,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24732,7 +24735,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24758,7 +24761,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24784,7 +24787,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24810,7 +24813,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24836,7 +24839,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24862,7 +24865,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24888,7 +24891,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24914,7 +24917,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24940,7 +24943,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24966,7 +24969,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24992,7 +24995,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25018,7 +25021,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25044,7 +25047,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25070,7 +25073,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25096,7 +25099,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25122,7 +25125,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25148,7 +25151,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25174,7 +25177,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25200,7 +25203,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25226,7 +25229,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25252,7 +25255,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25278,7 +25281,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25304,7 +25307,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25330,7 +25333,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25356,7 +25359,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25382,7 +25385,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25408,7 +25411,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25434,7 +25437,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25460,7 +25463,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25486,7 +25489,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25512,7 +25515,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25538,7 +25541,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25564,7 +25567,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25590,7 +25593,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25616,7 +25619,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25642,7 +25645,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25668,7 +25671,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25694,7 +25697,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25720,7 +25723,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25746,7 +25749,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G843" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25772,7 +25775,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25798,7 +25801,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25824,7 +25827,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25850,7 +25853,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G847" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25876,7 +25879,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25902,7 +25905,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25928,7 +25931,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25954,7 +25957,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25980,7 +25983,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26006,7 +26009,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26032,7 +26035,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26058,7 +26061,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26084,7 +26087,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26110,7 +26113,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26136,7 +26139,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26162,7 +26165,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26188,7 +26191,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26214,7 +26217,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26240,7 +26243,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26266,7 +26269,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26292,7 +26295,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26318,7 +26321,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26344,7 +26347,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26370,7 +26373,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26396,7 +26399,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26422,7 +26425,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26448,7 +26451,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26474,7 +26477,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G871" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26500,7 +26503,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26526,7 +26529,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G873" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26552,7 +26555,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26578,7 +26581,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26604,7 +26607,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26630,7 +26633,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26656,7 +26659,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26682,7 +26685,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26708,7 +26711,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26734,7 +26737,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26760,7 +26763,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26786,7 +26789,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26812,7 +26815,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26838,7 +26841,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26864,7 +26867,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26890,7 +26893,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26916,7 +26919,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26942,7 +26945,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26968,7 +26971,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26994,7 +26997,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27020,7 +27023,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27046,7 +27049,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27072,7 +27075,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G894" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27098,7 +27101,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27124,7 +27127,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27150,7 +27153,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27176,7 +27179,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27202,7 +27205,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27228,7 +27231,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27254,7 +27257,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27280,7 +27283,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27306,7 +27309,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27332,7 +27335,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27358,7 +27361,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27384,7 +27387,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27410,7 +27413,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27436,7 +27439,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27462,7 +27465,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27488,7 +27491,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27514,7 +27517,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27540,7 +27543,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G912" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27566,7 +27569,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27592,7 +27595,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27618,7 +27621,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27644,7 +27647,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27670,7 +27673,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27696,7 +27699,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27722,7 +27725,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27748,7 +27751,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27774,7 +27777,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27800,7 +27803,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27826,7 +27829,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27852,7 +27855,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27878,7 +27881,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27904,7 +27907,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27930,7 +27933,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27956,7 +27959,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27982,7 +27985,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28008,7 +28011,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28034,7 +28037,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28060,7 +28063,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G932" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28086,7 +28089,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28112,7 +28115,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28138,7 +28141,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28164,7 +28167,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28190,7 +28193,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28216,7 +28219,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28242,7 +28245,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28268,7 +28271,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28294,7 +28297,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28320,7 +28323,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28346,7 +28349,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28372,7 +28375,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28398,7 +28401,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28424,7 +28427,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28450,7 +28453,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28476,7 +28479,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28502,7 +28505,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28528,7 +28531,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28554,7 +28557,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28580,7 +28583,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28606,7 +28609,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28632,7 +28635,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28658,7 +28661,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28684,7 +28687,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28710,7 +28713,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28736,7 +28739,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28762,7 +28765,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28788,7 +28791,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28814,7 +28817,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28840,7 +28843,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28866,7 +28869,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28892,7 +28895,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28918,7 +28921,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28944,7 +28947,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28970,7 +28973,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28996,7 +28999,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29022,7 +29025,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29048,7 +29051,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29074,7 +29077,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29100,7 +29103,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29126,7 +29129,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29152,7 +29155,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29178,7 +29181,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29204,7 +29207,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29230,7 +29233,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29256,7 +29259,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29282,7 +29285,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29308,7 +29311,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29334,7 +29337,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G981" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29360,7 +29363,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29386,7 +29389,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29412,7 +29415,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29438,7 +29441,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29464,7 +29467,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29490,7 +29493,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G987" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29516,7 +29519,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29542,7 +29545,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29568,7 +29571,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29594,7 +29597,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29620,7 +29623,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29646,7 +29649,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G993" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29672,7 +29675,7 @@
         <v>19.3618068695068</v>
       </c>
       <c r="G994" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29698,7 +29701,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29724,7 +29727,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29750,7 +29753,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29776,7 +29779,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29802,7 +29805,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29828,7 +29831,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29854,7 +29857,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1001" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29880,7 +29883,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29906,7 +29909,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29932,7 +29935,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29958,7 +29961,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29984,7 +29987,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30010,7 +30013,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30036,7 +30039,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30062,7 +30065,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30088,7 +30091,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30114,7 +30117,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30140,7 +30143,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30166,7 +30169,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30192,7 +30195,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30218,7 +30221,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30244,7 +30247,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30270,7 +30273,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G1017" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30296,7 +30299,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30322,7 +30325,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30348,7 +30351,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30374,7 +30377,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30400,7 +30403,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30426,7 +30429,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30452,7 +30455,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30478,7 +30481,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30504,7 +30507,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30530,7 +30533,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30556,7 +30559,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30582,7 +30585,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30608,7 +30611,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1030" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30634,7 +30637,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1031" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30660,7 +30663,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30686,7 +30689,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30712,7 +30715,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30738,7 +30741,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30764,7 +30767,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30790,7 +30793,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30816,7 +30819,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30842,7 +30845,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G1039" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30868,7 +30871,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30894,7 +30897,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30920,7 +30923,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30946,7 +30949,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30972,7 +30975,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30998,7 +31001,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31024,7 +31027,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31050,7 +31053,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31076,7 +31079,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31102,7 +31105,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1049" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31128,7 +31131,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31154,7 +31157,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31180,7 +31183,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31206,7 +31209,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31232,7 +31235,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31258,7 +31261,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31284,7 +31287,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31310,7 +31313,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31336,7 +31339,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31362,7 +31365,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31388,7 +31391,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1060" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31414,7 +31417,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31440,7 +31443,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31466,7 +31469,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1063" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31492,7 +31495,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31518,7 +31521,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31544,7 +31547,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31570,7 +31573,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31596,7 +31599,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31622,7 +31625,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1069" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31648,7 +31651,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31674,7 +31677,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31700,7 +31703,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31726,7 +31729,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31752,7 +31755,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31778,7 +31781,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31804,7 +31807,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31830,7 +31833,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31856,7 +31859,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31882,7 +31885,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31908,7 +31911,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31934,7 +31937,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31960,7 +31963,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31986,7 +31989,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32012,7 +32015,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32038,7 +32041,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32064,7 +32067,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32090,7 +32093,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32116,7 +32119,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32142,7 +32145,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32168,7 +32171,7 @@
         <v>18.6821041107178</v>
       </c>
       <c r="G1090" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32194,7 +32197,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32220,7 +32223,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32246,7 +32249,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32272,7 +32275,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G1094" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32298,7 +32301,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32324,7 +32327,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32350,7 +32353,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32376,7 +32379,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32402,7 +32405,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32428,7 +32431,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32454,7 +32457,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32480,7 +32483,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32506,7 +32509,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32532,7 +32535,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32558,7 +32561,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32584,7 +32587,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32610,7 +32613,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32636,7 +32639,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32662,7 +32665,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32688,7 +32691,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32714,7 +32717,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G1111" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32740,7 +32743,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32766,7 +32769,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32792,7 +32795,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32818,7 +32821,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32844,7 +32847,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32870,7 +32873,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32896,7 +32899,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32922,7 +32925,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32948,7 +32951,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32974,7 +32977,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33000,7 +33003,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33026,7 +33029,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1123" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33052,7 +33055,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33078,7 +33081,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1125" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33104,7 +33107,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33130,7 +33133,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33156,7 +33159,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33182,7 +33185,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33208,7 +33211,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33234,7 +33237,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33260,7 +33263,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33286,7 +33289,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33312,7 +33315,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33364,7 +33367,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33390,7 +33393,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33416,7 +33419,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33468,7 +33471,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33728,7 +33731,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33910,7 +33913,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33936,7 +33939,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33988,7 +33991,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34014,7 +34017,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1161" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34040,7 +34043,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1162" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34170,7 +34173,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34404,7 +34407,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1176" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34430,7 +34433,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34482,7 +34485,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34508,7 +34511,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34612,7 +34615,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34664,7 +34667,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34742,7 +34745,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34950,7 +34953,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35392,7 +35395,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35444,7 +35447,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35964,7 +35967,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35990,7 +35993,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36042,7 +36045,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36094,7 +36097,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36250,7 +36253,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36302,7 +36305,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36562,7 +36565,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36588,7 +36591,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36614,7 +36617,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -52352,7 +52355,7 @@
     </row>
     <row r="1867">
       <c r="A1867" s="1" t="n">
-        <v>45943.6493865741</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1867" t="n">
         <v>108133</v>
@@ -52373,6 +52376,32 @@
         <v>1161</v>
       </c>
       <c r="H1867" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="1" t="n">
+        <v>45944.6517824074</v>
+      </c>
+      <c r="B1868" t="n">
+        <v>173106</v>
+      </c>
+      <c r="C1868" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="D1868" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="F1868" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="G1868" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H1868" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="1165">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125925064087</t>
+    <t xml:space="preserve">7.58125829696655</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288782119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099224090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71910047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68969202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348127365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721315383911</t>
+    <t xml:space="preserve">7.90288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099367141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71909999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68969297409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348031997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721220016479</t>
   </si>
   <si>
     <t xml:space="preserve">7.67407083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97640132904053</t>
+    <t xml:space="preserve">7.97640037536621</t>
   </si>
   <si>
     <t xml:space="preserve">7.44433641433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30281972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206916809082</t>
+    <t xml:space="preserve">7.30281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46639108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57206869125366</t>
   </si>
   <si>
     <t xml:space="preserve">7.44341707229614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52612161636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54449987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64742231369019</t>
+    <t xml:space="preserve">7.52612257003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54450035095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64742183685303</t>
   </si>
   <si>
     <t xml:space="preserve">7.8018045425415</t>
@@ -101,58 +101,58 @@
     <t xml:space="preserve">7.85693979263306</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92218494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00397109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86612939834595</t>
+    <t xml:space="preserve">7.92218589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00397205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86612844467163</t>
   </si>
   <si>
     <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81466960906982</t>
+    <t xml:space="preserve">7.81466865539551</t>
   </si>
   <si>
     <t xml:space="preserve">7.7650465965271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85142612457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336938858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74666833877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56379890441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67315149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78526306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74850606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002712249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11424255371094</t>
+    <t xml:space="preserve">7.85142803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79261445999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74666738510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910341262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56379842758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67315101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78526401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74850559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11424446105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.30354499816895</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">8.46343994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48641395568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75382709503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966911315918</t>
+    <t xml:space="preserve">8.48641490936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382518768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966815948486</t>
   </si>
   <si>
     <t xml:space="preserve">8.60128211975098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28884315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25208568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3623571395874</t>
+    <t xml:space="preserve">8.28884220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25208473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36235809326172</t>
   </si>
   <si>
     <t xml:space="preserve">8.45425128936768</t>
@@ -194,58 +194,58 @@
     <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61598587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66560649871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79426002502441</t>
+    <t xml:space="preserve">8.61598682403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66560840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7942590713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.00561618804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86869430541992</t>
+    <t xml:space="preserve">8.86869335174561</t>
   </si>
   <si>
     <t xml:space="preserve">9.11588954925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14345645904541</t>
+    <t xml:space="preserve">9.14345741271973</t>
   </si>
   <si>
     <t xml:space="preserve">9.33643436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09751033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680889129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18572807312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06167030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02399349212646</t>
+    <t xml:space="preserve">9.09751129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091243743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18572902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06167125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0239953994751</t>
   </si>
   <si>
     <t xml:space="preserve">8.76577091217041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9936695098877</t>
+    <t xml:space="preserve">8.99366855621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.04237270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90177536010742</t>
+    <t xml:space="preserve">8.90177440643311</t>
   </si>
   <si>
     <t xml:space="preserve">8.67112159729004</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">7.98191452026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30630111694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40830421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54614543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5920934677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63803958892822</t>
+    <t xml:space="preserve">8.30630302429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40830326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54614448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59209251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63803863525391</t>
   </si>
   <si>
     <t xml:space="preserve">8.80804252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126266479492</t>
+    <t xml:space="preserve">8.02970314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126314163208</t>
   </si>
   <si>
     <t xml:space="preserve">7.9212646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34214115142822</t>
+    <t xml:space="preserve">8.34214210510254</t>
   </si>
   <si>
     <t xml:space="preserve">8.77496147155762</t>
@@ -293,43 +293,43 @@
     <t xml:space="preserve">8.77771949768066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7547435760498</t>
+    <t xml:space="preserve">8.75474452972412</t>
   </si>
   <si>
     <t xml:space="preserve">8.50571155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59944343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70144653320312</t>
+    <t xml:space="preserve">8.59944438934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70144748687744</t>
   </si>
   <si>
     <t xml:space="preserve">8.57738971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3926830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34122180938721</t>
+    <t xml:space="preserve">8.39268112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34122085571289</t>
   </si>
   <si>
     <t xml:space="preserve">8.56084823608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71982479095459</t>
+    <t xml:space="preserve">8.71982383728027</t>
   </si>
   <si>
     <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04164791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08667659759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18867778778076</t>
+    <t xml:space="preserve">8.04164695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0866756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18867683410645</t>
   </si>
   <si>
     <t xml:space="preserve">8.54890251159668</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">8.92107486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03869724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664257049561</t>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9743709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664352416992</t>
   </si>
   <si>
     <t xml:space="preserve">9.15264701843262</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">9.07912921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85582828521729</t>
+    <t xml:space="preserve">8.85583019256592</t>
   </si>
   <si>
     <t xml:space="preserve">8.30446434020996</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">8.27046394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33754539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20062351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40370845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27413940429688</t>
+    <t xml:space="preserve">8.33754634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20062446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40371036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27414035797119</t>
   </si>
   <si>
     <t xml:space="preserve">8.2980318069458</t>
@@ -413,94 +413,94 @@
     <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48365783691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.709716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77128410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72074413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.100266456604</t>
+    <t xml:space="preserve">8.48365688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70971584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77128505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72074222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10026550292969</t>
   </si>
   <si>
     <t xml:space="preserve">9.06534671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89809894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97712898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05156230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23535060882568</t>
+    <t xml:space="preserve">8.89809799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469486236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97712707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0515604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23535251617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.20594501495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36216354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3952465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027908325195</t>
+    <t xml:space="preserve">9.36216449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39524745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69482231140137</t>
+    <t xml:space="preserve">9.69482135772705</t>
   </si>
   <si>
     <t xml:space="preserve">9.59373760223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64335918426514</t>
+    <t xml:space="preserve">9.64336109161377</t>
   </si>
   <si>
     <t xml:space="preserve">9.31989288330078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61763000488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51103401184082</t>
+    <t xml:space="preserve">9.6176290512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5110330581665</t>
   </si>
   <si>
     <t xml:space="preserve">9.28497409820557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46324825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3309211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12875461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26291847229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14713382720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06075286865234</t>
+    <t xml:space="preserve">9.46324729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33092021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12875366210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26291942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14713287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06075191497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.9412899017334</t>
@@ -509,10 +509,10 @@
     <t xml:space="preserve">8.37798023223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76025676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00653457641602</t>
+    <t xml:space="preserve">8.7602596282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00653553009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.18940353393555</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">8.96885776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10670185089111</t>
+    <t xml:space="preserve">9.1067008972168</t>
   </si>
   <si>
     <t xml:space="preserve">9.44670581817627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39157199859619</t>
+    <t xml:space="preserve">9.39157009124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.74076747894287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53859996795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75914669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68563079833984</t>
+    <t xml:space="preserve">9.46508693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53860092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75914859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68563270568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.90617656707764</t>
@@ -551,52 +551,52 @@
     <t xml:space="preserve">9.99807262420654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0532083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79590606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92455673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.814284324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94293403625488</t>
+    <t xml:space="preserve">10.0532073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7959041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455577850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81428337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9429349899292</t>
   </si>
   <si>
     <t xml:space="preserve">10.0715866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1083421707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6672534942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77752590179443</t>
+    <t xml:space="preserve">10.1083431243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66725444793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77752494812012</t>
   </si>
   <si>
     <t xml:space="preserve">9.83266162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86941909790039</t>
+    <t xml:space="preserve">9.86942005157471</t>
   </si>
   <si>
     <t xml:space="preserve">10.1451015472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1634798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348300933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.016450881958</t>
+    <t xml:space="preserve">10.1634817123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105115890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348291397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164499282837</t>
   </si>
   <si>
     <t xml:space="preserve">10.1267223358154</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">10.512677192688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6045722961426</t>
+    <t xml:space="preserve">10.6045713424683</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7332239151001</t>
+    <t xml:space="preserve">10.7332229614258</t>
   </si>
   <si>
     <t xml:space="preserve">10.4207849502563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4759216308594</t>
+    <t xml:space="preserve">10.4759206771851</t>
   </si>
   <si>
     <t xml:space="preserve">10.4391622543335</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">10.3288898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97969341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821947097778</t>
+    <t xml:space="preserve">9.97969245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85103893280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821956634521</t>
   </si>
   <si>
     <t xml:space="preserve">9.941086769104</t>
@@ -647,61 +647,61 @@
     <t xml:space="preserve">9.99672603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.200740814209</t>
+    <t xml:space="preserve">10.2007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">10.2192878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0894622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399360656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523662567139</t>
+    <t xml:space="preserve">10.0894603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523672103882</t>
   </si>
   <si>
     <t xml:space="preserve">9.7370719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86689949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1636486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5531311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4047565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3862104415894</t>
+    <t xml:space="preserve">9.86690044403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.163646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5531320571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4047574996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4233026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386209487915</t>
   </si>
   <si>
     <t xml:space="preserve">10.3676633834839</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82980537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3120241165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338201522827</t>
+    <t xml:space="preserve">9.82980632781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3120231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338220596313</t>
   </si>
   <si>
     <t xml:space="preserve">9.81125926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.070915222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080083847046</t>
+    <t xml:space="preserve">10.0709161758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.79271125793457</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">10.8498802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789438247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0554218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1651754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6102991104126</t>
+    <t xml:space="preserve">10.4789447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0554227828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1651763916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102981567383</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062843322754</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">11.5175657272339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9626874923706</t>
+    <t xml:space="preserve">11.9626893997192</t>
   </si>
   <si>
     <t xml:space="preserve">12.1481561660767</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">12.2408905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4449043273926</t>
+    <t xml:space="preserve">12.4449052810669</t>
   </si>
   <si>
     <t xml:space="preserve">12.593279838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1852493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.573205947876</t>
+    <t xml:space="preserve">12.185248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5732049942017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5917520523071</t>
@@ -764,55 +764,55 @@
     <t xml:space="preserve">11.7401266098022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4804706573486</t>
+    <t xml:space="preserve">11.4804716110229</t>
   </si>
   <si>
     <t xml:space="preserve">11.925594329834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1110639572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1667032241821</t>
+    <t xml:space="preserve">12.11106300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1667041778564</t>
   </si>
   <si>
     <t xml:space="preserve">12.2223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5190944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.686014175415</t>
+    <t xml:space="preserve">12.5190935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6860132217407</t>
   </si>
   <si>
     <t xml:space="preserve">12.982762336731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2609634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536996841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5020732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0584764480591</t>
+    <t xml:space="preserve">13.2609643936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5020713806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584783554077</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125907897949</t>
+    <t xml:space="preserve">13.2053251266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125917434692</t>
   </si>
   <si>
     <t xml:space="preserve">12.3892641067505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3521718978882</t>
+    <t xml:space="preserve">12.3521709442139</t>
   </si>
   <si>
     <t xml:space="preserve">12.2965307235718</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">12.407811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2037954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779855728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5963344573975</t>
+    <t xml:space="preserve">12.2037973403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779836654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5963354110718</t>
   </si>
   <si>
     <t xml:space="preserve">13.9101037979126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4093389511108</t>
+    <t xml:space="preserve">13.4093399047852</t>
   </si>
   <si>
     <t xml:space="preserve">13.168231010437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.852933883667</t>
+    <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
     <t xml:space="preserve">12.7045602798462</t>
@@ -848,28 +848,28 @@
     <t xml:space="preserve">12.5561857223511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3707180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7787475585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8158407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940456390381</t>
+    <t xml:space="preserve">12.3707189559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7787485122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940427780151</t>
   </si>
   <si>
     <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.335150718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569486618042</t>
+    <t xml:space="preserve">13.3351516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569496154785</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489191055298</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">12.4263582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514080047607</t>
+    <t xml:space="preserve">11.8514060974121</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772207260132</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">11.2950038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0167999267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0353479385376</t>
+    <t xml:space="preserve">11.0168008804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090989112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0353469848633</t>
   </si>
   <si>
     <t xml:space="preserve">10.7571449279785</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">11.1280822753906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2764558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2208156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3691902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095352172852</t>
+    <t xml:space="preserve">11.2764568328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2208166122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3691892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095342636108</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
@@ -929,25 +929,25 @@
     <t xml:space="preserve">9.40322875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88391971588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55160427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71699810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80973243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20696067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24405479431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19768619537354</t>
+    <t xml:space="preserve">8.8839168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55160331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71699905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80973148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20695972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24405288696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19768714904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.53152942657471</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">9.64433765411377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7200546264648</t>
+    <t xml:space="preserve">10.7200527191162</t>
   </si>
   <si>
     <t xml:space="preserve">9.77416515350342</t>
@@ -968,40 +968,40 @@
     <t xml:space="preserve">10.2934770584106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2378349304199</t>
+    <t xml:space="preserve">10.2378358840942</t>
   </si>
   <si>
     <t xml:space="preserve">9.71852397918701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0152750015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7015047073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6844863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8699541091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4819993972778</t>
+    <t xml:space="preserve">10.0152740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7015056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6844882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8699531555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4819974899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.6118249893188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7586727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7246341705322</t>
+    <t xml:space="preserve">11.758674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7246351242065</t>
   </si>
   <si>
     <t xml:space="preserve">13.4835271835327</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6504487991333</t>
+    <t xml:space="preserve">13.650447845459</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930835723877</t>
@@ -1016,43 +1016,43 @@
     <t xml:space="preserve">14.2439451217651</t>
   </si>
   <si>
-    <t xml:space="preserve">15.282567024231</t>
+    <t xml:space="preserve">15.2825660705566</t>
   </si>
   <si>
     <t xml:space="preserve">15.7462368011475</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9687976837158</t>
+    <t xml:space="preserve">15.9687967300415</t>
   </si>
   <si>
     <t xml:space="preserve">15.3938455581665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9487228393555</t>
+    <t xml:space="preserve">14.9487237930298</t>
   </si>
   <si>
     <t xml:space="preserve">14.6148815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0399303436279</t>
+    <t xml:space="preserve">14.4665079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0399293899536</t>
   </si>
   <si>
     <t xml:space="preserve">14.1326637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7988214492798</t>
+    <t xml:space="preserve">13.7988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">13.8173685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6689939498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0770244598389</t>
+    <t xml:space="preserve">13.6689949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0770225524902</t>
   </si>
   <si>
     <t xml:space="preserve">14.3181324005127</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">14.9858160018921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560493469238</t>
+    <t xml:space="preserve">14.5560483932495</t>
   </si>
   <si>
     <t xml:space="preserve">14.7989616394043</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">14.8923892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7802753448486</t>
+    <t xml:space="preserve">14.7802762985229</t>
   </si>
   <si>
     <t xml:space="preserve">14.7615909576416</t>
@@ -1082,40 +1082,40 @@
     <t xml:space="preserve">14.9858169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2661008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287302017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4155864715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221559524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0045032501221</t>
+    <t xml:space="preserve">15.2660989761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4155855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221569061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
     <t xml:space="preserve">14.6121063232422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0792455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.911075592041</t>
+    <t xml:space="preserve">15.0792446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9110765457153</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1353015899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0231885910034</t>
+    <t xml:space="preserve">15.1353034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.929759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
@@ -1127,19 +1127,19 @@
     <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5650682449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1630077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9664859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6765403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.723575592041</t>
+    <t xml:space="preserve">15.5650691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1630058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9664878845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6765365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7235736846924</t>
   </si>
   <si>
     <t xml:space="preserve">16.8730583190918</t>
@@ -1160,100 +1160,100 @@
     <t xml:space="preserve">18.0128765106201</t>
   </si>
   <si>
-    <t xml:space="preserve">17.882080078125</t>
+    <t xml:space="preserve">17.8820762634277</t>
   </si>
   <si>
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6578502655029</t>
+    <t xml:space="preserve">18.3118495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6578540802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9941940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6855583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3305339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2184200286865</t>
+    <t xml:space="preserve">17.9941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6855602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1526966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3305320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2184181213379</t>
   </si>
   <si>
     <t xml:space="preserve">18.0315647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.377571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9568214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4709987640381</t>
+    <t xml:space="preserve">17.3775672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9568195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4709968566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9291152954102</t>
+    <t xml:space="preserve">16.9291133880615</t>
   </si>
   <si>
     <t xml:space="preserve">16.667516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266677856445</t>
+    <t xml:space="preserve">15.8266668319702</t>
   </si>
   <si>
     <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9574661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.378212928772</t>
+    <t xml:space="preserve">15.957465171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3782138824463</t>
   </si>
   <si>
     <t xml:space="preserve">15.7706089019775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5927753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2938041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4246044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2751216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8543739318848</t>
+    <t xml:space="preserve">16.5367183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4246063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2751235961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8543701171875</t>
   </si>
   <si>
     <t xml:space="preserve">16.7048892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3311786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4993457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3685512542725</t>
+    <t xml:space="preserve">16.3311767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4993495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3685474395752</t>
   </si>
   <si>
     <t xml:space="preserve">16.3498630523682</t>
@@ -1265,64 +1265,64 @@
     <t xml:space="preserve">16.6301460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7609443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7983150482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7892951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434271812439</t>
+    <t xml:space="preserve">16.6114597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7609462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7983169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7892942428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4342708587646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6868476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5373640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3215103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.518030166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6211252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8827228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4806632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4432926177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9478015899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0785980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6488342285156</t>
+    <t xml:space="preserve">14.6868486404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5373649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.32151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5180339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6211261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8827238082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4806652069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4432888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9477996826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0785999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648832321167</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104270935059</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">17.9007625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0876216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.536075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9194488525391</t>
+    <t xml:space="preserve">18.0876197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5360736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9194507598877</t>
   </si>
   <si>
     <t xml:space="preserve">18.0502490997314</t>
@@ -1355,31 +1355,31 @@
     <t xml:space="preserve">16.5554046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3124904632568</t>
+    <t xml:space="preserve">16.3124923706055</t>
   </si>
   <si>
     <t xml:space="preserve">17.0225448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.069580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8453521728516</t>
+    <t xml:space="preserve">16.0695819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8453531265259</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6024408340454</t>
+    <t xml:space="preserve">15.6024417877197</t>
   </si>
   <si>
     <t xml:space="preserve">16.0135250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9014091491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761505126953</t>
+    <t xml:space="preserve">15.9014101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9761514663696</t>
   </si>
   <si>
     <t xml:space="preserve">15.3595275878906</t>
@@ -1391,70 +1391,70 @@
     <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.855019569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.50901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6398105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6771802902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5276975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145557403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716424942017</t>
+    <t xml:space="preserve">14.8550186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5090112686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6398115158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6771821975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5276985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.471640586853</t>
   </si>
   <si>
     <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584978103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8640394210815</t>
+    <t xml:space="preserve">15.6584968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8640384674072</t>
   </si>
   <si>
     <t xml:space="preserve">16.2190647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0972862243652</t>
+    <t xml:space="preserve">17.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">17.1346569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9381351470947</t>
+    <t xml:space="preserve">17.9381370544434</t>
   </si>
   <si>
     <t xml:space="preserve">17.5831108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7699642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1249904632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6391658782959</t>
+    <t xml:space="preserve">17.7699661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1249923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6391677856445</t>
   </si>
   <si>
     <t xml:space="preserve">18.480016708374</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0689315795898</t>
+    <t xml:space="preserve">18.0689334869385</t>
   </si>
   <si>
     <t xml:space="preserve">17.1720294952393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5644226074219</t>
+    <t xml:space="preserve">17.5644264221191</t>
   </si>
   <si>
     <t xml:space="preserve">17.6017932891846</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">17.7512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7132663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8066902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4329814910889</t>
+    <t xml:space="preserve">19.713264465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8066921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">19.5264053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9935474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5541114807129</t>
+    <t xml:space="preserve">19.9935455322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5541133880615</t>
   </si>
   <si>
     <t xml:space="preserve">20.4606857299805</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9468326568604</t>
+    <t xml:space="preserve">19.946834564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271156311035</t>
@@ -1499,28 +1499,28 @@
     <t xml:space="preserve">20.6008281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6475410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2081089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5818176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9555320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3015384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8343963623047</t>
+    <t xml:space="preserve">20.6475429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2081069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5818195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.955530166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3015365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8343982696533</t>
   </si>
   <si>
     <t xml:space="preserve">20.0869750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7599773406982</t>
+    <t xml:space="preserve">19.7599754333496</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796943664551</t>
@@ -1529,34 +1529,34 @@
     <t xml:space="preserve">19.1994113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7350749969482</t>
+    <t xml:space="preserve">19.7350769042969</t>
   </si>
   <si>
     <t xml:space="preserve">19.9700183868408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7820644378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4531497955322</t>
+    <t xml:space="preserve">19.7820663452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4531478881836</t>
   </si>
   <si>
     <t xml:space="preserve">19.5471248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001354217529</t>
+    <t xml:space="preserve">19.5001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">19.6880893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">19.030252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8422985076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1712169647217</t>
+    <t xml:space="preserve">19.0302505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8423004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1712188720703</t>
   </si>
   <si>
     <t xml:space="preserve">19.0772399902344</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290557861328</t>
+    <t xml:space="preserve">19.8290538787842</t>
   </si>
   <si>
     <t xml:space="preserve">19.2651920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4194068908691</t>
+    <t xml:space="preserve">18.4194049835205</t>
   </si>
   <si>
     <t xml:space="preserve">18.6261558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4757919311523</t>
+    <t xml:space="preserve">18.475793838501</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765159606934</t>
@@ -1598,43 +1598,43 @@
     <t xml:space="preserve">18.7953109741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6449508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639953613281</t>
+    <t xml:space="preserve">18.6449489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639934539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.3929138183594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8158073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2856903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0844917297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4603996276855</t>
+    <t xml:space="preserve">20.8158054351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2856884002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0844898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4603958129883</t>
   </si>
   <si>
     <t xml:space="preserve">22.9772701263428</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2122077941895</t>
+    <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
     <t xml:space="preserve">23.494140625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1652221679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0712413787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.58811378479</t>
+    <t xml:space="preserve">23.1652202606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0712432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5881156921387</t>
   </si>
   <si>
     <t xml:space="preserve">24.1989631652832</t>
@@ -1649,49 +1649,49 @@
     <t xml:space="preserve">23.0242557525635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8363056182861</t>
+    <t xml:space="preserve">22.8363037109375</t>
   </si>
   <si>
     <t xml:space="preserve">22.8832912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5411262512207</t>
+    <t xml:space="preserve">23.5411281585693</t>
   </si>
   <si>
     <t xml:space="preserve">22.9302787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.447151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.870044708252</t>
+    <t xml:space="preserve">23.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8700428009033</t>
   </si>
   <si>
     <t xml:space="preserve">21.7555732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7085838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1314792633057</t>
+    <t xml:space="preserve">21.7085876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1314811706543</t>
   </si>
   <si>
     <t xml:space="preserve">21.9435272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5676193237305</t>
+    <t xml:space="preserve">21.5676212310791</t>
   </si>
   <si>
     <t xml:space="preserve">21.1447257995605</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567718505859</t>
+    <t xml:space="preserve">20.9097862243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567737579346</t>
   </si>
   <si>
     <t xml:space="preserve">20.7688179016113</t>
@@ -1706,31 +1706,31 @@
     <t xml:space="preserve">21.8495483398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8098106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977645874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3869152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4001636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6351051330566</t>
+    <t xml:space="preserve">24.8098087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4339027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3869171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4001617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6351013183594</t>
   </si>
   <si>
     <t xml:space="preserve">24.1519756317139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8230590820312</t>
+    <t xml:space="preserve">23.8230571746826</t>
   </si>
   <si>
     <t xml:space="preserve">24.2929401397705</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">24.4808921813965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5616207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206581115723</t>
+    <t xml:space="preserve">25.5616226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.6555995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3736724853516</t>
+    <t xml:space="preserve">25.3736705780029</t>
   </si>
   <si>
     <t xml:space="preserve">25.2796936035156</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">23.3061847686768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.554370880127</t>
+    <t xml:space="preserve">22.5543727874756</t>
   </si>
   <si>
     <t xml:space="preserve">22.2724437713623</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">24.2459506988525</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7158336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278797149658</t>
+    <t xml:space="preserve">24.7158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">24.7628231048584</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">24.0110111236572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8568019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6218566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1857166290283</t>
+    <t xml:space="preserve">24.8568000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6218585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.185718536377</t>
   </si>
   <si>
     <t xml:space="preserve">25.138729095459</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">21.5206317901611</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1917133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266567230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4398994445801</t>
+    <t xml:space="preserve">21.1917152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
   </si>
   <si>
     <t xml:space="preserve">21.8025608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8627967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326797485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146068572998</t>
+    <t xml:space="preserve">20.8627948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146087646484</t>
   </si>
   <si>
     <t xml:space="preserve">21.3796653747559</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">20.2519474029541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3459243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.218204498291</t>
+    <t xml:space="preserve">20.34592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2182064056396</t>
   </si>
   <si>
     <t xml:space="preserve">18.5697650909424</t>
@@ -1841,40 +1841,40 @@
     <t xml:space="preserve">19.8760414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.674840927124</t>
+    <t xml:space="preserve">20.6748428344727</t>
   </si>
   <si>
     <t xml:space="preserve">19.3591709136963</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2126579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3292751312256</t>
+    <t xml:space="preserve">18.2126560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3292770385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.0473480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8218040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3066349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1938629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.663745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.990514755249</t>
+    <t xml:space="preserve">16.8218021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3066329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1938591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9905128479004</t>
   </si>
   <si>
     <t xml:space="preserve">22.3194332122803</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">21.4736423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4868907928467</t>
+    <t xml:space="preserve">20.486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">20.2989368438721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0170059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7389259338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7013320922852</t>
+    <t xml:space="preserve">20.0170078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7389278411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7013339996338</t>
   </si>
   <si>
     <t xml:space="preserve">21.8965358734131</t>
@@ -1904,34 +1904,34 @@
     <t xml:space="preserve">20.2049598693848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5338745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3254299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9683170318604</t>
+    <t xml:space="preserve">20.5338764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3254261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">17.8931369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2165031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977100372314</t>
+    <t xml:space="preserve">17.2165050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977119445801</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9418792724609</t>
+    <t xml:space="preserve">16.9418773651123</t>
   </si>
   <si>
     <t xml:space="preserve">16.9039745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923091888428</t>
+    <t xml:space="preserve">16.3923072814941</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596530914307</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">17.5293464660645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9652099609375</t>
+    <t xml:space="preserve">17.9652118682861</t>
   </si>
   <si>
     <t xml:space="preserve">17.813606262207</t>
@@ -1952,37 +1952,37 @@
     <t xml:space="preserve">18.2684230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2494735717773</t>
+    <t xml:space="preserve">18.2494716644287</t>
   </si>
   <si>
     <t xml:space="preserve">18.1736679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.950647354126</t>
+    <t xml:space="preserve">18.9506454467773</t>
   </si>
   <si>
     <t xml:space="preserve">18.6284866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5716342926025</t>
+    <t xml:space="preserve">18.5716323852539</t>
   </si>
   <si>
     <t xml:space="preserve">18.7800922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9462623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5905838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8507995605469</t>
+    <t xml:space="preserve">17.9462604522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5905818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8508014678955</t>
   </si>
   <si>
     <t xml:space="preserve">20.1824378967285</t>
@@ -1997,34 +1997,34 @@
     <t xml:space="preserve">20.9404621124268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8930854797363</t>
+    <t xml:space="preserve">20.893087387085</t>
   </si>
   <si>
     <t xml:space="preserve">21.0352153778076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2771911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0775012969971</t>
+    <t xml:space="preserve">20.2771892547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0774993896484</t>
   </si>
   <si>
     <t xml:space="preserve">22.6933975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2670097351074</t>
+    <t xml:space="preserve">22.2670078277588</t>
   </si>
   <si>
     <t xml:space="preserve">22.4565143585205</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0301265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4616069793701</t>
+    <t xml:space="preserve">22.5986442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0301246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.6511116027832</t>
@@ -2036,79 +2036,79 @@
     <t xml:space="preserve">20.9878387451172</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7983341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4193210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6612949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9455528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2349052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5665397644043</t>
+    <t xml:space="preserve">20.7983322143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.419319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6612930297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9455547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2349033355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5665416717529</t>
   </si>
   <si>
     <t xml:space="preserve">20.0403079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7560482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1875286102295</t>
+    <t xml:space="preserve">19.756046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1875267028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.9980220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0453987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3631763458252</t>
+    <t xml:space="preserve">19.0453968048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3631744384766</t>
   </si>
   <si>
     <t xml:space="preserve">17.9273128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2305221557617</t>
+    <t xml:space="preserve">18.2305202484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.7188549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3821239471436</t>
+    <t xml:space="preserve">18.3821258544922</t>
   </si>
   <si>
     <t xml:space="preserve">17.7757053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7946548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357669830322</t>
+    <t xml:space="preserve">17.7946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357650756836</t>
   </si>
   <si>
     <t xml:space="preserve">19.0927772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.087682723999</t>
+    <t xml:space="preserve">20.0876846313477</t>
   </si>
   <si>
     <t xml:space="preserve">18.7990398406982</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">18.1547183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2873725891113</t>
+    <t xml:space="preserve">18.28737449646</t>
   </si>
   <si>
     <t xml:space="preserve">18.5147819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0599632263184</t>
+    <t xml:space="preserve">18.059965133667</t>
   </si>
   <si>
     <t xml:space="preserve">18.2115707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">18.476879119873</t>
+    <t xml:space="preserve">18.4768772125244</t>
   </si>
   <si>
     <t xml:space="preserve">20.6562023162842</t>
@@ -2138,22 +2138,22 @@
     <t xml:space="preserve">20.6088275909424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5140743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5038890838623</t>
+    <t xml:space="preserve">20.5140762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5038928985596</t>
   </si>
   <si>
     <t xml:space="preserve">23.3092956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.162073135376</t>
+    <t xml:space="preserve">24.1620750427246</t>
   </si>
   <si>
     <t xml:space="preserve">24.7779693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3566722869873</t>
+    <t xml:space="preserve">23.3566703796387</t>
   </si>
   <si>
     <t xml:space="preserve">23.4040470123291</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">22.9302806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6883068084717</t>
+    <t xml:space="preserve">23.6883087158203</t>
   </si>
   <si>
     <t xml:space="preserve">22.1248798370361</t>
@@ -2171,31 +2171,31 @@
     <t xml:space="preserve">22.8829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7881526947021</t>
+    <t xml:space="preserve">22.7881507873535</t>
   </si>
   <si>
     <t xml:space="preserve">23.0250339508057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1722564697266</t>
+    <t xml:space="preserve">22.1722545623779</t>
   </si>
   <si>
     <t xml:space="preserve">22.8355274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4514236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3515777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.167163848877</t>
+    <t xml:space="preserve">23.4514217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3515796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1671657562256</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9827499389648</t>
+    <t xml:space="preserve">21.9827480316162</t>
   </si>
   <si>
     <t xml:space="preserve">22.5512676239014</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">21.7458667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6037368774414</t>
+    <t xml:space="preserve">21.6037349700928</t>
   </si>
   <si>
     <t xml:space="preserve">21.7932434082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6984882354736</t>
+    <t xml:space="preserve">21.6984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">21.5563583374023</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">21.5089817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">23.49880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6832160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9725666046143</t>
+    <t xml:space="preserve">23.4987983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6832141876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9725646972656</t>
   </si>
   <si>
     <t xml:space="preserve">24.2568264007568</t>
@@ -2267,31 +2267,31 @@
     <t xml:space="preserve">25.7255001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6358394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5359935760498</t>
+    <t xml:space="preserve">24.6358375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5359954833984</t>
   </si>
   <si>
     <t xml:space="preserve">25.772876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3464870452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5935554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5461769104004</t>
+    <t xml:space="preserve">25.3464889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5935535430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.546178817749</t>
   </si>
   <si>
     <t xml:space="preserve">23.1197872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9776554107666</t>
+    <t xml:space="preserve">23.2619152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9776573181152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2145404815674</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">23.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7830581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3194751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6460227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.361759185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622310638428</t>
+    <t xml:space="preserve">23.7830600738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3194770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6460208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3617630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4835300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3887748718262</t>
+    <t xml:space="preserve">26.483528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">26.6256561279297</t>
@@ -2336,25 +2336,25 @@
     <t xml:space="preserve">26.1992664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.820255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5309047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6730308532715</t>
+    <t xml:space="preserve">25.8202533721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5309028625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6730327606201</t>
   </si>
   <si>
     <t xml:space="preserve">26.3201923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7480125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6526489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843376159668</t>
+    <t xml:space="preserve">25.7480144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6526508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8433742523193</t>
   </si>
   <si>
     <t xml:space="preserve">25.6049690246582</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">25.891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0817832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5096035003662</t>
+    <t xml:space="preserve">26.0817813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5096054077148</t>
   </si>
   <si>
     <t xml:space="preserve">26.1294651031494</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">25.9387378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7956943511963</t>
+    <t xml:space="preserve">25.7956962585449</t>
   </si>
   <si>
     <t xml:space="preserve">25.12815284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.223518371582</t>
+    <t xml:space="preserve">25.2235164642334</t>
   </si>
   <si>
     <t xml:space="preserve">25.2711982727051</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">24.9851093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1758346557617</t>
+    <t xml:space="preserve">25.1758327484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.5559749603271</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">24.6990203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9361133575439</t>
+    <t xml:space="preserve">23.9361152648926</t>
   </si>
   <si>
     <t xml:space="preserve">24.937427520752</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">24.8420639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5082931518555</t>
+    <t xml:space="preserve">24.5082912445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.8884334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.222204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6977081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8407535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3175678253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.079158782959</t>
+    <t xml:space="preserve">24.2222061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6977062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8407516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.317569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0791606903076</t>
   </si>
   <si>
     <t xml:space="preserve">24.6513366699219</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">22.9824848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871212005615</t>
+    <t xml:space="preserve">22.8871231079102</t>
   </si>
   <si>
     <t xml:space="preserve">22.0288562774658</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">21.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1705875396729</t>
+    <t xml:space="preserve">21.1705894470215</t>
   </si>
   <si>
     <t xml:space="preserve">21.0752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9321804046631</t>
+    <t xml:space="preserve">20.9321784973145</t>
   </si>
   <si>
     <t xml:space="preserve">20.5984115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136310577393</t>
+    <t xml:space="preserve">21.3136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.6474018096924</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">20.8368167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.88450050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0739116668701</t>
+    <t xml:space="preserve">20.8844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0739135742188</t>
   </si>
   <si>
     <t xml:space="preserve">21.1229057312012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">20.6460933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.939094543457</t>
+    <t xml:space="preserve">18.9390926361084</t>
   </si>
   <si>
     <t xml:space="preserve">19.4063720703125</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">18.6339321136475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5385684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5194969177246</t>
+    <t xml:space="preserve">18.5385704040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.519495010376</t>
   </si>
   <si>
     <t xml:space="preserve">18.0426826477051</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.6993732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8710269927979</t>
+    <t xml:space="preserve">17.8710289001465</t>
   </si>
   <si>
     <t xml:space="preserve">18.7674388885498</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">20.2169570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8355045318604</t>
+    <t xml:space="preserve">19.835506439209</t>
   </si>
   <si>
     <t xml:space="preserve">20.5030479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.789134979248</t>
+    <t xml:space="preserve">20.7891368865967</t>
   </si>
   <si>
     <t xml:space="preserve">21.7904472351074</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">19.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7894744873047</t>
+    <t xml:space="preserve">19.7894763946533</t>
   </si>
   <si>
     <t xml:space="preserve">20.5751628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9188995361328</t>
+    <t xml:space="preserve">20.9188976287842</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">22.6375885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">22.883113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7849044799805</t>
+    <t xml:space="preserve">22.8831157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7849063873291</t>
   </si>
   <si>
     <t xml:space="preserve">21.9010066986084</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">21.6554794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2268524169922</t>
+    <t xml:space="preserve">23.2268543243408</t>
   </si>
   <si>
     <t xml:space="preserve">24.0125408172607</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">22.6866931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340110778809</t>
+    <t xml:space="preserve">22.8340091705322</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5393772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1956405639648</t>
+    <t xml:space="preserve">22.539379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1956386566162</t>
   </si>
   <si>
     <t xml:space="preserve">22.4902725219727</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">22.4411659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7045860290527</t>
+    <t xml:space="preserve">21.7045879364014</t>
   </si>
   <si>
     <t xml:space="preserve">22.293851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8519039154053</t>
+    <t xml:space="preserve">21.8519020080566</t>
   </si>
   <si>
     <t xml:space="preserve">22.2447452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501132965088</t>
+    <t xml:space="preserve">21.9501152038574</t>
   </si>
   <si>
     <t xml:space="preserve">22.3429565429688</t>
@@ -2684,22 +2684,22 @@
     <t xml:space="preserve">21.6063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.017110824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4590587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1153202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4099540710449</t>
+    <t xml:space="preserve">21.2135334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4590606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1153221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4099521636963</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403697967529</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">19.6028747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3278865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9350414276123</t>
+    <t xml:space="preserve">19.3278846740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9350433349609</t>
   </si>
   <si>
     <t xml:space="preserve">18.954683303833</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">19.5046634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1823196411133</t>
+    <t xml:space="preserve">20.1823177337646</t>
   </si>
   <si>
     <t xml:space="preserve">20.1332130432129</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">19.985897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6912631988525</t>
+    <t xml:space="preserve">19.6912651062012</t>
   </si>
   <si>
     <t xml:space="preserve">19.5832328796387</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">19.3671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7386207580566</t>
+    <t xml:space="preserve">18.738618850708</t>
   </si>
   <si>
     <t xml:space="preserve">18.4047031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1689987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2279243469238</t>
+    <t xml:space="preserve">18.1689968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2279224395752</t>
   </si>
   <si>
     <t xml:space="preserve">18.0904293060303</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">18.1493549346924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7172298431396</t>
+    <t xml:space="preserve">17.717227935791</t>
   </si>
   <si>
     <t xml:space="preserve">18.6796951293945</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">18.6404094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5029144287109</t>
+    <t xml:space="preserve">18.5029125213623</t>
   </si>
   <si>
     <t xml:space="preserve">18.8761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4225940704346</t>
+    <t xml:space="preserve">17.4225959777832</t>
   </si>
   <si>
     <t xml:space="preserve">18.2868518829346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2475662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547607421875</t>
+    <t xml:space="preserve">18.2475643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547626495361</t>
   </si>
   <si>
     <t xml:space="preserve">18.4832706451416</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">17.9529342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1297130584717</t>
+    <t xml:space="preserve">18.129711151123</t>
   </si>
   <si>
     <t xml:space="preserve">17.5208072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2654571533203</t>
+    <t xml:space="preserve">17.2654590606689</t>
   </si>
   <si>
     <t xml:space="preserve">17.3243827819824</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">17.4618797302246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1083221435547</t>
+    <t xml:space="preserve">17.1083202362061</t>
   </si>
   <si>
     <t xml:space="preserve">17.2458152770996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7744026184082</t>
+    <t xml:space="preserve">16.7744045257568</t>
   </si>
   <si>
     <t xml:space="preserve">16.9904670715332</t>
@@ -3504,6 +3504,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.1000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9500007629395</t>
   </si>
 </sst>
 </file>
@@ -52410,7 +52413,7 @@
     </row>
     <row r="1869">
       <c r="A1869" s="1" t="n">
-        <v>45945.6494097222</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1869" t="n">
         <v>116517</v>
@@ -52431,6 +52434,32 @@
         <v>1163</v>
       </c>
       <c r="H1869" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="1" t="n">
+        <v>45946.6509606481</v>
+      </c>
+      <c r="B1870" t="n">
+        <v>176753</v>
+      </c>
+      <c r="C1870" t="n">
+        <v>21.0499992370605</v>
+      </c>
+      <c r="D1870" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>20.9500007629395</v>
+      </c>
+      <c r="G1870" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H1870" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">7.90288639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81099462509155</t>
+    <t xml:space="preserve">7.8109917640686</t>
   </si>
   <si>
     <t xml:space="preserve">7.71909999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68969249725342</t>
+    <t xml:space="preserve">7.68969202041626</t>
   </si>
   <si>
     <t xml:space="preserve">7.87348079681396</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">7.97640085220337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44433641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.302818775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520275115967</t>
+    <t xml:space="preserve">7.4443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30281972885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520322799683</t>
   </si>
   <si>
     <t xml:space="preserve">7.46639060974121</t>
@@ -86,25 +86,25 @@
     <t xml:space="preserve">7.4434175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52612209320068</t>
+    <t xml:space="preserve">7.52612113952637</t>
   </si>
   <si>
     <t xml:space="preserve">7.54450082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64742183685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180501937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85693979263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92218399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00397109985352</t>
+    <t xml:space="preserve">7.64742136001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80180358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85693883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92218542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00397205352783</t>
   </si>
   <si>
     <t xml:space="preserve">7.86612939834595</t>
@@ -113,43 +113,43 @@
     <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81466913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76504755020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142755508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336843490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79261445999146</t>
+    <t xml:space="preserve">7.81466960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76504564285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142660140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79261541366577</t>
   </si>
   <si>
     <t xml:space="preserve">7.74666786193848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88910388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56379842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67315149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78526449203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74850559234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478197097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002616882324</t>
+    <t xml:space="preserve">7.88910341262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56379890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67315244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78526401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74850654602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478101730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002521514893</t>
   </si>
   <si>
     <t xml:space="preserve">8.11424350738525</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">8.30354499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46344089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48641395568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75382614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60128211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28884410858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25208473205566</t>
+    <t xml:space="preserve">8.46343994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382518768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60128116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28884220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25208377838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.46987247467041</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">8.3623571395874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45425224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7115535736084</t>
+    <t xml:space="preserve">8.45425128936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71155548095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.74831295013428</t>
@@ -200,61 +200,61 @@
     <t xml:space="preserve">8.66560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7942590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00561618804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86869335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11588954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14345741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09751033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680603027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091148376465</t>
+    <t xml:space="preserve">8.79426097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86869430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11588764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14345645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09750938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091339111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.18572902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06166934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02399444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76577091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99366855621338</t>
+    <t xml:space="preserve">9.06167030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02399349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76577281951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9936695098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.04237270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90177440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67112064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98191452026367</t>
+    <t xml:space="preserve">8.90177536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67112255096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50754737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98191595077515</t>
   </si>
   <si>
     <t xml:space="preserve">8.30630302429199</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">8.54614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59209251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63803958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970218658447</t>
+    <t xml:space="preserve">8.5920934677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63804054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80804347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970123291016</t>
   </si>
   <si>
     <t xml:space="preserve">7.75126314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92126607894897</t>
+    <t xml:space="preserve">7.92126512527466</t>
   </si>
   <si>
     <t xml:space="preserve">8.34214019775391</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">8.77496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77771854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75474452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50571250915527</t>
+    <t xml:space="preserve">8.77771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50571346282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.59944438934326</t>
@@ -305,31 +305,31 @@
     <t xml:space="preserve">8.70144748687744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57738971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3926830291748</t>
+    <t xml:space="preserve">8.57739067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39268207550049</t>
   </si>
   <si>
     <t xml:space="preserve">8.34122180938721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56085014343262</t>
+    <t xml:space="preserve">8.5608491897583</t>
   </si>
   <si>
     <t xml:space="preserve">8.71982574462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05451393127441</t>
+    <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
     <t xml:space="preserve">8.04164695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0866756439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18867588043213</t>
+    <t xml:space="preserve">8.08667469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18867778778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.548903465271</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">8.5093879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9210729598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03869724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437191009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15264797210693</t>
+    <t xml:space="preserve">8.92107391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97437000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1526460647583</t>
   </si>
   <si>
     <t xml:space="preserve">8.84939670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07913017272949</t>
+    <t xml:space="preserve">9.07913112640381</t>
   </si>
   <si>
     <t xml:space="preserve">8.8558292388916</t>
@@ -371,46 +371,46 @@
     <t xml:space="preserve">8.23370552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27046298980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33754634857178</t>
+    <t xml:space="preserve">8.27046394348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33754539489746</t>
   </si>
   <si>
     <t xml:space="preserve">8.20062255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40371036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27413845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29803276062012</t>
+    <t xml:space="preserve">8.40370941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27413940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2980318069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.5001974105835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43587112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22451591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35408687591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22084045410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15283966064453</t>
+    <t xml:space="preserve">8.43587207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22451686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35408782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22083950042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15283870697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.39911556243896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.426682472229</t>
+    <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
     <t xml:space="preserve">8.48365783691406</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">8.72074413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.100266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06534576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89809989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469390869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97712898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05156135559082</t>
+    <t xml:space="preserve">9.10026741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06534671783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89809894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97712993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05156326293945</t>
   </si>
   <si>
     <t xml:space="preserve">9.23535060882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20594501495361</t>
+    <t xml:space="preserve">9.2059440612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.36216354370117</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">9.3952465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61027812957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64887428283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69482040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64336109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61763000488281</t>
+    <t xml:space="preserve">9.61027908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64887523651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69482135772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59373760223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64336013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31989288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6176290512085</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5110330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28497505187988</t>
+    <t xml:space="preserve">9.51103210449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28497409820557</t>
   </si>
   <si>
     <t xml:space="preserve">9.46324729919434</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">9.12875461578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26291847229004</t>
+    <t xml:space="preserve">9.26291942596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.14713287353516</t>
@@ -509,160 +509,163 @@
     <t xml:space="preserve">8.37797927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7602596282959</t>
+    <t xml:space="preserve">8.76025772094727</t>
   </si>
   <si>
     <t xml:space="preserve">9.0065336227417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18940448760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96885871887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10669994354248</t>
+    <t xml:space="preserve">9.18940353393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96885681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10669898986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.44670677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39157104492188</t>
+    <t xml:space="preserve">9.39157009124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.74076843261719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53860187530518</t>
+    <t xml:space="preserve">9.46508693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53860092163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.75914669036865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68563270568848</t>
+    <t xml:space="preserve">9.68563365936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.90617656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807262420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79590511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92455768585205</t>
+    <t xml:space="preserve">9.99807071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532064437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79590225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455673217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.81428146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94293594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0715866088867</t>
+    <t xml:space="preserve">9.9429349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0715856552124</t>
   </si>
   <si>
     <t xml:space="preserve">10.108344078064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66725254058838</t>
+    <t xml:space="preserve">9.66725444793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266353607178</t>
+    <t xml:space="preserve">9.83266067504883</t>
   </si>
   <si>
     <t xml:space="preserve">9.86941909790039</t>
   </si>
   <si>
+    <t xml:space="preserve">10.1451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.163480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105115890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348291397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5126781463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6045713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659707069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7332239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207849502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97969341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85104084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821966171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.941086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88544464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253875732422</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.1451005935669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.163480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348291397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.016450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5126781463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6045713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597080230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7332239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4759206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97969341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253971099854</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.99672603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2007398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2192878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0894613265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73707294464111</t>
+    <t xml:space="preserve">10.2007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2192888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0894603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523672103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7370719909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.86689949035645</t>
@@ -680,28 +683,28 @@
     <t xml:space="preserve">10.4233045578003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3862104415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82980537414551</t>
+    <t xml:space="preserve">10.3862113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3676624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82980728149414</t>
   </si>
   <si>
     <t xml:space="preserve">10.3120231628418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338201522827</t>
+    <t xml:space="preserve">10.033821105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.81125926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0709161758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080083847046</t>
+    <t xml:space="preserve">10.070915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.79271221160889</t>
@@ -710,7 +713,7 @@
     <t xml:space="preserve">10.2563819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498802185059</t>
+    <t xml:space="preserve">10.8498792648315</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789438247681</t>
@@ -719,19 +722,19 @@
     <t xml:space="preserve">12.0554227828979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6102991104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062852859497</t>
+    <t xml:space="preserve">11.1651754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6103000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062833786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361108779907</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6288461685181</t>
+    <t xml:space="preserve">11.6288452148438</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175647735596</t>
@@ -740,37 +743,37 @@
     <t xml:space="preserve">11.9626884460449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2408905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4449052810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.593279838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.185248374939</t>
+    <t xml:space="preserve">12.1481561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2408895492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4449043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5932788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1852493286133</t>
   </si>
   <si>
     <t xml:space="preserve">11.573205947876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5917530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401266098022</t>
+    <t xml:space="preserve">11.5917520523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401275634766</t>
   </si>
   <si>
     <t xml:space="preserve">11.4804716110229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.11106300354</t>
+    <t xml:space="preserve">11.9255933761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1110620498657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1667022705078</t>
@@ -779,19 +782,19 @@
     <t xml:space="preserve">12.2223434448242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5190925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.686014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2609634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536996841431</t>
+    <t xml:space="preserve">12.5190935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6860132217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2609643936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536987304688</t>
   </si>
   <si>
     <t xml:space="preserve">13.5020723342896</t>
@@ -800,40 +803,40 @@
     <t xml:space="preserve">14.0584764480591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4649791717529</t>
+    <t xml:space="preserve">13.4649782180786</t>
   </si>
   <si>
     <t xml:space="preserve">13.2053241729736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1125926971436</t>
+    <t xml:space="preserve">13.1125907897949</t>
   </si>
   <si>
     <t xml:space="preserve">12.3892650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3521718978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2965307235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4078121185303</t>
+    <t xml:space="preserve">12.3521709442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2965316772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.407811164856</t>
   </si>
   <si>
     <t xml:space="preserve">12.2037963867188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5963344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9101037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4093389511108</t>
+    <t xml:space="preserve">12.2779846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5963354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9101028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4093399047852</t>
   </si>
   <si>
     <t xml:space="preserve">13.1682319641113</t>
@@ -842,7 +845,7 @@
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045602798462</t>
+    <t xml:space="preserve">12.7045612335205</t>
   </si>
   <si>
     <t xml:space="preserve">12.5561866760254</t>
@@ -854,13 +857,13 @@
     <t xml:space="preserve">12.7787475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8158407211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940456390381</t>
+    <t xml:space="preserve">12.815842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940446853638</t>
   </si>
   <si>
     <t xml:space="preserve">13.075496673584</t>
@@ -869,10 +872,10 @@
     <t xml:space="preserve">13.3351516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569486618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489200592041</t>
+    <t xml:space="preserve">13.0569505691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489191055298</t>
   </si>
   <si>
     <t xml:space="preserve">12.3150777816772</t>
@@ -884,19 +887,19 @@
     <t xml:space="preserve">12.4263582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514080047607</t>
+    <t xml:space="preserve">11.8514089584351</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772207260132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2950019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0168008804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909881591797</t>
+    <t xml:space="preserve">11.2950029373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0168018341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090989112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353488922119</t>
@@ -911,22 +914,22 @@
     <t xml:space="preserve">11.1280822753906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2764568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.220817565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3691902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095342636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40322780609131</t>
+    <t xml:space="preserve">11.2764549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2208166122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3691892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40322875976562</t>
   </si>
   <si>
     <t xml:space="preserve">8.88391780853271</t>
@@ -935,55 +938,55 @@
     <t xml:space="preserve">9.55160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71699714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80973243713379</t>
+    <t xml:space="preserve">8.71699810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80973148345947</t>
   </si>
   <si>
     <t xml:space="preserve">8.20696067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24405479431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19768714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53153038024902</t>
+    <t xml:space="preserve">8.24405384063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19768619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53152942657471</t>
   </si>
   <si>
     <t xml:space="preserve">8.43879508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6443395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7741641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2934770584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2378358840942</t>
+    <t xml:space="preserve">9.64433765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200517654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77416706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.293478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">9.71852493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0152740478516</t>
+    <t xml:space="preserve">10.0152750015259</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015047073364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6844863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8699541091919</t>
+    <t xml:space="preserve">11.6844873428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8699550628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.4819993972778</t>
@@ -992,19 +995,19 @@
     <t xml:space="preserve">12.6118259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7586736679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7246341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4835262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.650447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930826187134</t>
+    <t xml:space="preserve">11.7586727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7246332168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4835252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6504487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930835723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.0414581298828</t>
@@ -1016,49 +1019,49 @@
     <t xml:space="preserve">14.2439451217651</t>
   </si>
   <si>
-    <t xml:space="preserve">15.282567024231</t>
+    <t xml:space="preserve">15.2825660705566</t>
   </si>
   <si>
     <t xml:space="preserve">15.7462358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9687967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487218856812</t>
+    <t xml:space="preserve">15.9687986373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938455581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487228393555</t>
   </si>
   <si>
     <t xml:space="preserve">14.6148824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4665069580078</t>
+    <t xml:space="preserve">14.4665079116821</t>
   </si>
   <si>
     <t xml:space="preserve">14.0399293899536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1326637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7988224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8173694610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6689929962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0770244598389</t>
+    <t xml:space="preserve">14.132664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7988214492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8173685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6689939498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0770235061646</t>
   </si>
   <si>
     <t xml:space="preserve">14.3181324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">14.707615852356</t>
+    <t xml:space="preserve">14.7076148986816</t>
   </si>
   <si>
     <t xml:space="preserve">14.9858169555664</t>
@@ -1070,79 +1073,76 @@
     <t xml:space="preserve">14.79896068573</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8923892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7802762985229</t>
+    <t xml:space="preserve">14.8923902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7802743911743</t>
   </si>
   <si>
     <t xml:space="preserve">14.7615909576416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9858179092407</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.2661008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2287292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4155864715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221559524536</t>
+    <t xml:space="preserve">15.2287302017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.415584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221569061279</t>
   </si>
   <si>
     <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6121072769165</t>
+    <t xml:space="preserve">14.6121053695679</t>
   </si>
   <si>
     <t xml:space="preserve">15.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9110746383667</t>
+    <t xml:space="preserve">14.911075592041</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297618865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0231876373291</t>
+    <t xml:space="preserve">15.1353034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297609329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0231885910034</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9484462738037</t>
+    <t xml:space="preserve">14.9484453201294</t>
   </si>
   <si>
     <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5650682449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1630077362061</t>
+    <t xml:space="preserve">15.5650691986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1630058288574</t>
   </si>
   <si>
     <t xml:space="preserve">16.9664878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6765403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.723575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8730583190918</t>
+    <t xml:space="preserve">17.6765384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7235736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8730602264404</t>
   </si>
   <si>
     <t xml:space="preserve">17.4336242675781</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">17.4149398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3962554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7886505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0128784179688</t>
+    <t xml:space="preserve">17.3962535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7886524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0128765106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.8820781707764</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118457794189</t>
+    <t xml:space="preserve">18.3118476867676</t>
   </si>
   <si>
     <t xml:space="preserve">17.6578521728516</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9941940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6855602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1526966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3305339813232</t>
+    <t xml:space="preserve">17.9941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6855583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1526947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3305320739746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2184181213379</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">18.0315647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3775672912598</t>
+    <t xml:space="preserve">17.3775691986084</t>
   </si>
   <si>
     <t xml:space="preserve">17.9568214416504</t>
@@ -1211,25 +1211,25 @@
     <t xml:space="preserve">16.667516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266668319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4619750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3782138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706098556519</t>
+    <t xml:space="preserve">15.8266639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4619770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9574661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706117630005</t>
   </si>
   <si>
     <t xml:space="preserve">16.5367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927753448486</t>
+    <t xml:space="preserve">16.5927772521973</t>
   </si>
   <si>
     <t xml:space="preserve">16.2938060760498</t>
@@ -1238,124 +1238,124 @@
     <t xml:space="preserve">16.4246063232422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2751235961914</t>
+    <t xml:space="preserve">16.2751216888428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8543739318848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7048892974854</t>
+    <t xml:space="preserve">16.704891204834</t>
   </si>
   <si>
     <t xml:space="preserve">16.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4993457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3685493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3498611450195</t>
+    <t xml:space="preserve">16.4993476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3685474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3498630523682</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862049102783</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6301460266113</t>
+    <t xml:space="preserve">16.63014793396</t>
   </si>
   <si>
     <t xml:space="preserve">16.6114597320557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7609443664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170032501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7983150482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7892980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4342708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6868467330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5373649597168</t>
+    <t xml:space="preserve">16.7609462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.798318862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7892942428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.434271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6868486404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5373640060425</t>
   </si>
   <si>
     <t xml:space="preserve">17.3215103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5180339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6211261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8827209472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377490997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4806613922119</t>
+    <t xml:space="preserve">16.5180320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6211252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8827219009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4806632995605</t>
   </si>
   <si>
     <t xml:space="preserve">16.8356895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4432907104492</t>
+    <t xml:space="preserve">16.4432926177979</t>
   </si>
   <si>
     <t xml:space="preserve">16.9478015899658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0785980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6488304138184</t>
+    <t xml:space="preserve">17.0785999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648832321167</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8917446136475</t>
+    <t xml:space="preserve">16.8917465209961</t>
   </si>
   <si>
     <t xml:space="preserve">17.9007625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0876197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.536075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9194507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0502471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5740909576416</t>
+    <t xml:space="preserve">18.0876178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5360736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9194488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0502490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.574089050293</t>
   </si>
   <si>
     <t xml:space="preserve">16.742259979248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5554027557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3124942779541</t>
+    <t xml:space="preserve">16.5554046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3124923706055</t>
   </si>
   <si>
     <t xml:space="preserve">17.0225429534912</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">16.069580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8453531265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7519273757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6024398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0135231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9014101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761514663696</t>
+    <t xml:space="preserve">15.8453521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7519254684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6024408340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0135250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9014091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9761505126953</t>
   </si>
   <si>
     <t xml:space="preserve">15.3595285415649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5186777114868</t>
+    <t xml:space="preserve">14.5186786651611</t>
   </si>
   <si>
     <t xml:space="preserve">14.1636524200439</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">14.8550186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5090112686157</t>
+    <t xml:space="preserve">15.50901222229</t>
   </si>
   <si>
     <t xml:space="preserve">15.6398105621338</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6771802902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5276975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716424942017</t>
+    <t xml:space="preserve">15.6771812438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5276985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716415405273</t>
   </si>
   <si>
     <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584968566895</t>
+    <t xml:space="preserve">15.6584978103638</t>
   </si>
   <si>
     <t xml:space="preserve">15.8640394210815</t>
@@ -1439,13 +1439,13 @@
     <t xml:space="preserve">17.7699642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1249923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6391639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.480016708374</t>
+    <t xml:space="preserve">18.1249904632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6391677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4800186157227</t>
   </si>
   <si>
     <t xml:space="preserve">18.0689334869385</t>
@@ -1454,49 +1454,49 @@
     <t xml:space="preserve">17.1720275878906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5644245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7132663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8066883087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4329814910889</t>
+    <t xml:space="preserve">17.5644226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6017932891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.751277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.713264465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8066921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">19.5264053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9935474395752</t>
+    <t xml:space="preserve">19.9935455322266</t>
   </si>
   <si>
     <t xml:space="preserve">20.5541152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4606857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1336898803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9468326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2271156311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.600830078125</t>
+    <t xml:space="preserve">20.4606876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2738285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1336879730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.946834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2271175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6008281707764</t>
   </si>
   <si>
     <t xml:space="preserve">20.6475410461426</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">21.2081069946289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5818214416504</t>
+    <t xml:space="preserve">21.5818195343018</t>
   </si>
   <si>
     <t xml:space="preserve">21.955530166626</t>
@@ -1514,103 +1514,103 @@
     <t xml:space="preserve">21.3015365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8343963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0869770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7599773406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1994132995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7350769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9700183868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7820644378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4531478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5471248626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6880912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.030252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8423004150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1712188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0772399902344</t>
+    <t xml:space="preserve">20.8343982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0869750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7599754333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4796943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1994113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7350749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9700164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7820625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.453145980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5471229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5001354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6880893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0302543640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8422985076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1712169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.077241897583</t>
   </si>
   <si>
     <t xml:space="preserve">18.9362773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832649230957</t>
+    <t xml:space="preserve">19.6410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832668304443</t>
   </si>
   <si>
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290557861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.265193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4194049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6261539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4757900238037</t>
+    <t xml:space="preserve">19.8290538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2651920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4194068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6261558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4757919311523</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765140533447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5133819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7953128814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6449508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8158054351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2856922149658</t>
+    <t xml:space="preserve">18.5133800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7953109741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.644947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639934539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3929119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8158073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2856903076172</t>
   </si>
   <si>
     <t xml:space="preserve">22.0844917297363</t>
@@ -1625,571 +1625,571 @@
     <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1652221679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0712432861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5881156921387</t>
+    <t xml:space="preserve">23.4941425323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1652240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0712451934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.58811378479</t>
   </si>
   <si>
     <t xml:space="preserve">24.1989650726318</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7760677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7290821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0242576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8363018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8832912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5411281585693</t>
+    <t xml:space="preserve">23.7760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7290802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0242557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8363037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8832931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5411262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9302768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7085857391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.131477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9435291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.909782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7688179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2387027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8495502471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8098125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4339046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3869171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4001636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6351013183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9640216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4808921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5616226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6555995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3736705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2724456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1182346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2459506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278835296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9170322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0110111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8568000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6218585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.138729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1917133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266567230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8025608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8627948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3796653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2519474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.34592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2182064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5697689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3591709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3292751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0473480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3066349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1938610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4736423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.486888885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2989387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0170078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7389259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7013359069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8965377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049617767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.533878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3254280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9683151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.893138885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9418773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9039745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3923091888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.259651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5293464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.813606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2494716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5716342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7800922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5905838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8508014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9404621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.893087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0775032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.693395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4565143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0301246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4616069793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6511116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4142284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9878387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7983341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.419319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6612949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9455528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2349052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5665416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0403079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.756046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9980220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0453987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3631763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9273109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2305221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7188549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3821239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7946548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.087682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7990398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1547183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2873725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5147800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0599632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2115688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.476879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6562023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6088275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5140762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5038909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3092937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.162073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7779693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3566722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4040489196777</t>
   </si>
   <si>
     <t xml:space="preserve">22.9302787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.447151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7085876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1314792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9435253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.76881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5808658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2387008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8495483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8098106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3869152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4001617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6351051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2929382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9640216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4808921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5616226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6556015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3736705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061847686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2724456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1182346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2459526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7628211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9170341491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0110111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8568000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6218585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1857166290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.138729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1917152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4398994445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8025608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8627967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3796653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2519493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3459243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6748447418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3591690063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3292751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0473480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3066329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1938610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6637439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3194332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4736423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2989387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0170059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7389259338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7013339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8965358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5338764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3254280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9683170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931350708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2165050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9418773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9039745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3923072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5293464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.813606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2494716644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.950647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7800903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5905818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8508014678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7509574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8457107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.893087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2771892547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0775012969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6933975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2670078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4565162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0301246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6511116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4142303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9878387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7983322143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.419319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6612949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2349033355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5665416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0403079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.756046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9980220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0453987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3631744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9273109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2305202484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7188549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3821258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7946548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0927753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0876846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7990398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1547164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.28737449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5147819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0599632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.476879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6562042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6088275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5140762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5038909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3092937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1620750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7779693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3566703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4040470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6883068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1248779296875</t>
+    <t xml:space="preserve">23.6883087158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">22.8829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7881507873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0250339508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1722545623779</t>
+    <t xml:space="preserve">22.7881526947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0250358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1722564697266</t>
   </si>
   <si>
     <t xml:space="preserve">22.8355274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4514217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3515777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.167163848877</t>
+    <t xml:space="preserve">23.4514236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3515796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1671657562256</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">21.7458667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6037349700928</t>
+    <t xml:space="preserve">21.6037368774414</t>
   </si>
   <si>
     <t xml:space="preserve">21.7932434082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6984901428223</t>
+    <t xml:space="preserve">21.6984882354736</t>
   </si>
   <si>
     <t xml:space="preserve">21.5563583374023</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">21.5089817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4987983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6832141876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9725646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2568264007568</t>
+    <t xml:space="preserve">23.49880027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6832160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9725666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2568244934082</t>
   </si>
   <si>
     <t xml:space="preserve">24.0673198699951</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2991104125977</t>
+    <t xml:space="preserve">25.2991123199463</t>
   </si>
   <si>
     <t xml:space="preserve">24.9200992584229</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">24.825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7305908203125</t>
+    <t xml:space="preserve">24.7305927276611</t>
   </si>
   <si>
     <t xml:space="preserve">24.3989562988281</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">24.4937076568604</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0148506164551</t>
+    <t xml:space="preserve">25.0148525238037</t>
   </si>
   <si>
     <t xml:space="preserve">25.7255001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6358375549316</t>
+    <t xml:space="preserve">24.6358394622803</t>
   </si>
   <si>
     <t xml:space="preserve">25.5359935760498</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">25.772876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3464889526367</t>
+    <t xml:space="preserve">25.3464870452881</t>
   </si>
   <si>
     <t xml:space="preserve">23.5935535430908</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">23.2619171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9776573181152</t>
+    <t xml:space="preserve">22.9776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.2145404815674</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">23.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7830600738525</t>
+    <t xml:space="preserve">23.7830581665039</t>
   </si>
   <si>
     <t xml:space="preserve">21.3194751739502</t>
@@ -2315,46 +2315,46 @@
     <t xml:space="preserve">22.6460208892822</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3617630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622291564941</t>
+    <t xml:space="preserve">22.361759185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622310638428</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4835262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3887729644775</t>
+    <t xml:space="preserve">26.483528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3887748718262</t>
   </si>
   <si>
     <t xml:space="preserve">26.6256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1992664337158</t>
+    <t xml:space="preserve">26.1992683410645</t>
   </si>
   <si>
     <t xml:space="preserve">25.8202533721924</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5309028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6730327606201</t>
+    <t xml:space="preserve">26.5309047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6730308532715</t>
   </si>
   <si>
     <t xml:space="preserve">26.3201923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7480144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6526508331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8433742523193</t>
+    <t xml:space="preserve">25.7480125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6526489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.843376159668</t>
   </si>
   <si>
     <t xml:space="preserve">25.6049690246582</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">25.891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0817813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5096054077148</t>
+    <t xml:space="preserve">26.0817832946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5096035003662</t>
   </si>
   <si>
     <t xml:space="preserve">26.1294651031494</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">25.9387378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7956962585449</t>
+    <t xml:space="preserve">25.7956943511963</t>
   </si>
   <si>
     <t xml:space="preserve">25.12815284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2235164642334</t>
+    <t xml:space="preserve">25.223518371582</t>
   </si>
   <si>
     <t xml:space="preserve">25.2711982727051</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">24.9851093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1758327484131</t>
+    <t xml:space="preserve">25.1758346557617</t>
   </si>
   <si>
     <t xml:space="preserve">24.5559749603271</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">24.6990203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9361152648926</t>
+    <t xml:space="preserve">23.9361133575439</t>
   </si>
   <si>
     <t xml:space="preserve">24.937427520752</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">24.8420639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5082912445068</t>
+    <t xml:space="preserve">24.5082931518555</t>
   </si>
   <si>
     <t xml:space="preserve">23.8884334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2222061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6977062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8407516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.317569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0791606903076</t>
+    <t xml:space="preserve">24.222204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6977081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8407535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3175678253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.079158782959</t>
   </si>
   <si>
     <t xml:space="preserve">24.6513366699219</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">22.9824848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871231079102</t>
+    <t xml:space="preserve">22.8871212005615</t>
   </si>
   <si>
     <t xml:space="preserve">22.0288562774658</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">21.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1705894470215</t>
+    <t xml:space="preserve">21.1705875396729</t>
   </si>
   <si>
     <t xml:space="preserve">21.0752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9321784973145</t>
+    <t xml:space="preserve">20.9321804046631</t>
   </si>
   <si>
     <t xml:space="preserve">20.5984115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136329650879</t>
+    <t xml:space="preserve">21.3136310577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.6474018096924</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">20.8368167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0739135742188</t>
+    <t xml:space="preserve">20.88450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0739116668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.1229057312012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">20.6460933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9390926361084</t>
+    <t xml:space="preserve">18.939094543457</t>
   </si>
   <si>
     <t xml:space="preserve">19.4063720703125</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">18.6339321136475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5385704040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.519495010376</t>
+    <t xml:space="preserve">18.5385684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5194969177246</t>
   </si>
   <si>
     <t xml:space="preserve">18.0426826477051</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.6993732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8710289001465</t>
+    <t xml:space="preserve">17.8710269927979</t>
   </si>
   <si>
     <t xml:space="preserve">18.7674388885498</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">20.2169570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.835506439209</t>
+    <t xml:space="preserve">19.8355045318604</t>
   </si>
   <si>
     <t xml:space="preserve">20.5030479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7891368865967</t>
+    <t xml:space="preserve">20.789134979248</t>
   </si>
   <si>
     <t xml:space="preserve">21.7904472351074</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">19.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7894763946533</t>
+    <t xml:space="preserve">19.7894744873047</t>
   </si>
   <si>
     <t xml:space="preserve">20.5751628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9188976287842</t>
+    <t xml:space="preserve">20.9188995361328</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">22.6375885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8831157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7849063873291</t>
+    <t xml:space="preserve">22.883113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7849044799805</t>
   </si>
   <si>
     <t xml:space="preserve">21.9010066986084</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">21.6554794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2268543243408</t>
+    <t xml:space="preserve">23.2268524169922</t>
   </si>
   <si>
     <t xml:space="preserve">24.0125408172607</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">22.6866931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340091705322</t>
+    <t xml:space="preserve">22.8340110778809</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.539379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1956386566162</t>
+    <t xml:space="preserve">22.5393772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1956405639648</t>
   </si>
   <si>
     <t xml:space="preserve">22.4902725219727</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">22.4411659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7045879364014</t>
+    <t xml:space="preserve">21.7045860290527</t>
   </si>
   <si>
     <t xml:space="preserve">22.293851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8519020080566</t>
+    <t xml:space="preserve">21.8519039154053</t>
   </si>
   <si>
     <t xml:space="preserve">22.2447452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501152038574</t>
+    <t xml:space="preserve">21.9501132965088</t>
   </si>
   <si>
     <t xml:space="preserve">22.3429565429688</t>
@@ -2684,22 +2684,22 @@
     <t xml:space="preserve">21.6063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135334014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4590606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1153221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4099521636963</t>
+    <t xml:space="preserve">21.2135314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.017110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4590587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1153202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4099540710449</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403697967529</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">19.6028747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3278846740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9350433349609</t>
+    <t xml:space="preserve">19.3278865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9350414276123</t>
   </si>
   <si>
     <t xml:space="preserve">18.954683303833</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">19.5046634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1823177337646</t>
+    <t xml:space="preserve">20.1823196411133</t>
   </si>
   <si>
     <t xml:space="preserve">20.1332130432129</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">19.985897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6912651062012</t>
+    <t xml:space="preserve">19.6912631988525</t>
   </si>
   <si>
     <t xml:space="preserve">19.5832328796387</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">19.3671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738618850708</t>
+    <t xml:space="preserve">18.7386207580566</t>
   </si>
   <si>
     <t xml:space="preserve">18.4047031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1689968109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2279224395752</t>
+    <t xml:space="preserve">18.1689987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2279243469238</t>
   </si>
   <si>
     <t xml:space="preserve">18.0904293060303</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">18.1493549346924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.717227935791</t>
+    <t xml:space="preserve">17.7172298431396</t>
   </si>
   <si>
     <t xml:space="preserve">18.6796951293945</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">18.6404094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5029125213623</t>
+    <t xml:space="preserve">18.5029144287109</t>
   </si>
   <si>
     <t xml:space="preserve">18.8761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4225959777832</t>
+    <t xml:space="preserve">17.4225940704346</t>
   </si>
   <si>
     <t xml:space="preserve">18.2868518829346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547626495361</t>
+    <t xml:space="preserve">18.2475662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547607421875</t>
   </si>
   <si>
     <t xml:space="preserve">18.4832706451416</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">17.9529342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.129711151123</t>
+    <t xml:space="preserve">18.1297130584717</t>
   </si>
   <si>
     <t xml:space="preserve">17.5208072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2654590606689</t>
+    <t xml:space="preserve">17.2654571533203</t>
   </si>
   <si>
     <t xml:space="preserve">17.3243827819824</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">17.4618797302246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1083202362061</t>
+    <t xml:space="preserve">17.1083221435547</t>
   </si>
   <si>
     <t xml:space="preserve">17.2458152770996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7744045257568</t>
+    <t xml:space="preserve">16.7744026184082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9904670715332</t>
@@ -10831,7 +10831,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10857,7 +10857,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10883,7 +10883,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10909,7 +10909,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10935,7 +10935,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10961,7 +10961,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10987,7 +10987,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -11013,7 +11013,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -11039,7 +11039,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -11065,7 +11065,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -11091,7 +11091,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -11117,7 +11117,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -11169,7 +11169,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -11247,7 +11247,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -11273,7 +11273,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -11299,7 +11299,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -11325,7 +11325,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -11351,7 +11351,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -11377,7 +11377,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -11403,7 +11403,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -11429,7 +11429,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -11455,7 +11455,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -11481,7 +11481,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -11507,7 +11507,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -11533,7 +11533,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -11559,7 +11559,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -11585,7 +11585,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11611,7 +11611,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11637,7 +11637,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11663,7 +11663,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11689,7 +11689,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11715,7 +11715,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11741,7 +11741,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11767,7 +11767,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11793,7 +11793,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11819,7 +11819,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11845,7 +11845,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11871,7 +11871,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11897,7 +11897,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11923,7 +11923,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11949,7 +11949,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11975,7 +11975,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -12001,7 +12001,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -12027,7 +12027,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -12053,7 +12053,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -12079,7 +12079,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -12105,7 +12105,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -12131,7 +12131,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -12157,7 +12157,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -12183,7 +12183,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -12209,7 +12209,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -12235,7 +12235,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -12261,7 +12261,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -12287,7 +12287,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -12313,7 +12313,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -12339,7 +12339,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -12365,7 +12365,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -12391,7 +12391,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -12417,7 +12417,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -12443,7 +12443,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -12469,7 +12469,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -12495,7 +12495,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -12521,7 +12521,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -12547,7 +12547,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -12573,7 +12573,7 @@
         <v>12.2929019927979</v>
       </c>
       <c r="G336" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12599,7 +12599,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12625,7 +12625,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12651,7 +12651,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12677,7 +12677,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12703,7 +12703,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12729,7 +12729,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12755,7 +12755,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12781,7 +12781,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12807,7 +12807,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12833,7 +12833,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12859,7 +12859,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12885,7 +12885,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12911,7 +12911,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12937,7 +12937,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12963,7 +12963,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12989,7 +12989,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -13015,7 +13015,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -13041,7 +13041,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -13067,7 +13067,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -13093,7 +13093,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -13119,7 +13119,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -13145,7 +13145,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -13171,7 +13171,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -13197,7 +13197,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -13223,7 +13223,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -13249,7 +13249,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -13275,7 +13275,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -13301,7 +13301,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -13327,7 +13327,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -13353,7 +13353,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -13379,7 +13379,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -13405,7 +13405,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -13431,7 +13431,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -13457,7 +13457,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -13483,7 +13483,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -13509,7 +13509,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -13535,7 +13535,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -13561,7 +13561,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -13587,7 +13587,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13613,7 +13613,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13639,7 +13639,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13665,7 +13665,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13691,7 +13691,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13717,7 +13717,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13743,7 +13743,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13769,7 +13769,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13795,7 +13795,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13821,7 +13821,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13847,7 +13847,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13873,7 +13873,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13899,7 +13899,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13925,7 +13925,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13951,7 +13951,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13977,7 +13977,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14003,7 +14003,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -14029,7 +14029,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -14055,7 +14055,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14081,7 +14081,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -14107,7 +14107,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14133,7 +14133,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14159,7 +14159,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14185,7 +14185,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14211,7 +14211,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14237,7 +14237,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14263,7 +14263,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14289,7 +14289,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14315,7 +14315,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14341,7 +14341,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14367,7 +14367,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14393,7 +14393,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14419,7 +14419,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14445,7 +14445,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14471,7 +14471,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14497,7 +14497,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14523,7 +14523,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14549,7 +14549,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14575,7 +14575,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14601,7 +14601,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14627,7 +14627,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14653,7 +14653,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14679,7 +14679,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14705,7 +14705,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14731,7 +14731,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14757,7 +14757,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14783,7 +14783,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14809,7 +14809,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14835,7 +14835,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14861,7 +14861,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14887,7 +14887,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14913,7 +14913,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14939,7 +14939,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14965,7 +14965,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14991,7 +14991,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -15017,7 +15017,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -15043,7 +15043,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -15069,7 +15069,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15095,7 +15095,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15121,7 +15121,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15147,7 +15147,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15173,7 +15173,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15199,7 +15199,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15225,7 +15225,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15251,7 +15251,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15277,7 +15277,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15303,7 +15303,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15329,7 +15329,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15355,7 +15355,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15381,7 +15381,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15407,7 +15407,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15433,7 +15433,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15459,7 +15459,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15511,7 +15511,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15537,7 +15537,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15563,7 +15563,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15589,7 +15589,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15615,7 +15615,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15641,7 +15641,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15667,7 +15667,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15693,7 +15693,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15719,7 +15719,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15745,7 +15745,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15771,7 +15771,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15797,7 +15797,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15823,7 +15823,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15849,7 +15849,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15875,7 +15875,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15901,7 +15901,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15927,7 +15927,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15953,7 +15953,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15979,7 +15979,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16005,7 +16005,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -16031,7 +16031,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -16057,7 +16057,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16083,7 +16083,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16109,7 +16109,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16135,7 +16135,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16161,7 +16161,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16187,7 +16187,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16213,7 +16213,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16239,7 +16239,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16265,7 +16265,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16291,7 +16291,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16317,7 +16317,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16343,7 +16343,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16369,7 +16369,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16395,7 +16395,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16421,7 +16421,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16447,7 +16447,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16473,7 +16473,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16499,7 +16499,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16525,7 +16525,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16551,7 +16551,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16577,7 +16577,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16603,7 +16603,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16629,7 +16629,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16655,7 +16655,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16681,7 +16681,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16707,7 +16707,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16733,7 +16733,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16759,7 +16759,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16785,7 +16785,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16811,7 +16811,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16837,7 +16837,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16863,7 +16863,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16889,7 +16889,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16915,7 +16915,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16941,7 +16941,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16967,7 +16967,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16993,7 +16993,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -17019,7 +17019,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -17045,7 +17045,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -17071,7 +17071,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17097,7 +17097,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17123,7 +17123,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17149,7 +17149,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17175,7 +17175,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17201,7 +17201,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17227,7 +17227,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17253,7 +17253,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17279,7 +17279,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17305,7 +17305,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17331,7 +17331,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17383,7 +17383,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17929,7 +17929,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -21933,7 +21933,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -52491,10 +52491,10 @@
     </row>
     <row r="1872">
       <c r="A1872" s="1" t="n">
-        <v>45950.649375</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1872" t="n">
-        <v>162756</v>
+        <v>175713</v>
       </c>
       <c r="C1872" t="n">
         <v>22.8500003814697</v>
@@ -52512,6 +52512,32 @@
         <v>1121</v>
       </c>
       <c r="H1872" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="1" t="n">
+        <v>45951.6494444444</v>
+      </c>
+      <c r="B1873" t="n">
+        <v>88333</v>
+      </c>
+      <c r="C1873" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="D1873" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="G1873" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H1873" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -44,61 +44,61 @@
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8109917640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68969202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348079681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721220016479</t>
+    <t xml:space="preserve">7.90288686752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099319458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68969297409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348031997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721315383911</t>
   </si>
   <si>
     <t xml:space="preserve">7.67407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97640085220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4443359375</t>
+    <t xml:space="preserve">7.97640180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44433689117432</t>
   </si>
   <si>
     <t xml:space="preserve">7.30281972885132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52520322799683</t>
+    <t xml:space="preserve">7.52520275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.46639060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57206869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4434175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52612113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54450082778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64742136001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85693883895874</t>
+    <t xml:space="preserve">7.57206916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44341707229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52612161636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54450035095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8569393157959</t>
   </si>
   <si>
     <t xml:space="preserve">7.92218542098999</t>
@@ -107,67 +107,67 @@
     <t xml:space="preserve">8.00397205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86612939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01959228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81466960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76504564285278</t>
+    <t xml:space="preserve">7.86612844467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01959323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81466865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76504707336426</t>
   </si>
   <si>
     <t xml:space="preserve">7.85142660140991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69336891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79261541366577</t>
+    <t xml:space="preserve">7.69336843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79261445999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.74666786193848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88910341262817</t>
+    <t xml:space="preserve">7.88910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.56379890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67315244674683</t>
+    <t xml:space="preserve">7.67315196990967</t>
   </si>
   <si>
     <t xml:space="preserve">7.78526401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74850654602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478101730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11424350738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30354499816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46343994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48641300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75382518768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966911315918</t>
+    <t xml:space="preserve">7.74850559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11424255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46344089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48641395568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966815948486</t>
   </si>
   <si>
     <t xml:space="preserve">8.60128116607666</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">8.46987247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3623571395874</t>
+    <t xml:space="preserve">8.36235809326172</t>
   </si>
   <si>
     <t xml:space="preserve">8.45425128936768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71155548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74831295013428</t>
+    <t xml:space="preserve">8.71155452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
     <t xml:space="preserve">8.61598491668701</t>
@@ -209,103 +209,103 @@
     <t xml:space="preserve">8.86869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11588764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14345645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09750938415527</t>
+    <t xml:space="preserve">9.11588954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14345550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09751033782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.11680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99091339111328</t>
+    <t xml:space="preserve">8.99091243743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.18572902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06167030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02399349212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76577281951904</t>
+    <t xml:space="preserve">9.06166934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76577186584473</t>
   </si>
   <si>
     <t xml:space="preserve">8.9936695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04237270355225</t>
+    <t xml:space="preserve">9.04237365722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.90177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67112255096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50754737854004</t>
+    <t xml:space="preserve">8.67112159729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50754833221436</t>
   </si>
   <si>
     <t xml:space="preserve">7.98191595077515</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30630302429199</t>
+    <t xml:space="preserve">8.30630207061768</t>
   </si>
   <si>
     <t xml:space="preserve">8.40830421447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54614543914795</t>
+    <t xml:space="preserve">8.54614639282227</t>
   </si>
   <si>
     <t xml:space="preserve">8.5920934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63804054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80804347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126314163208</t>
+    <t xml:space="preserve">8.63803958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80804443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126361846924</t>
   </si>
   <si>
     <t xml:space="preserve">7.92126512527466</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34214019775391</t>
+    <t xml:space="preserve">8.34214115142822</t>
   </si>
   <si>
     <t xml:space="preserve">8.77496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77771759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50571346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59944438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70144748687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57739067077637</t>
+    <t xml:space="preserve">8.77771949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75474452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50571155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70144653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57738971710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.39268207550049</t>
@@ -317,112 +317,112 @@
     <t xml:space="preserve">8.5608491897583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71982574462891</t>
+    <t xml:space="preserve">8.71982479095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04164695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08667469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18867778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.548903465271</t>
+    <t xml:space="preserve">8.04164791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0866756439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18867683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.33479022979736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5093879699707</t>
+    <t xml:space="preserve">8.50938892364502</t>
   </si>
   <si>
     <t xml:space="preserve">8.92107391357422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0386962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437000274658</t>
+    <t xml:space="preserve">9.03869724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9743709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.01664352416992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1526460647583</t>
+    <t xml:space="preserve">9.15264701843262</t>
   </si>
   <si>
     <t xml:space="preserve">8.84939670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07913112640381</t>
+    <t xml:space="preserve">9.07912921905518</t>
   </si>
   <si>
     <t xml:space="preserve">8.8558292388916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30446338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23370552062988</t>
+    <t xml:space="preserve">8.30446529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23370456695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.27046394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33754539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20062255859375</t>
+    <t xml:space="preserve">8.33754634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20062351226807</t>
   </si>
   <si>
     <t xml:space="preserve">8.40370941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27413940429688</t>
+    <t xml:space="preserve">8.27413845062256</t>
   </si>
   <si>
     <t xml:space="preserve">8.2980318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5001974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43587207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22451686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35408782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22083950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15283870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39911556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42668342590332</t>
+    <t xml:space="preserve">8.50019836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43587303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22451591491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35408687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22084045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15283966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39911460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42668437957764</t>
   </si>
   <si>
     <t xml:space="preserve">8.48365783691406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70971584320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77128410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72074413299561</t>
+    <t xml:space="preserve">8.709716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77128601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72074317932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.10026741027832</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">8.89809894561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83469295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97712993621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05156326293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23535060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2059440612793</t>
+    <t xml:space="preserve">8.83469390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97712802886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05156230926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20594501495361</t>
   </si>
   <si>
     <t xml:space="preserve">9.36216354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3952465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64887523651123</t>
+    <t xml:space="preserve">9.39524745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
     <t xml:space="preserve">9.69482135772705</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">9.59373760223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64336013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989288330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6176290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49265480041504</t>
+    <t xml:space="preserve">9.64336109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3198938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61763000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49265575408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.51103210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28497409820557</t>
+    <t xml:space="preserve">9.28497314453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.46324729919434</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">9.33092021942139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12875461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26291942596436</t>
+    <t xml:space="preserve">9.12875366210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26291847229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.14713287353516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06075286865234</t>
+    <t xml:space="preserve">9.06075096130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.9412899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37797927856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76025772094727</t>
+    <t xml:space="preserve">8.37798023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76025867462158</t>
   </si>
   <si>
     <t xml:space="preserve">9.0065336227417</t>
@@ -518,49 +518,49 @@
     <t xml:space="preserve">9.18940353393555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96885681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10669898986816</t>
+    <t xml:space="preserve">8.96885776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10669994354248</t>
   </si>
   <si>
     <t xml:space="preserve">9.44670677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39157009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46508693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53860092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75914669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68563365936279</t>
+    <t xml:space="preserve">9.39157104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74076747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46508598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53860282897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75914573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68563175201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.90617656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532064437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79590225219727</t>
+    <t xml:space="preserve">9.99807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7959041595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.92455673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81428146362305</t>
+    <t xml:space="preserve">9.81428241729736</t>
   </si>
   <si>
     <t xml:space="preserve">9.9429349899292</t>
@@ -578,91 +578,91 @@
     <t xml:space="preserve">9.77752590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86941909790039</t>
+    <t xml:space="preserve">9.83266162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86941814422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.163480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105115890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348291397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.016450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267223358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5126791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6045713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659707069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7332239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207849502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4759206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97969341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85104084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88544750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253971099854</t>
   </si>
   <si>
     <t xml:space="preserve">10.1451015472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.163480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105115890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348291397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0164499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5126781463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6045713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659707069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7332239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207849502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97969341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85104084014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821966171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.941086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88544464111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451005935669</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.99672603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2007427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2192888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0894603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523672103882</t>
+    <t xml:space="preserve">10.2007417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2192878723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0894613265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399265289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523681640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.7370719909668</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">10.4047574996948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4233045578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3862113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3676624298096</t>
+    <t xml:space="preserve">10.423303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3676633834839</t>
   </si>
   <si>
     <t xml:space="preserve">9.82980728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3120231628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.033821105957</t>
+    <t xml:space="preserve">10.3120241165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338220596313</t>
   </si>
   <si>
     <t xml:space="preserve">9.81125926971436</t>
@@ -704,34 +704,34 @@
     <t xml:space="preserve">10.070915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79271221160889</t>
+    <t xml:space="preserve">10.1080083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7927131652832</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4789438247681</t>
+    <t xml:space="preserve">10.8498802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4789428710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554227828979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103000640869</t>
+    <t xml:space="preserve">11.1651744842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102991104126</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062833786011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5361108779907</t>
+    <t xml:space="preserve">11.536111831665</t>
   </si>
   <si>
     <t xml:space="preserve">11.6288452148438</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">11.5175647735596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9626884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1481561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2408895492554</t>
+    <t xml:space="preserve">11.9626903533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.148157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2408885955811</t>
   </si>
   <si>
     <t xml:space="preserve">12.4449043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5932788848877</t>
+    <t xml:space="preserve">12.5932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">12.1852493286133</t>
@@ -764,19 +764,19 @@
     <t xml:space="preserve">11.5917520523071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4804716110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9255933761597</t>
+    <t xml:space="preserve">11.7401285171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4804725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.925594329834</t>
   </si>
   <si>
     <t xml:space="preserve">12.1110620498657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1667022705078</t>
+    <t xml:space="preserve">12.1667032241821</t>
   </si>
   <si>
     <t xml:space="preserve">12.2223434448242</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">12.6860132217407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.982762336731</t>
+    <t xml:space="preserve">12.9827632904053</t>
   </si>
   <si>
     <t xml:space="preserve">13.2609643936157</t>
@@ -800,31 +800,31 @@
     <t xml:space="preserve">13.5020723342896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0584764480591</t>
+    <t xml:space="preserve">14.058479309082</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3892650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3521709442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2965316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.407811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2037963867188</t>
+    <t xml:space="preserve">13.2053251266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125898361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3892641067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3521718978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2965297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4078121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2037973403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779846191406</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">14.5963354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9101028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4093399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1682319641113</t>
+    <t xml:space="preserve">13.9101037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4093389511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.168231010437</t>
   </si>
   <si>
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561866760254</t>
+    <t xml:space="preserve">12.7045602798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561857223511</t>
   </si>
   <si>
     <t xml:space="preserve">12.3707189559937</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">12.8900299072266</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0940446853638</t>
+    <t xml:space="preserve">13.0940437316895</t>
   </si>
   <si>
     <t xml:space="preserve">13.075496673584</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">13.3351516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569505691528</t>
+    <t xml:space="preserve">13.0569496154785</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489191055298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150777816772</t>
+    <t xml:space="preserve">12.3150787353516</t>
   </si>
   <si>
     <t xml:space="preserve">12.4634523391724</t>
@@ -887,37 +887,37 @@
     <t xml:space="preserve">12.4263582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514089584351</t>
+    <t xml:space="preserve">11.8514070510864</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772207260132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2950029373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0168018341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090989112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0353488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7571449279785</t>
+    <t xml:space="preserve">11.2950038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0168008804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0909881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0353498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7571458816528</t>
   </si>
   <si>
     <t xml:space="preserve">11.313549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2764549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2208166122437</t>
+    <t xml:space="preserve">11.1280832290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2764558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2208156585693</t>
   </si>
   <si>
     <t xml:space="preserve">11.3691892623901</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40322875976562</t>
+    <t xml:space="preserve">9.40322780609131</t>
   </si>
   <si>
     <t xml:space="preserve">8.88391780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55160427093506</t>
+    <t xml:space="preserve">9.55160331726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.71699810028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80973148345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20696067810059</t>
+    <t xml:space="preserve">8.80973243713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20695972442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.24405384063721</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">8.53152942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43879508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64433765411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200517654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77416706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.293478012085</t>
+    <t xml:space="preserve">8.438796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64433860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77416515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2934770584106</t>
   </si>
   <si>
     <t xml:space="preserve">10.2378349304199</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">11.6844873428345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8699550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4819993972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6118259429932</t>
+    <t xml:space="preserve">11.8699541091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6118268966675</t>
   </si>
   <si>
     <t xml:space="preserve">11.7586727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7246332168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4835252761841</t>
+    <t xml:space="preserve">13.7246341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
     <t xml:space="preserve">13.6504487991333</t>
@@ -1022,22 +1022,22 @@
     <t xml:space="preserve">15.2825660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687986373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938455581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6148824691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4665079116821</t>
+    <t xml:space="preserve">15.7462377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487237930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6148815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4665069580078</t>
   </si>
   <si>
     <t xml:space="preserve">14.0399293899536</t>
@@ -1058,46 +1058,49 @@
     <t xml:space="preserve">14.0770235061646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3181324005127</t>
+    <t xml:space="preserve">14.318133354187</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076148986816</t>
   </si>
   <si>
+    <t xml:space="preserve">14.9858179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5560503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.79896068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.892388343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7615909576416</t>
+  </si>
+  <si>
     <t xml:space="preserve">14.9858169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.79896068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923902511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7802743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7615909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2661008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287302017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.415584564209</t>
+    <t xml:space="preserve">15.2660999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4155855178833</t>
   </si>
   <si>
     <t xml:space="preserve">15.3221569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0045022964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6121053695679</t>
+    <t xml:space="preserve">15.0045032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6121063232422</t>
   </si>
   <si>
     <t xml:space="preserve">15.0792446136475</t>
@@ -1106,37 +1109,37 @@
     <t xml:space="preserve">14.911075592041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6494770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1353034973145</t>
+    <t xml:space="preserve">14.6494779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1353025436401</t>
   </si>
   <si>
     <t xml:space="preserve">14.9297609329224</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0231885910034</t>
+    <t xml:space="preserve">15.0231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9484453201294</t>
+    <t xml:space="preserve">14.948447227478</t>
   </si>
   <si>
     <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5650691986084</t>
+    <t xml:space="preserve">15.5650682449341</t>
   </si>
   <si>
     <t xml:space="preserve">16.1630058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9664878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6765384674072</t>
+    <t xml:space="preserve">16.9664859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6765403747559</t>
   </si>
   <si>
     <t xml:space="preserve">16.7235736846924</t>
@@ -1154,10 +1157,10 @@
     <t xml:space="preserve">17.3962535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7886524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0128765106201</t>
+    <t xml:space="preserve">17.7886505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0128784179688</t>
   </si>
   <si>
     <t xml:space="preserve">17.8820781707764</t>
@@ -1166,7 +1169,7 @@
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118476867676</t>
+    <t xml:space="preserve">18.3118457794189</t>
   </si>
   <si>
     <t xml:space="preserve">17.6578521728516</t>
@@ -1175,13 +1178,13 @@
     <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9941921234131</t>
+    <t xml:space="preserve">17.9941940307617</t>
   </si>
   <si>
     <t xml:space="preserve">18.6855583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1526947021484</t>
+    <t xml:space="preserve">19.1526966094971</t>
   </si>
   <si>
     <t xml:space="preserve">18.3305320739746</t>
@@ -1190,7 +1193,7 @@
     <t xml:space="preserve">18.2184181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0315647125244</t>
+    <t xml:space="preserve">18.031566619873</t>
   </si>
   <si>
     <t xml:space="preserve">17.3775691986084</t>
@@ -1205,37 +1208,37 @@
     <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9291152954102</t>
+    <t xml:space="preserve">16.9291133880615</t>
   </si>
   <si>
     <t xml:space="preserve">16.667516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4619770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9574661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.378212928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706117630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5927772521973</t>
+    <t xml:space="preserve">15.8266658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4619750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9574680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3782119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5367183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5927753448486</t>
   </si>
   <si>
     <t xml:space="preserve">16.2938060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4246063232422</t>
+    <t xml:space="preserve">16.4246044158936</t>
   </si>
   <si>
     <t xml:space="preserve">16.2751216888428</t>
@@ -1244,16 +1247,16 @@
     <t xml:space="preserve">16.8543739318848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.704891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3311767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4993476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3685474395752</t>
+    <t xml:space="preserve">16.7048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3311786651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4993457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3685493469238</t>
   </si>
   <si>
     <t xml:space="preserve">16.3498630523682</t>
@@ -1262,31 +1265,31 @@
     <t xml:space="preserve">16.6862049102783</t>
   </si>
   <si>
-    <t xml:space="preserve">16.63014793396</t>
+    <t xml:space="preserve">16.6301441192627</t>
   </si>
   <si>
     <t xml:space="preserve">16.6114597320557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7609462738037</t>
+    <t xml:space="preserve">16.7609481811523</t>
   </si>
   <si>
     <t xml:space="preserve">16.8170013427734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.798318862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7892942428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6868486404419</t>
+    <t xml:space="preserve">16.7983169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7892971038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4342708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6868476867676</t>
   </si>
   <si>
     <t xml:space="preserve">14.5373640060425</t>
@@ -1295,16 +1298,16 @@
     <t xml:space="preserve">17.3215103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5180320739746</t>
+    <t xml:space="preserve">16.518030166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.6211252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8827219009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377471923828</t>
+    <t xml:space="preserve">15.8827238082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377490997314</t>
   </si>
   <si>
     <t xml:space="preserve">16.4806632995605</t>
@@ -1319,34 +1322,34 @@
     <t xml:space="preserve">16.9478015899658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0785999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.648832321167</t>
+    <t xml:space="preserve">17.0785980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6488342285156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8917465209961</t>
+    <t xml:space="preserve">16.8917446136475</t>
   </si>
   <si>
     <t xml:space="preserve">17.9007625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0876178741455</t>
+    <t xml:space="preserve">18.0876197814941</t>
   </si>
   <si>
     <t xml:space="preserve">18.5360736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9194488525391</t>
+    <t xml:space="preserve">17.9194507598877</t>
   </si>
   <si>
     <t xml:space="preserve">18.0502490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.574089050293</t>
+    <t xml:space="preserve">16.5740909576416</t>
   </si>
   <si>
     <t xml:space="preserve">16.742259979248</t>
@@ -1361,25 +1364,25 @@
     <t xml:space="preserve">17.0225429534912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.069580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8453521728516</t>
+    <t xml:space="preserve">16.0695819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8453512191772</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6024408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0135250091553</t>
+    <t xml:space="preserve">15.6024398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0135231018066</t>
   </si>
   <si>
     <t xml:space="preserve">15.9014091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9761505126953</t>
+    <t xml:space="preserve">15.9761524200439</t>
   </si>
   <si>
     <t xml:space="preserve">15.3595285415649</t>
@@ -1388,7 +1391,7 @@
     <t xml:space="preserve">14.5186786651611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1636524200439</t>
+    <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8550186157227</t>
@@ -1397,40 +1400,40 @@
     <t xml:space="preserve">15.50901222229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6398105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6771812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5276985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145528793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716415405273</t>
+    <t xml:space="preserve">15.6398115158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6771821975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5276975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.471640586853</t>
   </si>
   <si>
     <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584978103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8640394210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2190608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0972881317139</t>
+    <t xml:space="preserve">15.6584987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8640403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2190628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0972862243652</t>
   </si>
   <si>
     <t xml:space="preserve">17.1346588134766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9381351470947</t>
+    <t xml:space="preserve">17.9381370544434</t>
   </si>
   <si>
     <t xml:space="preserve">17.5831108093262</t>
@@ -1454,16 +1457,16 @@
     <t xml:space="preserve">17.1720275878906</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5644226074219</t>
+    <t xml:space="preserve">17.5644245147705</t>
   </si>
   <si>
     <t xml:space="preserve">17.6017932891846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.751277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.713264465332</t>
+    <t xml:space="preserve">17.7512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7132663726807</t>
   </si>
   <si>
     <t xml:space="preserve">19.8066921234131</t>
@@ -1472,34 +1475,34 @@
     <t xml:space="preserve">19.4329795837402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5264053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9935455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5541152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4606876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2738285064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1336879730225</t>
+    <t xml:space="preserve">19.5264072418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9935474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5541133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2738304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1336898803711</t>
   </si>
   <si>
     <t xml:space="preserve">19.946834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2271175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6008281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6475410461426</t>
+    <t xml:space="preserve">20.2271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6008262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6475391387939</t>
   </si>
   <si>
     <t xml:space="preserve">21.2081069946289</t>
@@ -1508,19 +1511,19 @@
     <t xml:space="preserve">21.5818195343018</t>
   </si>
   <si>
-    <t xml:space="preserve">21.955530166626</t>
+    <t xml:space="preserve">21.9555320739746</t>
   </si>
   <si>
     <t xml:space="preserve">21.3015365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8343982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0869750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7599754333496</t>
+    <t xml:space="preserve">20.8343963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0869770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7599773406982</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796943664551</t>
@@ -1529,25 +1532,25 @@
     <t xml:space="preserve">19.1994113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7350749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9700164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7820625305176</t>
+    <t xml:space="preserve">19.7350769042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9700145721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7820644378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.453145980835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5471229553223</t>
+    <t xml:space="preserve">19.5471248626709</t>
   </si>
   <si>
     <t xml:space="preserve">19.5001354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6880893707275</t>
+    <t xml:space="preserve">19.6880912780762</t>
   </si>
   <si>
     <t xml:space="preserve">19.0302543640137</t>
@@ -1562,25 +1565,25 @@
     <t xml:space="preserve">19.077241897583</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9362773895264</t>
+    <t xml:space="preserve">18.9362754821777</t>
   </si>
   <si>
     <t xml:space="preserve">19.6410999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9832668304443</t>
+    <t xml:space="preserve">18.9832649230957</t>
   </si>
   <si>
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290538787842</t>
+    <t xml:space="preserve">19.8290557861328</t>
   </si>
   <si>
     <t xml:space="preserve">19.2651920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4194068908691</t>
+    <t xml:space="preserve">18.4194049835205</t>
   </si>
   <si>
     <t xml:space="preserve">18.6261558532715</t>
@@ -1589,19 +1592,19 @@
     <t xml:space="preserve">18.4757919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7765140533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5133800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7953109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.644947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639934539795</t>
+    <t xml:space="preserve">18.7765159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5133819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7953128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6449489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639953613281</t>
   </si>
   <si>
     <t xml:space="preserve">20.3929119110107</t>
@@ -1610,10 +1613,10 @@
     <t xml:space="preserve">20.8158073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2856903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0844917297363</t>
+    <t xml:space="preserve">21.2856884002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0844898223877</t>
   </si>
   <si>
     <t xml:space="preserve">22.4603977203369</t>
@@ -1622,55 +1625,55 @@
     <t xml:space="preserve">22.9772682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2122097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4941425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1652240753174</t>
+    <t xml:space="preserve">23.2122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4941387176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1652221679688</t>
   </si>
   <si>
     <t xml:space="preserve">23.0712451934814</t>
   </si>
   <si>
-    <t xml:space="preserve">23.58811378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1989650726318</t>
+    <t xml:space="preserve">23.5881156921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1989631652832</t>
   </si>
   <si>
     <t xml:space="preserve">23.7760696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7290802001953</t>
+    <t xml:space="preserve">23.7290821075439</t>
   </si>
   <si>
     <t xml:space="preserve">23.0242557525635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8363037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8832931518555</t>
+    <t xml:space="preserve">22.8363018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8832912445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.5411262512207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302768707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2591953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4471530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555732727051</t>
+    <t xml:space="preserve">22.9302787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.447151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8700466156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555751800537</t>
   </si>
   <si>
     <t xml:space="preserve">21.7085857391357</t>
@@ -1679,13 +1682,13 @@
     <t xml:space="preserve">22.131477355957</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9435291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447238922119</t>
+    <t xml:space="preserve">21.9435272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447257995605</t>
   </si>
   <si>
     <t xml:space="preserve">20.909782409668</t>
@@ -1700,19 +1703,19 @@
     <t xml:space="preserve">20.5808658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2387027740479</t>
+    <t xml:space="preserve">21.2387046813965</t>
   </si>
   <si>
     <t xml:space="preserve">21.8495502471924</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8098125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977607727051</t>
+    <t xml:space="preserve">24.8098106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977626800537</t>
   </si>
   <si>
     <t xml:space="preserve">24.4339046478271</t>
@@ -1721,22 +1724,22 @@
     <t xml:space="preserve">24.3869171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4001636505127</t>
+    <t xml:space="preserve">23.4001617431641</t>
   </si>
   <si>
     <t xml:space="preserve">23.6351013183594</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1519737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230571746826</t>
+    <t xml:space="preserve">24.1519718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230590820312</t>
   </si>
   <si>
     <t xml:space="preserve">24.2929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9640216827393</t>
+    <t xml:space="preserve">23.9640235900879</t>
   </si>
   <si>
     <t xml:space="preserve">24.4808921813965</t>
@@ -1745,19 +1748,19 @@
     <t xml:space="preserve">25.5616226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4206600189209</t>
+    <t xml:space="preserve">25.4206619262695</t>
   </si>
   <si>
     <t xml:space="preserve">25.6555995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3736705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061847686768</t>
+    <t xml:space="preserve">25.3736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2796955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061866760254</t>
   </si>
   <si>
     <t xml:space="preserve">22.5543746948242</t>
@@ -1766,22 +1769,22 @@
     <t xml:space="preserve">22.2724456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1182346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2459506988525</t>
+    <t xml:space="preserve">23.1182327270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2459526062012</t>
   </si>
   <si>
     <t xml:space="preserve">24.7158355712891</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5278835296631</t>
+    <t xml:space="preserve">24.5278816223145</t>
   </si>
   <si>
     <t xml:space="preserve">24.7628231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9170322418213</t>
+    <t xml:space="preserve">23.9170341491699</t>
   </si>
   <si>
     <t xml:space="preserve">24.0110111236572</t>
@@ -1802,10 +1805,10 @@
     <t xml:space="preserve">21.5206298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1917133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266567230225</t>
+    <t xml:space="preserve">21.1917152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266548156738</t>
   </si>
   <si>
     <t xml:space="preserve">20.4399013519287</t>
@@ -1814,7 +1817,7 @@
     <t xml:space="preserve">21.8025608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8627948760986</t>
+    <t xml:space="preserve">20.8627967834473</t>
   </si>
   <si>
     <t xml:space="preserve">21.3326778411865</t>
@@ -1832,22 +1835,22 @@
     <t xml:space="preserve">20.34592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2182064056396</t>
+    <t xml:space="preserve">19.218204498291</t>
   </si>
   <si>
     <t xml:space="preserve">18.5697689056396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8760414123535</t>
+    <t xml:space="preserve">19.8760395050049</t>
   </si>
   <si>
     <t xml:space="preserve">20.6748428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3591709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
+    <t xml:space="preserve">19.3591690063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126560211182</t>
   </si>
   <si>
     <t xml:space="preserve">17.3292751312256</t>
@@ -1859,7 +1862,7 @@
     <t xml:space="preserve">16.8218040466309</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3066349029541</t>
+    <t xml:space="preserve">18.3066329956055</t>
   </si>
   <si>
     <t xml:space="preserve">18.1938610076904</t>
@@ -1868,13 +1871,13 @@
     <t xml:space="preserve">18.6637439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9230308532715</t>
+    <t xml:space="preserve">19.9230289459229</t>
   </si>
   <si>
     <t xml:space="preserve">21.6615962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">21.990514755249</t>
+    <t xml:space="preserve">21.9905128479004</t>
   </si>
   <si>
     <t xml:space="preserve">22.3194313049316</t>
@@ -1889,13 +1892,13 @@
     <t xml:space="preserve">20.2989387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0170078277588</t>
+    <t xml:space="preserve">20.0170059204102</t>
   </si>
   <si>
     <t xml:space="preserve">18.7389259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7013359069824</t>
+    <t xml:space="preserve">18.7013339996338</t>
   </si>
   <si>
     <t xml:space="preserve">21.8965377807617</t>
@@ -1904,19 +1907,19 @@
     <t xml:space="preserve">20.2049617767334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.533878326416</t>
+    <t xml:space="preserve">20.5338764190674</t>
   </si>
   <si>
     <t xml:space="preserve">18.3254280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9683151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.893138885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2165069580078</t>
+    <t xml:space="preserve">17.9683170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8931369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2165050506592</t>
   </si>
   <si>
     <t xml:space="preserve">17.1977100372314</t>
@@ -1925,7 +1928,7 @@
     <t xml:space="preserve">16.7713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9418773651123</t>
+    <t xml:space="preserve">16.9418754577637</t>
   </si>
   <si>
     <t xml:space="preserve">16.9039745330811</t>
@@ -1934,16 +1937,16 @@
     <t xml:space="preserve">16.3923091888428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.259651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5293464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652118682861</t>
+    <t xml:space="preserve">16.2596530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5293445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652137756348</t>
   </si>
   <si>
     <t xml:space="preserve">17.813606262207</t>
@@ -1967,13 +1970,13 @@
     <t xml:space="preserve">18.5716342926025</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7800922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200267791748</t>
+    <t xml:space="preserve">18.7800903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462604522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200286865234</t>
   </si>
   <si>
     <t xml:space="preserve">18.5905838012695</t>
@@ -1982,13 +1985,13 @@
     <t xml:space="preserve">18.7611389160156</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8508014678955</t>
+    <t xml:space="preserve">19.8508033752441</t>
   </si>
   <si>
     <t xml:space="preserve">20.1824378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7509574890137</t>
+    <t xml:space="preserve">20.750955581665</t>
   </si>
   <si>
     <t xml:space="preserve">20.8457107543945</t>
@@ -2000,43 +2003,43 @@
     <t xml:space="preserve">20.893087387085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2771911621094</t>
+    <t xml:space="preserve">21.0352172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2771892547607</t>
   </si>
   <si>
     <t xml:space="preserve">22.0775032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.693395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2670097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4565143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986423492432</t>
+    <t xml:space="preserve">22.6933975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2670078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4565162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986442565918</t>
   </si>
   <si>
     <t xml:space="preserve">22.0301246643066</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4616069793701</t>
+    <t xml:space="preserve">21.4616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.6511116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4142284393311</t>
+    <t xml:space="preserve">21.4142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">20.9878387451172</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7983341217041</t>
+    <t xml:space="preserve">20.7983322143555</t>
   </si>
   <si>
     <t xml:space="preserve">20.419319152832</t>
@@ -2048,10 +2051,10 @@
     <t xml:space="preserve">20.2298145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9455528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086696624756</t>
+    <t xml:space="preserve">19.9455547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086715698242</t>
   </si>
   <si>
     <t xml:space="preserve">19.2349052429199</t>
@@ -2060,7 +2063,7 @@
     <t xml:space="preserve">19.5665416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0403079986572</t>
+    <t xml:space="preserve">20.0403060913086</t>
   </si>
   <si>
     <t xml:space="preserve">19.756046295166</t>
@@ -2078,19 +2081,19 @@
     <t xml:space="preserve">18.5526809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3631763458252</t>
+    <t xml:space="preserve">18.3631744384766</t>
   </si>
   <si>
     <t xml:space="preserve">17.9273109436035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2305221557617</t>
+    <t xml:space="preserve">18.2305202484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.7188549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3821239471436</t>
+    <t xml:space="preserve">18.3821258544922</t>
   </si>
   <si>
     <t xml:space="preserve">17.7757053375244</t>
@@ -2099,13 +2102,13 @@
     <t xml:space="preserve">17.7946548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9987297058105</t>
+    <t xml:space="preserve">16.9987316131592</t>
   </si>
   <si>
     <t xml:space="preserve">18.1357669830322</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0927772521973</t>
+    <t xml:space="preserve">19.0927753448486</t>
   </si>
   <si>
     <t xml:space="preserve">20.087682723999</t>
@@ -2114,10 +2117,10 @@
     <t xml:space="preserve">18.7990398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1547183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2873725891113</t>
+    <t xml:space="preserve">18.1547164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.28737449646</t>
   </si>
   <si>
     <t xml:space="preserve">18.5147800445557</t>
@@ -2132,7 +2135,7 @@
     <t xml:space="preserve">18.476879119873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6562023162842</t>
+    <t xml:space="preserve">20.6562042236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.6088275909424</t>
@@ -2147,7 +2150,7 @@
     <t xml:space="preserve">23.3092937469482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.162073135376</t>
+    <t xml:space="preserve">24.1620750427246</t>
   </si>
   <si>
     <t xml:space="preserve">24.7779693603516</t>
@@ -2159,10 +2162,7 @@
     <t xml:space="preserve">23.4040489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6883087158203</t>
+    <t xml:space="preserve">23.6883068084717</t>
   </si>
   <si>
     <t xml:space="preserve">22.1248798370361</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">22.7881526947021</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0250358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1722564697266</t>
+    <t xml:space="preserve">23.0250339508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1722545623779</t>
   </si>
   <si>
     <t xml:space="preserve">22.8355274200439</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">23.4514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3515796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1671657562256</t>
+    <t xml:space="preserve">24.3515777587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.167163848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">21.7458667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6037368774414</t>
+    <t xml:space="preserve">21.6037349700928</t>
   </si>
   <si>
     <t xml:space="preserve">21.7932434082031</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">24.2568244934082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0673198699951</t>
+    <t xml:space="preserve">24.0673217773438</t>
   </si>
   <si>
     <t xml:space="preserve">25.2991123199463</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">24.4937076568604</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0148525238037</t>
+    <t xml:space="preserve">25.0148506164551</t>
   </si>
   <si>
     <t xml:space="preserve">25.7255001068115</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">25.772876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3464870452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5935535430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5461769104004</t>
+    <t xml:space="preserve">25.3464889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5935516357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5461750030518</t>
   </si>
   <si>
     <t xml:space="preserve">23.1197872161865</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">23.2145404815674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6409320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0199432373047</t>
+    <t xml:space="preserve">23.6409301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0199451446533</t>
   </si>
   <si>
     <t xml:space="preserve">23.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7830581665039</t>
+    <t xml:space="preserve">23.7830600738525</t>
   </si>
   <si>
     <t xml:space="preserve">21.3194751739502</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">22.6460208892822</t>
   </si>
   <si>
-    <t xml:space="preserve">22.361759185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622310638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5833721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.483528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3887748718262</t>
+    <t xml:space="preserve">22.3617610931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5833740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4835262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">26.6256561279297</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">26.5309047698975</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6730308532715</t>
+    <t xml:space="preserve">26.6730327606201</t>
   </si>
   <si>
     <t xml:space="preserve">26.3201923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7480125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6526489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843376159668</t>
+    <t xml:space="preserve">25.7480144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6526508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8433742523193</t>
   </si>
   <si>
     <t xml:space="preserve">25.6049690246582</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">25.891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0817832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5096035003662</t>
+    <t xml:space="preserve">26.0817813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5096054077148</t>
   </si>
   <si>
     <t xml:space="preserve">26.1294651031494</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">25.9387378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7956943511963</t>
+    <t xml:space="preserve">25.7956962585449</t>
   </si>
   <si>
     <t xml:space="preserve">25.12815284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.223518371582</t>
+    <t xml:space="preserve">25.2235164642334</t>
   </si>
   <si>
     <t xml:space="preserve">25.2711982727051</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">24.9851093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1758346557617</t>
+    <t xml:space="preserve">25.1758327484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.5559749603271</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">24.6990203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9361133575439</t>
+    <t xml:space="preserve">23.9361152648926</t>
   </si>
   <si>
     <t xml:space="preserve">24.937427520752</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">24.8420639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5082931518555</t>
+    <t xml:space="preserve">24.5082912445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.8884334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.222204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6977081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8407535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3175678253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.079158782959</t>
+    <t xml:space="preserve">24.2222061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6977062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8407516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.317569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0791606903076</t>
   </si>
   <si>
     <t xml:space="preserve">24.6513366699219</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">22.9824848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871212005615</t>
+    <t xml:space="preserve">22.8871231079102</t>
   </si>
   <si>
     <t xml:space="preserve">22.0288562774658</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">21.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1705875396729</t>
+    <t xml:space="preserve">21.1705894470215</t>
   </si>
   <si>
     <t xml:space="preserve">21.0752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9321804046631</t>
+    <t xml:space="preserve">20.9321784973145</t>
   </si>
   <si>
     <t xml:space="preserve">20.5984115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136310577393</t>
+    <t xml:space="preserve">21.3136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.6474018096924</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">20.8368167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.88450050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0739116668701</t>
+    <t xml:space="preserve">20.8844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0739135742188</t>
   </si>
   <si>
     <t xml:space="preserve">21.1229057312012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">20.6460933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.939094543457</t>
+    <t xml:space="preserve">18.9390926361084</t>
   </si>
   <si>
     <t xml:space="preserve">19.4063720703125</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">18.6339321136475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5385684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5194969177246</t>
+    <t xml:space="preserve">18.5385704040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.519495010376</t>
   </si>
   <si>
     <t xml:space="preserve">18.0426826477051</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.6993732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8710269927979</t>
+    <t xml:space="preserve">17.8710289001465</t>
   </si>
   <si>
     <t xml:space="preserve">18.7674388885498</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">20.2169570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8355045318604</t>
+    <t xml:space="preserve">19.835506439209</t>
   </si>
   <si>
     <t xml:space="preserve">20.5030479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.789134979248</t>
+    <t xml:space="preserve">20.7891368865967</t>
   </si>
   <si>
     <t xml:space="preserve">21.7904472351074</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">19.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7894744873047</t>
+    <t xml:space="preserve">19.7894763946533</t>
   </si>
   <si>
     <t xml:space="preserve">20.5751628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9188995361328</t>
+    <t xml:space="preserve">20.9188976287842</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">22.6375885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">22.883113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7849044799805</t>
+    <t xml:space="preserve">22.8831157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7849063873291</t>
   </si>
   <si>
     <t xml:space="preserve">21.9010066986084</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">21.6554794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2268524169922</t>
+    <t xml:space="preserve">23.2268543243408</t>
   </si>
   <si>
     <t xml:space="preserve">24.0125408172607</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">22.6866931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340110778809</t>
+    <t xml:space="preserve">22.8340091705322</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5393772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1956405639648</t>
+    <t xml:space="preserve">22.539379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1956386566162</t>
   </si>
   <si>
     <t xml:space="preserve">22.4902725219727</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">22.4411659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7045860290527</t>
+    <t xml:space="preserve">21.7045879364014</t>
   </si>
   <si>
     <t xml:space="preserve">22.293851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8519039154053</t>
+    <t xml:space="preserve">21.8519020080566</t>
   </si>
   <si>
     <t xml:space="preserve">22.2447452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501132965088</t>
+    <t xml:space="preserve">21.9501152038574</t>
   </si>
   <si>
     <t xml:space="preserve">22.3429565429688</t>
@@ -2684,22 +2684,22 @@
     <t xml:space="preserve">21.6063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.017110824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4590587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1153202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4099540710449</t>
+    <t xml:space="preserve">21.2135334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4590606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1153221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4099521636963</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403697967529</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">19.6028747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3278865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9350414276123</t>
+    <t xml:space="preserve">19.3278846740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9350433349609</t>
   </si>
   <si>
     <t xml:space="preserve">18.954683303833</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">19.5046634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1823196411133</t>
+    <t xml:space="preserve">20.1823177337646</t>
   </si>
   <si>
     <t xml:space="preserve">20.1332130432129</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">19.985897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6912631988525</t>
+    <t xml:space="preserve">19.6912651062012</t>
   </si>
   <si>
     <t xml:space="preserve">19.5832328796387</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">19.3671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7386207580566</t>
+    <t xml:space="preserve">18.738618850708</t>
   </si>
   <si>
     <t xml:space="preserve">18.4047031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1689987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2279243469238</t>
+    <t xml:space="preserve">18.1689968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2279224395752</t>
   </si>
   <si>
     <t xml:space="preserve">18.0904293060303</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">18.1493549346924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7172298431396</t>
+    <t xml:space="preserve">17.717227935791</t>
   </si>
   <si>
     <t xml:space="preserve">18.6796951293945</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">18.6404094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5029144287109</t>
+    <t xml:space="preserve">18.5029125213623</t>
   </si>
   <si>
     <t xml:space="preserve">18.8761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4225940704346</t>
+    <t xml:space="preserve">17.4225959777832</t>
   </si>
   <si>
     <t xml:space="preserve">18.2868518829346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2475662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547607421875</t>
+    <t xml:space="preserve">18.2475643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547626495361</t>
   </si>
   <si>
     <t xml:space="preserve">18.4832706451416</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">17.9529342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1297130584717</t>
+    <t xml:space="preserve">18.129711151123</t>
   </si>
   <si>
     <t xml:space="preserve">17.5208072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2654571533203</t>
+    <t xml:space="preserve">17.2654590606689</t>
   </si>
   <si>
     <t xml:space="preserve">17.3243827819824</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">17.4618797302246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1083221435547</t>
+    <t xml:space="preserve">17.1083202362061</t>
   </si>
   <si>
     <t xml:space="preserve">17.2458152770996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7744026184082</t>
+    <t xml:space="preserve">16.7744045257568</t>
   </si>
   <si>
     <t xml:space="preserve">16.9904670715332</t>
@@ -17331,7 +17331,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17357,7 +17357,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17409,7 +17409,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17435,7 +17435,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17461,7 +17461,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17487,7 +17487,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17513,7 +17513,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17539,7 +17539,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17565,7 +17565,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17591,7 +17591,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17617,7 +17617,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17643,7 +17643,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17669,7 +17669,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17695,7 +17695,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17721,7 +17721,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17747,7 +17747,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17773,7 +17773,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17799,7 +17799,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17825,7 +17825,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17851,7 +17851,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17877,7 +17877,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17903,7 +17903,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17955,7 +17955,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17981,7 +17981,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18007,7 +18007,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18033,7 +18033,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -18059,7 +18059,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18085,7 +18085,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18111,7 +18111,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18137,7 +18137,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18163,7 +18163,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18189,7 +18189,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18215,7 +18215,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18241,7 +18241,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18267,7 +18267,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18293,7 +18293,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18319,7 +18319,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18345,7 +18345,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18371,7 +18371,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18397,7 +18397,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18423,7 +18423,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18449,7 +18449,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18475,7 +18475,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18501,7 +18501,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18527,7 +18527,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18553,7 +18553,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18579,7 +18579,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18605,7 +18605,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18631,7 +18631,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18657,7 +18657,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18683,7 +18683,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18709,7 +18709,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18735,7 +18735,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18761,7 +18761,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18787,7 +18787,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18813,7 +18813,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18839,7 +18839,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18865,7 +18865,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18891,7 +18891,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18917,7 +18917,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18943,7 +18943,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18969,7 +18969,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18995,7 +18995,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19021,7 +19021,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -19047,7 +19047,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -19073,7 +19073,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19099,7 +19099,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19125,7 +19125,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19151,7 +19151,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19177,7 +19177,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19203,7 +19203,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19229,7 +19229,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19255,7 +19255,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19281,7 +19281,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19307,7 +19307,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19333,7 +19333,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19359,7 +19359,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19385,7 +19385,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19411,7 +19411,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19437,7 +19437,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19463,7 +19463,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19489,7 +19489,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19515,7 +19515,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19541,7 +19541,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19567,7 +19567,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19593,7 +19593,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19619,7 +19619,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19645,7 +19645,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19671,7 +19671,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19697,7 +19697,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19723,7 +19723,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19749,7 +19749,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19775,7 +19775,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19801,7 +19801,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19827,7 +19827,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19853,7 +19853,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19879,7 +19879,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19905,7 +19905,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19931,7 +19931,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19957,7 +19957,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19983,7 +19983,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20009,7 +20009,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -20035,7 +20035,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20061,7 +20061,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20087,7 +20087,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20113,7 +20113,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20139,7 +20139,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20165,7 +20165,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20191,7 +20191,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20217,7 +20217,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20243,7 +20243,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20269,7 +20269,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20295,7 +20295,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20321,7 +20321,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20347,7 +20347,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20373,7 +20373,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20399,7 +20399,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20425,7 +20425,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20451,7 +20451,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20477,7 +20477,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20503,7 +20503,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20529,7 +20529,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20555,7 +20555,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20581,7 +20581,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20607,7 +20607,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20633,7 +20633,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20659,7 +20659,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20685,7 +20685,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20711,7 +20711,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20737,7 +20737,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20763,7 +20763,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20789,7 +20789,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20815,7 +20815,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20841,7 +20841,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20867,7 +20867,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20893,7 +20893,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20919,7 +20919,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20945,7 +20945,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20971,7 +20971,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20997,7 +20997,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -21023,7 +21023,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21049,7 +21049,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21075,7 +21075,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21101,7 +21101,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21127,7 +21127,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21153,7 +21153,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21179,7 +21179,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21205,7 +21205,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21231,7 +21231,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21257,7 +21257,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21283,7 +21283,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21309,7 +21309,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21335,7 +21335,7 @@
         <v>17.6916809082031</v>
       </c>
       <c r="G673" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21361,7 +21361,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21387,7 +21387,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21413,7 +21413,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21439,7 +21439,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21465,7 +21465,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21491,7 +21491,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21517,7 +21517,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21543,7 +21543,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21569,7 +21569,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21595,7 +21595,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21621,7 +21621,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21647,7 +21647,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21673,7 +21673,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21699,7 +21699,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21725,7 +21725,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21751,7 +21751,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21777,7 +21777,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21803,7 +21803,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21829,7 +21829,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21855,7 +21855,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21881,7 +21881,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21907,7 +21907,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21959,7 +21959,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21985,7 +21985,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22011,7 +22011,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22037,7 +22037,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22063,7 +22063,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22089,7 +22089,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22115,7 +22115,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22141,7 +22141,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22167,7 +22167,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22193,7 +22193,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22219,7 +22219,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22245,7 +22245,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22271,7 +22271,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22297,7 +22297,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22323,7 +22323,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22349,7 +22349,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22375,7 +22375,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22401,7 +22401,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22427,7 +22427,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22453,7 +22453,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22479,7 +22479,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22505,7 +22505,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22531,7 +22531,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22557,7 +22557,7 @@
         <v>18.2742824554443</v>
       </c>
       <c r="G720" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22583,7 +22583,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22609,7 +22609,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22635,7 +22635,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22661,7 +22661,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22687,7 +22687,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22713,7 +22713,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22739,7 +22739,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22765,7 +22765,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22791,7 +22791,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22817,7 +22817,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22843,7 +22843,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22869,7 +22869,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22895,7 +22895,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22921,7 +22921,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22947,7 +22947,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22973,7 +22973,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22999,7 +22999,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23025,7 +23025,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23051,7 +23051,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23077,7 +23077,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23103,7 +23103,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G741" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23129,7 +23129,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23155,7 +23155,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23181,7 +23181,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23207,7 +23207,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23233,7 +23233,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23259,7 +23259,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23285,7 +23285,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23311,7 +23311,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23337,7 +23337,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23363,7 +23363,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23389,7 +23389,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23415,7 +23415,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23441,7 +23441,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23467,7 +23467,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23493,7 +23493,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23519,7 +23519,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23545,7 +23545,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23571,7 +23571,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23597,7 +23597,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23623,7 +23623,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23649,7 +23649,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23675,7 +23675,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G763" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23701,7 +23701,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23727,7 +23727,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23753,7 +23753,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23779,7 +23779,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23805,7 +23805,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G768" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23831,7 +23831,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23857,7 +23857,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23883,7 +23883,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23909,7 +23909,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23935,7 +23935,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23961,7 +23961,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23987,7 +23987,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24013,7 +24013,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24039,7 +24039,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24065,7 +24065,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24091,7 +24091,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24117,7 +24117,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24143,7 +24143,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24169,7 +24169,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24195,7 +24195,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24221,7 +24221,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24247,7 +24247,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24273,7 +24273,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24299,7 +24299,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24325,7 +24325,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24351,7 +24351,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24377,7 +24377,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24403,7 +24403,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24429,7 +24429,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24455,7 +24455,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24481,7 +24481,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24507,7 +24507,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24533,7 +24533,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24559,7 +24559,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24585,7 +24585,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24611,7 +24611,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G799" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24637,7 +24637,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24663,7 +24663,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24689,7 +24689,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24715,7 +24715,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24741,7 +24741,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24767,7 +24767,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24793,7 +24793,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24819,7 +24819,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24845,7 +24845,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24871,7 +24871,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24897,7 +24897,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24923,7 +24923,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24949,7 +24949,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24975,7 +24975,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25001,7 +25001,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25027,7 +25027,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25053,7 +25053,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25079,7 +25079,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25105,7 +25105,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25131,7 +25131,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25157,7 +25157,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25183,7 +25183,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25209,7 +25209,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25235,7 +25235,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25261,7 +25261,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25287,7 +25287,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25313,7 +25313,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25339,7 +25339,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25365,7 +25365,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25391,7 +25391,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25417,7 +25417,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25443,7 +25443,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25469,7 +25469,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25495,7 +25495,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25521,7 +25521,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25547,7 +25547,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25573,7 +25573,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25599,7 +25599,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25625,7 +25625,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25651,7 +25651,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25677,7 +25677,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25703,7 +25703,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25729,7 +25729,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25755,7 +25755,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G843" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25781,7 +25781,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25807,7 +25807,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25833,7 +25833,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25859,7 +25859,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G847" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25885,7 +25885,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25911,7 +25911,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25937,7 +25937,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25963,7 +25963,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25989,7 +25989,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26015,7 +26015,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26041,7 +26041,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26067,7 +26067,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26093,7 +26093,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26119,7 +26119,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26145,7 +26145,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26171,7 +26171,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26197,7 +26197,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26223,7 +26223,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26249,7 +26249,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26275,7 +26275,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26301,7 +26301,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26327,7 +26327,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26353,7 +26353,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26379,7 +26379,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26405,7 +26405,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26431,7 +26431,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26457,7 +26457,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26483,7 +26483,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G871" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26509,7 +26509,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26535,7 +26535,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G873" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26561,7 +26561,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26587,7 +26587,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26613,7 +26613,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26639,7 +26639,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26665,7 +26665,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26691,7 +26691,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26717,7 +26717,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26743,7 +26743,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26769,7 +26769,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26795,7 +26795,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26821,7 +26821,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26847,7 +26847,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26873,7 +26873,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26899,7 +26899,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26925,7 +26925,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26951,7 +26951,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26977,7 +26977,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27003,7 +27003,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27029,7 +27029,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27055,7 +27055,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27081,7 +27081,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G894" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27107,7 +27107,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27133,7 +27133,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27159,7 +27159,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27185,7 +27185,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27211,7 +27211,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27237,7 +27237,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27263,7 +27263,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27289,7 +27289,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27315,7 +27315,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27341,7 +27341,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27367,7 +27367,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27393,7 +27393,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27419,7 +27419,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27445,7 +27445,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27471,7 +27471,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27497,7 +27497,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27523,7 +27523,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27549,7 +27549,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G912" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27575,7 +27575,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27601,7 +27601,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27627,7 +27627,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27653,7 +27653,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27679,7 +27679,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27705,7 +27705,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27731,7 +27731,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27757,7 +27757,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27783,7 +27783,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27809,7 +27809,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27835,7 +27835,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27861,7 +27861,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27887,7 +27887,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27913,7 +27913,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27939,7 +27939,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27965,7 +27965,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27991,7 +27991,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28017,7 +28017,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28043,7 +28043,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28069,7 +28069,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G932" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28095,7 +28095,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28121,7 +28121,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28147,7 +28147,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28173,7 +28173,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28199,7 +28199,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28225,7 +28225,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28251,7 +28251,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28277,7 +28277,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28303,7 +28303,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28329,7 +28329,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28355,7 +28355,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28381,7 +28381,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28407,7 +28407,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28433,7 +28433,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28459,7 +28459,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28485,7 +28485,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28511,7 +28511,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28537,7 +28537,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28563,7 +28563,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28589,7 +28589,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28615,7 +28615,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28641,7 +28641,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28667,7 +28667,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28693,7 +28693,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28719,7 +28719,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28745,7 +28745,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28771,7 +28771,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28797,7 +28797,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28823,7 +28823,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28849,7 +28849,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28875,7 +28875,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28901,7 +28901,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28927,7 +28927,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28953,7 +28953,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28979,7 +28979,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29005,7 +29005,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29031,7 +29031,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29057,7 +29057,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29083,7 +29083,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29109,7 +29109,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29135,7 +29135,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29161,7 +29161,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29187,7 +29187,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29213,7 +29213,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29239,7 +29239,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29265,7 +29265,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29291,7 +29291,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29317,7 +29317,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29343,7 +29343,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G981" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29369,7 +29369,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29395,7 +29395,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29421,7 +29421,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29447,7 +29447,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29473,7 +29473,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29499,7 +29499,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G987" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29525,7 +29525,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29551,7 +29551,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29577,7 +29577,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29603,7 +29603,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29629,7 +29629,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29655,7 +29655,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G993" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29681,7 +29681,7 @@
         <v>19.3618068695068</v>
       </c>
       <c r="G994" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29707,7 +29707,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29733,7 +29733,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29759,7 +29759,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29785,7 +29785,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29811,7 +29811,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29837,7 +29837,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29863,7 +29863,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1001" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29889,7 +29889,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29915,7 +29915,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29941,7 +29941,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29967,7 +29967,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29993,7 +29993,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30019,7 +30019,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30045,7 +30045,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30071,7 +30071,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30097,7 +30097,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30123,7 +30123,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30149,7 +30149,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30175,7 +30175,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30201,7 +30201,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30227,7 +30227,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30253,7 +30253,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30279,7 +30279,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G1017" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30305,7 +30305,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30331,7 +30331,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30357,7 +30357,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30383,7 +30383,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30409,7 +30409,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30435,7 +30435,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30461,7 +30461,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30487,7 +30487,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30513,7 +30513,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30539,7 +30539,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30565,7 +30565,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30591,7 +30591,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30617,7 +30617,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1030" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30643,7 +30643,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1031" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30669,7 +30669,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30695,7 +30695,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30721,7 +30721,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30747,7 +30747,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30773,7 +30773,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30799,7 +30799,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30825,7 +30825,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30851,7 +30851,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G1039" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30877,7 +30877,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30903,7 +30903,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30929,7 +30929,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30955,7 +30955,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30981,7 +30981,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31007,7 +31007,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31033,7 +31033,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31059,7 +31059,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31085,7 +31085,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31111,7 +31111,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1049" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31137,7 +31137,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31163,7 +31163,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31189,7 +31189,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31215,7 +31215,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31241,7 +31241,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31267,7 +31267,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31293,7 +31293,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31319,7 +31319,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31345,7 +31345,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31371,7 +31371,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31397,7 +31397,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1060" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31423,7 +31423,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31449,7 +31449,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31475,7 +31475,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1063" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31501,7 +31501,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31527,7 +31527,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31553,7 +31553,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31579,7 +31579,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31605,7 +31605,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31631,7 +31631,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1069" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31657,7 +31657,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31683,7 +31683,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31709,7 +31709,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31735,7 +31735,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31761,7 +31761,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31787,7 +31787,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31813,7 +31813,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31839,7 +31839,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31865,7 +31865,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31891,7 +31891,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31917,7 +31917,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31943,7 +31943,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31969,7 +31969,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31995,7 +31995,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32021,7 +32021,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32047,7 +32047,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32073,7 +32073,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32099,7 +32099,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32125,7 +32125,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32151,7 +32151,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32177,7 +32177,7 @@
         <v>18.6821041107178</v>
       </c>
       <c r="G1090" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32203,7 +32203,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32229,7 +32229,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32255,7 +32255,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32281,7 +32281,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G1094" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32307,7 +32307,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32333,7 +32333,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32359,7 +32359,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32385,7 +32385,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32411,7 +32411,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32437,7 +32437,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32463,7 +32463,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32489,7 +32489,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32515,7 +32515,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32541,7 +32541,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32567,7 +32567,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32593,7 +32593,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32619,7 +32619,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32645,7 +32645,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32671,7 +32671,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32697,7 +32697,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32723,7 +32723,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G1111" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32749,7 +32749,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32775,7 +32775,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32801,7 +32801,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32827,7 +32827,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32853,7 +32853,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32879,7 +32879,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32905,7 +32905,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32931,7 +32931,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32957,7 +32957,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32983,7 +32983,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33009,7 +33009,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33035,7 +33035,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1123" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33061,7 +33061,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33087,7 +33087,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1125" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33113,7 +33113,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33139,7 +33139,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33165,7 +33165,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33191,7 +33191,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33217,7 +33217,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33243,7 +33243,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33269,7 +33269,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33295,7 +33295,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33321,7 +33321,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33373,7 +33373,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33399,7 +33399,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33425,7 +33425,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33477,7 +33477,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33737,7 +33737,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33919,7 +33919,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33945,7 +33945,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33997,7 +33997,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34023,7 +34023,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1161" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34049,7 +34049,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1162" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34179,7 +34179,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34413,7 +34413,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1176" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34439,7 +34439,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34491,7 +34491,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34517,7 +34517,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34621,7 +34621,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34673,7 +34673,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34751,7 +34751,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34959,7 +34959,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35401,7 +35401,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35453,7 +35453,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35973,7 +35973,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35999,7 +35999,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36051,7 +36051,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36103,7 +36103,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36259,7 +36259,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36311,7 +36311,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36571,7 +36571,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>715</v>
+        <v>549</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36597,7 +36597,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36623,7 +36623,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -52517,10 +52517,10 @@
     </row>
     <row r="1873">
       <c r="A1873" s="1" t="n">
-        <v>45951.6494444444</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1873" t="n">
-        <v>88333</v>
+        <v>97667</v>
       </c>
       <c r="C1873" t="n">
         <v>23.3999996185303</v>
@@ -52538,6 +52538,32 @@
         <v>1128</v>
       </c>
       <c r="H1873" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="1" t="n">
+        <v>45952.6494791667</v>
+      </c>
+      <c r="B1874" t="n">
+        <v>149362</v>
+      </c>
+      <c r="C1874" t="n">
+        <v>23.6499996185303</v>
+      </c>
+      <c r="D1874" t="n">
+        <v>23.0499992370605</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>23.0499992370605</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>23.1499996185303</v>
+      </c>
+      <c r="G1874" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H1874" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="1166">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125829696655</t>
+    <t xml:space="preserve">7.58125782012939</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288686752319</t>
+    <t xml:space="preserve">7.90288734436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.81099319458008</t>
@@ -53,22 +53,22 @@
     <t xml:space="preserve">7.71910047531128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68969297409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348031997681</t>
+    <t xml:space="preserve">7.68969202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87347984313965</t>
   </si>
   <si>
     <t xml:space="preserve">7.96721315383911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67407035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97640180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44433689117432</t>
+    <t xml:space="preserve">7.67406988143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97640085220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44433641433716</t>
   </si>
   <si>
     <t xml:space="preserve">7.30281972885132</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">7.57206916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44341707229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52612161636353</t>
+    <t xml:space="preserve">7.4434175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52612209320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.54450035095215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64742231369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8018045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8569393157959</t>
+    <t xml:space="preserve">7.64742183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80180501937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85693883895874</t>
   </si>
   <si>
     <t xml:space="preserve">7.92218542098999</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">8.00397205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86612844467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01959323883057</t>
+    <t xml:space="preserve">7.86612892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
     <t xml:space="preserve">7.81466865539551</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">7.69336843490601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79261445999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74666786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910293579102</t>
+    <t xml:space="preserve">7.7926139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74666738510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910388946533</t>
   </si>
   <si>
     <t xml:space="preserve">7.56379890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67315196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78526401519775</t>
+    <t xml:space="preserve">7.67315101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7852635383606</t>
   </si>
   <si>
     <t xml:space="preserve">7.74850559234619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99478197097778</t>
+    <t xml:space="preserve">7.99478101730347</t>
   </si>
   <si>
     <t xml:space="preserve">8.06002616882324</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">8.46344089508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48641395568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75382423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60128116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28884220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25208377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36235809326172</t>
+    <t xml:space="preserve">8.48641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382518768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60128211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28884124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25208568572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3623571395874</t>
   </si>
   <si>
     <t xml:space="preserve">8.45425128936768</t>
@@ -194,16 +194,16 @@
     <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61598491668701</t>
+    <t xml:space="preserve">8.6159839630127</t>
   </si>
   <si>
     <t xml:space="preserve">8.66560840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79426097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.005615234375</t>
+    <t xml:space="preserve">8.79426002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00561618804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.86869430541992</t>
@@ -212,52 +212,52 @@
     <t xml:space="preserve">9.11588954925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14345550537109</t>
+    <t xml:space="preserve">9.14345645904541</t>
   </si>
   <si>
     <t xml:space="preserve">9.33643341064453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09751033782959</t>
+    <t xml:space="preserve">9.09750938415527</t>
   </si>
   <si>
     <t xml:space="preserve">9.11680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99091243743896</t>
+    <t xml:space="preserve">8.99091053009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.18572902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06166934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02399253845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9936695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04237365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90177536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67112159729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98191595077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30630207061768</t>
+    <t xml:space="preserve">9.06167030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02399349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76577091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99366855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04237270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90177440643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50755023956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9819164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30630397796631</t>
   </si>
   <si>
     <t xml:space="preserve">8.40830421447754</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">8.54614639282227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5920934677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63803958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80804443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970027923584</t>
+    <t xml:space="preserve">8.59209442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63803863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80804347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970123291016</t>
   </si>
   <si>
     <t xml:space="preserve">7.75126361846924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92126512527466</t>
+    <t xml:space="preserve">7.92126607894897</t>
   </si>
   <si>
     <t xml:space="preserve">8.34214115142822</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.77496147155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77771949768066</t>
+    <t xml:space="preserve">8.77772045135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.75474452972412</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">8.57738971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39268207550049</t>
+    <t xml:space="preserve">8.3926830291748</t>
   </si>
   <si>
     <t xml:space="preserve">8.34122180938721</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">8.5608491897583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71982479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0545129776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04164791107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0866756439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18867683410645</t>
+    <t xml:space="preserve">8.71982574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05451393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04164695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08667659759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18867778778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.54890251159668</t>
@@ -341,37 +341,37 @@
     <t xml:space="preserve">8.50938892364502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03869724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9743709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15264701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84939670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07912921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8558292388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446529388428</t>
+    <t xml:space="preserve">8.9210729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97437191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1526460647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84939575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07913017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85582828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446434020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.23370456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27046394348145</t>
+    <t xml:space="preserve">8.27046298980713</t>
   </si>
   <si>
     <t xml:space="preserve">8.33754634857178</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">8.20062351226807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40370941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27413845062256</t>
+    <t xml:space="preserve">8.40371036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27414035797119</t>
   </si>
   <si>
     <t xml:space="preserve">8.2980318069458</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">8.43587303161621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22451591491699</t>
+    <t xml:space="preserve">8.22451686859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.35408687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22084045410156</t>
+    <t xml:space="preserve">8.22083950042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.15283966064453</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">8.42668437957764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48365783691406</t>
+    <t xml:space="preserve">8.48365688323975</t>
   </si>
   <si>
     <t xml:space="preserve">8.709716796875</t>
@@ -422,46 +422,46 @@
     <t xml:space="preserve">8.77128601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72074317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10026741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06534671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89809894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469390869141</t>
+    <t xml:space="preserve">8.72074222564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.100266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06534767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89809989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469295501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.97712802886963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05156230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20594501495361</t>
+    <t xml:space="preserve">9.05156135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23535060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20594596862793</t>
   </si>
   <si>
     <t xml:space="preserve">9.36216354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39524745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027812957764</t>
+    <t xml:space="preserve">9.3952465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027908325195</t>
   </si>
   <si>
     <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69482135772705</t>
+    <t xml:space="preserve">9.69482326507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.59373760223389</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">9.64336109161377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3198938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61763000488281</t>
+    <t xml:space="preserve">9.31989288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6176290512085</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265575408936</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">9.46324729919434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33092021942139</t>
+    <t xml:space="preserve">9.33091926574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.12875366210938</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">8.76025867462158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0065336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18940353393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96885776519775</t>
+    <t xml:space="preserve">9.00653266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18940544128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96885681152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.10669994354248</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">9.44670677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39157104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74076747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46508598327637</t>
+    <t xml:space="preserve">9.39157009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46508502960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.53860282897949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75914573669434</t>
+    <t xml:space="preserve">9.75914669036865</t>
   </si>
   <si>
     <t xml:space="preserve">9.68563175201416</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">9.7959041595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92455673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81428241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9429349899292</t>
+    <t xml:space="preserve">9.92455768585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81428337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94293689727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.0715856552124</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">10.108344078064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66725444793701</t>
+    <t xml:space="preserve">9.66725254058838</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86941814422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.163480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105115890503</t>
+    <t xml:space="preserve">9.83266067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86941909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1634798049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.310510635376</t>
   </si>
   <si>
     <t xml:space="preserve">10.0348291397095</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">10.1267223358154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5126791000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6045713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659707069397</t>
+    <t xml:space="preserve">10.5126781463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6045722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597061157227</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332239151001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4207849502563</t>
+    <t xml:space="preserve">10.420783996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.4759206771851</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">9.85104084014893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821956634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88544750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451015472412</t>
+    <t xml:space="preserve">10.1821947097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.941086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8854455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451005935669</t>
   </si>
   <si>
     <t xml:space="preserve">9.99672603607178</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">9.90399265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0523681640625</t>
+    <t xml:space="preserve">10.0523672103882</t>
   </si>
   <si>
     <t xml:space="preserve">9.7370719909668</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">10.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4047574996948</t>
+    <t xml:space="preserve">10.4047565460205</t>
   </si>
   <si>
     <t xml:space="preserve">10.423303604126</t>
@@ -686,34 +686,34 @@
     <t xml:space="preserve">10.386209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3676633834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82980728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3120241165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338220596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81125926971436</t>
+    <t xml:space="preserve">10.3676624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3120222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81126022338867</t>
   </si>
   <si>
     <t xml:space="preserve">10.070915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7927131652832</t>
+    <t xml:space="preserve">10.1080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79271125793457</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498802185059</t>
+    <t xml:space="preserve">10.8498792648315</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789428710938</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">12.0554227828979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651744842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6102991104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062833786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.536111831665</t>
+    <t xml:space="preserve">11.1651754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361108779907</t>
   </si>
   <si>
     <t xml:space="preserve">11.6288452148438</t>
@@ -740,34 +740,34 @@
     <t xml:space="preserve">11.5175647735596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9626903533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.148157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2408885955811</t>
+    <t xml:space="preserve">11.9626884460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1481561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2408895492554</t>
   </si>
   <si>
     <t xml:space="preserve">12.4449043273926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5932807922363</t>
+    <t xml:space="preserve">12.5932788848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.1852493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.573205947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5917520523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7401285171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4804725646973</t>
+    <t xml:space="preserve">11.5732040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5917510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7401256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4804716110229</t>
   </si>
   <si>
     <t xml:space="preserve">11.925594329834</t>
@@ -779,67 +779,67 @@
     <t xml:space="preserve">12.1667032241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2223434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5190935134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6860132217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2609643936157</t>
+    <t xml:space="preserve">12.2223424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5190925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6860122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2609634399414</t>
   </si>
   <si>
     <t xml:space="preserve">13.3536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5020723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.058479309082</t>
+    <t xml:space="preserve">13.5020713806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584783554077</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053251266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125898361206</t>
+    <t xml:space="preserve">13.2053241729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125907897949</t>
   </si>
   <si>
     <t xml:space="preserve">12.3892641067505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3521718978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2965297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4078121185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2037973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779846191406</t>
+    <t xml:space="preserve">12.3521699905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2965307235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.407811164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2037954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779836654663</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9101037979126</t>
+    <t xml:space="preserve">13.9101028442383</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093389511108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.168231010437</t>
+    <t xml:space="preserve">13.1682300567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.8529348373413</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">12.7045602798462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5561857223511</t>
+    <t xml:space="preserve">12.5561847686768</t>
   </si>
   <si>
     <t xml:space="preserve">12.3707189559937</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">12.7787475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.815842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900299072266</t>
+    <t xml:space="preserve">12.8158407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900279998779</t>
   </si>
   <si>
     <t xml:space="preserve">13.0940437316895</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3351516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569496154785</t>
+    <t xml:space="preserve">13.335150718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569486618042</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489191055298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4634523391724</t>
+    <t xml:space="preserve">12.3150777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.463451385498</t>
   </si>
   <si>
     <t xml:space="preserve">12.4263582229614</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">11.8514070510864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2950038909912</t>
+    <t xml:space="preserve">11.7772197723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2950029373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.0168008804321</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">11.0909881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0353498458862</t>
+    <t xml:space="preserve">11.0353479385376</t>
   </si>
   <si>
     <t xml:space="preserve">10.7571458816528</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">11.313549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280832290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2764558792114</t>
+    <t xml:space="preserve">11.1280813217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2764568328857</t>
   </si>
   <si>
     <t xml:space="preserve">11.2208156585693</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">11.1095352172852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40322780609131</t>
+    <t xml:space="preserve">9.42177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40322875976562</t>
   </si>
   <si>
     <t xml:space="preserve">8.88391780853271</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">9.55160331726074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71699810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80973243713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20695972442627</t>
+    <t xml:space="preserve">8.71699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80973148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20696067810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.24405384063721</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">8.53152942657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.438796043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64433860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200527191162</t>
+    <t xml:space="preserve">8.43879699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64433765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200517654419</t>
   </si>
   <si>
     <t xml:space="preserve">9.77416515350342</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">9.71852493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0152750015259</t>
+    <t xml:space="preserve">10.0152740478516</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015047073364</t>
@@ -986,67 +986,67 @@
     <t xml:space="preserve">11.6844873428345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8699541091919</t>
+    <t xml:space="preserve">11.8699522018433</t>
   </si>
   <si>
     <t xml:space="preserve">12.4819974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6118268966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7586727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7246341705322</t>
+    <t xml:space="preserve">12.6118259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7586736679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7246351242065</t>
   </si>
   <si>
     <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6504487991333</t>
+    <t xml:space="preserve">13.650447845459</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930835723877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0414581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2439451217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462377548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487237930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6148815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4665069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0399293899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.132664680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7988214492798</t>
+    <t xml:space="preserve">15.0414590835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2439460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.282567024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687986373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938474655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6148824691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4665079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0399303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1326656341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">13.8173685073853</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">14.0770235061646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318133354187</t>
+    <t xml:space="preserve">14.3181324005127</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076148986816</t>
   </si>
   <si>
+    <t xml:space="preserve">14.9858169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5560483932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7989616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8923892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7802762985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7615909576416</t>
+  </si>
+  <si>
     <t xml:space="preserve">14.9858179092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.79896068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.892388343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7802753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7615909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9858169555664</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.2660999298096</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4155855178833</t>
+    <t xml:space="preserve">15.4155864715576</t>
   </si>
   <si>
     <t xml:space="preserve">15.3221569061279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0045032501221</t>
+    <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
     <t xml:space="preserve">14.6121063232422</t>
@@ -1109,22 +1109,22 @@
     <t xml:space="preserve">14.911075592041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6494779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1353025436401</t>
+    <t xml:space="preserve">14.6494770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1353034973145</t>
   </si>
   <si>
     <t xml:space="preserve">14.9297609329224</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0231876373291</t>
+    <t xml:space="preserve">15.0231885910034</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.948447227478</t>
+    <t xml:space="preserve">14.9484462738037</t>
   </si>
   <si>
     <t xml:space="preserve">14.4813070297241</t>
@@ -1139,28 +1139,28 @@
     <t xml:space="preserve">16.9664859771729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6765403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7235736846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8730602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4149398803711</t>
+    <t xml:space="preserve">17.6765384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.723575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8730564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4149417877197</t>
   </si>
   <si>
     <t xml:space="preserve">17.3962535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7886505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0128784179688</t>
+    <t xml:space="preserve">17.7886524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0128765106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.8820781707764</t>
@@ -1169,22 +1169,22 @@
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118457794189</t>
+    <t xml:space="preserve">18.3118476867676</t>
   </si>
   <si>
     <t xml:space="preserve">17.6578521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5270538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9941940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6855583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1526966094971</t>
+    <t xml:space="preserve">17.5270519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9941902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6855602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1526985168457</t>
   </si>
   <si>
     <t xml:space="preserve">18.3305320739746</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">18.2184181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.031566619873</t>
+    <t xml:space="preserve">18.0315647125244</t>
   </si>
   <si>
     <t xml:space="preserve">17.3775691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9568214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4709968566895</t>
+    <t xml:space="preserve">17.9568195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4709987640381</t>
   </si>
   <si>
     <t xml:space="preserve">17.8073348999023</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">16.667516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266658782959</t>
+    <t xml:space="preserve">15.8266687393188</t>
   </si>
   <si>
     <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9574680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3782119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706108093262</t>
+    <t xml:space="preserve">15.9574670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706089019775</t>
   </si>
   <si>
     <t xml:space="preserve">16.5367183685303</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">16.2751216888428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8543739318848</t>
+    <t xml:space="preserve">16.8543720245361</t>
   </si>
   <si>
     <t xml:space="preserve">16.7048873901367</t>
@@ -1253,40 +1253,40 @@
     <t xml:space="preserve">16.3311786651611</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4993457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3685493469238</t>
+    <t xml:space="preserve">16.4993476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3685474395752</t>
   </si>
   <si>
     <t xml:space="preserve">16.3498630523682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6862049102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114597320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7609481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8170013427734</t>
+    <t xml:space="preserve">16.6862030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7609462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8170032501221</t>
   </si>
   <si>
     <t xml:space="preserve">16.7983169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4342708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671325683594</t>
+    <t xml:space="preserve">15.7892961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.434271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671316146851</t>
   </si>
   <si>
     <t xml:space="preserve">14.6868476867676</t>
@@ -1295,40 +1295,40 @@
     <t xml:space="preserve">14.5373640060425</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3215103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.518030166626</t>
+    <t xml:space="preserve">17.32151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5180339813232</t>
   </si>
   <si>
     <t xml:space="preserve">15.6211252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8827238082886</t>
+    <t xml:space="preserve">15.8827219009399</t>
   </si>
   <si>
     <t xml:space="preserve">16.2377490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4806632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4432926177979</t>
+    <t xml:space="preserve">16.4806652069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4432888031006</t>
   </si>
   <si>
     <t xml:space="preserve">16.9478015899658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0785980224609</t>
+    <t xml:space="preserve">17.0785999298096</t>
   </si>
   <si>
     <t xml:space="preserve">16.6488342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9104270935059</t>
+    <t xml:space="preserve">16.9104290008545</t>
   </si>
   <si>
     <t xml:space="preserve">16.8917446136475</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">18.5360736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9194507598877</t>
+    <t xml:space="preserve">17.9194488525391</t>
   </si>
   <si>
     <t xml:space="preserve">18.0502490997314</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">16.5554046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3124923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0225429534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0695819854736</t>
+    <t xml:space="preserve">16.3124904632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.069580078125</t>
   </si>
   <si>
     <t xml:space="preserve">15.8453512191772</t>
@@ -1373,37 +1373,37 @@
     <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6024398803711</t>
+    <t xml:space="preserve">15.6024408340454</t>
   </si>
   <si>
     <t xml:space="preserve">16.0135231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9014091491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186786651611</t>
+    <t xml:space="preserve">15.9014101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.976149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3595275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186777114868</t>
   </si>
   <si>
     <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8550186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.50901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6398115158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6771821975708</t>
+    <t xml:space="preserve">14.855019569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5090112686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6398105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6771812438965</t>
   </si>
   <si>
     <t xml:space="preserve">15.5276975631714</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584987640381</t>
+    <t xml:space="preserve">15.6584968566895</t>
   </si>
   <si>
     <t xml:space="preserve">15.8640403747559</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">16.2190628051758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0972862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1346588134766</t>
+    <t xml:space="preserve">17.0972881317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1346569061279</t>
   </si>
   <si>
     <t xml:space="preserve">17.9381370544434</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">17.5831108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7699642181396</t>
+    <t xml:space="preserve">17.7699661254883</t>
   </si>
   <si>
     <t xml:space="preserve">18.1249904632568</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">17.6391677856445</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4800186157227</t>
+    <t xml:space="preserve">18.480016708374</t>
   </si>
   <si>
     <t xml:space="preserve">18.0689334869385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1720275878906</t>
+    <t xml:space="preserve">17.1720294952393</t>
   </si>
   <si>
     <t xml:space="preserve">17.5644245147705</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6017932891846</t>
+    <t xml:space="preserve">17.6017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">17.7512798309326</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">19.7132663726807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8066921234131</t>
+    <t xml:space="preserve">19.8066902160645</t>
   </si>
   <si>
     <t xml:space="preserve">19.4329795837402</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">19.5264072418213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9935474395752</t>
+    <t xml:space="preserve">19.9935455322266</t>
   </si>
   <si>
     <t xml:space="preserve">20.5541133880615</t>
@@ -1487,25 +1487,25 @@
     <t xml:space="preserve">20.4606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1336898803711</t>
+    <t xml:space="preserve">20.273832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
     <t xml:space="preserve">19.946834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2271194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6008262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6475391387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2081069946289</t>
+    <t xml:space="preserve">20.2271175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6008281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6475429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2081089019775</t>
   </si>
   <si>
     <t xml:space="preserve">21.5818195343018</t>
@@ -1517,13 +1517,13 @@
     <t xml:space="preserve">21.3015365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8343963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0869770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7599773406982</t>
+    <t xml:space="preserve">20.8343982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0869750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7599754333496</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796943664551</t>
@@ -1535,13 +1535,13 @@
     <t xml:space="preserve">19.7350769042969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9700145721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7820644378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.453145980835</t>
+    <t xml:space="preserve">19.9700164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7820663452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4531478881836</t>
   </si>
   <si>
     <t xml:space="preserve">19.5471248626709</t>
@@ -1550,25 +1550,25 @@
     <t xml:space="preserve">19.5001354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6880912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0302543640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8422985076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1712169647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.077241897583</t>
+    <t xml:space="preserve">19.6880893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.030252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8423004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1712188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0772399902344</t>
   </si>
   <si>
     <t xml:space="preserve">18.9362754821777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410999298096</t>
+    <t xml:space="preserve">19.6410980224609</t>
   </si>
   <si>
     <t xml:space="preserve">18.9832649230957</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">19.8290557861328</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2651920318604</t>
+    <t xml:space="preserve">19.265193939209</t>
   </si>
   <si>
     <t xml:space="preserve">18.4194049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6261558532715</t>
+    <t xml:space="preserve">18.6261539459229</t>
   </si>
   <si>
     <t xml:space="preserve">18.4757919311523</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">18.7765159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5133819580078</t>
+    <t xml:space="preserve">18.5133838653564</t>
   </si>
   <si>
     <t xml:space="preserve">18.7953128814697</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">20.0639953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3929119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8158073425293</t>
+    <t xml:space="preserve">20.3929138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8158054351807</t>
   </si>
   <si>
     <t xml:space="preserve">21.2856884002686</t>
@@ -1619,19 +1619,19 @@
     <t xml:space="preserve">22.0844898223877</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4603977203369</t>
+    <t xml:space="preserve">22.4603958129883</t>
   </si>
   <si>
     <t xml:space="preserve">22.9772682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2122116088867</t>
+    <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
     <t xml:space="preserve">23.4941387176514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1652221679688</t>
+    <t xml:space="preserve">23.1652202606201</t>
   </si>
   <si>
     <t xml:space="preserve">23.0712451934814</t>
@@ -1643,58 +1643,58 @@
     <t xml:space="preserve">24.1989631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7760696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7290821075439</t>
+    <t xml:space="preserve">23.7760677337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7290802001953</t>
   </si>
   <si>
     <t xml:space="preserve">23.0242557525635</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8363018035889</t>
+    <t xml:space="preserve">22.8363037109375</t>
   </si>
   <si>
     <t xml:space="preserve">22.8832912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5411262512207</t>
+    <t xml:space="preserve">23.5411281585693</t>
   </si>
   <si>
     <t xml:space="preserve">22.9302787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.447151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8700466156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555751800537</t>
+    <t xml:space="preserve">23.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555732727051</t>
   </si>
   <si>
     <t xml:space="preserve">21.7085857391357</t>
   </si>
   <si>
-    <t xml:space="preserve">22.131477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.909782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567718505859</t>
+    <t xml:space="preserve">22.1314811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9435253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9097843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567737579346</t>
   </si>
   <si>
     <t xml:space="preserve">20.7688179016113</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">20.5808658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2387046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8495502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8098106384277</t>
+    <t xml:space="preserve">21.2387027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8495483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8098087310791</t>
   </si>
   <si>
     <t xml:space="preserve">24.6688442230225</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">24.9977626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4339046478271</t>
+    <t xml:space="preserve">24.4339027404785</t>
   </si>
   <si>
     <t xml:space="preserve">24.3869171142578</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">23.6351013183594</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1519718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230590820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2929401397705</t>
+    <t xml:space="preserve">24.1519737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2929382324219</t>
   </si>
   <si>
     <t xml:space="preserve">23.9640235900879</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">25.5616226196289</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4206619262695</t>
+    <t xml:space="preserve">25.4206600189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.6555995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3736724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5543746948242</t>
+    <t xml:space="preserve">25.3736705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2796936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543727874756</t>
   </si>
   <si>
     <t xml:space="preserve">22.2724456787109</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">24.7158355712891</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5278816223145</t>
+    <t xml:space="preserve">24.5278797149658</t>
   </si>
   <si>
     <t xml:space="preserve">24.7628231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9170341491699</t>
+    <t xml:space="preserve">23.9170322418213</t>
   </si>
   <si>
     <t xml:space="preserve">24.0110111236572</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">24.6218585968018</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1857147216797</t>
+    <t xml:space="preserve">25.1857166290283</t>
   </si>
   <si>
     <t xml:space="preserve">25.138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5206298828125</t>
+    <t xml:space="preserve">21.5206317901611</t>
   </si>
   <si>
     <t xml:space="preserve">21.1917152404785</t>
@@ -1835,25 +1835,25 @@
     <t xml:space="preserve">20.34592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5697689056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760395050049</t>
+    <t xml:space="preserve">19.2182064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5697650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760414123535</t>
   </si>
   <si>
     <t xml:space="preserve">20.6748428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3591690063477</t>
+    <t xml:space="preserve">19.3591709136963</t>
   </si>
   <si>
     <t xml:space="preserve">18.2126560211182</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3292751312256</t>
+    <t xml:space="preserve">17.3292770385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.0473480224609</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">18.3066329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1938610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6637439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230289459229</t>
+    <t xml:space="preserve">18.1938591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230308532715</t>
   </si>
   <si>
     <t xml:space="preserve">21.6615962982178</t>
@@ -1886,16 +1886,16 @@
     <t xml:space="preserve">21.4736423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.486888885498</t>
+    <t xml:space="preserve">20.4868907928467</t>
   </si>
   <si>
     <t xml:space="preserve">20.2989387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0170059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7389259338379</t>
+    <t xml:space="preserve">20.0170078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7389278411865</t>
   </si>
   <si>
     <t xml:space="preserve">18.7013339996338</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">21.8965377807617</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2049617767334</t>
+    <t xml:space="preserve">20.2049598693848</t>
   </si>
   <si>
     <t xml:space="preserve">20.5338764190674</t>
@@ -1913,28 +1913,28 @@
     <t xml:space="preserve">18.3254280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9683170318604</t>
+    <t xml:space="preserve">17.9683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">17.8931369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2165050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9418754577637</t>
+    <t xml:space="preserve">17.2165031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713203430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9418773651123</t>
   </si>
   <si>
     <t xml:space="preserve">16.9039745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923091888428</t>
+    <t xml:space="preserve">16.3923072814941</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596530914307</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">16.8281726837158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5293445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652137756348</t>
+    <t xml:space="preserve">17.5293464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652118682861</t>
   </si>
   <si>
     <t xml:space="preserve">17.813606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2684230804443</t>
+    <t xml:space="preserve">18.2684211730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.2494716644287</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">18.950647354126</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716342926025</t>
+    <t xml:space="preserve">18.6284847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5716323852539</t>
   </si>
   <si>
     <t xml:space="preserve">18.7800903320312</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">18.4200286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5905838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8508033752441</t>
+    <t xml:space="preserve">18.5905818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8508014678955</t>
   </si>
   <si>
     <t xml:space="preserve">20.1824378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.750955581665</t>
+    <t xml:space="preserve">20.7509574890137</t>
   </si>
   <si>
     <t xml:space="preserve">20.8457107543945</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">20.2771892547607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0775032043457</t>
+    <t xml:space="preserve">22.0775012969971</t>
   </si>
   <si>
     <t xml:space="preserve">22.6933975219727</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">19.7086715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2349052429199</t>
+    <t xml:space="preserve">19.2349033355713</t>
   </si>
   <si>
     <t xml:space="preserve">19.5665416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0403060913086</t>
+    <t xml:space="preserve">20.0403079986572</t>
   </si>
   <si>
     <t xml:space="preserve">19.756046295166</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">19.0453987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5526809692383</t>
+    <t xml:space="preserve">18.5526828765869</t>
   </si>
   <si>
     <t xml:space="preserve">18.3631744384766</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">17.7946548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9987316131592</t>
+    <t xml:space="preserve">16.9987297058105</t>
   </si>
   <si>
     <t xml:space="preserve">18.1357669830322</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">19.0927753448486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.087682723999</t>
+    <t xml:space="preserve">20.0876846313477</t>
   </si>
   <si>
     <t xml:space="preserve">18.7990398406982</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">18.28737449646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5147800445557</t>
+    <t xml:space="preserve">18.5147819519043</t>
   </si>
   <si>
     <t xml:space="preserve">18.0599632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2115688323975</t>
+    <t xml:space="preserve">18.2115707397461</t>
   </si>
   <si>
     <t xml:space="preserve">18.476879119873</t>
@@ -2156,22 +2156,25 @@
     <t xml:space="preserve">24.7779693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3566722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4040489196777</t>
+    <t xml:space="preserve">23.3566703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4040470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9302806854248</t>
   </si>
   <si>
     <t xml:space="preserve">23.6883068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1248798370361</t>
+    <t xml:space="preserve">22.1248779296875</t>
   </si>
   <si>
     <t xml:space="preserve">22.8829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7881526947021</t>
+    <t xml:space="preserve">22.7881507873535</t>
   </si>
   <si>
     <t xml:space="preserve">23.0250339508057</t>
@@ -2183,7 +2186,7 @@
     <t xml:space="preserve">22.8355274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4514236450195</t>
+    <t xml:space="preserve">23.4514217376709</t>
   </si>
   <si>
     <t xml:space="preserve">24.3515777587891</t>
@@ -2210,7 +2213,7 @@
     <t xml:space="preserve">21.7932434082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6984882354736</t>
+    <t xml:space="preserve">21.6984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">21.5563583374023</t>
@@ -2225,22 +2228,22 @@
     <t xml:space="preserve">21.5089817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">23.49880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6832160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9725666046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2568244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0673217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2991123199463</t>
+    <t xml:space="preserve">23.4987983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6832141876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9725646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2568264007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0673198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2991104125977</t>
   </si>
   <si>
     <t xml:space="preserve">24.9200992584229</t>
@@ -2249,7 +2252,7 @@
     <t xml:space="preserve">24.825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7305927276611</t>
+    <t xml:space="preserve">24.7305908203125</t>
   </si>
   <si>
     <t xml:space="preserve">24.3989562988281</t>
@@ -2267,7 +2270,7 @@
     <t xml:space="preserve">25.7255001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6358394622803</t>
+    <t xml:space="preserve">24.6358375549316</t>
   </si>
   <si>
     <t xml:space="preserve">25.5359935760498</t>
@@ -2279,10 +2282,10 @@
     <t xml:space="preserve">25.3464889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5935516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5461750030518</t>
+    <t xml:space="preserve">23.5935535430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5461769104004</t>
   </si>
   <si>
     <t xml:space="preserve">23.1197872161865</t>
@@ -2291,16 +2294,16 @@
     <t xml:space="preserve">23.2619171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9776554107666</t>
+    <t xml:space="preserve">22.9776573181152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2145404815674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6409301757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0199451446533</t>
+    <t xml:space="preserve">23.6409320831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0199432373047</t>
   </si>
   <si>
     <t xml:space="preserve">23.8778133392334</t>
@@ -2315,13 +2318,13 @@
     <t xml:space="preserve">22.6460208892822</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3617610931396</t>
+    <t xml:space="preserve">22.3617630004883</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5833740234375</t>
+    <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
     <t xml:space="preserve">26.4835262298584</t>
@@ -2333,13 +2336,13 @@
     <t xml:space="preserve">26.6256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1992683410645</t>
+    <t xml:space="preserve">26.1992664337158</t>
   </si>
   <si>
     <t xml:space="preserve">25.8202533721924</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5309047698975</t>
+    <t xml:space="preserve">26.5309028625488</t>
   </si>
   <si>
     <t xml:space="preserve">26.6730327606201</t>
@@ -33295,7 +33298,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>549</v>
+        <v>716</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33347,7 +33350,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33399,7 +33402,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>549</v>
+        <v>716</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33451,7 +33454,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33503,7 +33506,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33529,7 +33532,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33555,7 +33558,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33581,7 +33584,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33607,7 +33610,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33633,7 +33636,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33659,7 +33662,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33685,7 +33688,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1148" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33711,7 +33714,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33763,7 +33766,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1151" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33789,7 +33792,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33815,7 +33818,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33841,7 +33844,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33867,7 +33870,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33893,7 +33896,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1156" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33971,7 +33974,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34075,7 +34078,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34101,7 +34104,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1164" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34127,7 +34130,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34153,7 +34156,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34205,7 +34208,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G1168" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34231,7 +34234,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34257,7 +34260,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34283,7 +34286,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1171" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34309,7 +34312,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34335,7 +34338,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34361,7 +34364,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34387,7 +34390,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34439,7 +34442,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>549</v>
+        <v>716</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34465,7 +34468,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34543,7 +34546,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34569,7 +34572,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34595,7 +34598,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34647,7 +34650,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34699,7 +34702,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34725,7 +34728,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34777,7 +34780,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1190" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34803,7 +34806,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34829,7 +34832,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34855,7 +34858,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34881,7 +34884,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1194" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34907,7 +34910,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G1195" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34933,7 +34936,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34985,7 +34988,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35011,7 +35014,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35037,7 +35040,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35063,7 +35066,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35089,7 +35092,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1202" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35115,7 +35118,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35141,7 +35144,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35167,7 +35170,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35193,7 +35196,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35219,7 +35222,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35245,7 +35248,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35271,7 +35274,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1209" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35297,7 +35300,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35323,7 +35326,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35349,7 +35352,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G1212" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35375,7 +35378,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35427,7 +35430,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35453,7 +35456,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>549</v>
+        <v>716</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35479,7 +35482,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35505,7 +35508,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35531,7 +35534,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1219" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35557,7 +35560,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35583,7 +35586,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1221" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35609,7 +35612,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1222" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35635,7 +35638,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35661,7 +35664,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1224" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35687,7 +35690,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G1225" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35713,7 +35716,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35739,7 +35742,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35765,7 +35768,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1228" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35791,7 +35794,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35817,7 +35820,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1230" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35843,7 +35846,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35869,7 +35872,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35895,7 +35898,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35921,7 +35924,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1234" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35947,7 +35950,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36025,7 +36028,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36077,7 +36080,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36129,7 +36132,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36155,7 +36158,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36181,7 +36184,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1244" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36207,7 +36210,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1245" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36233,7 +36236,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36285,7 +36288,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36337,7 +36340,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36363,7 +36366,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1251" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36389,7 +36392,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36415,7 +36418,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1253" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36441,7 +36444,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36467,7 +36470,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36493,7 +36496,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1256" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36519,7 +36522,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36545,7 +36548,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36571,7 +36574,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>549</v>
+        <v>716</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36649,7 +36652,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36675,7 +36678,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36701,7 +36704,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1264" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36727,7 +36730,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1265" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36753,7 +36756,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36779,7 +36782,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1267" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36805,7 +36808,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1268" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36831,7 +36834,7 @@
         <v>27.1395435333252</v>
       </c>
       <c r="G1269" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36857,7 +36860,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1270" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36883,7 +36886,7 @@
         <v>27.285192489624</v>
       </c>
       <c r="G1271" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36909,7 +36912,7 @@
         <v>26.8482418060303</v>
       </c>
       <c r="G1272" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36935,7 +36938,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36961,7 +36964,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1274" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36987,7 +36990,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1275" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37013,7 +37016,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1276" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37039,7 +37042,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1277" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37065,7 +37068,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37091,7 +37094,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37117,7 +37120,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1280" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37143,7 +37146,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1281" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37169,7 +37172,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1282" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37195,7 +37198,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37221,7 +37224,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37247,7 +37250,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1285" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37273,7 +37276,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37299,7 +37302,7 @@
         <v>26.5569400787354</v>
       </c>
       <c r="G1287" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37325,7 +37328,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37351,7 +37354,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37377,7 +37380,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37403,7 +37406,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37429,7 +37432,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1292" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37455,7 +37458,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1293" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37481,7 +37484,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1294" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37507,7 +37510,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37533,7 +37536,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1296" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37559,7 +37562,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1297" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37585,7 +37588,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37611,7 +37614,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G1299" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37637,7 +37640,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1300" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37663,7 +37666,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37689,7 +37692,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37715,7 +37718,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1303" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37741,7 +37744,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1304" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37767,7 +37770,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37793,7 +37796,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1306" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37819,7 +37822,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37845,7 +37848,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1308" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37871,7 +37874,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37897,7 +37900,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1310" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37923,7 +37926,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1311" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37949,7 +37952,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1312" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37975,7 +37978,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38001,7 +38004,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38027,7 +38030,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38053,7 +38056,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38079,7 +38082,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38105,7 +38108,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38131,7 +38134,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1319" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38157,7 +38160,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1320" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38183,7 +38186,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38209,7 +38212,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38235,7 +38238,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38261,7 +38264,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38287,7 +38290,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38313,7 +38316,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38339,7 +38342,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38365,7 +38368,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38391,7 +38394,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38417,7 +38420,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38443,7 +38446,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38469,7 +38472,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1332" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38495,7 +38498,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38521,7 +38524,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1334" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38547,7 +38550,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1335" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38573,7 +38576,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38599,7 +38602,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38625,7 +38628,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1338" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38651,7 +38654,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38677,7 +38680,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38703,7 +38706,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38729,7 +38732,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1342" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38755,7 +38758,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38781,7 +38784,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1344" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38807,7 +38810,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38833,7 +38836,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1346" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38859,7 +38862,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1347" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38885,7 +38888,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1348" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38911,7 +38914,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G1349" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38937,7 +38940,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38963,7 +38966,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38989,7 +38992,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1352" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39015,7 +39018,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1353" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39041,7 +39044,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1354" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39067,7 +39070,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1355" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39093,7 +39096,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1356" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39119,7 +39122,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1357" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39145,7 +39148,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1358" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39171,7 +39174,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1359" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39197,7 +39200,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1360" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39223,7 +39226,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39249,7 +39252,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1362" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39275,7 +39278,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39301,7 +39304,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1364" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39327,7 +39330,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39353,7 +39356,7 @@
         <v>19.759916305542</v>
       </c>
       <c r="G1366" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39379,7 +39382,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -39405,7 +39408,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39431,7 +39434,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -39457,7 +39460,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1370" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39483,7 +39486,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G1371" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39509,7 +39512,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39535,7 +39538,7 @@
         <v>18.1966018676758</v>
       </c>
       <c r="G1373" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39561,7 +39564,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39587,7 +39590,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G1375" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39613,7 +39616,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1376" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39639,7 +39642,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39665,7 +39668,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39691,7 +39694,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1379" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39717,7 +39720,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1380" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39743,7 +39746,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1381" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39769,7 +39772,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1382" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39795,7 +39798,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1383" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39821,7 +39824,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -39847,7 +39850,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1385" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -39873,7 +39876,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G1386" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39899,7 +39902,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39925,7 +39928,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1388" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39951,7 +39954,7 @@
         <v>20.25</v>
       </c>
       <c r="G1389" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39977,7 +39980,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40003,7 +40006,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40029,7 +40032,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1392" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40055,7 +40058,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40081,7 +40084,7 @@
         <v>22.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40107,7 +40110,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1395" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40133,7 +40136,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40159,7 +40162,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40185,7 +40188,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1398" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40211,7 +40214,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40237,7 +40240,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40263,7 +40266,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1401" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40289,7 +40292,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40315,7 +40318,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1403" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40341,7 +40344,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1404" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40367,7 +40370,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1405" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40393,7 +40396,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40419,7 +40422,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1407" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40445,7 +40448,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40471,7 +40474,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40497,7 +40500,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40523,7 +40526,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40549,7 +40552,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40575,7 +40578,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40601,7 +40604,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40627,7 +40630,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40653,7 +40656,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40679,7 +40682,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -40705,7 +40708,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40731,7 +40734,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40757,7 +40760,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40783,7 +40786,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1421" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40809,7 +40812,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40835,7 +40838,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -40861,7 +40864,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1424" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40887,7 +40890,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1425" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40913,7 +40916,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1426" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -40939,7 +40942,7 @@
         <v>22.5</v>
       </c>
       <c r="G1427" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40965,7 +40968,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40991,7 +40994,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41017,7 +41020,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41043,7 +41046,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1431" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41069,7 +41072,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41095,7 +41098,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41121,7 +41124,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1434" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41147,7 +41150,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41173,7 +41176,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1436" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41199,7 +41202,7 @@
         <v>22.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41225,7 +41228,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41251,7 +41254,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41277,7 +41280,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41303,7 +41306,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41329,7 +41332,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1442" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41355,7 +41358,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1443" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41381,7 +41384,7 @@
         <v>22.75</v>
       </c>
       <c r="G1444" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41407,7 +41410,7 @@
         <v>22.5</v>
       </c>
       <c r="G1445" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41433,7 +41436,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41459,7 +41462,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41485,7 +41488,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41511,7 +41514,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41537,7 +41540,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1450" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41563,7 +41566,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41589,7 +41592,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41615,7 +41618,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41641,7 +41644,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41667,7 +41670,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1455" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41693,7 +41696,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41719,7 +41722,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41745,7 +41748,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41771,7 +41774,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1459" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41797,7 +41800,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1460" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41823,7 +41826,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41849,7 +41852,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -41875,7 +41878,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -41901,7 +41904,7 @@
         <v>20</v>
       </c>
       <c r="G1464" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -41927,7 +41930,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1465" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -41953,7 +41956,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1466" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -41979,7 +41982,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1467" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42005,7 +42008,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42031,7 +42034,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42057,7 +42060,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42083,7 +42086,7 @@
         <v>19.5</v>
       </c>
       <c r="G1471" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42109,7 +42112,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42135,7 +42138,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42161,7 +42164,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1474" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42187,7 +42190,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1475" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42213,7 +42216,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42239,7 +42242,7 @@
         <v>21</v>
       </c>
       <c r="G1477" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42265,7 +42268,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42291,7 +42294,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42317,7 +42320,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1480" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42343,7 +42346,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42369,7 +42372,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1482" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42395,7 +42398,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42421,7 +42424,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1484" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42447,7 +42450,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1485" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42473,7 +42476,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42499,7 +42502,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42525,7 +42528,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1488" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42551,7 +42554,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42577,7 +42580,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42603,7 +42606,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42629,7 +42632,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42655,7 +42658,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1493" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42681,7 +42684,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42707,7 +42710,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42733,7 +42736,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1496" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42759,7 +42762,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42785,7 +42788,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1498" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42811,7 +42814,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42837,7 +42840,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -42863,7 +42866,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42889,7 +42892,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -42915,7 +42918,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -42941,7 +42944,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1504" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -42967,7 +42970,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42993,7 +42996,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43019,7 +43022,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43045,7 +43048,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43071,7 +43074,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43097,7 +43100,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1510" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43123,7 +43126,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1511" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43149,7 +43152,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43175,7 +43178,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1513" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43201,7 +43204,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1514" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43227,7 +43230,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43253,7 +43256,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1516" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43279,7 +43282,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1517" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43305,7 +43308,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43331,7 +43334,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1519" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43357,7 +43360,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43383,7 +43386,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1521" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43409,7 +43412,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43435,7 +43438,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43461,7 +43464,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43487,7 +43490,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1525" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43513,7 +43516,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43539,7 +43542,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1527" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43565,7 +43568,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43591,7 +43594,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43617,7 +43620,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43643,7 +43646,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1531" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43669,7 +43672,7 @@
         <v>17</v>
       </c>
       <c r="G1532" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43695,7 +43698,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43721,7 +43724,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43747,7 +43750,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43773,7 +43776,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43799,7 +43802,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1537" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43825,7 +43828,7 @@
         <v>17.5</v>
       </c>
       <c r="G1538" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43851,7 +43854,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43877,7 +43880,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43903,7 +43906,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -43929,7 +43932,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43955,7 +43958,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43981,7 +43984,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1544" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44007,7 +44010,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1545" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44033,7 +44036,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44059,7 +44062,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44085,7 +44088,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1548" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44111,7 +44114,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1549" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44137,7 +44140,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1550" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44163,7 +44166,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1551" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44189,7 +44192,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1552" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44215,7 +44218,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44241,7 +44244,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44267,7 +44270,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44293,7 +44296,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1556" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44319,7 +44322,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44345,7 +44348,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1558" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44371,7 +44374,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1559" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44397,7 +44400,7 @@
         <v>17</v>
       </c>
       <c r="G1560" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44423,7 +44426,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44449,7 +44452,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44475,7 +44478,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44501,7 +44504,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44527,7 +44530,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1565" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44553,7 +44556,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1566" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44579,7 +44582,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44605,7 +44608,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44631,7 +44634,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1569" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44657,7 +44660,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44683,7 +44686,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44709,7 +44712,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44735,7 +44738,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44761,7 +44764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44787,7 +44790,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44813,7 +44816,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44839,7 +44842,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1577" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44865,7 +44868,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44891,7 +44894,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44917,7 +44920,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1580" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44943,7 +44946,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1581" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44969,7 +44972,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1582" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -44995,7 +44998,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45021,7 +45024,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1584" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45047,7 +45050,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1585" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45073,7 +45076,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1586" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45099,7 +45102,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1587" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45125,7 +45128,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45151,7 +45154,7 @@
         <v>17</v>
       </c>
       <c r="G1589" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45177,7 +45180,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45203,7 +45206,7 @@
         <v>17</v>
       </c>
       <c r="G1591" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45229,7 +45232,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1592" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45255,7 +45258,7 @@
         <v>17</v>
       </c>
       <c r="G1593" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45281,7 +45284,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45307,7 +45310,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45333,7 +45336,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45359,7 +45362,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1597" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45385,7 +45388,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1598" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45411,7 +45414,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45437,7 +45440,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1600" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45463,7 +45466,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1601" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45489,7 +45492,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1602" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45515,7 +45518,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1603" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45541,7 +45544,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1604" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45567,7 +45570,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45593,7 +45596,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1606" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45619,7 +45622,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1607" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45645,7 +45648,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1608" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45671,7 +45674,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45697,7 +45700,7 @@
         <v>19.5</v>
       </c>
       <c r="G1610" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45723,7 +45726,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1611" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45749,7 +45752,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45775,7 +45778,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45801,7 +45804,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45827,7 +45830,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45853,7 +45856,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1616" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45879,7 +45882,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1617" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45905,7 +45908,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45931,7 +45934,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1619" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45957,7 +45960,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1620" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45983,7 +45986,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46009,7 +46012,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46035,7 +46038,7 @@
         <v>19</v>
       </c>
       <c r="G1623" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46061,7 +46064,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46087,7 +46090,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1625" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46113,7 +46116,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1626" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46139,7 +46142,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1627" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46165,7 +46168,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1628" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46191,7 +46194,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46217,7 +46220,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46243,7 +46246,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46269,7 +46272,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46295,7 +46298,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1633" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46321,7 +46324,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46347,7 +46350,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46373,7 +46376,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46399,7 +46402,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1637" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46425,7 +46428,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46451,7 +46454,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1639" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46477,7 +46480,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1640" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46503,7 +46506,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1641" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46529,7 +46532,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46555,7 +46558,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1643" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46581,7 +46584,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46607,7 +46610,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46633,7 +46636,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1646" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46659,7 +46662,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46685,7 +46688,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1648" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46711,7 +46714,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1649" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46737,7 +46740,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1650" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46763,7 +46766,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1651" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46789,7 +46792,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46815,7 +46818,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1653" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46841,7 +46844,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1654" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46867,7 +46870,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46893,7 +46896,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46919,7 +46922,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46945,7 +46948,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46971,7 +46974,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -46997,7 +47000,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1660" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47023,7 +47026,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1661" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47049,7 +47052,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47075,7 +47078,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1663" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47101,7 +47104,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1664" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47127,7 +47130,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47153,7 +47156,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1666" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47179,7 +47182,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1667" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47205,7 +47208,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1668" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47231,7 +47234,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1669" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47257,7 +47260,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1670" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47283,7 +47286,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1671" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47309,7 +47312,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1672" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47335,7 +47338,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1673" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47361,7 +47364,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1674" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47387,7 +47390,7 @@
         <v>18</v>
       </c>
       <c r="G1675" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47413,7 +47416,7 @@
         <v>17.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47439,7 +47442,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47465,7 +47468,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1678" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47491,7 +47494,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1679" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47517,7 +47520,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47543,7 +47546,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47569,7 +47572,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47595,7 +47598,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1683" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47621,7 +47624,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47647,7 +47650,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47673,7 +47676,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1686" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47699,7 +47702,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1687" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47725,7 +47728,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47751,7 +47754,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1689" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47777,7 +47780,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1690" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47803,7 +47806,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47829,7 +47832,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47855,7 +47858,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47881,7 +47884,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1694" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47907,7 +47910,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47933,7 +47936,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1696" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47959,7 +47962,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47985,7 +47988,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48011,7 +48014,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48037,7 +48040,7 @@
         <v>21.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48063,7 +48066,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1701" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48089,7 +48092,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48115,7 +48118,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1703" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48141,7 +48144,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48167,7 +48170,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48193,7 +48196,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48219,7 +48222,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48245,7 +48248,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48271,7 +48274,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1709" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48297,7 +48300,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48323,7 +48326,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48349,7 +48352,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48375,7 +48378,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48401,7 +48404,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48427,7 +48430,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48453,7 +48456,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1716" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48479,7 +48482,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48505,7 +48508,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48531,7 +48534,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1719" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48557,7 +48560,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48583,7 +48586,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1721" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48609,7 +48612,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1722" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48635,7 +48638,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1723" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48661,7 +48664,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48687,7 +48690,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1725" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48713,7 +48716,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1726" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48739,7 +48742,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1727" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48765,7 +48768,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1728" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48791,7 +48794,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48817,7 +48820,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1730" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48843,7 +48846,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48869,7 +48872,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48895,7 +48898,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1733" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48921,7 +48924,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48947,7 +48950,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1735" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48973,7 +48976,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48999,7 +49002,7 @@
         <v>15.5</v>
       </c>
       <c r="G1737" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49025,7 +49028,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1738" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49051,7 +49054,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1739" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49077,7 +49080,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49103,7 +49106,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1741" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49129,7 +49132,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49155,7 +49158,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49181,7 +49184,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1744" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49207,7 +49210,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1745" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49233,7 +49236,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1746" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49259,7 +49262,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49285,7 +49288,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49311,7 +49314,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1749" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49337,7 +49340,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1750" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49363,7 +49366,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1751" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49389,7 +49392,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1752" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49415,7 +49418,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1753" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49441,7 +49444,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49467,7 +49470,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1755" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49493,7 +49496,7 @@
         <v>18.5</v>
       </c>
       <c r="G1756" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49519,7 +49522,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1757" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49545,7 +49548,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49571,7 +49574,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49597,7 +49600,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1760" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49623,7 +49626,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49649,7 +49652,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49675,7 +49678,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49701,7 +49704,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49727,7 +49730,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1765" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49753,7 +49756,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49779,7 +49782,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49805,7 +49808,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49831,7 +49834,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1769" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49857,7 +49860,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49883,7 +49886,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49909,7 +49912,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49935,7 +49938,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49961,7 +49964,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49987,7 +49990,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1775" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50013,7 +50016,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50039,7 +50042,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50065,7 +50068,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50091,7 +50094,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1779" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50117,7 +50120,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50143,7 +50146,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1781" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50169,7 +50172,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1782" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50195,7 +50198,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50221,7 +50224,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50247,7 +50250,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50273,7 +50276,7 @@
         <v>22.5</v>
       </c>
       <c r="G1786" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50299,7 +50302,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1787" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50325,7 +50328,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50351,7 +50354,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50377,7 +50380,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50403,7 +50406,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1791" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50429,7 +50432,7 @@
         <v>23.75</v>
       </c>
       <c r="G1792" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50455,7 +50458,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50481,7 +50484,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1794" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50507,7 +50510,7 @@
         <v>22.5</v>
       </c>
       <c r="G1795" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50533,7 +50536,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1796" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50559,7 +50562,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50585,7 +50588,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50611,7 +50614,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50637,7 +50640,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50663,7 +50666,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50689,7 +50692,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1802" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50715,7 +50718,7 @@
         <v>22.75</v>
       </c>
       <c r="G1803" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50741,7 +50744,7 @@
         <v>23.75</v>
       </c>
       <c r="G1804" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50767,7 +50770,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50793,7 +50796,7 @@
         <v>23.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50819,7 +50822,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1807" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50845,7 +50848,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50871,7 +50874,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1809" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50897,7 +50900,7 @@
         <v>23.5</v>
       </c>
       <c r="G1810" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50923,7 +50926,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50949,7 +50952,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50975,7 +50978,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51001,7 +51004,7 @@
         <v>23.5</v>
       </c>
       <c r="G1814" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51027,7 +51030,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1815" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51053,7 +51056,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1816" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51079,7 +51082,7 @@
         <v>22.25</v>
       </c>
       <c r="G1817" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51105,7 +51108,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1818" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51131,7 +51134,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51157,7 +51160,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51183,7 +51186,7 @@
         <v>25</v>
       </c>
       <c r="G1821" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51209,7 +51212,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G1822" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51235,7 +51238,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51261,7 +51264,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1824" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51287,7 +51290,7 @@
         <v>25</v>
       </c>
       <c r="G1825" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51313,7 +51316,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51339,7 +51342,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51365,7 +51368,7 @@
         <v>26</v>
       </c>
       <c r="G1828" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51391,7 +51394,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1829" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51417,7 +51420,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51443,7 +51446,7 @@
         <v>25</v>
       </c>
       <c r="G1831" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51469,7 +51472,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51495,7 +51498,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51521,7 +51524,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51547,7 +51550,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1835" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51573,7 +51576,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51599,7 +51602,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1837" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51625,7 +51628,7 @@
         <v>22.75</v>
       </c>
       <c r="G1838" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51651,7 +51654,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51677,7 +51680,7 @@
         <v>22.5</v>
       </c>
       <c r="G1840" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51703,7 +51706,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51729,7 +51732,7 @@
         <v>23.5</v>
       </c>
       <c r="G1842" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51755,7 +51758,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1843" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51781,7 +51784,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1844" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51807,7 +51810,7 @@
         <v>23</v>
       </c>
       <c r="G1845" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51833,7 +51836,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51859,7 +51862,7 @@
         <v>23</v>
       </c>
       <c r="G1847" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51885,7 +51888,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51911,7 +51914,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51937,7 +51940,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51963,7 +51966,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1851" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51989,7 +51992,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52015,7 +52018,7 @@
         <v>23.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52041,7 +52044,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52067,7 +52070,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1855" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52093,7 +52096,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52119,7 +52122,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52145,7 +52148,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52171,7 +52174,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1859" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52197,7 +52200,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1860" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52223,7 +52226,7 @@
         <v>23</v>
       </c>
       <c r="G1861" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52249,7 +52252,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52275,7 +52278,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1863" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52301,7 +52304,7 @@
         <v>22</v>
       </c>
       <c r="G1864" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52327,7 +52330,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1865" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52353,7 +52356,7 @@
         <v>21</v>
       </c>
       <c r="G1866" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52379,7 +52382,7 @@
         <v>21.5</v>
       </c>
       <c r="G1867" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52405,7 +52408,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52431,7 +52434,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1869" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52457,7 +52460,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52483,7 +52486,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1871" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52509,7 +52512,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1872" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52535,7 +52538,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52543,7 +52546,7 @@
     </row>
     <row r="1874">
       <c r="A1874" s="1" t="n">
-        <v>45952.6494791667</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1874" t="n">
         <v>149362</v>
@@ -52561,9 +52564,35 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1874" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1874" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="1" t="n">
+        <v>45953.6494791667</v>
+      </c>
+      <c r="B1875" t="n">
+        <v>39264</v>
+      </c>
+      <c r="C1875" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="D1875" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="G1875" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H1875" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="1165">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125877380371</t>
+    <t xml:space="preserve">7.58125925064087</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288782119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099319458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68969249725342</t>
+    <t xml:space="preserve">7.90288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099367141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68969202041626</t>
   </si>
   <si>
     <t xml:space="preserve">7.87348079681396</t>
@@ -65,82 +65,82 @@
     <t xml:space="preserve">7.67406988143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97640085220337</t>
+    <t xml:space="preserve">7.97640180587769</t>
   </si>
   <si>
     <t xml:space="preserve">7.4443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.302818775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520227432251</t>
+    <t xml:space="preserve">7.30281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.46639060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57206916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4434175491333</t>
+    <t xml:space="preserve">7.57206869125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44341707229614</t>
   </si>
   <si>
     <t xml:space="preserve">7.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54450082778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64742183685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180501937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85694026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92218542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00397205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86612892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01959419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81466865539551</t>
+    <t xml:space="preserve">7.54450035095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80180406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85693979263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92218589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00397109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86612844467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01959228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81466960906982</t>
   </si>
   <si>
     <t xml:space="preserve">7.7650465965271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85142707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336938858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79261493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74666738510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910245895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56379842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67315101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78526306152344</t>
+    <t xml:space="preserve">7.85142660140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79261541366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74666786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56379890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67315149307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78526401519775</t>
   </si>
   <si>
     <t xml:space="preserve">7.74850559234619</t>
@@ -149,49 +149,49 @@
     <t xml:space="preserve">7.99478197097778</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06002712249756</t>
+    <t xml:space="preserve">8.06002616882324</t>
   </si>
   <si>
     <t xml:space="preserve">8.11424350738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30354499816895</t>
+    <t xml:space="preserve">8.30354595184326</t>
   </si>
   <si>
     <t xml:space="preserve">8.46344089508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48641300201416</t>
+    <t xml:space="preserve">8.48641490936279</t>
   </si>
   <si>
     <t xml:space="preserve">8.75382518768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95966720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60128211975098</t>
+    <t xml:space="preserve">8.9596700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60128116607666</t>
   </si>
   <si>
     <t xml:space="preserve">8.28884220123291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25208377838135</t>
+    <t xml:space="preserve">8.25208473205566</t>
   </si>
   <si>
     <t xml:space="preserve">8.46987247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3623571395874</t>
+    <t xml:space="preserve">8.36235809326172</t>
   </si>
   <si>
     <t xml:space="preserve">8.45425128936768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71155548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74831199645996</t>
+    <t xml:space="preserve">8.71155452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74831295013428</t>
   </si>
   <si>
     <t xml:space="preserve">8.61598491668701</t>
@@ -200,40 +200,40 @@
     <t xml:space="preserve">8.66560745239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79426002502441</t>
+    <t xml:space="preserve">8.7942590713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.00561618804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86869525909424</t>
+    <t xml:space="preserve">8.86869430541992</t>
   </si>
   <si>
     <t xml:space="preserve">9.11588954925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14345645904541</t>
+    <t xml:space="preserve">9.14345741271973</t>
   </si>
   <si>
     <t xml:space="preserve">9.33643436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09750938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680793762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18572807312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06167030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02399444580078</t>
+    <t xml:space="preserve">9.09751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18572902679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06166934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02399349212646</t>
   </si>
   <si>
     <t xml:space="preserve">8.76577281951904</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">8.99366855621338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04237365722656</t>
+    <t xml:space="preserve">9.04237270355225</t>
   </si>
   <si>
     <t xml:space="preserve">8.90177536010742</t>
@@ -251,73 +251,73 @@
     <t xml:space="preserve">8.67112159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98191499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30630397796631</t>
+    <t xml:space="preserve">8.50754833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98191547393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30630302429199</t>
   </si>
   <si>
     <t xml:space="preserve">8.40830421447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54614543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59209251403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63803863525391</t>
+    <t xml:space="preserve">8.54614639282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5920934677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63803958892822</t>
   </si>
   <si>
     <t xml:space="preserve">8.80804252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126266479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126512527466</t>
+    <t xml:space="preserve">8.02970123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126607894897</t>
   </si>
   <si>
     <t xml:space="preserve">8.34214019775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7749605178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77771759033203</t>
+    <t xml:space="preserve">8.77496147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77771854400635</t>
   </si>
   <si>
     <t xml:space="preserve">8.75474452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50571060180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59944534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70144748687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57739067077637</t>
+    <t xml:space="preserve">8.50571250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70144653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57738971710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.3926830291748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34122276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56084823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71982479095459</t>
+    <t xml:space="preserve">8.34122180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5608491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71982574462891</t>
   </si>
   <si>
     <t xml:space="preserve">8.05451393127441</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">8.18867683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.548903465271</t>
+    <t xml:space="preserve">8.54890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.33478927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50938701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0386962890625</t>
+    <t xml:space="preserve">8.5093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92107200622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03869724273682</t>
   </si>
   <si>
     <t xml:space="preserve">8.97437191009521</t>
@@ -353,85 +353,85 @@
     <t xml:space="preserve">9.01664257049561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1526460647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84939670562744</t>
+    <t xml:space="preserve">9.15264701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84939575195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.07913017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8558292388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446243286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23370552062988</t>
+    <t xml:space="preserve">8.85583019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23370456695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.27046394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33754634857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20062351226807</t>
+    <t xml:space="preserve">8.33754539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20062255859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.40370941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27414035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29803085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50019836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43587207794189</t>
+    <t xml:space="preserve">8.27413940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5001974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43587112426758</t>
   </si>
   <si>
     <t xml:space="preserve">8.22451591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35408592224121</t>
+    <t xml:space="preserve">8.35408782958984</t>
   </si>
   <si>
     <t xml:space="preserve">8.22084045410156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15283870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39911556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42668437957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48365688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.709716796875</t>
+    <t xml:space="preserve">8.15283966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39911460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42668342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48365783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70971488952637</t>
   </si>
   <si>
     <t xml:space="preserve">8.77128410339355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72074222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.100266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06534671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89809989929199</t>
+    <t xml:space="preserve">8.72074413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10026741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06534576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89810085296631</t>
   </si>
   <si>
     <t xml:space="preserve">8.83469295501709</t>
@@ -440,67 +440,67 @@
     <t xml:space="preserve">8.97712898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05156135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2353515625</t>
+    <t xml:space="preserve">9.05156230926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23535060882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.20594501495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36216449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39524745941162</t>
+    <t xml:space="preserve">9.36216354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3952465057373</t>
   </si>
   <si>
     <t xml:space="preserve">9.61027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64887523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69482135772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59373760223389</t>
+    <t xml:space="preserve">9.6488733291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69482231140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5937385559082</t>
   </si>
   <si>
     <t xml:space="preserve">9.64336109161377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31989288330078</t>
+    <t xml:space="preserve">9.31989192962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.61763000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49265480041504</t>
+    <t xml:space="preserve">9.49265575408936</t>
   </si>
   <si>
     <t xml:space="preserve">9.51103210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28497314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46324825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33091926574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12875556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26291751861572</t>
+    <t xml:space="preserve">9.28497409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46324729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3309211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12875461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26291847229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.14713287353516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06075096130371</t>
+    <t xml:space="preserve">9.06075286865234</t>
   </si>
   <si>
     <t xml:space="preserve">8.94128894805908</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">8.76025772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00653457641602</t>
+    <t xml:space="preserve">9.0065336227417</t>
   </si>
   <si>
     <t xml:space="preserve">9.18940544128418</t>
@@ -527,52 +527,52 @@
     <t xml:space="preserve">9.44670677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39157104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7407693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53860092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75914669036865</t>
+    <t xml:space="preserve">9.39157199859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46508502960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53860187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">9.68563175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90617561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99807071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7959041595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92455768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81428241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94293594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0715866088867</t>
+    <t xml:space="preserve">9.90617752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99807262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79590606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.814284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0715856552124</t>
   </si>
   <si>
     <t xml:space="preserve">10.1083431243896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6672534942627</t>
+    <t xml:space="preserve">9.66725254058838</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752590179443</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">9.83266162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86941814422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.163480758667</t>
+    <t xml:space="preserve">9.86941909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1634798049927</t>
   </si>
   <si>
     <t xml:space="preserve">10.310510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0348300933838</t>
+    <t xml:space="preserve">10.0348291397095</t>
   </si>
   <si>
     <t xml:space="preserve">10.016450881958</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">10.1267223358154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5126791000366</t>
+    <t xml:space="preserve">10.5126781463623</t>
   </si>
   <si>
     <t xml:space="preserve">10.6045713424683</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">10.7332220077515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4207820892334</t>
+    <t xml:space="preserve">10.420783996582</t>
   </si>
   <si>
     <t xml:space="preserve">10.4759206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4391622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288879394531</t>
+    <t xml:space="preserve">10.4391613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288898468018</t>
   </si>
   <si>
     <t xml:space="preserve">9.97969341278076</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">9.94108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451015472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99672603607178</t>
+    <t xml:space="preserve">9.88544750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99672698974609</t>
   </si>
   <si>
     <t xml:space="preserve">10.200740814209</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">10.2192878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0894603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73707294464111</t>
+    <t xml:space="preserve">10.0894613265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523691177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7370719909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.86689949035645</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">10.1636476516724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5531311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4047565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4233016967773</t>
+    <t xml:space="preserve">10.5531301498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4047574996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4233045578003</t>
   </si>
   <si>
     <t xml:space="preserve">10.3862104415894</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">10.3120231628418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0338220596313</t>
+    <t xml:space="preserve">10.033821105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.81125926971436</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">9.79271221160889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498792648315</t>
+    <t xml:space="preserve">10.2563829421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498802185059</t>
   </si>
   <si>
     <t xml:space="preserve">10.4789438247681</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">12.0554218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103000640869</t>
+    <t xml:space="preserve">11.1651763916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102991104126</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062852859497</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">11.6288452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175657272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9626874923706</t>
+    <t xml:space="preserve">11.5175666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9626884460449</t>
   </si>
   <si>
     <t xml:space="preserve">12.1481561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2408895492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4449052810669</t>
+    <t xml:space="preserve">12.2408905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4449043273926</t>
   </si>
   <si>
     <t xml:space="preserve">12.593279838562</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">12.1852493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.573205947876</t>
+    <t xml:space="preserve">11.5732049942017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5917520523071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401266098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4804706573486</t>
+    <t xml:space="preserve">11.7401256561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4804716110229</t>
   </si>
   <si>
     <t xml:space="preserve">11.925594329834</t>
@@ -776,28 +776,28 @@
     <t xml:space="preserve">12.1110620498657</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1667032241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2223434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5190935134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6860132217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2609643936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5020713806152</t>
+    <t xml:space="preserve">12.1667022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2223424911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5190925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.686014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2609634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5020732879639</t>
   </si>
   <si>
     <t xml:space="preserve">14.0584774017334</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">13.2053241729736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1125907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3892641067505</t>
+    <t xml:space="preserve">13.1125917434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3892650604248</t>
   </si>
   <si>
     <t xml:space="preserve">12.3521718978882</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">12.2037973403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5963354110718</t>
+    <t xml:space="preserve">12.277982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5963344573975</t>
   </si>
   <si>
     <t xml:space="preserve">13.9101028442383</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">13.4093389511108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.168231010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8529357910156</t>
+    <t xml:space="preserve">13.1682319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
     <t xml:space="preserve">12.7045593261719</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">12.5561866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3707189559937</t>
+    <t xml:space="preserve">12.370719909668</t>
   </si>
   <si>
     <t xml:space="preserve">12.7787485122681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8158416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8900289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940437316895</t>
+    <t xml:space="preserve">12.8158407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8900279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940446853638</t>
   </si>
   <si>
     <t xml:space="preserve">13.075496673584</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">13.3351516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569496154785</t>
+    <t xml:space="preserve">13.0569486618042</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489191055298</t>
@@ -881,121 +881,121 @@
     <t xml:space="preserve">12.3150787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4634523391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4263572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2950038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0168008804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090989112854</t>
+    <t xml:space="preserve">12.463451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4263582229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514070510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2950029373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0167999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0909881591797</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353488922119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7571458816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3135509490967</t>
+    <t xml:space="preserve">10.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3135499954224</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280832290649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2764577865601</t>
+    <t xml:space="preserve">11.2764568328857</t>
   </si>
   <si>
     <t xml:space="preserve">11.2208166122437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3691902160645</t>
+    <t xml:space="preserve">11.3691883087158</t>
   </si>
   <si>
     <t xml:space="preserve">11.1095342636108</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40322971343994</t>
+    <t xml:space="preserve">9.42177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40322875976562</t>
   </si>
   <si>
     <t xml:space="preserve">8.88391780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55160427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71699714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80973148345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20696067810059</t>
+    <t xml:space="preserve">9.55160331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71699810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80973243713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20695972442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.24405384063721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19768810272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53152942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43879508972168</t>
+    <t xml:space="preserve">8.19768714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53153038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.438796043396</t>
   </si>
   <si>
     <t xml:space="preserve">9.64433860778809</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7200536727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77416610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2934770584106</t>
+    <t xml:space="preserve">10.7200527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7741641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2934761047363</t>
   </si>
   <si>
     <t xml:space="preserve">10.2378358840942</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71852397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152750015259</t>
+    <t xml:space="preserve">9.71852493286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152740478516</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6844873428345</t>
+    <t xml:space="preserve">11.6844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">11.8699541091919</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4819993972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6118259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7586727142334</t>
+    <t xml:space="preserve">12.4819984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6118268966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7586736679077</t>
   </si>
   <si>
     <t xml:space="preserve">13.7246341705322</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.650447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930826187134</t>
+    <t xml:space="preserve">13.6504487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930835723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.0414581298828</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">14.9301767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2439451217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282567024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687995910645</t>
+    <t xml:space="preserve">14.2439460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687986373901</t>
   </si>
   <si>
     <t xml:space="preserve">15.3938455581665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9487237930298</t>
+    <t xml:space="preserve">14.9487228393555</t>
   </si>
   <si>
     <t xml:space="preserve">14.6148824691772</t>
@@ -1043,31 +1043,31 @@
     <t xml:space="preserve">14.0399303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.132664680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7988233566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8173685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6689939498901</t>
+    <t xml:space="preserve">14.1326637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7988224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8173694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6689929962158</t>
   </si>
   <si>
     <t xml:space="preserve">14.0770244598389</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318133354187</t>
+    <t xml:space="preserve">14.3181324005127</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9858169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5560493469238</t>
+    <t xml:space="preserve">14.9858179092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5560503005981</t>
   </si>
   <si>
     <t xml:space="preserve">14.79896068573</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">14.7615909576416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2660999298096</t>
+    <t xml:space="preserve">15.2661008834839</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4155855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221578598022</t>
+    <t xml:space="preserve">15.4155864715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221559524536</t>
   </si>
   <si>
     <t xml:space="preserve">15.0045022964478</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">14.9297609329224</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0231885910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.396900177002</t>
+    <t xml:space="preserve">15.0231876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3968992233276</t>
   </si>
   <si>
     <t xml:space="preserve">14.9484462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813079833984</t>
+    <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
     <t xml:space="preserve">15.5650682449341</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">16.1630058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9664878845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6765384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7235736846924</t>
+    <t xml:space="preserve">16.9664897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6765403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8730564117432</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">17.3962554931641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7886524200439</t>
+    <t xml:space="preserve">17.7886505126953</t>
   </si>
   <si>
     <t xml:space="preserve">18.0128784179688</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6578521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5270519256592</t>
+    <t xml:space="preserve">18.3118457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6578502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
     <t xml:space="preserve">17.9941940307617</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">18.6855602264404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3305339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2184162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0315628051758</t>
+    <t xml:space="preserve">19.1526966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3305320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2184181213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0315647125244</t>
   </si>
   <si>
     <t xml:space="preserve">17.3775691986084</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">17.9568214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4709949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.807336807251</t>
+    <t xml:space="preserve">17.4709968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9291152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.667516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4619770050049</t>
+    <t xml:space="preserve">16.6675148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266668319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
     <t xml:space="preserve">15.9574661254883</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">15.3782138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706117630005</t>
+    <t xml:space="preserve">15.7706098556519</t>
   </si>
   <si>
     <t xml:space="preserve">16.5367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2938041687012</t>
+    <t xml:space="preserve">16.5927753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2938079833984</t>
   </si>
   <si>
     <t xml:space="preserve">16.4246063232422</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">16.2751235961914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8543720245361</t>
+    <t xml:space="preserve">16.8543739318848</t>
   </si>
   <si>
     <t xml:space="preserve">16.7048892974854</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">16.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4993476867676</t>
+    <t xml:space="preserve">16.4993457794189</t>
   </si>
   <si>
     <t xml:space="preserve">16.3685474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3498611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.63014793396</t>
+    <t xml:space="preserve">16.3498630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862049102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301460266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.6114597320557</t>
@@ -1271,40 +1271,40 @@
     <t xml:space="preserve">16.7609462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8170013427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7983150482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4342708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9671316146851</t>
+    <t xml:space="preserve">16.8170032501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7983169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7892961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.434271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9671325683594</t>
   </si>
   <si>
     <t xml:space="preserve">14.6868476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5373630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.32151222229</t>
+    <t xml:space="preserve">14.5373649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3215103149414</t>
   </si>
   <si>
     <t xml:space="preserve">16.5180339813232</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6211252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8827238082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377471923828</t>
+    <t xml:space="preserve">15.6211261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8827228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377490997314</t>
   </si>
   <si>
     <t xml:space="preserve">16.4806613922119</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">16.9478015899658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0785999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.648832321167</t>
+    <t xml:space="preserve">17.0785961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6488304138184</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104270935059</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">16.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">17.900764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0876178741455</t>
+    <t xml:space="preserve">17.9007625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0876197814941</t>
   </si>
   <si>
     <t xml:space="preserve">18.5360736846924</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">17.9194507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0502471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5740909576416</t>
+    <t xml:space="preserve">18.0502490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.574089050293</t>
   </si>
   <si>
     <t xml:space="preserve">16.742259979248</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">16.5554046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3124923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0225448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0695819854736</t>
+    <t xml:space="preserve">16.3124942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0225429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.069580078125</t>
   </si>
   <si>
     <t xml:space="preserve">15.8453531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7519245147705</t>
+    <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
     <t xml:space="preserve">15.6024398803711</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">16.0135231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9014120101929</t>
+    <t xml:space="preserve">15.9014101028442</t>
   </si>
   <si>
     <t xml:space="preserve">15.9761514663696</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">14.5186777114868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1636524200439</t>
+    <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
     <t xml:space="preserve">14.8550186157227</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">15.5090112686157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6398105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6771812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5276985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145509719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716415405273</t>
+    <t xml:space="preserve">15.6398115158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6771802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5276975631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716424942017</t>
   </si>
   <si>
     <t xml:space="preserve">15.4529552459717</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">15.6584968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8640403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2190628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0972862243652</t>
+    <t xml:space="preserve">15.8640394210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2190608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">17.1346588134766</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">17.5831108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7699661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1249904632568</t>
+    <t xml:space="preserve">17.7699642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1249923706055</t>
   </si>
   <si>
     <t xml:space="preserve">17.6391658782959</t>
@@ -1448,46 +1448,46 @@
     <t xml:space="preserve">18.480016708374</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0689334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1720275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5644226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6017932891846</t>
+    <t xml:space="preserve">18.0689315795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1720294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5644245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">17.7512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.713264465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8066921234131</t>
+    <t xml:space="preserve">19.7132663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8066902160645</t>
   </si>
   <si>
     <t xml:space="preserve">19.4329814910889</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5264072418213</t>
+    <t xml:space="preserve">19.5264053344727</t>
   </si>
   <si>
     <t xml:space="preserve">19.9935455322266</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5541133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4606857299805</t>
+    <t xml:space="preserve">20.5541152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4606876373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.2738304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1336860656738</t>
+    <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
     <t xml:space="preserve">19.9468326568604</t>
@@ -1496,28 +1496,28 @@
     <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.600830078125</t>
+    <t xml:space="preserve">20.6008281707764</t>
   </si>
   <si>
     <t xml:space="preserve">20.6475391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2081050872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5818195343018</t>
+    <t xml:space="preserve">21.2081089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5818214416504</t>
   </si>
   <si>
     <t xml:space="preserve">21.955530166626</t>
   </si>
   <si>
-    <t xml:space="preserve">21.30153465271</t>
+    <t xml:space="preserve">21.3015365600586</t>
   </si>
   <si>
     <t xml:space="preserve">20.8343982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0869750976562</t>
+    <t xml:space="preserve">20.0869770050049</t>
   </si>
   <si>
     <t xml:space="preserve">19.7599773406982</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">19.1994132995605</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7350769042969</t>
+    <t xml:space="preserve">19.7350749969482</t>
   </si>
   <si>
     <t xml:space="preserve">19.9700183868408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7820625305176</t>
+    <t xml:space="preserve">19.7820644378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.4531478881836</t>
@@ -1544,28 +1544,28 @@
     <t xml:space="preserve">19.5471248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6880893707275</t>
+    <t xml:space="preserve">19.5001335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6880912780762</t>
   </si>
   <si>
     <t xml:space="preserve">19.030252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8422985076904</t>
+    <t xml:space="preserve">18.8423004150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.1712188720703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.077241897583</t>
+    <t xml:space="preserve">19.0772399902344</t>
   </si>
   <si>
     <t xml:space="preserve">18.9362773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410999298096</t>
+    <t xml:space="preserve">19.6410980224609</t>
   </si>
   <si>
     <t xml:space="preserve">18.9832649230957</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2651920318604</t>
+    <t xml:space="preserve">19.8290557861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.265193939209</t>
   </si>
   <si>
     <t xml:space="preserve">18.4194049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6261558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4757919311523</t>
+    <t xml:space="preserve">18.6261539459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4757900238037</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765159606934</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">18.5133819580078</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7953109741211</t>
+    <t xml:space="preserve">18.7953128814697</t>
   </si>
   <si>
     <t xml:space="preserve">18.6449489593506</t>
@@ -1619,37 +1619,37 @@
     <t xml:space="preserve">22.4603977203369</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9772682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2122077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.494140625</t>
+    <t xml:space="preserve">22.9772663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2122097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4941387176514</t>
   </si>
   <si>
     <t xml:space="preserve">23.1652221679688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0712413787842</t>
+    <t xml:space="preserve">23.0712451934814</t>
   </si>
   <si>
     <t xml:space="preserve">23.5881156921387</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1989631652832</t>
+    <t xml:space="preserve">24.1989650726318</t>
   </si>
   <si>
     <t xml:space="preserve">23.7760677337646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7290802001953</t>
+    <t xml:space="preserve">23.7290821075439</t>
   </si>
   <si>
     <t xml:space="preserve">23.0242576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8363037109375</t>
+    <t xml:space="preserve">22.8363018035889</t>
   </si>
   <si>
     <t xml:space="preserve">22.8832912445068</t>
@@ -1658,34 +1658,34 @@
     <t xml:space="preserve">23.5411281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.447151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555713653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7085857391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.131477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447257995605</t>
+    <t xml:space="preserve">22.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8700466156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7085876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1314792633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9435253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
   </si>
   <si>
     <t xml:space="preserve">20.9097843170166</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">20.7688179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5808658599854</t>
+    <t xml:space="preserve">20.580867767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.2387008666992</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">21.8495483398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8098125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688461303711</t>
+    <t xml:space="preserve">24.8098106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688442230225</t>
   </si>
   <si>
     <t xml:space="preserve">24.9977626800537</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">24.4339046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3869152069092</t>
+    <t xml:space="preserve">24.3869171142578</t>
   </si>
   <si>
     <t xml:space="preserve">23.4001617431641</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">23.635103225708</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1519756317139</t>
+    <t xml:space="preserve">24.1519718170166</t>
   </si>
   <si>
     <t xml:space="preserve">23.8230590820312</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2929401397705</t>
+    <t xml:space="preserve">24.2929382324219</t>
   </si>
   <si>
     <t xml:space="preserve">23.9640216827393</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">24.4808921813965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5616226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206581115723</t>
+    <t xml:space="preserve">25.5616245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.6556015014648</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">25.3736705780029</t>
   </si>
   <si>
-    <t xml:space="preserve">25.279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061847686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2724437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1182346343994</t>
+    <t xml:space="preserve">25.2796936035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2724456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1182327270508</t>
   </si>
   <si>
     <t xml:space="preserve">24.2459526062012</t>
@@ -1778,103 +1778,103 @@
     <t xml:space="preserve">24.5278816223145</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7628211975098</t>
+    <t xml:space="preserve">24.7628231048584</t>
   </si>
   <si>
     <t xml:space="preserve">23.9170341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0110130310059</t>
+    <t xml:space="preserve">24.0110111236572</t>
   </si>
   <si>
     <t xml:space="preserve">24.8568000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6218566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1857147216797</t>
+    <t xml:space="preserve">24.6218585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1857166290283</t>
   </si>
   <si>
     <t xml:space="preserve">25.138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5206317901611</t>
+    <t xml:space="preserve">21.5206298828125</t>
   </si>
   <si>
     <t xml:space="preserve">21.1917152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4266529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4398994445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.802562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8627986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326759338379</t>
+    <t xml:space="preserve">21.4266548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8025608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8627967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326778411865</t>
   </si>
   <si>
     <t xml:space="preserve">21.6146087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3796672821045</t>
+    <t xml:space="preserve">21.3796653747559</t>
   </si>
   <si>
     <t xml:space="preserve">20.2519474029541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3459243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2182064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3591709136963</t>
+    <t xml:space="preserve">20.34592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.218204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.569766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6748447418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3591690063477</t>
   </si>
   <si>
     <t xml:space="preserve">18.2126579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3292770385742</t>
+    <t xml:space="preserve">17.3292751312256</t>
   </si>
   <si>
     <t xml:space="preserve">17.0473480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8218021392822</t>
+    <t xml:space="preserve">16.8218040466309</t>
   </si>
   <si>
     <t xml:space="preserve">18.3066329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1938629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6637420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9905128479004</t>
+    <t xml:space="preserve">18.1938610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615943908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.990514755249</t>
   </si>
   <si>
     <t xml:space="preserve">22.3194332122803</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">18.7389259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7013320922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8965358734131</t>
+    <t xml:space="preserve">18.7013339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8965377807617</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049598693848</t>
@@ -1910,19 +1910,19 @@
     <t xml:space="preserve">18.3254280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9683170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2165031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713222503662</t>
+    <t xml:space="preserve">17.9683151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8931350708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2165050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713203430176</t>
   </si>
   <si>
     <t xml:space="preserve">16.9418773651123</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">16.2596530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281745910645</t>
+    <t xml:space="preserve">16.8281726837158</t>
   </si>
   <si>
     <t xml:space="preserve">17.5293464660645</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">17.813606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2684230804443</t>
+    <t xml:space="preserve">18.2684211730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.2494716644287</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">18.1736679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9506454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284866333008</t>
+    <t xml:space="preserve">18.950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284847259521</t>
   </si>
   <si>
     <t xml:space="preserve">18.5716323852539</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7800922393799</t>
+    <t xml:space="preserve">18.7800903320312</t>
   </si>
   <si>
     <t xml:space="preserve">17.9462604522705</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">20.893087387085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0352153778076</t>
+    <t xml:space="preserve">21.0352172851562</t>
   </si>
   <si>
     <t xml:space="preserve">20.2771892547607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0774993896484</t>
+    <t xml:space="preserve">22.0775012969971</t>
   </si>
   <si>
     <t xml:space="preserve">22.6933975219727</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">22.2670078277588</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4565143585205</t>
+    <t xml:space="preserve">22.4565162658691</t>
   </si>
   <si>
     <t xml:space="preserve">22.5986442565918</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">21.6511116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4142284393311</t>
+    <t xml:space="preserve">21.4142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">20.9878387451172</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">20.419319152832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6612930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298126220703</t>
+    <t xml:space="preserve">19.6612949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298145294189</t>
   </si>
   <si>
     <t xml:space="preserve">19.9455547332764</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">19.756046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1875267028809</t>
+    <t xml:space="preserve">19.1875286102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.9980220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0453968048096</t>
+    <t xml:space="preserve">19.0453987121582</t>
   </si>
   <si>
     <t xml:space="preserve">18.5526828765869</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">18.3631744384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9273128509521</t>
+    <t xml:space="preserve">17.9273109436035</t>
   </si>
   <si>
     <t xml:space="preserve">18.2305202484131</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">17.7757053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7946529388428</t>
+    <t xml:space="preserve">17.7946548461914</t>
   </si>
   <si>
     <t xml:space="preserve">16.9987297058105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1357650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0927772521973</t>
+    <t xml:space="preserve">18.1357669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0927753448486</t>
   </si>
   <si>
     <t xml:space="preserve">20.0876846313477</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">18.7990398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1547183990479</t>
+    <t xml:space="preserve">18.1547164916992</t>
   </si>
   <si>
     <t xml:space="preserve">18.28737449646</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">18.5147819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.059965133667</t>
+    <t xml:space="preserve">18.0599632263184</t>
   </si>
   <si>
     <t xml:space="preserve">18.2115707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6562023162842</t>
+    <t xml:space="preserve">18.476879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6562042236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.6088275909424</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">20.5140762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5038928985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3092956542969</t>
+    <t xml:space="preserve">22.5038909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3092937469482</t>
   </si>
   <si>
     <t xml:space="preserve">24.1620750427246</t>
@@ -2159,13 +2159,10 @@
     <t xml:space="preserve">23.4040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6883087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1248798370361</t>
+    <t xml:space="preserve">23.6883068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1248779296875</t>
   </si>
   <si>
     <t xml:space="preserve">22.8829040527344</t>
@@ -2186,10 +2183,10 @@
     <t xml:space="preserve">23.4514217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3515796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1671657562256</t>
+    <t xml:space="preserve">24.3515777587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.167163848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
@@ -2237,19 +2234,19 @@
     <t xml:space="preserve">24.2568264007568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0673179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2991123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9201011657715</t>
+    <t xml:space="preserve">24.0673198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2991104125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9200992584229</t>
   </si>
   <si>
     <t xml:space="preserve">24.825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7305927276611</t>
+    <t xml:space="preserve">24.7305908203125</t>
   </si>
   <si>
     <t xml:space="preserve">24.3989562988281</t>
@@ -2258,7 +2255,7 @@
     <t xml:space="preserve">24.5884628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.493709564209</t>
+    <t xml:space="preserve">24.4937076568604</t>
   </si>
   <si>
     <t xml:space="preserve">25.0148506164551</t>
@@ -2270,7 +2267,7 @@
     <t xml:space="preserve">24.6358375549316</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5359954833984</t>
+    <t xml:space="preserve">25.5359935760498</t>
   </si>
   <si>
     <t xml:space="preserve">25.772876739502</t>
@@ -2282,13 +2279,13 @@
     <t xml:space="preserve">23.5935535430908</t>
   </si>
   <si>
-    <t xml:space="preserve">23.546178817749</t>
+    <t xml:space="preserve">23.5461769104004</t>
   </si>
   <si>
     <t xml:space="preserve">23.1197872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2619152069092</t>
+    <t xml:space="preserve">23.2619171142578</t>
   </si>
   <si>
     <t xml:space="preserve">22.9776573181152</t>
@@ -2309,7 +2306,7 @@
     <t xml:space="preserve">23.7830600738525</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3194770812988</t>
+    <t xml:space="preserve">21.3194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">22.6460208892822</t>
@@ -2324,7 +2321,7 @@
     <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.483528137207</t>
+    <t xml:space="preserve">26.4835262298584</t>
   </si>
   <si>
     <t xml:space="preserve">26.3887729644775</t>
@@ -33298,7 +33295,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>715</v>
+        <v>548</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33350,7 +33347,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33402,7 +33399,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>715</v>
+        <v>548</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33454,7 +33451,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33506,7 +33503,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33532,7 +33529,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33558,7 +33555,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33584,7 +33581,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33610,7 +33607,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33636,7 +33633,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33662,7 +33659,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33688,7 +33685,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1148" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33714,7 +33711,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33766,7 +33763,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1151" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33792,7 +33789,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33818,7 +33815,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33844,7 +33841,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33870,7 +33867,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33896,7 +33893,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1156" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33974,7 +33971,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34078,7 +34075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34104,7 +34101,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1164" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34130,7 +34127,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34156,7 +34153,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34208,7 +34205,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G1168" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34234,7 +34231,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34260,7 +34257,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34286,7 +34283,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1171" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34312,7 +34309,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34338,7 +34335,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34364,7 +34361,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34390,7 +34387,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34442,7 +34439,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>715</v>
+        <v>548</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34468,7 +34465,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34546,7 +34543,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34572,7 +34569,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34598,7 +34595,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34650,7 +34647,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34702,7 +34699,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34728,7 +34725,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34780,7 +34777,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1190" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34806,7 +34803,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34832,7 +34829,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34858,7 +34855,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34884,7 +34881,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1194" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34910,7 +34907,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G1195" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34936,7 +34933,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34988,7 +34985,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35014,7 +35011,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35040,7 +35037,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35066,7 +35063,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35092,7 +35089,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1202" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35118,7 +35115,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35144,7 +35141,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35170,7 +35167,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35196,7 +35193,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35222,7 +35219,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35248,7 +35245,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35274,7 +35271,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1209" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35300,7 +35297,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35326,7 +35323,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35352,7 +35349,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G1212" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35378,7 +35375,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35430,7 +35427,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35456,7 +35453,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>715</v>
+        <v>548</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35482,7 +35479,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35508,7 +35505,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35534,7 +35531,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1219" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35560,7 +35557,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35586,7 +35583,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1221" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35612,7 +35609,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1222" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35638,7 +35635,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35664,7 +35661,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1224" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35690,7 +35687,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G1225" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35716,7 +35713,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35742,7 +35739,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35768,7 +35765,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1228" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35794,7 +35791,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35820,7 +35817,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1230" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35846,7 +35843,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35872,7 +35869,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35898,7 +35895,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35924,7 +35921,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1234" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35950,7 +35947,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36028,7 +36025,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36080,7 +36077,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36132,7 +36129,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36158,7 +36155,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36184,7 +36181,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1244" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36210,7 +36207,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1245" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36236,7 +36233,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36288,7 +36285,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36340,7 +36337,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36366,7 +36363,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1251" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36392,7 +36389,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36418,7 +36415,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1253" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36444,7 +36441,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36470,7 +36467,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36496,7 +36493,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1256" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36522,7 +36519,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36548,7 +36545,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36574,7 +36571,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>715</v>
+        <v>548</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36652,7 +36649,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36678,7 +36675,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36704,7 +36701,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1264" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36730,7 +36727,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1265" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36756,7 +36753,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36782,7 +36779,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1267" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36808,7 +36805,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1268" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36834,7 +36831,7 @@
         <v>27.1395435333252</v>
       </c>
       <c r="G1269" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36860,7 +36857,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1270" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36886,7 +36883,7 @@
         <v>27.285192489624</v>
       </c>
       <c r="G1271" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36912,7 +36909,7 @@
         <v>26.8482418060303</v>
       </c>
       <c r="G1272" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36938,7 +36935,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36964,7 +36961,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1274" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36990,7 +36987,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1275" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37016,7 +37013,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1276" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37042,7 +37039,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1277" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37068,7 +37065,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37094,7 +37091,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37120,7 +37117,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1280" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37146,7 +37143,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1281" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37172,7 +37169,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1282" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37198,7 +37195,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37224,7 +37221,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37250,7 +37247,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1285" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37276,7 +37273,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37302,7 +37299,7 @@
         <v>26.5569400787354</v>
       </c>
       <c r="G1287" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37328,7 +37325,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37354,7 +37351,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37380,7 +37377,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37406,7 +37403,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37432,7 +37429,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1292" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37458,7 +37455,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1293" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37484,7 +37481,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1294" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37510,7 +37507,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37536,7 +37533,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1296" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37562,7 +37559,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1297" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37588,7 +37585,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37614,7 +37611,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G1299" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37640,7 +37637,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1300" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37666,7 +37663,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37692,7 +37689,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37718,7 +37715,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1303" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37744,7 +37741,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1304" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37770,7 +37767,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37796,7 +37793,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1306" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37822,7 +37819,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37848,7 +37845,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1308" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37874,7 +37871,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37900,7 +37897,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1310" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37926,7 +37923,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1311" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37952,7 +37949,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1312" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37978,7 +37975,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38004,7 +38001,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38030,7 +38027,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38056,7 +38053,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38082,7 +38079,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38108,7 +38105,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38134,7 +38131,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1319" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38160,7 +38157,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1320" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38186,7 +38183,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38212,7 +38209,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38238,7 +38235,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38264,7 +38261,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38290,7 +38287,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38316,7 +38313,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38342,7 +38339,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38368,7 +38365,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38394,7 +38391,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38420,7 +38417,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38446,7 +38443,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38472,7 +38469,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1332" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38498,7 +38495,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38524,7 +38521,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1334" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38550,7 +38547,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1335" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38576,7 +38573,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38602,7 +38599,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38628,7 +38625,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1338" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38654,7 +38651,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38680,7 +38677,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38706,7 +38703,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38732,7 +38729,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1342" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38758,7 +38755,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38784,7 +38781,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1344" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38810,7 +38807,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38836,7 +38833,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1346" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38862,7 +38859,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1347" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38888,7 +38885,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1348" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38914,7 +38911,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G1349" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38940,7 +38937,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38966,7 +38963,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38992,7 +38989,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1352" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39018,7 +39015,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1353" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39044,7 +39041,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1354" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39070,7 +39067,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1355" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39096,7 +39093,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1356" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39122,7 +39119,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1357" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39148,7 +39145,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1358" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39174,7 +39171,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1359" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39200,7 +39197,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1360" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39226,7 +39223,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39252,7 +39249,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1362" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39278,7 +39275,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39304,7 +39301,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1364" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39330,7 +39327,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39356,7 +39353,7 @@
         <v>19.759916305542</v>
       </c>
       <c r="G1366" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39382,7 +39379,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -39408,7 +39405,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39434,7 +39431,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -39460,7 +39457,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1370" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39486,7 +39483,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G1371" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39512,7 +39509,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39538,7 +39535,7 @@
         <v>18.1966018676758</v>
       </c>
       <c r="G1373" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39564,7 +39561,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39590,7 +39587,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G1375" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39616,7 +39613,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1376" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39642,7 +39639,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39668,7 +39665,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39694,7 +39691,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1379" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39720,7 +39717,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1380" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39746,7 +39743,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1381" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39772,7 +39769,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1382" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39798,7 +39795,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1383" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39824,7 +39821,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -39850,7 +39847,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1385" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -39876,7 +39873,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G1386" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39902,7 +39899,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39928,7 +39925,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1388" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39954,7 +39951,7 @@
         <v>20.25</v>
       </c>
       <c r="G1389" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39980,7 +39977,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40006,7 +40003,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40032,7 +40029,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1392" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40058,7 +40055,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40084,7 +40081,7 @@
         <v>22.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40110,7 +40107,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1395" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40136,7 +40133,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40162,7 +40159,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40188,7 +40185,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1398" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40214,7 +40211,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40240,7 +40237,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40266,7 +40263,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1401" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40292,7 +40289,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40318,7 +40315,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1403" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40344,7 +40341,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1404" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40370,7 +40367,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1405" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40396,7 +40393,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40422,7 +40419,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1407" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40448,7 +40445,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40474,7 +40471,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40500,7 +40497,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40526,7 +40523,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40552,7 +40549,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40578,7 +40575,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40604,7 +40601,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40630,7 +40627,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40656,7 +40653,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40682,7 +40679,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -40708,7 +40705,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40734,7 +40731,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40760,7 +40757,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40786,7 +40783,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1421" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40812,7 +40809,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40838,7 +40835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -40864,7 +40861,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1424" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40890,7 +40887,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1425" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40916,7 +40913,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1426" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -40942,7 +40939,7 @@
         <v>22.5</v>
       </c>
       <c r="G1427" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40968,7 +40965,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40994,7 +40991,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41020,7 +41017,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41046,7 +41043,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1431" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41072,7 +41069,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41098,7 +41095,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41124,7 +41121,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1434" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41150,7 +41147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41176,7 +41173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1436" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41202,7 +41199,7 @@
         <v>22.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41228,7 +41225,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41254,7 +41251,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41280,7 +41277,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41306,7 +41303,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41332,7 +41329,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1442" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41358,7 +41355,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1443" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41384,7 +41381,7 @@
         <v>22.75</v>
       </c>
       <c r="G1444" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41410,7 +41407,7 @@
         <v>22.5</v>
       </c>
       <c r="G1445" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41436,7 +41433,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41462,7 +41459,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41488,7 +41485,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41514,7 +41511,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41540,7 +41537,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1450" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41566,7 +41563,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41592,7 +41589,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41618,7 +41615,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41644,7 +41641,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41670,7 +41667,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1455" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41696,7 +41693,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41722,7 +41719,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41748,7 +41745,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41774,7 +41771,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1459" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41800,7 +41797,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1460" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41826,7 +41823,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41852,7 +41849,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -41878,7 +41875,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -41904,7 +41901,7 @@
         <v>20</v>
       </c>
       <c r="G1464" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -41930,7 +41927,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1465" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -41956,7 +41953,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1466" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -41982,7 +41979,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1467" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42008,7 +42005,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42034,7 +42031,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42060,7 +42057,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42086,7 +42083,7 @@
         <v>19.5</v>
       </c>
       <c r="G1471" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42112,7 +42109,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42138,7 +42135,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42164,7 +42161,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1474" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42190,7 +42187,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1475" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42216,7 +42213,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42242,7 +42239,7 @@
         <v>21</v>
       </c>
       <c r="G1477" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42268,7 +42265,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42294,7 +42291,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42320,7 +42317,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1480" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42346,7 +42343,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42372,7 +42369,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1482" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42398,7 +42395,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42424,7 +42421,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1484" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42450,7 +42447,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1485" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42476,7 +42473,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42502,7 +42499,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42528,7 +42525,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1488" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42554,7 +42551,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42580,7 +42577,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42606,7 +42603,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42632,7 +42629,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42658,7 +42655,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1493" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42684,7 +42681,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42710,7 +42707,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42736,7 +42733,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1496" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42762,7 +42759,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42788,7 +42785,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1498" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42814,7 +42811,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42840,7 +42837,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -42866,7 +42863,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42892,7 +42889,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -42918,7 +42915,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -42944,7 +42941,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1504" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -42970,7 +42967,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42996,7 +42993,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43022,7 +43019,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43048,7 +43045,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43074,7 +43071,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43100,7 +43097,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1510" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43126,7 +43123,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1511" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43152,7 +43149,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43178,7 +43175,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1513" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43204,7 +43201,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1514" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43230,7 +43227,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43256,7 +43253,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1516" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43282,7 +43279,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1517" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43308,7 +43305,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43334,7 +43331,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1519" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43360,7 +43357,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43386,7 +43383,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1521" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43412,7 +43409,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43438,7 +43435,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43464,7 +43461,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43490,7 +43487,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1525" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43516,7 +43513,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43542,7 +43539,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1527" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43568,7 +43565,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43594,7 +43591,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43620,7 +43617,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43646,7 +43643,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1531" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43672,7 +43669,7 @@
         <v>17</v>
       </c>
       <c r="G1532" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43698,7 +43695,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43724,7 +43721,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43750,7 +43747,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43776,7 +43773,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43802,7 +43799,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1537" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43828,7 +43825,7 @@
         <v>17.5</v>
       </c>
       <c r="G1538" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43854,7 +43851,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43880,7 +43877,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43906,7 +43903,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -43932,7 +43929,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43958,7 +43955,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43984,7 +43981,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1544" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44010,7 +44007,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1545" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44036,7 +44033,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44062,7 +44059,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44088,7 +44085,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1548" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44114,7 +44111,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1549" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44140,7 +44137,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1550" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44166,7 +44163,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1551" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44192,7 +44189,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1552" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44218,7 +44215,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44244,7 +44241,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44270,7 +44267,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44296,7 +44293,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1556" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44322,7 +44319,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44348,7 +44345,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1558" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44374,7 +44371,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1559" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44400,7 +44397,7 @@
         <v>17</v>
       </c>
       <c r="G1560" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44426,7 +44423,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44452,7 +44449,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44478,7 +44475,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44504,7 +44501,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44530,7 +44527,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1565" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44556,7 +44553,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1566" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44582,7 +44579,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44608,7 +44605,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44634,7 +44631,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1569" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44660,7 +44657,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44686,7 +44683,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44712,7 +44709,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44738,7 +44735,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44764,7 +44761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44790,7 +44787,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44816,7 +44813,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44842,7 +44839,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1577" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44868,7 +44865,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44894,7 +44891,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44920,7 +44917,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1580" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44946,7 +44943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1581" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44972,7 +44969,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1582" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -44998,7 +44995,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45024,7 +45021,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1584" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45050,7 +45047,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1585" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45076,7 +45073,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1586" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45102,7 +45099,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1587" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45128,7 +45125,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45154,7 +45151,7 @@
         <v>17</v>
       </c>
       <c r="G1589" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45180,7 +45177,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45206,7 +45203,7 @@
         <v>17</v>
       </c>
       <c r="G1591" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45232,7 +45229,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1592" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45258,7 +45255,7 @@
         <v>17</v>
       </c>
       <c r="G1593" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45284,7 +45281,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45310,7 +45307,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45336,7 +45333,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45362,7 +45359,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1597" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45388,7 +45385,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1598" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45414,7 +45411,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45440,7 +45437,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1600" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45466,7 +45463,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1601" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45492,7 +45489,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1602" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45518,7 +45515,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1603" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45544,7 +45541,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1604" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45570,7 +45567,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45596,7 +45593,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1606" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45622,7 +45619,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1607" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45648,7 +45645,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1608" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45674,7 +45671,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45700,7 +45697,7 @@
         <v>19.5</v>
       </c>
       <c r="G1610" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45726,7 +45723,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1611" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45752,7 +45749,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45778,7 +45775,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45804,7 +45801,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45830,7 +45827,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45856,7 +45853,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1616" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45882,7 +45879,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1617" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45908,7 +45905,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45934,7 +45931,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1619" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45960,7 +45957,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1620" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45986,7 +45983,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46012,7 +46009,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46038,7 +46035,7 @@
         <v>19</v>
       </c>
       <c r="G1623" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46064,7 +46061,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46090,7 +46087,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1625" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46116,7 +46113,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1626" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46142,7 +46139,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1627" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46168,7 +46165,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1628" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46194,7 +46191,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46220,7 +46217,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46246,7 +46243,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46272,7 +46269,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46298,7 +46295,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1633" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46324,7 +46321,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46350,7 +46347,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46376,7 +46373,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46402,7 +46399,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1637" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46428,7 +46425,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46454,7 +46451,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1639" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46480,7 +46477,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1640" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46506,7 +46503,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1641" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46532,7 +46529,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46558,7 +46555,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1643" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46584,7 +46581,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46610,7 +46607,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46636,7 +46633,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1646" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46662,7 +46659,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46688,7 +46685,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1648" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46714,7 +46711,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1649" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46740,7 +46737,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1650" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46766,7 +46763,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1651" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46792,7 +46789,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46818,7 +46815,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1653" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46844,7 +46841,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1654" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46870,7 +46867,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46896,7 +46893,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46922,7 +46919,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46948,7 +46945,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46974,7 +46971,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47000,7 +46997,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1660" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47026,7 +47023,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1661" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47052,7 +47049,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47078,7 +47075,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1663" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47104,7 +47101,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1664" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47130,7 +47127,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47156,7 +47153,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1666" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47182,7 +47179,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1667" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47208,7 +47205,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1668" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47234,7 +47231,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1669" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47260,7 +47257,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1670" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47286,7 +47283,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1671" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47312,7 +47309,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1672" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47338,7 +47335,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1673" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47364,7 +47361,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1674" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47390,7 +47387,7 @@
         <v>18</v>
       </c>
       <c r="G1675" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47416,7 +47413,7 @@
         <v>17.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47442,7 +47439,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47468,7 +47465,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1678" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47494,7 +47491,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1679" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47520,7 +47517,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47546,7 +47543,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47572,7 +47569,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47598,7 +47595,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1683" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47624,7 +47621,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47650,7 +47647,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47676,7 +47673,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1686" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47702,7 +47699,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1687" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47728,7 +47725,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47754,7 +47751,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1689" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47780,7 +47777,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1690" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47806,7 +47803,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47832,7 +47829,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47858,7 +47855,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47884,7 +47881,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1694" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47910,7 +47907,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47936,7 +47933,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1696" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47962,7 +47959,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47988,7 +47985,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48014,7 +48011,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48040,7 +48037,7 @@
         <v>21.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48066,7 +48063,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1701" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48092,7 +48089,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48118,7 +48115,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1703" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48144,7 +48141,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48170,7 +48167,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48196,7 +48193,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48222,7 +48219,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48248,7 +48245,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48274,7 +48271,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1709" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48300,7 +48297,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48326,7 +48323,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48352,7 +48349,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48378,7 +48375,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48404,7 +48401,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48430,7 +48427,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48456,7 +48453,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1716" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48482,7 +48479,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48508,7 +48505,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48534,7 +48531,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1719" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48560,7 +48557,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48586,7 +48583,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1721" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48612,7 +48609,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1722" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48638,7 +48635,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1723" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48664,7 +48661,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48690,7 +48687,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1725" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48716,7 +48713,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1726" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48742,7 +48739,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1727" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48768,7 +48765,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1728" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48794,7 +48791,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48820,7 +48817,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1730" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48846,7 +48843,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48872,7 +48869,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48898,7 +48895,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1733" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48924,7 +48921,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48950,7 +48947,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1735" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48976,7 +48973,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49002,7 +48999,7 @@
         <v>15.5</v>
       </c>
       <c r="G1737" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49028,7 +49025,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1738" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49054,7 +49051,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1739" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49080,7 +49077,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49106,7 +49103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1741" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49132,7 +49129,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49158,7 +49155,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49184,7 +49181,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1744" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49210,7 +49207,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1745" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49236,7 +49233,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1746" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49262,7 +49259,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49288,7 +49285,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49314,7 +49311,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1749" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49340,7 +49337,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1750" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49366,7 +49363,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1751" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49392,7 +49389,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1752" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49418,7 +49415,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1753" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49444,7 +49441,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49470,7 +49467,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1755" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49496,7 +49493,7 @@
         <v>18.5</v>
       </c>
       <c r="G1756" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49522,7 +49519,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1757" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49548,7 +49545,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49574,7 +49571,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49600,7 +49597,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1760" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49626,7 +49623,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49652,7 +49649,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49678,7 +49675,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49704,7 +49701,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49730,7 +49727,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1765" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49756,7 +49753,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49782,7 +49779,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49808,7 +49805,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49834,7 +49831,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1769" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49860,7 +49857,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49886,7 +49883,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49912,7 +49909,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49938,7 +49935,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49964,7 +49961,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49990,7 +49987,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1775" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50016,7 +50013,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50042,7 +50039,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50068,7 +50065,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50094,7 +50091,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1779" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50120,7 +50117,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50146,7 +50143,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1781" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50172,7 +50169,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1782" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50198,7 +50195,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50224,7 +50221,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50250,7 +50247,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50276,7 +50273,7 @@
         <v>22.5</v>
       </c>
       <c r="G1786" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50302,7 +50299,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1787" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50328,7 +50325,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50354,7 +50351,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50380,7 +50377,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50406,7 +50403,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1791" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50432,7 +50429,7 @@
         <v>23.75</v>
       </c>
       <c r="G1792" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50458,7 +50455,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50484,7 +50481,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1794" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50510,7 +50507,7 @@
         <v>22.5</v>
       </c>
       <c r="G1795" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50536,7 +50533,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1796" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50562,7 +50559,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50588,7 +50585,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50614,7 +50611,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50640,7 +50637,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50666,7 +50663,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50692,7 +50689,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1802" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50718,7 +50715,7 @@
         <v>22.75</v>
       </c>
       <c r="G1803" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50744,7 +50741,7 @@
         <v>23.75</v>
       </c>
       <c r="G1804" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50770,7 +50767,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50796,7 +50793,7 @@
         <v>23.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50822,7 +50819,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1807" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50848,7 +50845,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50874,7 +50871,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1809" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50900,7 +50897,7 @@
         <v>23.5</v>
       </c>
       <c r="G1810" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50926,7 +50923,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50952,7 +50949,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50978,7 +50975,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51004,7 +51001,7 @@
         <v>23.5</v>
       </c>
       <c r="G1814" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51030,7 +51027,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1815" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51056,7 +51053,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1816" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51082,7 +51079,7 @@
         <v>22.25</v>
       </c>
       <c r="G1817" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51108,7 +51105,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1818" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51134,7 +51131,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51160,7 +51157,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51186,7 +51183,7 @@
         <v>25</v>
       </c>
       <c r="G1821" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51212,7 +51209,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G1822" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51238,7 +51235,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51264,7 +51261,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1824" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51290,7 +51287,7 @@
         <v>25</v>
       </c>
       <c r="G1825" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51316,7 +51313,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51342,7 +51339,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51368,7 +51365,7 @@
         <v>26</v>
       </c>
       <c r="G1828" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51394,7 +51391,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1829" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51420,7 +51417,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51446,7 +51443,7 @@
         <v>25</v>
       </c>
       <c r="G1831" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51472,7 +51469,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51498,7 +51495,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51524,7 +51521,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51550,7 +51547,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1835" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51576,7 +51573,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51602,7 +51599,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1837" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51628,7 +51625,7 @@
         <v>22.75</v>
       </c>
       <c r="G1838" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51654,7 +51651,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51680,7 +51677,7 @@
         <v>22.5</v>
       </c>
       <c r="G1840" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51706,7 +51703,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51732,7 +51729,7 @@
         <v>23.5</v>
       </c>
       <c r="G1842" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51758,7 +51755,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1843" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51784,7 +51781,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1844" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51810,7 +51807,7 @@
         <v>23</v>
       </c>
       <c r="G1845" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51836,7 +51833,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51862,7 +51859,7 @@
         <v>23</v>
       </c>
       <c r="G1847" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51888,7 +51885,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51914,7 +51911,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51940,7 +51937,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51966,7 +51963,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1851" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51992,7 +51989,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52018,7 +52015,7 @@
         <v>23.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52044,7 +52041,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52070,7 +52067,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1855" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52096,7 +52093,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52122,7 +52119,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52148,7 +52145,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52174,7 +52171,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1859" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52200,7 +52197,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1860" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52226,7 +52223,7 @@
         <v>23</v>
       </c>
       <c r="G1861" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52252,7 +52249,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52278,7 +52275,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1863" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52304,7 +52301,7 @@
         <v>22</v>
       </c>
       <c r="G1864" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52330,7 +52327,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1865" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52356,7 +52353,7 @@
         <v>21</v>
       </c>
       <c r="G1866" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52382,7 +52379,7 @@
         <v>21.5</v>
       </c>
       <c r="G1867" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52408,7 +52405,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52434,7 +52431,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1869" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52460,7 +52457,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52486,7 +52483,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1871" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52512,7 +52509,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1872" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52538,7 +52535,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52564,7 +52561,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1874" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52590,7 +52587,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52616,7 +52613,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1876" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52642,7 +52639,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1877" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52650,7 +52647,7 @@
     </row>
     <row r="1878">
       <c r="A1878" s="1" t="n">
-        <v>45958.6909953704</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1878" t="n">
         <v>18327</v>
@@ -52668,9 +52665,35 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1878" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H1878" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="1" t="n">
+        <v>45959.6911111111</v>
+      </c>
+      <c r="B1879" t="n">
+        <v>37139</v>
+      </c>
+      <c r="C1879" t="n">
+        <v>22.9500007629395</v>
+      </c>
+      <c r="D1879" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="E1879" t="n">
+        <v>22.9500007629395</v>
+      </c>
+      <c r="F1879" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="G1879" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H1879" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="1165">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125925064087</t>
+    <t xml:space="preserve">7.58125877380371</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099319458008</t>
+    <t xml:space="preserve">7.90288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099224090576</t>
   </si>
   <si>
     <t xml:space="preserve">7.71910047531128</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">7.68969297409058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87348127365112</t>
+    <t xml:space="preserve">7.87348079681396</t>
   </si>
   <si>
     <t xml:space="preserve">7.96721267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67407035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97640180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44433641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.302818775177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520322799683</t>
+    <t xml:space="preserve">7.67407083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97640085220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44433546066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520370483398</t>
   </si>
   <si>
     <t xml:space="preserve">7.46639108657837</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">7.57206869125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44341802597046</t>
+    <t xml:space="preserve">7.44341850280762</t>
   </si>
   <si>
     <t xml:space="preserve">7.52612161636353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54450130462646</t>
+    <t xml:space="preserve">7.54450082778931</t>
   </si>
   <si>
     <t xml:space="preserve">7.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85694026947021</t>
+    <t xml:space="preserve">7.8018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85694122314453</t>
   </si>
   <si>
     <t xml:space="preserve">7.92218542098999</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">7.86612844467163</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01959323883057</t>
+    <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
     <t xml:space="preserve">7.81466913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76504611968994</t>
+    <t xml:space="preserve">7.7650465965271</t>
   </si>
   <si>
     <t xml:space="preserve">7.85142707824707</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">7.69336843490601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79261445999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74666738510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910293579102</t>
+    <t xml:space="preserve">7.7926139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74666833877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.56379842758179</t>
@@ -152,28 +152,28 @@
     <t xml:space="preserve">8.06002616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11424255371094</t>
+    <t xml:space="preserve">8.11424350738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.30354499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46343994140625</t>
+    <t xml:space="preserve">8.46344089508057</t>
   </si>
   <si>
     <t xml:space="preserve">8.48641300201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75382614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966911315918</t>
+    <t xml:space="preserve">8.75382518768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966815948486</t>
   </si>
   <si>
     <t xml:space="preserve">8.60128116607666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28884220123291</t>
+    <t xml:space="preserve">8.28884029388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.25208473205566</t>
@@ -182,34 +182,34 @@
     <t xml:space="preserve">8.46987342834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3623571395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45425319671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7115535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74831199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6159839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66560745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79426002502441</t>
+    <t xml:space="preserve">8.36235809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45425224304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71155261993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74831295013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61598491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66560649871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7942590713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86869430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11588859558105</t>
+    <t xml:space="preserve">8.86869335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11588764190674</t>
   </si>
   <si>
     <t xml:space="preserve">9.14345645904541</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">9.09751033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11680698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091243743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18572807312012</t>
+    <t xml:space="preserve">9.11680889129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091339111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18572902679443</t>
   </si>
   <si>
     <t xml:space="preserve">9.06167030334473</t>
@@ -236,49 +236,49 @@
     <t xml:space="preserve">9.02399349212646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76577091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99366855621338</t>
+    <t xml:space="preserve">8.76577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9936695098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.04237365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90177440643311</t>
+    <t xml:space="preserve">8.90177536010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.67112255096436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50755023956299</t>
+    <t xml:space="preserve">8.50754928588867</t>
   </si>
   <si>
     <t xml:space="preserve">7.98191547393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30630302429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40830326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54614639282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5920934677124</t>
+    <t xml:space="preserve">8.30630207061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40830421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54614543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59209251403809</t>
   </si>
   <si>
     <t xml:space="preserve">8.63803958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80804443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126218795776</t>
+    <t xml:space="preserve">8.80804347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126171112061</t>
   </si>
   <si>
     <t xml:space="preserve">7.92126560211182</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.34214019775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7749605178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77771854400635</t>
+    <t xml:space="preserve">8.77496147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77771949768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.75474548339844</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">8.50571155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59944438934326</t>
+    <t xml:space="preserve">8.59944343566895</t>
   </si>
   <si>
     <t xml:space="preserve">8.70144653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57739067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39268207550049</t>
+    <t xml:space="preserve">8.57738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3926830291748</t>
   </si>
   <si>
     <t xml:space="preserve">8.34122276306152</t>
@@ -326,70 +326,70 @@
     <t xml:space="preserve">8.04164695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0866756439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18867683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54890251159668</t>
+    <t xml:space="preserve">8.08667469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18867778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.548903465271</t>
   </si>
   <si>
     <t xml:space="preserve">8.33479022979736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50938701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03869724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9743709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664352416992</t>
+    <t xml:space="preserve">8.5093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9210729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97437000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664257049561</t>
   </si>
   <si>
     <t xml:space="preserve">9.1526460647583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84939765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07913017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8558292388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23370456695557</t>
+    <t xml:space="preserve">8.84939670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07913112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85582828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23370552062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.27046394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33754730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20062446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40370750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27414035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29803276062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50019931793213</t>
+    <t xml:space="preserve">8.33754634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20062351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40370845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27413940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29803371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50019836425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.43587207794189</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">8.22451591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35408592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22084045410156</t>
+    <t xml:space="preserve">8.35408496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22083950042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.15283966064453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39911460876465</t>
+    <t xml:space="preserve">8.39911556243896</t>
   </si>
   <si>
     <t xml:space="preserve">8.42668342590332</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">8.48365592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70971584320068</t>
+    <t xml:space="preserve">8.709716796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.77128601074219</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">8.72074413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10026550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06534671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89809894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97712898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05156135559082</t>
+    <t xml:space="preserve">9.100266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06534576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89809799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97712993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05156230926514</t>
   </si>
   <si>
     <t xml:space="preserve">9.2353515625</t>
@@ -449,91 +449,91 @@
     <t xml:space="preserve">9.20594501495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36216259002686</t>
+    <t xml:space="preserve">9.36216354370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.3952465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.610276222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6488733291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69482135772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59373760223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64336204528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989288330078</t>
+    <t xml:space="preserve">9.61027717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64887428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69482040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5937385559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64336013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31989192962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.61763000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49265480041504</t>
+    <t xml:space="preserve">9.49265384674072</t>
   </si>
   <si>
     <t xml:space="preserve">9.5110330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28497314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46325016021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33092021942139</t>
+    <t xml:space="preserve">9.28497219085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46324825286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3309211730957</t>
   </si>
   <si>
     <t xml:space="preserve">9.12875461578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26291847229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14713287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06075191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94129085540771</t>
+    <t xml:space="preserve">9.26291942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14713382720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06075286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9412899017334</t>
   </si>
   <si>
     <t xml:space="preserve">8.37797927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7602596282959</t>
+    <t xml:space="preserve">8.76025867462158</t>
   </si>
   <si>
     <t xml:space="preserve">9.00653457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18940544128418</t>
+    <t xml:space="preserve">9.18940448760986</t>
   </si>
   <si>
     <t xml:space="preserve">8.96885776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10669994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4467077255249</t>
+    <t xml:space="preserve">9.1067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44670677185059</t>
   </si>
   <si>
     <t xml:space="preserve">9.39157104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74076747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46508693695068</t>
+    <t xml:space="preserve">9.74076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46508598327637</t>
   </si>
   <si>
     <t xml:space="preserve">9.53859996795654</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">9.75914669036865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68563175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90617656707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99807071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79590606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92455768585205</t>
+    <t xml:space="preserve">9.68563270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90617752075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79590511322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455673217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.81428337097168</t>
@@ -566,40 +566,40 @@
     <t xml:space="preserve">9.94293594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0715866088867</t>
+    <t xml:space="preserve">10.0715856552124</t>
   </si>
   <si>
     <t xml:space="preserve">10.108344078064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66725444793701</t>
+    <t xml:space="preserve">9.6672534942627</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752494812012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86941814422607</t>
+    <t xml:space="preserve">9.83266353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86941909790039</t>
   </si>
   <si>
     <t xml:space="preserve">10.1451025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1634798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105115890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348300933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.016450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267213821411</t>
+    <t xml:space="preserve">10.1634788513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.310510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348291397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267223358154</t>
   </si>
   <si>
     <t xml:space="preserve">10.5126781463623</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">10.4207830429077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4759206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391622543335</t>
+    <t xml:space="preserve">10.4759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.3288898468018</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">9.97969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821956634521</t>
+    <t xml:space="preserve">9.85104084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821937561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.94108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88544750213623</t>
+    <t xml:space="preserve">9.88544654846191</t>
   </si>
   <si>
     <t xml:space="preserve">9.92253875732422</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">9.99672603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.200740814209</t>
+    <t xml:space="preserve">10.2007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">10.2192878723145</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">10.0894603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90399360656738</t>
+    <t xml:space="preserve">9.90399265289307</t>
   </si>
   <si>
     <t xml:space="preserve">10.0523672103882</t>
@@ -674,67 +674,67 @@
     <t xml:space="preserve">10.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4047565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3862104415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3676633834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82980632781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3120231628418</t>
+    <t xml:space="preserve">10.4047555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4233045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3862113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3676624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82980728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3120241165161</t>
   </si>
   <si>
     <t xml:space="preserve">10.033821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81126022338867</t>
+    <t xml:space="preserve">9.81125926971436</t>
   </si>
   <si>
     <t xml:space="preserve">10.070915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79271221160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2563819885254</t>
+    <t xml:space="preserve">10.1080083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7927131652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2563810348511</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789438247681</t>
+    <t xml:space="preserve">10.4789428710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651763916016</t>
+    <t xml:space="preserve">11.1651754379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.6103000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062843322754</t>
+    <t xml:space="preserve">11.4062852859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.536111831665</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6288471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175657272339</t>
+    <t xml:space="preserve">11.6288461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175647735596</t>
   </si>
   <si>
     <t xml:space="preserve">11.9626884460449</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">12.4449052810669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.593279838562</t>
+    <t xml:space="preserve">12.5932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">12.1852502822876</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">11.5732049942017</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5917530059814</t>
+    <t xml:space="preserve">11.5917520523071</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401275634766</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">11.4804706573486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9255933761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.11106300354</t>
+    <t xml:space="preserve">11.925594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1110620498657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1667032241821</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">12.2223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5190925598145</t>
+    <t xml:space="preserve">12.5190935134888</t>
   </si>
   <si>
     <t xml:space="preserve">12.686014175415</t>
@@ -788,70 +788,70 @@
     <t xml:space="preserve">12.9827632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2609643936157</t>
+    <t xml:space="preserve">13.26096534729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5020723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0584774017334</t>
+    <t xml:space="preserve">13.5020742416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.058479309082</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649801254272</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053251266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125898361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3892650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3521709442139</t>
+    <t xml:space="preserve">13.2053241729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3892641067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3521718978882</t>
   </si>
   <si>
     <t xml:space="preserve">12.2965307235718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.407811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2037963867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.277982711792</t>
+    <t xml:space="preserve">12.4078121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2037954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2779846191406</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9101028442383</t>
+    <t xml:space="preserve">13.9101037979126</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093389511108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.168231010437</t>
+    <t xml:space="preserve">13.1682300567627</t>
   </si>
   <si>
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045602798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561857223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3707189559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7787485122681</t>
+    <t xml:space="preserve">12.7045612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3707180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7787475585938</t>
   </si>
   <si>
     <t xml:space="preserve">12.8158416748047</t>
@@ -863,49 +863,49 @@
     <t xml:space="preserve">13.0940446853638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0754957199097</t>
+    <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
     <t xml:space="preserve">13.3351526260376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3150768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.463454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4263591766357</t>
+    <t xml:space="preserve">13.0569486618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489191055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3150777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.463451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4263582229614</t>
   </si>
   <si>
     <t xml:space="preserve">11.8514080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2950038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0168018341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909881591797</t>
+    <t xml:space="preserve">11.7772216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2950048446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0168008804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090989112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353479385376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7571468353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3135499954224</t>
+    <t xml:space="preserve">10.7571449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.313549041748</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280813217163</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">11.2764558792114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2208156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3691892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177486419678</t>
+    <t xml:space="preserve">11.2208166122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3691911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095361709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.40322875976562</t>
@@ -932,52 +932,52 @@
     <t xml:space="preserve">8.88391780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55160522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71699905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80973052978516</t>
+    <t xml:space="preserve">9.55160331726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71699810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80973148345947</t>
   </si>
   <si>
     <t xml:space="preserve">8.20695972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24405384063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19768714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53152942657471</t>
+    <t xml:space="preserve">8.24405479431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19768810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53153038024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.43879508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64433670043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77416610717773</t>
+    <t xml:space="preserve">9.64433765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200517654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77416515350342</t>
   </si>
   <si>
     <t xml:space="preserve">10.2934761047363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2378349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71852397918701</t>
+    <t xml:space="preserve">10.2378358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71852493286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.0152750015259</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7015047073364</t>
+    <t xml:space="preserve">10.7015066146851</t>
   </si>
   <si>
     <t xml:space="preserve">11.6844863891602</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">12.4819984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6118268966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7586736679077</t>
+    <t xml:space="preserve">12.6118249893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7586727142334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7246341705322</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.650447845459</t>
+    <t xml:space="preserve">13.6504497528076</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930816650391</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">14.2439451217651</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462368011475</t>
+    <t xml:space="preserve">15.282567024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462377548218</t>
   </si>
   <si>
     <t xml:space="preserve">15.9687967300415</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3938455581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487237930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6148815155029</t>
+    <t xml:space="preserve">15.3938465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6148824691772</t>
   </si>
   <si>
     <t xml:space="preserve">14.4665069580078</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">14.0399293899536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1326637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7988214492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8173694610596</t>
+    <t xml:space="preserve">14.132664680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7988224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8173685073853</t>
   </si>
   <si>
     <t xml:space="preserve">13.6689939498901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0770244598389</t>
+    <t xml:space="preserve">14.0770225524902</t>
   </si>
   <si>
     <t xml:space="preserve">14.318133354187</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">14.5560493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7989616394043</t>
+    <t xml:space="preserve">14.79896068573</t>
   </si>
   <si>
     <t xml:space="preserve">14.8923892974854</t>
@@ -1076,19 +1076,19 @@
     <t xml:space="preserve">14.7802753448486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7615900039673</t>
+    <t xml:space="preserve">14.7615909576416</t>
   </si>
   <si>
     <t xml:space="preserve">15.2660999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2287311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4155855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221559524536</t>
+    <t xml:space="preserve">15.2287302017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.415584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221569061279</t>
   </si>
   <si>
     <t xml:space="preserve">15.0045013427734</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">14.6494770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297609329224</t>
+    <t xml:space="preserve">15.1353034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297618865967</t>
   </si>
   <si>
     <t xml:space="preserve">15.0231876373291</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">14.9484462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813079833984</t>
+    <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
     <t xml:space="preserve">15.5650682449341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1630077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9664897918701</t>
+    <t xml:space="preserve">16.1630096435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9664878845215</t>
   </si>
   <si>
     <t xml:space="preserve">17.6765384674072</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">17.4149398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3962554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7886524200439</t>
+    <t xml:space="preserve">17.3962535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7886543273926</t>
   </si>
   <si>
     <t xml:space="preserve">18.0128784179688</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">18.2744750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6578521728516</t>
+    <t xml:space="preserve">18.3118495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6578540802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9941940307617</t>
+    <t xml:space="preserve">17.9941921234131</t>
   </si>
   <si>
     <t xml:space="preserve">18.6855583190918</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">19.1526966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">18.330530166626</t>
+    <t xml:space="preserve">18.3305320739746</t>
   </si>
   <si>
     <t xml:space="preserve">18.2184181213379</t>
@@ -1205,31 +1205,31 @@
     <t xml:space="preserve">16.9291152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6675148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266687393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4619770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.957465171814</t>
+    <t xml:space="preserve">16.667516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266668319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4619750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9574670791626</t>
   </si>
   <si>
     <t xml:space="preserve">15.378212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5367183685303</t>
+    <t xml:space="preserve">15.7706089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5367202758789</t>
   </si>
   <si>
     <t xml:space="preserve">16.5927772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2938060760498</t>
+    <t xml:space="preserve">16.2938079833984</t>
   </si>
   <si>
     <t xml:space="preserve">16.4246044158936</t>
@@ -1238,22 +1238,22 @@
     <t xml:space="preserve">16.2751216888428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8543720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7048873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3311805725098</t>
+    <t xml:space="preserve">16.8543701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7048892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3311786651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.4993457794189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3685493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3498611450195</t>
+    <t xml:space="preserve">16.3685512542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3498592376709</t>
   </si>
   <si>
     <t xml:space="preserve">16.6862030029297</t>
@@ -1262,22 +1262,22 @@
     <t xml:space="preserve">16.6301441192627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7609462738037</t>
+    <t xml:space="preserve">16.6114597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7609443664551</t>
   </si>
   <si>
     <t xml:space="preserve">16.8170013427734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7983169555664</t>
+    <t xml:space="preserve">16.798318862915</t>
   </si>
   <si>
     <t xml:space="preserve">15.7892971038818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.434271812439</t>
+    <t xml:space="preserve">15.4342708587646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671316146851</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">17.32151222229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5180320739746</t>
+    <t xml:space="preserve">16.5180339813232</t>
   </si>
   <si>
     <t xml:space="preserve">15.6211252212524</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">16.2377510070801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4806652069092</t>
+    <t xml:space="preserve">16.4806613922119</t>
   </si>
   <si>
     <t xml:space="preserve">16.8356895446777</t>
@@ -1313,22 +1313,22 @@
     <t xml:space="preserve">16.4432907104492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9477996826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0785980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.648832321167</t>
+    <t xml:space="preserve">16.9478015899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0786018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6488342285156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8917446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9007625579834</t>
+    <t xml:space="preserve">16.8917427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.900764465332</t>
   </si>
   <si>
     <t xml:space="preserve">18.0876197814941</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">18.0502490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.574089050293</t>
+    <t xml:space="preserve">16.5740909576416</t>
   </si>
   <si>
     <t xml:space="preserve">16.742259979248</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">16.3124923706055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0225448608398</t>
+    <t xml:space="preserve">17.0225429534912</t>
   </si>
   <si>
     <t xml:space="preserve">16.0695781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8453559875488</t>
+    <t xml:space="preserve">15.8453540802002</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519273757935</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">15.6024408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0135231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9014091491699</t>
+    <t xml:space="preserve">16.0135250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9014072418213</t>
   </si>
   <si>
     <t xml:space="preserve">15.9761524200439</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186786651611</t>
+    <t xml:space="preserve">15.3595275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186777114868</t>
   </si>
   <si>
     <t xml:space="preserve">14.1636533737183</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">15.6398105621338</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6771812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5276985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.471643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.452956199646</t>
+    <t xml:space="preserve">15.6771802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5277004241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145557403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716424942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4529571533203</t>
   </si>
   <si>
     <t xml:space="preserve">15.6584968566895</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">17.1346549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9381351470947</t>
+    <t xml:space="preserve">17.9381370544434</t>
   </si>
   <si>
     <t xml:space="preserve">17.5831089019775</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">17.7699642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1249904632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6391677856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4800148010254</t>
+    <t xml:space="preserve">18.1249885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6391658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.480016708374</t>
   </si>
   <si>
     <t xml:space="preserve">18.0689334869385</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">17.172025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5644245147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6017971038818</t>
+    <t xml:space="preserve">17.5644226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">17.7512798309326</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">19.713264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8066902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4329795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5264053344727</t>
+    <t xml:space="preserve">19.8066921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4329814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5264072418213</t>
   </si>
   <si>
     <t xml:space="preserve">19.9935455322266</t>
@@ -1478,16 +1478,16 @@
     <t xml:space="preserve">20.5541133880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4606876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.273832321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1336879730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9468326568604</t>
+    <t xml:space="preserve">20.4606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2738304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1336860656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.946834564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271175384521</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">21.2081069946289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5818214416504</t>
+    <t xml:space="preserve">21.581823348999</t>
   </si>
   <si>
     <t xml:space="preserve">21.9555320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3015365600586</t>
+    <t xml:space="preserve">21.3015384674072</t>
   </si>
   <si>
     <t xml:space="preserve">20.8343963623047</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0869731903076</t>
+    <t xml:space="preserve">20.0869750976562</t>
   </si>
   <si>
     <t xml:space="preserve">19.7599773406982</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">19.4796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1994094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7350769042969</t>
+    <t xml:space="preserve">19.1994113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7350749969482</t>
   </si>
   <si>
     <t xml:space="preserve">19.9700164794922</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">18.8422985076904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1712188720703</t>
+    <t xml:space="preserve">19.1712169647217</t>
   </si>
   <si>
     <t xml:space="preserve">19.0772399902344</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">18.9362773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1579704284668</t>
+    <t xml:space="preserve">19.6410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832668304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1579723358154</t>
   </si>
   <si>
     <t xml:space="preserve">19.8290557861328</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">18.4757919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">18.776517868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5133819580078</t>
+    <t xml:space="preserve">18.7765159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5133800506592</t>
   </si>
   <si>
     <t xml:space="preserve">18.7953109741211</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">18.6449489593506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0639953613281</t>
+    <t xml:space="preserve">20.0639934539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.3929138183594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8158054351807</t>
+    <t xml:space="preserve">20.8158073425293</t>
   </si>
   <si>
     <t xml:space="preserve">21.2856903076172</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">22.9772682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2122097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.494140625</t>
+    <t xml:space="preserve">23.2122077941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4941425323486</t>
   </si>
   <si>
     <t xml:space="preserve">23.1652240753174</t>
@@ -1652,508 +1652,511 @@
     <t xml:space="preserve">22.8832912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5411262512207</t>
+    <t xml:space="preserve">23.5411243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9302787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7085857391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1314792633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9435272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.909782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7688179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2387008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8495483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8098106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688480377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4339046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3869171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4001636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.635103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9640235900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4808921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5616226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206581115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6555995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3736705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543727874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1182346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2459506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158336639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9170322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0110111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8568019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6218585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1857166290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.138729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1917133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266567230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8025608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8627948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326797485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3796653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2519474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3459243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2182064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.569766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.674840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3591709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3292751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0473480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3066349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1938610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.663745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9905166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3194332122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4736423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4868907928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2989368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0170059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7389259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7013339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8965377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5338764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3254299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9683170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8931369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2165050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9418792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9039745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3923091888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5293464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.813606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2494735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5716342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7800922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5905838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8507995605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9404621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8930854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0775012969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6933975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4565143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0301265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4616069793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6511116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4142284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9878387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7983341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4193210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6612949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9455528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2349052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5665397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0403079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7560482025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9980220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0453987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3631763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9273128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2305221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7188549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3821239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7946548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.087682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7990398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1547183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2873725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5147819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0599632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2115707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.476879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6562023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6088275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5140743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5038890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3092956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.162073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7779693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3566722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4040470123291</t>
   </si>
   <si>
     <t xml:space="preserve">22.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4471530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.870044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555751800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7085857391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1314792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9435253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7688159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.580867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2387008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8495502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8098087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3869171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4001655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.635103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9640235900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4808921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5616226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6555976867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3736705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061847686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5543727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2724437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1182346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2459526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9170322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0110111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8568019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6218585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1857166290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.138729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5206317901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1917152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266567230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4399013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8025608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8627967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3796653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2519474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.34592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2182064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.569766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3591709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3292751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0473480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3066349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1938610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.663745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9905166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3194313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4736423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2989368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0170078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7389259338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7013339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8965377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5338745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3254299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9683170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2165050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9418792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9039745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3923091888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5293464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.813606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2494735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.950647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7800922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5905838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8507995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7509574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8457107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8930854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2771911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0775012969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6933975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2670097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4565143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0301265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4616069793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6511116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4142284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9878387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7983341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4193210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6612949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9455528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2349052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5665397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0403079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7560482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9980220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0453987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3631763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9273128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2305221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7188549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3821239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7946548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.087682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7990398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1547183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2873725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5147819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0599632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.476879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6562023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6088275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5140743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5038890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3092956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.162073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7779693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3566722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4040470123291</t>
   </si>
   <si>
     <t xml:space="preserve">23.6883068084717</t>
@@ -33292,7 +33295,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>547</v>
+        <v>714</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33344,7 +33347,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1135" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33396,7 +33399,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>547</v>
+        <v>714</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33448,7 +33451,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1139" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33500,7 +33503,7 @@
         <v>23.4497299194336</v>
       </c>
       <c r="G1141" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33526,7 +33529,7 @@
         <v>23.3526306152344</v>
       </c>
       <c r="G1142" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33552,7 +33555,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1143" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33578,7 +33581,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1144" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33604,7 +33607,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G1145" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33630,7 +33633,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1146" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33656,7 +33659,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1147" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33682,7 +33685,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1148" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33708,7 +33711,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1149" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33760,7 +33763,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1151" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33786,7 +33789,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G1152" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33812,7 +33815,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1153" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33838,7 +33841,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G1154" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33864,7 +33867,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1155" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33890,7 +33893,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1156" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33968,7 +33971,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1159" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34072,7 +34075,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1163" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34098,7 +34101,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1164" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34124,7 +34127,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G1165" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34150,7 +34153,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1166" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34202,7 +34205,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G1168" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34228,7 +34231,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G1169" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34254,7 +34257,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G1170" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34280,7 +34283,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G1171" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34306,7 +34309,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1172" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34332,7 +34335,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1173" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34358,7 +34361,7 @@
         <v>22.9642276763916</v>
       </c>
       <c r="G1174" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34384,7 +34387,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1175" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34436,7 +34439,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>547</v>
+        <v>714</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34462,7 +34465,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1178" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34540,7 +34543,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1181" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34566,7 +34569,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G1182" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34592,7 +34595,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1183" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34644,7 +34647,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1185" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34696,7 +34699,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1187" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34722,7 +34725,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G1188" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34774,7 +34777,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1190" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34800,7 +34803,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1191" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34826,7 +34829,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1192" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34852,7 +34855,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G1193" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34878,7 +34881,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1194" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34904,7 +34907,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G1195" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34930,7 +34933,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1196" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34982,7 +34985,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1198" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35008,7 +35011,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1199" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35034,7 +35037,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1200" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35060,7 +35063,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1201" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35086,7 +35089,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1202" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35112,7 +35115,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1203" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35138,7 +35141,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1204" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35164,7 +35167,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1205" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35190,7 +35193,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1206" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35216,7 +35219,7 @@
         <v>25.9257888793945</v>
       </c>
       <c r="G1207" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35242,7 +35245,7 @@
         <v>26.1685390472412</v>
       </c>
       <c r="G1208" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35268,7 +35271,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1209" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35294,7 +35297,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1210" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35320,7 +35323,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1211" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35346,7 +35349,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G1212" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35372,7 +35375,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1213" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35424,7 +35427,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1215" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35450,7 +35453,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>547</v>
+        <v>714</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35476,7 +35479,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1217" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35502,7 +35505,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1218" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35528,7 +35531,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1219" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35554,7 +35557,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1220" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35580,7 +35583,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1221" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35606,7 +35609,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1222" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35632,7 +35635,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1223" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35658,7 +35661,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1224" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35684,7 +35687,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G1225" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35710,7 +35713,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1226" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35736,7 +35739,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1227" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35762,7 +35765,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1228" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35788,7 +35791,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1229" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35814,7 +35817,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1230" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35840,7 +35843,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1231" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35866,7 +35869,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1232" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35892,7 +35895,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G1233" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35918,7 +35921,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1234" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35944,7 +35947,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1235" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36022,7 +36025,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1238" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36074,7 +36077,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G1240" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36126,7 +36129,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1242" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36152,7 +36155,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1243" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36178,7 +36181,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1244" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36204,7 +36207,7 @@
         <v>23.1098785400391</v>
       </c>
       <c r="G1245" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36230,7 +36233,7 @@
         <v>22.915678024292</v>
       </c>
       <c r="G1246" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36282,7 +36285,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G1248" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36334,7 +36337,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1250" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36360,7 +36363,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G1251" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36386,7 +36389,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1252" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36412,7 +36415,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1253" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36438,7 +36441,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1254" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36464,7 +36467,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G1255" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36490,7 +36493,7 @@
         <v>23.5468292236328</v>
       </c>
       <c r="G1256" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36516,7 +36519,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G1257" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36542,7 +36545,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G1258" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36568,7 +36571,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>547</v>
+        <v>714</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36646,7 +36649,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1262" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36672,7 +36675,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1263" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36698,7 +36701,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1264" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36724,7 +36727,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G1265" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36750,7 +36753,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1266" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36776,7 +36779,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1267" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36802,7 +36805,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1268" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36828,7 +36831,7 @@
         <v>27.1395435333252</v>
       </c>
       <c r="G1269" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36854,7 +36857,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1270" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36880,7 +36883,7 @@
         <v>27.285192489624</v>
       </c>
       <c r="G1271" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36906,7 +36909,7 @@
         <v>26.8482418060303</v>
       </c>
       <c r="G1272" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36932,7 +36935,7 @@
         <v>26.4598407745361</v>
       </c>
       <c r="G1273" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36958,7 +36961,7 @@
         <v>27.0424423217773</v>
       </c>
       <c r="G1274" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36984,7 +36987,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1275" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37010,7 +37013,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1276" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37036,7 +37039,7 @@
         <v>27.1880931854248</v>
       </c>
       <c r="G1277" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37062,7 +37065,7 @@
         <v>27.3337421417236</v>
       </c>
       <c r="G1278" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37088,7 +37091,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1279" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37114,7 +37117,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1280" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37140,7 +37143,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1281" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37166,7 +37169,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1282" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37192,7 +37195,7 @@
         <v>26.3141899108887</v>
       </c>
       <c r="G1283" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37218,7 +37221,7 @@
         <v>26.071439743042</v>
       </c>
       <c r="G1284" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37244,7 +37247,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1285" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37270,7 +37273,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1286" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37296,7 +37299,7 @@
         <v>26.5569400787354</v>
       </c>
       <c r="G1287" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37322,7 +37325,7 @@
         <v>26.7996921539307</v>
       </c>
       <c r="G1288" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37348,7 +37351,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G1289" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37374,7 +37377,7 @@
         <v>26.6054916381836</v>
       </c>
       <c r="G1290" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37400,7 +37403,7 @@
         <v>26.3627395629883</v>
       </c>
       <c r="G1291" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37426,7 +37429,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1292" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37452,7 +37455,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G1293" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37478,7 +37481,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G1294" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37504,7 +37507,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G1295" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37530,7 +37533,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1296" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37556,7 +37559,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G1297" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37582,7 +37585,7 @@
         <v>25.7315883636475</v>
       </c>
       <c r="G1298" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37608,7 +37611,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G1299" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37634,7 +37637,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1300" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37660,7 +37663,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G1301" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37686,7 +37689,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1302" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37712,7 +37715,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1303" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37738,7 +37741,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1304" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37764,7 +37767,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1305" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37790,7 +37793,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1306" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37816,7 +37819,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1307" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37842,7 +37845,7 @@
         <v>25.1489868164062</v>
       </c>
       <c r="G1308" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37868,7 +37871,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G1309" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37894,7 +37897,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G1310" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37920,7 +37923,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1311" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37946,7 +37949,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G1312" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37972,7 +37975,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G1313" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37998,7 +38001,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1314" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38024,7 +38027,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1315" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38050,7 +38053,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1316" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38076,7 +38079,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G1317" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38102,7 +38105,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1318" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38128,7 +38131,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G1319" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38154,7 +38157,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G1320" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38180,7 +38183,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1321" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38206,7 +38209,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1322" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38232,7 +38235,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G1323" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38258,7 +38261,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G1324" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38284,7 +38287,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G1325" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38310,7 +38313,7 @@
         <v>24.1294326782227</v>
       </c>
       <c r="G1326" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38336,7 +38339,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1327" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38362,7 +38365,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1328" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38388,7 +38391,7 @@
         <v>24.8576850891113</v>
       </c>
       <c r="G1329" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38414,7 +38417,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G1330" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38440,7 +38443,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G1331" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38466,7 +38469,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G1332" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38492,7 +38495,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1333" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38518,7 +38521,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G1334" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38544,7 +38547,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G1335" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38570,7 +38573,7 @@
         <v>24.4692840576172</v>
       </c>
       <c r="G1336" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38596,7 +38599,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G1337" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38622,7 +38625,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1338" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38648,7 +38651,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1339" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38674,7 +38677,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1340" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38700,7 +38703,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G1341" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38726,7 +38729,7 @@
         <v>23.401180267334</v>
       </c>
       <c r="G1342" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38752,7 +38755,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G1343" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38778,7 +38781,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1344" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38804,7 +38807,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1345" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38830,7 +38833,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1346" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38856,7 +38859,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1347" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38882,7 +38885,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1348" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38908,7 +38911,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G1349" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -38934,7 +38937,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1350" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -38960,7 +38963,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1351" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -38986,7 +38989,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G1352" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39012,7 +39015,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1353" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39038,7 +39041,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1354" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39064,7 +39067,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1355" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39090,7 +39093,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1356" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39116,7 +39119,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1357" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39142,7 +39145,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1358" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39168,7 +39171,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1359" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39194,7 +39197,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1360" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39220,7 +39223,7 @@
         <v>21.7019233703613</v>
       </c>
       <c r="G1361" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39246,7 +39249,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1362" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39272,7 +39275,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1363" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39298,7 +39301,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1364" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39324,7 +39327,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G1365" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39350,7 +39353,7 @@
         <v>19.759916305542</v>
       </c>
       <c r="G1366" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39376,7 +39379,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1367" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -39402,7 +39405,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1368" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39428,7 +39431,7 @@
         <v>18.8568840026855</v>
       </c>
       <c r="G1369" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -39454,7 +39457,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1370" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39480,7 +39483,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G1371" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39506,7 +39509,7 @@
         <v>18.0218200683594</v>
       </c>
       <c r="G1372" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39532,7 +39535,7 @@
         <v>18.1966018676758</v>
       </c>
       <c r="G1373" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39558,7 +39561,7 @@
         <v>19.1093444824219</v>
       </c>
       <c r="G1374" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39584,7 +39587,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G1375" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39610,7 +39613,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1376" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39636,7 +39639,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1377" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39662,7 +39665,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1378" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39688,7 +39691,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1379" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39714,7 +39717,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1380" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39740,7 +39743,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1381" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39766,7 +39769,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1382" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39792,7 +39795,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1383" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39818,7 +39821,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G1384" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -39844,7 +39847,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1385" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -39870,7 +39873,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G1386" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39896,7 +39899,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1387" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -39922,7 +39925,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1388" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -39948,7 +39951,7 @@
         <v>20.25</v>
       </c>
       <c r="G1389" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -39974,7 +39977,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1390" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40000,7 +40003,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40026,7 +40029,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1392" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40052,7 +40055,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1393" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40078,7 +40081,7 @@
         <v>22.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40104,7 +40107,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1395" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40130,7 +40133,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1396" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40156,7 +40159,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40182,7 +40185,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1398" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40208,7 +40211,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40234,7 +40237,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1400" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40260,7 +40263,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1401" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40286,7 +40289,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1402" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40312,7 +40315,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1403" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40338,7 +40341,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1404" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40364,7 +40367,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1405" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40390,7 +40393,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1406" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40416,7 +40419,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1407" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40442,7 +40445,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1408" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40468,7 +40471,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1409" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40494,7 +40497,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1410" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40520,7 +40523,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40546,7 +40549,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40572,7 +40575,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40598,7 +40601,7 @@
         <v>24.75</v>
       </c>
       <c r="G1414" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40624,7 +40627,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40650,7 +40653,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1416" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40676,7 +40679,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1417" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -40702,7 +40705,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1418" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40728,7 +40731,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40754,7 +40757,7 @@
         <v>23.25</v>
       </c>
       <c r="G1420" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40780,7 +40783,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1421" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40806,7 +40809,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1422" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40832,7 +40835,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1423" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -40858,7 +40861,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1424" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40884,7 +40887,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1425" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40910,7 +40913,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1426" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -40936,7 +40939,7 @@
         <v>22.5</v>
       </c>
       <c r="G1427" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -40962,7 +40965,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -40988,7 +40991,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1429" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41014,7 +41017,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41040,7 +41043,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1431" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41066,7 +41069,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41092,7 +41095,7 @@
         <v>22.25</v>
       </c>
       <c r="G1433" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41118,7 +41121,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1434" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41144,7 +41147,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41170,7 +41173,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1436" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41196,7 +41199,7 @@
         <v>22.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41222,7 +41225,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1438" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41248,7 +41251,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1439" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41274,7 +41277,7 @@
         <v>22.25</v>
       </c>
       <c r="G1440" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41300,7 +41303,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41326,7 +41329,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1442" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41352,7 +41355,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1443" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41378,7 +41381,7 @@
         <v>22.75</v>
       </c>
       <c r="G1444" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41404,7 +41407,7 @@
         <v>22.5</v>
       </c>
       <c r="G1445" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41430,7 +41433,7 @@
         <v>22.25</v>
       </c>
       <c r="G1446" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41456,7 +41459,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41482,7 +41485,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1448" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41508,7 +41511,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1449" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41534,7 +41537,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1450" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41560,7 +41563,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41586,7 +41589,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41612,7 +41615,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1453" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41638,7 +41641,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1454" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41664,7 +41667,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1455" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41690,7 +41693,7 @@
         <v>22</v>
       </c>
       <c r="G1456" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41716,7 +41719,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41742,7 +41745,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1458" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41768,7 +41771,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1459" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41794,7 +41797,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1460" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41820,7 +41823,7 @@
         <v>21.5</v>
       </c>
       <c r="G1461" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41846,7 +41849,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1462" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -41872,7 +41875,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1463" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -41898,7 +41901,7 @@
         <v>20</v>
       </c>
       <c r="G1464" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -41924,7 +41927,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1465" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -41950,7 +41953,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1466" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -41976,7 +41979,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1467" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42002,7 +42005,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1468" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42028,7 +42031,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1469" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42054,7 +42057,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1470" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42080,7 +42083,7 @@
         <v>19.5</v>
       </c>
       <c r="G1471" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42106,7 +42109,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1472" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42132,7 +42135,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42158,7 +42161,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1474" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42184,7 +42187,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1475" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42210,7 +42213,7 @@
         <v>20.5</v>
       </c>
       <c r="G1476" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42236,7 +42239,7 @@
         <v>21</v>
       </c>
       <c r="G1477" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42262,7 +42265,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42288,7 +42291,7 @@
         <v>20.5</v>
       </c>
       <c r="G1479" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42314,7 +42317,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1480" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42340,7 +42343,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42366,7 +42369,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1482" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42392,7 +42395,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42418,7 +42421,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1484" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42444,7 +42447,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1485" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42470,7 +42473,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1486" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42496,7 +42499,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1487" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42522,7 +42525,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1488" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42548,7 +42551,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1489" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42574,7 +42577,7 @@
         <v>18.5</v>
       </c>
       <c r="G1490" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42600,7 +42603,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1491" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42626,7 +42629,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1492" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42652,7 +42655,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1493" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42678,7 +42681,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1494" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42704,7 +42707,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1495" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42730,7 +42733,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1496" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42756,7 +42759,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1497" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42782,7 +42785,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1498" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42808,7 +42811,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1499" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42834,7 +42837,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1500" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -42860,7 +42863,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1501" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42886,7 +42889,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1502" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -42912,7 +42915,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1503" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -42938,7 +42941,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1504" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -42964,7 +42967,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1505" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -42990,7 +42993,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1506" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43016,7 +43019,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1507" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43042,7 +43045,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1508" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43068,7 +43071,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1509" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43094,7 +43097,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1510" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43120,7 +43123,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1511" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43146,7 +43149,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1512" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43172,7 +43175,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1513" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43198,7 +43201,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1514" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43224,7 +43227,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1515" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43250,7 +43253,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1516" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43276,7 +43279,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1517" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43302,7 +43305,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1518" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43328,7 +43331,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1519" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43354,7 +43357,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1520" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43380,7 +43383,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1521" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43406,7 +43409,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1522" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43432,7 +43435,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1523" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43458,7 +43461,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1524" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43484,7 +43487,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1525" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43510,7 +43513,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43536,7 +43539,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1527" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43562,7 +43565,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43588,7 +43591,7 @@
         <v>18</v>
       </c>
       <c r="G1529" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43614,7 +43617,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1530" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43640,7 +43643,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1531" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43666,7 +43669,7 @@
         <v>17</v>
       </c>
       <c r="G1532" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43692,7 +43695,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1533" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43718,7 +43721,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1534" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43744,7 +43747,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1535" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43770,7 +43773,7 @@
         <v>17.5</v>
       </c>
       <c r="G1536" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43796,7 +43799,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1537" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43822,7 +43825,7 @@
         <v>17.5</v>
       </c>
       <c r="G1538" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43848,7 +43851,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43874,7 +43877,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1540" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43900,7 +43903,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1541" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -43926,7 +43929,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1542" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43952,7 +43955,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1543" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43978,7 +43981,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1544" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44004,7 +44007,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1545" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44030,7 +44033,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1546" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44056,7 +44059,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1547" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44082,7 +44085,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1548" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44108,7 +44111,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1549" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44134,7 +44137,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1550" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44160,7 +44163,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1551" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44186,7 +44189,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1552" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44212,7 +44215,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1553" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44238,7 +44241,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1554" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44264,7 +44267,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44290,7 +44293,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1556" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44316,7 +44319,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1557" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44342,7 +44345,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1558" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44368,7 +44371,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1559" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44394,7 +44397,7 @@
         <v>17</v>
       </c>
       <c r="G1560" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44420,7 +44423,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44446,7 +44449,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1562" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44472,7 +44475,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1563" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44498,7 +44501,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1564" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44524,7 +44527,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1565" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44550,7 +44553,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1566" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44576,7 +44579,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1567" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44602,7 +44605,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44628,7 +44631,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1569" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44654,7 +44657,7 @@
         <v>16.5</v>
       </c>
       <c r="G1570" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44680,7 +44683,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1571" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44706,7 +44709,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G1572" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44732,7 +44735,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1573" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44758,7 +44761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1574" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44784,7 +44787,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1575" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44810,7 +44813,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1576" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44836,7 +44839,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1577" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44862,7 +44865,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1578" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44888,7 +44891,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1579" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44914,7 +44917,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1580" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44940,7 +44943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1581" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44966,7 +44969,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1582" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -44992,7 +44995,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1583" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45018,7 +45021,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1584" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45044,7 +45047,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1585" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45070,7 +45073,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1586" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45096,7 +45099,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1587" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45122,7 +45125,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1588" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45148,7 +45151,7 @@
         <v>17</v>
       </c>
       <c r="G1589" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45174,7 +45177,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1590" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45200,7 +45203,7 @@
         <v>17</v>
       </c>
       <c r="G1591" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45226,7 +45229,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1592" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45252,7 +45255,7 @@
         <v>17</v>
       </c>
       <c r="G1593" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45278,7 +45281,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1594" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45304,7 +45307,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45330,7 +45333,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1596" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45356,7 +45359,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1597" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45382,7 +45385,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1598" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45408,7 +45411,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1599" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45434,7 +45437,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1600" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45460,7 +45463,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1601" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45486,7 +45489,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1602" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45512,7 +45515,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1603" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45538,7 +45541,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1604" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45564,7 +45567,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1605" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45590,7 +45593,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1606" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45616,7 +45619,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1607" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45642,7 +45645,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1608" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45668,7 +45671,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1609" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45694,7 +45697,7 @@
         <v>19.5</v>
       </c>
       <c r="G1610" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45720,7 +45723,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1611" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45746,7 +45749,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45772,7 +45775,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1613" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45798,7 +45801,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45824,7 +45827,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1615" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45850,7 +45853,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1616" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45876,7 +45879,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1617" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45902,7 +45905,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45928,7 +45931,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1619" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45954,7 +45957,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1620" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45980,7 +45983,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1621" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46006,7 +46009,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1622" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46032,7 +46035,7 @@
         <v>19</v>
       </c>
       <c r="G1623" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46058,7 +46061,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46084,7 +46087,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1625" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46110,7 +46113,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1626" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46136,7 +46139,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1627" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46162,7 +46165,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1628" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46188,7 +46191,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46214,7 +46217,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1630" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46240,7 +46243,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46266,7 +46269,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1632" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46292,7 +46295,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1633" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46318,7 +46321,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1634" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46344,7 +46347,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1635" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46370,7 +46373,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1636" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46396,7 +46399,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1637" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46422,7 +46425,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1638" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46448,7 +46451,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1639" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46474,7 +46477,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1640" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46500,7 +46503,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1641" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46526,7 +46529,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46552,7 +46555,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1643" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46578,7 +46581,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1644" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46604,7 +46607,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1645" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46630,7 +46633,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1646" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46656,7 +46659,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46682,7 +46685,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1648" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46708,7 +46711,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1649" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46734,7 +46737,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1650" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46760,7 +46763,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1651" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46786,7 +46789,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1652" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46812,7 +46815,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1653" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46838,7 +46841,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1654" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46864,7 +46867,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1655" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46890,7 +46893,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1656" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46916,7 +46919,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46942,7 +46945,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1658" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46968,7 +46971,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1659" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -46994,7 +46997,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1660" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47020,7 +47023,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1661" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47046,7 +47049,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1662" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47072,7 +47075,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1663" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47098,7 +47101,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1664" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47124,7 +47127,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1665" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47150,7 +47153,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1666" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47176,7 +47179,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1667" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47202,7 +47205,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1668" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47228,7 +47231,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1669" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47254,7 +47257,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1670" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47280,7 +47283,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1671" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47306,7 +47309,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1672" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47332,7 +47335,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1673" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47358,7 +47361,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1674" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47384,7 +47387,7 @@
         <v>18</v>
       </c>
       <c r="G1675" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47410,7 +47413,7 @@
         <v>17.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47436,7 +47439,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1677" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47462,7 +47465,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1678" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47488,7 +47491,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1679" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47514,7 +47517,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1680" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47540,7 +47543,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1681" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47566,7 +47569,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1682" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47592,7 +47595,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1683" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47618,7 +47621,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1684" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47644,7 +47647,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1685" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47670,7 +47673,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1686" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47696,7 +47699,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1687" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47722,7 +47725,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47748,7 +47751,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1689" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47774,7 +47777,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1690" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47800,7 +47803,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1691" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47826,7 +47829,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1692" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47852,7 +47855,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1693" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47878,7 +47881,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1694" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47904,7 +47907,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47930,7 +47933,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1696" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47956,7 +47959,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1697" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47982,7 +47985,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1698" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48008,7 +48011,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1699" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48034,7 +48037,7 @@
         <v>21.75</v>
       </c>
       <c r="G1700" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48060,7 +48063,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1701" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48086,7 +48089,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1702" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48112,7 +48115,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1703" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48138,7 +48141,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1704" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48164,7 +48167,7 @@
         <v>21</v>
       </c>
       <c r="G1705" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48190,7 +48193,7 @@
         <v>20.75</v>
       </c>
       <c r="G1706" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48216,7 +48219,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48242,7 +48245,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48268,7 +48271,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1709" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48294,7 +48297,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48320,7 +48323,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48346,7 +48349,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1712" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48372,7 +48375,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48398,7 +48401,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1714" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48424,7 +48427,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48450,7 +48453,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1716" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48476,7 +48479,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1717" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48502,7 +48505,7 @@
         <v>20</v>
       </c>
       <c r="G1718" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48528,7 +48531,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1719" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48554,7 +48557,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1720" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48580,7 +48583,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1721" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48606,7 +48609,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1722" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48632,7 +48635,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1723" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48658,7 +48661,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1724" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48684,7 +48687,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1725" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48710,7 +48713,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1726" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48736,7 +48739,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1727" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48762,7 +48765,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1728" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48788,7 +48791,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1729" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48814,7 +48817,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1730" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48840,7 +48843,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1731" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48866,7 +48869,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1732" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48892,7 +48895,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1733" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48918,7 +48921,7 @@
         <v>16.5</v>
       </c>
       <c r="G1734" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48944,7 +48947,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1735" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48970,7 +48973,7 @@
         <v>15</v>
       </c>
       <c r="G1736" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48996,7 +48999,7 @@
         <v>15.5</v>
       </c>
       <c r="G1737" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49022,7 +49025,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G1738" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49048,7 +49051,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1739" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49074,7 +49077,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49100,7 +49103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1741" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49126,7 +49129,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1742" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49152,7 +49155,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49178,7 +49181,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1744" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49204,7 +49207,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1745" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49230,7 +49233,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1746" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49256,7 +49259,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1747" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49282,7 +49285,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1748" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49308,7 +49311,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1749" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49334,7 +49337,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1750" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49360,7 +49363,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1751" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49386,7 +49389,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1752" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49412,7 +49415,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1753" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49438,7 +49441,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1754" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49464,7 +49467,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1755" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49490,7 +49493,7 @@
         <v>18.5</v>
       </c>
       <c r="G1756" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49516,7 +49519,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1757" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49542,7 +49545,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1758" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49568,7 +49571,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49594,7 +49597,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1760" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49620,7 +49623,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1761" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49646,7 +49649,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49672,7 +49675,7 @@
         <v>21</v>
       </c>
       <c r="G1763" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49698,7 +49701,7 @@
         <v>20.75</v>
       </c>
       <c r="G1764" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49724,7 +49727,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1765" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49750,7 +49753,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1766" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49776,7 +49779,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1767" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49802,7 +49805,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1768" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49828,7 +49831,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1769" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49854,7 +49857,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49880,7 +49883,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49906,7 +49909,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1772" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49932,7 +49935,7 @@
         <v>20.75</v>
       </c>
       <c r="G1773" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49958,7 +49961,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49984,7 +49987,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1775" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50010,7 +50013,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50036,7 +50039,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50062,7 +50065,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1778" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50088,7 +50091,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1779" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50114,7 +50117,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50140,7 +50143,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1781" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50166,7 +50169,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1782" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50192,7 +50195,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50218,7 +50221,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1784" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50244,7 +50247,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1785" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50270,7 +50273,7 @@
         <v>22.5</v>
       </c>
       <c r="G1786" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50296,7 +50299,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1787" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50322,7 +50325,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50348,7 +50351,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50374,7 +50377,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50400,7 +50403,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1791" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50426,7 +50429,7 @@
         <v>23.75</v>
       </c>
       <c r="G1792" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50452,7 +50455,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1793" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50478,7 +50481,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1794" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50504,7 +50507,7 @@
         <v>22.5</v>
       </c>
       <c r="G1795" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50530,7 +50533,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1796" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50556,7 +50559,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1797" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50582,7 +50585,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1798" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50608,7 +50611,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50634,7 +50637,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50660,7 +50663,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1801" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50686,7 +50689,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1802" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50712,7 +50715,7 @@
         <v>22.75</v>
       </c>
       <c r="G1803" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50738,7 +50741,7 @@
         <v>23.75</v>
       </c>
       <c r="G1804" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50764,7 +50767,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50790,7 +50793,7 @@
         <v>23.75</v>
       </c>
       <c r="G1806" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50816,7 +50819,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1807" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50842,7 +50845,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1808" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50868,7 +50871,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1809" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50894,7 +50897,7 @@
         <v>23.5</v>
       </c>
       <c r="G1810" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50920,7 +50923,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50946,7 +50949,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1812" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50972,7 +50975,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -50998,7 +51001,7 @@
         <v>23.5</v>
       </c>
       <c r="G1814" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51024,7 +51027,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1815" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51050,7 +51053,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1816" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51076,7 +51079,7 @@
         <v>22.25</v>
       </c>
       <c r="G1817" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51102,7 +51105,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1818" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51128,7 +51131,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G1819" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51154,7 +51157,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51180,7 +51183,7 @@
         <v>25</v>
       </c>
       <c r="G1821" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51206,7 +51209,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G1822" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51232,7 +51235,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51258,7 +51261,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1824" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51284,7 +51287,7 @@
         <v>25</v>
       </c>
       <c r="G1825" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51310,7 +51313,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51336,7 +51339,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51362,7 +51365,7 @@
         <v>26</v>
       </c>
       <c r="G1828" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51388,7 +51391,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1829" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51414,7 +51417,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51440,7 +51443,7 @@
         <v>25</v>
       </c>
       <c r="G1831" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51466,7 +51469,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51492,7 +51495,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1833" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51518,7 +51521,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51544,7 +51547,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1835" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51570,7 +51573,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51596,7 +51599,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1837" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51622,7 +51625,7 @@
         <v>22.75</v>
       </c>
       <c r="G1838" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51648,7 +51651,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1839" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51674,7 +51677,7 @@
         <v>22.5</v>
       </c>
       <c r="G1840" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51700,7 +51703,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1841" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51726,7 +51729,7 @@
         <v>23.5</v>
       </c>
       <c r="G1842" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51752,7 +51755,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1843" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51778,7 +51781,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1844" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51804,7 +51807,7 @@
         <v>23</v>
       </c>
       <c r="G1845" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51830,7 +51833,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51856,7 +51859,7 @@
         <v>23</v>
       </c>
       <c r="G1847" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51882,7 +51885,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51908,7 +51911,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51934,7 +51937,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51960,7 +51963,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1851" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51986,7 +51989,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1852" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52012,7 +52015,7 @@
         <v>23.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52038,7 +52041,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1854" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52064,7 +52067,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1855" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52090,7 +52093,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52116,7 +52119,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1857" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52142,7 +52145,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52168,7 +52171,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1859" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52194,7 +52197,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1860" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52220,7 +52223,7 @@
         <v>23</v>
       </c>
       <c r="G1861" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52246,7 +52249,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52272,7 +52275,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1863" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52298,7 +52301,7 @@
         <v>22</v>
       </c>
       <c r="G1864" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52324,7 +52327,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1865" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52350,7 +52353,7 @@
         <v>21</v>
       </c>
       <c r="G1866" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52376,7 +52379,7 @@
         <v>21.5</v>
       </c>
       <c r="G1867" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52402,7 +52405,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52428,7 +52431,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1869" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52454,7 +52457,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52480,7 +52483,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1871" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52506,7 +52509,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1872" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52532,7 +52535,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52558,7 +52561,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1874" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52584,7 +52587,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52610,7 +52613,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1876" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52636,7 +52639,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1877" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52662,7 +52665,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1878" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52688,7 +52691,7 @@
         <v>22.75</v>
       </c>
       <c r="G1879" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52696,7 +52699,7 @@
     </row>
     <row r="1880">
       <c r="A1880" s="1" t="n">
-        <v>45960.6911805556</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1880" t="n">
         <v>35747</v>
@@ -52714,9 +52717,35 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1880" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H1880" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="1" t="n">
+        <v>45961.6941087963</v>
+      </c>
+      <c r="B1881" t="n">
+        <v>29519</v>
+      </c>
+      <c r="C1881" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="D1881" t="n">
+        <v>22.5499992370605</v>
+      </c>
+      <c r="E1881" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>22.5499992370605</v>
+      </c>
+      <c r="G1881" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H1881" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="1166">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,55 +38,55 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125877380371</t>
+    <t xml:space="preserve">7.58125782012939</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099224090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71910047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68969297409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348079681396</t>
+    <t xml:space="preserve">7.90288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099128723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71909952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6896915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348127365112</t>
   </si>
   <si>
     <t xml:space="preserve">7.96721267700195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67407083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97640085220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44433546066284</t>
+    <t xml:space="preserve">7.67407035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97640180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4443359375</t>
   </si>
   <si>
     <t xml:space="preserve">7.30281925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52520370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46639108657837</t>
+    <t xml:space="preserve">7.52520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46639060974121</t>
   </si>
   <si>
     <t xml:space="preserve">7.57206869125366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44341850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52612161636353</t>
+    <t xml:space="preserve">7.4434175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52612209320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.54450082778931</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">7.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8018045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85694122314453</t>
+    <t xml:space="preserve">7.80180406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85694026947021</t>
   </si>
   <si>
     <t xml:space="preserve">7.92218542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00397109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86612844467163</t>
+    <t xml:space="preserve">8.00397205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86612892150879</t>
   </si>
   <si>
     <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81466913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7650465965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142707824707</t>
+    <t xml:space="preserve">7.81466865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76504564285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142803192139</t>
   </si>
   <si>
     <t xml:space="preserve">7.69336843490601</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">7.7926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74666833877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910245895386</t>
+    <t xml:space="preserve">7.74666786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.56379842758179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67315149307251</t>
+    <t xml:space="preserve">7.67315196990967</t>
   </si>
   <si>
     <t xml:space="preserve">7.7852635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74850606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002616882324</t>
+    <t xml:space="preserve">7.74850654602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002712249756</t>
   </si>
   <si>
     <t xml:space="preserve">8.11424350738525</t>
@@ -158,52 +158,52 @@
     <t xml:space="preserve">8.30354499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46344089508057</t>
+    <t xml:space="preserve">8.46343994140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.48641300201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75382518768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966815948486</t>
+    <t xml:space="preserve">8.75382614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966911315918</t>
   </si>
   <si>
     <t xml:space="preserve">8.60128116607666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28884029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25208473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46987342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36235809326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45425224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71155261993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74831295013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61598491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66560649871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7942590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.005615234375</t>
+    <t xml:space="preserve">8.28884124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25208377838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46987247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3623571395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45425319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7115535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74831199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6159839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66560745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79426002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00561618804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.86869335174561</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">9.11588764190674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14345645904541</t>
+    <t xml:space="preserve">9.14345550537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.33643341064453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09751033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680889129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091339111328</t>
+    <t xml:space="preserve">9.09750938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091243743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.18572902679443</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">9.06167030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02399349212646</t>
+    <t xml:space="preserve">9.02399444580078</t>
   </si>
   <si>
     <t xml:space="preserve">8.76577186584473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9936695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04237365722656</t>
+    <t xml:space="preserve">8.99366855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04237461090088</t>
   </si>
   <si>
     <t xml:space="preserve">8.90177536010742</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">7.98191547393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30630207061768</t>
+    <t xml:space="preserve">8.30630302429199</t>
   </si>
   <si>
     <t xml:space="preserve">8.40830421447754</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">8.54614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59209251403809</t>
+    <t xml:space="preserve">8.5920934677124</t>
   </si>
   <si>
     <t xml:space="preserve">8.63803958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80804347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126560211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34214019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77496147155762</t>
+    <t xml:space="preserve">8.80804252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9212646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34213924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7749605178833</t>
   </si>
   <si>
     <t xml:space="preserve">8.77771949768066</t>
@@ -308,19 +308,19 @@
     <t xml:space="preserve">8.57738971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3926830291748</t>
+    <t xml:space="preserve">8.39268112182617</t>
   </si>
   <si>
     <t xml:space="preserve">8.34122276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56085014343262</t>
+    <t xml:space="preserve">8.5608491897583</t>
   </si>
   <si>
     <t xml:space="preserve">8.71982479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05451202392578</t>
+    <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
     <t xml:space="preserve">8.04164695739746</t>
@@ -332,73 +332,73 @@
     <t xml:space="preserve">8.18867778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.548903465271</t>
+    <t xml:space="preserve">8.54890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.33479022979736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9210729598999</t>
+    <t xml:space="preserve">8.50938701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92107391357422</t>
   </si>
   <si>
     <t xml:space="preserve">9.0386962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97437000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1526460647583</t>
+    <t xml:space="preserve">8.9743709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15264511108398</t>
   </si>
   <si>
     <t xml:space="preserve">8.84939670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07913112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85582828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446529388428</t>
+    <t xml:space="preserve">9.07913208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85583019256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446434020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.23370552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27046394348145</t>
+    <t xml:space="preserve">8.27046489715576</t>
   </si>
   <si>
     <t xml:space="preserve">8.33754634857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20062351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40370845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27413940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29803371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50019836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43587207794189</t>
+    <t xml:space="preserve">8.20062446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40370941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27414131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5001974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43587112426758</t>
   </si>
   <si>
     <t xml:space="preserve">8.22451591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35408496856689</t>
+    <t xml:space="preserve">8.35408592224121</t>
   </si>
   <si>
     <t xml:space="preserve">8.22083950042725</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">8.15283966064453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39911556243896</t>
+    <t xml:space="preserve">8.39911651611328</t>
   </si>
   <si>
     <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48365592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.709716796875</t>
+    <t xml:space="preserve">8.48365783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70971584320068</t>
   </si>
   <si>
     <t xml:space="preserve">8.77128601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72074413299561</t>
+    <t xml:space="preserve">8.72074222564697</t>
   </si>
   <si>
     <t xml:space="preserve">9.100266456604</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">9.06534576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89809799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469390869141</t>
+    <t xml:space="preserve">8.89809989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469295501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.97712993621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05156230926514</t>
+    <t xml:space="preserve">9.05156326293945</t>
   </si>
   <si>
     <t xml:space="preserve">9.2353515625</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">9.20594501495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36216354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3952465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027717590332</t>
+    <t xml:space="preserve">9.36216449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39524555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027908325195</t>
   </si>
   <si>
     <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69482040405273</t>
+    <t xml:space="preserve">9.69482231140137</t>
   </si>
   <si>
     <t xml:space="preserve">9.5937385559082</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">9.64336013793945</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31989192962646</t>
+    <t xml:space="preserve">9.31989288330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.61763000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49265384674072</t>
+    <t xml:space="preserve">9.49265480041504</t>
   </si>
   <si>
     <t xml:space="preserve">9.5110330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28497219085693</t>
+    <t xml:space="preserve">9.28497314453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.46324825286865</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">9.12875461578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26291942596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14713382720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06075286865234</t>
+    <t xml:space="preserve">9.26291847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14713287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06075191497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.9412899017334</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">8.37797927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76025867462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00653457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18940448760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96885776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1067008972168</t>
+    <t xml:space="preserve">8.76025772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0065336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18940258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96885871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10669994354248</t>
   </si>
   <si>
     <t xml:space="preserve">9.44670677185059</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">9.90617752075195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807167053223</t>
+    <t xml:space="preserve">9.99807071685791</t>
   </si>
   <si>
     <t xml:space="preserve">10.0532073974609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79590511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92455673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81428337097168</t>
+    <t xml:space="preserve">9.7959041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455577850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81428146362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.94293594360352</t>
@@ -569,79 +569,79 @@
     <t xml:space="preserve">10.0715856552124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.108344078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6672534942627</t>
+    <t xml:space="preserve">10.1083450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66725540161133</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752494812012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86941909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1634788513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348291397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0164489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267223358154</t>
+    <t xml:space="preserve">9.83266258239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86942005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1634798049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105115890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348300933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267213821411</t>
   </si>
   <si>
     <t xml:space="preserve">10.5126781463623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6045703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597089767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7332229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207830429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288898468018</t>
+    <t xml:space="preserve">10.6045713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597080230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7332239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.420783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4759206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288888931274</t>
   </si>
   <si>
     <t xml:space="preserve">9.97969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85104084014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821937561035</t>
+    <t xml:space="preserve">9.85103988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821956634521</t>
   </si>
   <si>
     <t xml:space="preserve">9.94108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253875732422</t>
+    <t xml:space="preserve">9.8854455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253971099854</t>
   </si>
   <si>
     <t xml:space="preserve">9.99672603607178</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">10.0894603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90399265289307</t>
+    <t xml:space="preserve">9.90399169921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.0523672103882</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">9.86689949035645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1636476516724</t>
+    <t xml:space="preserve">10.163646697998</t>
   </si>
   <si>
     <t xml:space="preserve">10.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4047555923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4233045578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3862113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3676624298096</t>
+    <t xml:space="preserve">10.4047565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.423303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386212348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3676633834839</t>
   </si>
   <si>
     <t xml:space="preserve">9.82980728149414</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">9.7927131652832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4789428710938</t>
+    <t xml:space="preserve">10.2563819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498792648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4789438247681</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554218292236</t>
@@ -731,34 +731,34 @@
     <t xml:space="preserve">11.536111831665</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6288461685181</t>
+    <t xml:space="preserve">11.6288452148438</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175647735596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9626884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.148157119751</t>
+    <t xml:space="preserve">11.9626893997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1481561660767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2408905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4449052810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1852502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5732049942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5917520523071</t>
+    <t xml:space="preserve">12.4449043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5932788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1852493286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.573205947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5917510986328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401275634766</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">11.4804706573486</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925594329834</t>
+    <t xml:space="preserve">11.9255933761597</t>
   </si>
   <si>
     <t xml:space="preserve">12.1110620498657</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">12.1667032241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2223424911499</t>
+    <t xml:space="preserve">12.2223434448242</t>
   </si>
   <si>
     <t xml:space="preserve">12.5190935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.686014175415</t>
+    <t xml:space="preserve">12.6860132217407</t>
   </si>
   <si>
     <t xml:space="preserve">12.9827632904053</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">13.3536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5020742416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.058479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4649801254272</t>
+    <t xml:space="preserve">13.5020732879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4649791717529</t>
   </si>
   <si>
     <t xml:space="preserve">13.2053241729736</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">12.4078121185303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2037954330444</t>
+    <t xml:space="preserve">12.2037973403931</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779846191406</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">14.5963354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9101037979126</t>
+    <t xml:space="preserve">13.9101028442383</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093389511108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1682300567627</t>
+    <t xml:space="preserve">13.1682319641113</t>
   </si>
   <si>
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045612335205</t>
+    <t xml:space="preserve">12.7045602798462</t>
   </si>
   <si>
     <t xml:space="preserve">12.5561866760254</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3351526260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0569486618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489191055298</t>
+    <t xml:space="preserve">13.3351516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0569496154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489200592041</t>
   </si>
   <si>
     <t xml:space="preserve">12.3150777816772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.463451385498</t>
+    <t xml:space="preserve">12.4634532928467</t>
   </si>
   <si>
     <t xml:space="preserve">12.4263582229614</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">11.7772216796875</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2950048446655</t>
+    <t xml:space="preserve">11.2950029373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.0168008804321</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">10.7571449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.313549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280813217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2764558792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2208166122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3691911697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095361709595</t>
+    <t xml:space="preserve">11.3135499954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2764549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2208156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3691892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095352172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">9.40322875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88391780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55160331726074</t>
+    <t xml:space="preserve">8.88391876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55160427093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.71699810028076</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">8.80973148345947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20695972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24405479431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19768810272217</t>
+    <t xml:space="preserve">8.20696067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24405574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19768714904785</t>
   </si>
   <si>
     <t xml:space="preserve">8.53153038024902</t>
@@ -962,37 +962,37 @@
     <t xml:space="preserve">10.7200517654419</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77416515350342</t>
+    <t xml:space="preserve">9.77416610717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2934761047363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2378358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71852493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152750015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7015066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6844863891602</t>
+    <t xml:space="preserve">10.2378349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71852397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7015056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6844873428345</t>
   </si>
   <si>
     <t xml:space="preserve">11.8699531555176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4819984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6118249893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7586727142334</t>
+    <t xml:space="preserve">12.4819993972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6118259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7586736679077</t>
   </si>
   <si>
     <t xml:space="preserve">13.7246341705322</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6504497528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930816650391</t>
+    <t xml:space="preserve">13.650447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930835723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.0414581298828</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">14.9301767349243</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2439451217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282567024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462377548218</t>
+    <t xml:space="preserve">14.2439460754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462358474731</t>
   </si>
   <si>
     <t xml:space="preserve">15.9687967300415</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">15.3938465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9487228393555</t>
+    <t xml:space="preserve">14.9487218856812</t>
   </si>
   <si>
     <t xml:space="preserve">14.6148824691772</t>
@@ -1037,61 +1037,61 @@
     <t xml:space="preserve">14.4665069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0399293899536</t>
+    <t xml:space="preserve">14.0399303436279</t>
   </si>
   <si>
     <t xml:space="preserve">14.132664680481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7988224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8173685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6689939498901</t>
+    <t xml:space="preserve">13.7988214492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8173694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6689949035645</t>
   </si>
   <si>
     <t xml:space="preserve">14.0770225524902</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318133354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076148986816</t>
+    <t xml:space="preserve">14.3181324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076139450073</t>
   </si>
   <si>
     <t xml:space="preserve">14.9858160018921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560493469238</t>
+    <t xml:space="preserve">14.5560483932495</t>
   </si>
   <si>
     <t xml:space="preserve">14.79896068573</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8923892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7802753448486</t>
+    <t xml:space="preserve">14.8923902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7802762985229</t>
   </si>
   <si>
     <t xml:space="preserve">14.7615909576416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2660999298096</t>
+    <t xml:space="preserve">15.2660989761353</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287302017212</t>
   </si>
   <si>
-    <t xml:space="preserve">15.415584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0045013427734</t>
+    <t xml:space="preserve">15.4155855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221578598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
     <t xml:space="preserve">14.6121063232422</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">15.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9110765457153</t>
+    <t xml:space="preserve">14.911075592041</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494770050049</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">15.1353034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297618865967</t>
+    <t xml:space="preserve">14.9297609329224</t>
   </si>
   <si>
     <t xml:space="preserve">15.0231876373291</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">14.9484462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813070297241</t>
+    <t xml:space="preserve">14.4813079833984</t>
   </si>
   <si>
     <t xml:space="preserve">15.5650682449341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1630096435547</t>
+    <t xml:space="preserve">16.1630077362061</t>
   </si>
   <si>
     <t xml:space="preserve">16.9664878845215</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">17.6765384674072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235736846924</t>
+    <t xml:space="preserve">16.723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8730602264404</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">17.7886543273926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0128784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.882080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2744750976562</t>
+    <t xml:space="preserve">18.0128765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8820781707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2744770050049</t>
   </si>
   <si>
     <t xml:space="preserve">18.3118495941162</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9941921234131</t>
+    <t xml:space="preserve">17.9941940307617</t>
   </si>
   <si>
     <t xml:space="preserve">18.6855583190918</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">17.9568214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4709987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8073348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9291152954102</t>
+    <t xml:space="preserve">17.4709968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.807336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9291133880615</t>
   </si>
   <si>
     <t xml:space="preserve">16.667516708374</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9574670791626</t>
+    <t xml:space="preserve">15.957465171814</t>
   </si>
   <si>
     <t xml:space="preserve">15.378212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706089019775</t>
+    <t xml:space="preserve">15.7706108093262</t>
   </si>
   <si>
     <t xml:space="preserve">16.5367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2938079833984</t>
+    <t xml:space="preserve">16.5927791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2938060760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.4246044158936</t>
@@ -1241,49 +1241,49 @@
     <t xml:space="preserve">16.8543701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7048892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3311786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4993457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3685512542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3498592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301441192627</t>
+    <t xml:space="preserve">16.7048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3311767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4993476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3685474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3498611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862049102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301460266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.6114597320557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7609443664551</t>
+    <t xml:space="preserve">16.7609462738037</t>
   </si>
   <si>
     <t xml:space="preserve">16.8170013427734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.798318862915</t>
+    <t xml:space="preserve">16.7983169555664</t>
   </si>
   <si>
     <t xml:space="preserve">15.7892971038818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4342708587646</t>
+    <t xml:space="preserve">15.434271812439</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6868467330933</t>
+    <t xml:space="preserve">14.6868476867676</t>
   </si>
   <si>
     <t xml:space="preserve">14.5373640060425</t>
@@ -1301,31 +1301,31 @@
     <t xml:space="preserve">15.8827238082886</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2377510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4806613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4432907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9478015899658</t>
+    <t xml:space="preserve">16.2377490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4806632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4432926177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9477996826172</t>
   </si>
   <si>
     <t xml:space="preserve">17.0786018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6488342285156</t>
+    <t xml:space="preserve">16.648832321167</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8917427062988</t>
+    <t xml:space="preserve">16.8917446136475</t>
   </si>
   <si>
     <t xml:space="preserve">17.900764465332</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">18.0876197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5360717773438</t>
+    <t xml:space="preserve">18.5360736846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.9194488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0502490997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5740909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.742259979248</t>
+    <t xml:space="preserve">18.0502471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.574089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7422580718994</t>
   </si>
   <si>
     <t xml:space="preserve">16.5554046630859</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">17.0225429534912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0695781707764</t>
+    <t xml:space="preserve">16.069580078125</t>
   </si>
   <si>
     <t xml:space="preserve">15.8453540802002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7519273757935</t>
+    <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
     <t xml:space="preserve">15.6024408340454</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">16.0135250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9014072418213</t>
+    <t xml:space="preserve">15.9014091491699</t>
   </si>
   <si>
     <t xml:space="preserve">15.9761524200439</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3595275878906</t>
+    <t xml:space="preserve">15.3595285415649</t>
   </si>
   <si>
     <t xml:space="preserve">14.5186777114868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1636533737183</t>
+    <t xml:space="preserve">14.1636524200439</t>
   </si>
   <si>
     <t xml:space="preserve">14.855019569397</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">15.6771802902222</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5277004241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145557403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716424942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4529571533203</t>
+    <t xml:space="preserve">15.52769947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.452956199646</t>
   </si>
   <si>
     <t xml:space="preserve">15.6584968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8640384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2190628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0972862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1346549987793</t>
+    <t xml:space="preserve">15.8640403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2190647125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0972881317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1346569061279</t>
   </si>
   <si>
     <t xml:space="preserve">17.9381370544434</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">17.7699642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1249885559082</t>
+    <t xml:space="preserve">18.1249904632568</t>
   </si>
   <si>
     <t xml:space="preserve">17.6391658782959</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">18.0689334869385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.172025680542</t>
+    <t xml:space="preserve">17.1720275878906</t>
   </si>
   <si>
     <t xml:space="preserve">17.5644226074219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.713264465332</t>
+    <t xml:space="preserve">17.6017932891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7512817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7132663726807</t>
   </si>
   <si>
     <t xml:space="preserve">19.8066921234131</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">20.5541133880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4606857299805</t>
+    <t xml:space="preserve">20.4606876373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.2738304138184</t>
@@ -1493,31 +1493,31 @@
     <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6008262634277</t>
+    <t xml:space="preserve">20.6008281707764</t>
   </si>
   <si>
     <t xml:space="preserve">20.6475410461426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2081069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.581823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9555320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3015384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8343963623047</t>
+    <t xml:space="preserve">21.2081050872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5818214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.955530166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3015365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8343982696533</t>
   </si>
   <si>
     <t xml:space="preserve">20.0869750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7599773406982</t>
+    <t xml:space="preserve">19.7599754333496</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796924591064</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">19.7350749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9700164794922</t>
+    <t xml:space="preserve">19.9700183868408</t>
   </si>
   <si>
     <t xml:space="preserve">19.7820644378662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4531478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5471229553223</t>
+    <t xml:space="preserve">19.4531497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5471248626709</t>
   </si>
   <si>
     <t xml:space="preserve">19.5001354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6880874633789</t>
+    <t xml:space="preserve">19.6880893707275</t>
   </si>
   <si>
     <t xml:space="preserve">19.030252456665</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">18.9362773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832668304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1579723358154</t>
+    <t xml:space="preserve">19.6410980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
     <t xml:space="preserve">19.8290557861328</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">18.7765159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5133800506592</t>
+    <t xml:space="preserve">18.5133819580078</t>
   </si>
   <si>
     <t xml:space="preserve">18.7953109741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6449489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639934539795</t>
+    <t xml:space="preserve">18.6449508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639953613281</t>
   </si>
   <si>
     <t xml:space="preserve">20.3929138183594</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">22.0844917297363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4603977203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9772682189941</t>
+    <t xml:space="preserve">22.4603996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9772701263428</t>
   </si>
   <si>
     <t xml:space="preserve">23.2122077941895</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4941425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1652240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0712432861328</t>
+    <t xml:space="preserve">23.494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1652221679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0712413787842</t>
   </si>
   <si>
     <t xml:space="preserve">23.58811378479</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">22.8832912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5411243438721</t>
+    <t xml:space="preserve">23.5411262512207</t>
   </si>
   <si>
     <t xml:space="preserve">22.9302787780762</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">23.2591972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4471530914307</t>
+    <t xml:space="preserve">23.447151184082</t>
   </si>
   <si>
     <t xml:space="preserve">23.870044708252</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">21.7555732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7085857391357</t>
+    <t xml:space="preserve">21.7085838317871</t>
   </si>
   <si>
     <t xml:space="preserve">22.1314792633057</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">21.5676193237305</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1447238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.909782409668</t>
+    <t xml:space="preserve">21.1447257995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9097843170166</t>
   </si>
   <si>
     <t xml:space="preserve">20.9567718505859</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">24.6688480377197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9977626800537</t>
+    <t xml:space="preserve">24.9977645874023</t>
   </si>
   <si>
     <t xml:space="preserve">24.4339046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3869171142578</t>
+    <t xml:space="preserve">24.3869152069092</t>
   </si>
   <si>
     <t xml:space="preserve">23.4001636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.635103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230571746826</t>
+    <t xml:space="preserve">23.6351051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230590820312</t>
   </si>
   <si>
     <t xml:space="preserve">24.2929401397705</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">24.4808921813965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5616226196289</t>
+    <t xml:space="preserve">25.5616207122803</t>
   </si>
   <si>
     <t xml:space="preserve">25.4206581115723</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">25.6555995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3736705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.279691696167</t>
+    <t xml:space="preserve">25.3736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2796936035156</t>
   </si>
   <si>
     <t xml:space="preserve">23.3061847686768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5543727874756</t>
+    <t xml:space="preserve">22.554370880127</t>
   </si>
   <si>
     <t xml:space="preserve">22.2724437713623</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">24.7158336639404</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5278816223145</t>
+    <t xml:space="preserve">24.5278797149658</t>
   </si>
   <si>
     <t xml:space="preserve">24.7628231048584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9170322418213</t>
+    <t xml:space="preserve">23.9170341491699</t>
   </si>
   <si>
     <t xml:space="preserve">24.0110111236572</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">24.8568019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6218585968018</t>
+    <t xml:space="preserve">24.6218566894531</t>
   </si>
   <si>
     <t xml:space="preserve">25.1857166290283</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">25.138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5206298828125</t>
+    <t xml:space="preserve">21.5206317901611</t>
   </si>
   <si>
     <t xml:space="preserve">21.1917133331299</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">21.4266567230225</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4399013519287</t>
+    <t xml:space="preserve">20.4398994445801</t>
   </si>
   <si>
     <t xml:space="preserve">21.8025608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8627948760986</t>
+    <t xml:space="preserve">20.8627967834473</t>
   </si>
   <si>
     <t xml:space="preserve">21.3326797485352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6146087646484</t>
+    <t xml:space="preserve">21.6146068572998</t>
   </si>
   <si>
     <t xml:space="preserve">21.3796653747559</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">20.3459243774414</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2182064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.569766998291</t>
+    <t xml:space="preserve">19.218204498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5697650909424</t>
   </si>
   <si>
     <t xml:space="preserve">19.8760414123535</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">18.3066349029541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1938610076904</t>
+    <t xml:space="preserve">18.1938629150391</t>
   </si>
   <si>
     <t xml:space="preserve">18.663745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9230308532715</t>
+    <t xml:space="preserve">19.9230289459229</t>
   </si>
   <si>
     <t xml:space="preserve">21.6615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9905166625977</t>
+    <t xml:space="preserve">21.990514755249</t>
   </si>
   <si>
     <t xml:space="preserve">22.3194332122803</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">18.7389259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7013339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8965377807617</t>
+    <t xml:space="preserve">18.7013320922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8965358734131</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049598693848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5338764190674</t>
+    <t xml:space="preserve">20.5338745117188</t>
   </si>
   <si>
     <t xml:space="preserve">18.3254299163818</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">17.8931369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2165050506592</t>
+    <t xml:space="preserve">17.2165031433105</t>
   </si>
   <si>
     <t xml:space="preserve">17.1977100372314</t>
@@ -3507,6 +3507,9 @@
   </si>
   <si>
     <t xml:space="preserve">23.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -52725,7 +52728,7 @@
     </row>
     <row r="1881">
       <c r="A1881" s="1" t="n">
-        <v>45961.6941087963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1881" t="n">
         <v>29519</v>
@@ -52746,6 +52749,32 @@
         <v>1121</v>
       </c>
       <c r="H1881" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="1" t="n">
+        <v>45964.6911342593</v>
+      </c>
+      <c r="B1882" t="n">
+        <v>40260</v>
+      </c>
+      <c r="C1882" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="D1882" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="E1882" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>22.4500007629395</v>
+      </c>
+      <c r="G1882" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H1882" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="1167">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125782012939</t>
+    <t xml:space="preserve">7.58125925064087</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">7.90288639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81099128723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71909952163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6896915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348127365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721267700195</t>
+    <t xml:space="preserve">7.81099414825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68969202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721315383911</t>
   </si>
   <si>
     <t xml:space="preserve">7.67407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97640180587769</t>
+    <t xml:space="preserve">7.976402759552</t>
   </si>
   <si>
     <t xml:space="preserve">7.4443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30281925201416</t>
+    <t xml:space="preserve">7.302818775177</t>
   </si>
   <si>
     <t xml:space="preserve">7.52520275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206869125366</t>
+    <t xml:space="preserve">7.46639108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">7.4434175491333</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">7.54450082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64742231369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85694026947021</t>
+    <t xml:space="preserve">7.64742183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80180501937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8569393157959</t>
   </si>
   <si>
     <t xml:space="preserve">7.92218542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00397205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86612892150879</t>
+    <t xml:space="preserve">8.00397109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86612939834595</t>
   </si>
   <si>
     <t xml:space="preserve">8.01959228515625</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">7.81466865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76504564285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142803192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336843490601</t>
+    <t xml:space="preserve">7.76504707336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142755508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336891174316</t>
   </si>
   <si>
     <t xml:space="preserve">7.7926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74666786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56379842758179</t>
+    <t xml:space="preserve">7.74666690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910341262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56379890441895</t>
   </si>
   <si>
     <t xml:space="preserve">7.67315196990967</t>
@@ -143,49 +143,49 @@
     <t xml:space="preserve">7.7852635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74850654602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002712249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11424350738525</t>
+    <t xml:space="preserve">7.74850606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478197097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11424446105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.30354499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46343994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48641300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75382614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95966911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60128116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28884124755859</t>
+    <t xml:space="preserve">8.46344089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48641395568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60128307342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28884315490723</t>
   </si>
   <si>
     <t xml:space="preserve">8.25208377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46987247467041</t>
+    <t xml:space="preserve">8.46987342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.3623571395874</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45425319671631</t>
+    <t xml:space="preserve">8.45425224304199</t>
   </si>
   <si>
     <t xml:space="preserve">8.7115535736084</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6159839630127</t>
+    <t xml:space="preserve">8.61598491668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.66560745239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79426002502441</t>
+    <t xml:space="preserve">8.7942590713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.00561618804932</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">8.86869335174561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11588764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14345550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09750938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680793762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99091243743896</t>
+    <t xml:space="preserve">9.11588954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14345645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09751224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99091148376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.18572902679443</t>
@@ -233,28 +233,28 @@
     <t xml:space="preserve">9.06167030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02399444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99366855621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04237461090088</t>
+    <t xml:space="preserve">9.02399349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76577091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99367046356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04237365722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.90177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67112255096436</t>
+    <t xml:space="preserve">8.67112064361572</t>
   </si>
   <si>
     <t xml:space="preserve">8.50754928588867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98191547393799</t>
+    <t xml:space="preserve">7.98191452026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.30630302429199</t>
@@ -266,52 +266,52 @@
     <t xml:space="preserve">8.54614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5920934677124</t>
+    <t xml:space="preserve">8.59209251403809</t>
   </si>
   <si>
     <t xml:space="preserve">8.63803958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9212646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34213924407959</t>
+    <t xml:space="preserve">8.80804347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126218795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126703262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34214019775391</t>
   </si>
   <si>
     <t xml:space="preserve">8.7749605178833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77771949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50571155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59944343566895</t>
+    <t xml:space="preserve">8.77771854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75474452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50571250915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59944438934326</t>
   </si>
   <si>
     <t xml:space="preserve">8.70144653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57738971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39268112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34122276306152</t>
+    <t xml:space="preserve">8.57738876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39268207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34121990203857</t>
   </si>
   <si>
     <t xml:space="preserve">8.5608491897583</t>
@@ -323,157 +323,157 @@
     <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04164695739746</t>
+    <t xml:space="preserve">8.04164791107178</t>
   </si>
   <si>
     <t xml:space="preserve">8.08667469024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18867778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54890251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33479022979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50938701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0386962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9743709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15264511108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84939670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07913208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85583019256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446434020996</t>
+    <t xml:space="preserve">8.18867683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.548903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33479118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50938892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9210729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03869724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97437191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15264701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84939575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07913017272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85582828521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446338653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.23370552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27046489715576</t>
+    <t xml:space="preserve">8.27046394348145</t>
   </si>
   <si>
     <t xml:space="preserve">8.33754634857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20062446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40370941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27414131164551</t>
+    <t xml:space="preserve">8.20062255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40371036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27413940429688</t>
   </si>
   <si>
     <t xml:space="preserve">8.2980318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5001974105835</t>
+    <t xml:space="preserve">8.50019836425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.43587112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22451591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35408592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22083950042725</t>
+    <t xml:space="preserve">8.22451686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35408687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22083854675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.15283966064453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39911651611328</t>
+    <t xml:space="preserve">8.39911460876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48365783691406</t>
+    <t xml:space="preserve">8.48365688323975</t>
   </si>
   <si>
     <t xml:space="preserve">8.70971584320068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77128601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72074222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.100266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06534576416016</t>
+    <t xml:space="preserve">8.77128505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72074413299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10026550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06534671783447</t>
   </si>
   <si>
     <t xml:space="preserve">8.89809989929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83469295501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97712993621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05156326293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20594501495361</t>
+    <t xml:space="preserve">8.83469390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97712898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05156230926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23535060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2059440612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.36216449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39524555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64887428283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69482231140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5937385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64336013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989288330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61763000488281</t>
+    <t xml:space="preserve">9.3952465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027812957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64887237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69482040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59373760223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64335918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31989192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6176290512085</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265480041504</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">9.5110330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28497314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46324825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3309211730957</t>
+    <t xml:space="preserve">9.28497409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46324729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33091926574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.12875461578369</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">9.26291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14713287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06075191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9412899017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37797927856445</t>
+    <t xml:space="preserve">9.14713191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06075096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94128894805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37798023223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.76025772094727</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">9.0065336227417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18940258026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96885871887207</t>
+    <t xml:space="preserve">9.18940544128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96885681152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.10669994354248</t>
@@ -530,79 +530,79 @@
     <t xml:space="preserve">9.39157104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74076843261719</t>
+    <t xml:space="preserve">9.74076747894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.46508598327637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53859996795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75914669036865</t>
+    <t xml:space="preserve">9.53860092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">9.68563270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90617752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99807071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7959041595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92455577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81428146362305</t>
+    <t xml:space="preserve">9.90617656707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79590511322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81428241729736</t>
   </si>
   <si>
     <t xml:space="preserve">9.94293594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0715856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66725540161133</t>
+    <t xml:space="preserve">10.0715866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083431243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6672534942627</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752494812012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266258239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86942005157471</t>
+    <t xml:space="preserve">9.83266067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86941814422607</t>
   </si>
   <si>
     <t xml:space="preserve">10.1451015472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1634798049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105115890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348300933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0164499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5126781463623</t>
+    <t xml:space="preserve">10.163480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.310510635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348310470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164489746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267223358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.512677192688</t>
   </si>
   <si>
     <t xml:space="preserve">10.6045713424683</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">10.4759206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4391622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288888931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97969245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85103988647461</t>
+    <t xml:space="preserve">10.4391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97969341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85104084014893</t>
   </si>
   <si>
     <t xml:space="preserve">10.1821956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8854455947876</t>
+    <t xml:space="preserve">9.941086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88544654846191</t>
   </si>
   <si>
     <t xml:space="preserve">9.92253971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99672603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2007417678833</t>
+    <t xml:space="preserve">9.99672698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.200740814209</t>
   </si>
   <si>
     <t xml:space="preserve">10.2192878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0894603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399169921875</t>
+    <t xml:space="preserve">10.0894622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399265289307</t>
   </si>
   <si>
     <t xml:space="preserve">10.0523672103882</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">9.7370719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86689949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.163646697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5531311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4047565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.386212348938</t>
+    <t xml:space="preserve">9.86690044403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1636486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5531320571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4047574996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4233045578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3862104415894</t>
   </si>
   <si>
     <t xml:space="preserve">10.3676633834839</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82980728149414</t>
+    <t xml:space="preserve">9.82980632781982</t>
   </si>
   <si>
     <t xml:space="preserve">10.3120241165161</t>
@@ -695,49 +695,49 @@
     <t xml:space="preserve">10.033821105957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81125926971436</t>
+    <t xml:space="preserve">9.81126022338867</t>
   </si>
   <si>
     <t xml:space="preserve">10.070915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7927131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2563819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8498792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4789438247681</t>
+    <t xml:space="preserve">10.1080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79271221160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2563829421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8498811721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4789428710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103000640869</t>
+    <t xml:space="preserve">11.1651763916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102981567383</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062852859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.536111831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6288452148438</t>
+    <t xml:space="preserve">11.5361108779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6288461685181</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175647735596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9626893997192</t>
+    <t xml:space="preserve">11.9626874923706</t>
   </si>
   <si>
     <t xml:space="preserve">12.1481561660767</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">12.2408905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4449043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5932788848877</t>
+    <t xml:space="preserve">12.4449052810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.593279838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1852493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.573205947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5917510986328</t>
+    <t xml:space="preserve">11.5732069015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5917530059814</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401275634766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4804706573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9255933761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1110620498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1667032241821</t>
+    <t xml:space="preserve">11.4804716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.925594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.11106300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1667022705078</t>
   </si>
   <si>
     <t xml:space="preserve">12.2223434448242</t>
@@ -782,22 +782,22 @@
     <t xml:space="preserve">12.5190935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6860132217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
+    <t xml:space="preserve">12.686014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
   </si>
   <si>
     <t xml:space="preserve">13.26096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3536987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5020732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0584774017334</t>
+    <t xml:space="preserve">13.3536996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5020723342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584783554077</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649791717529</t>
@@ -806,34 +806,34 @@
     <t xml:space="preserve">13.2053241729736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1125907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3892641067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3521718978882</t>
+    <t xml:space="preserve">13.1125917434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3892650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3521709442139</t>
   </si>
   <si>
     <t xml:space="preserve">12.2965307235718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4078121185303</t>
+    <t xml:space="preserve">12.407811164856</t>
   </si>
   <si>
     <t xml:space="preserve">12.2037973403931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779846191406</t>
+    <t xml:space="preserve">12.2779836654663</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9101028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4093389511108</t>
+    <t xml:space="preserve">13.9101037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4093399047852</t>
   </si>
   <si>
     <t xml:space="preserve">13.1682319641113</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045602798462</t>
+    <t xml:space="preserve">12.7045593261719</t>
   </si>
   <si>
     <t xml:space="preserve">12.5561866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3707180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7787475585938</t>
+    <t xml:space="preserve">12.370719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7787485122681</t>
   </si>
   <si>
     <t xml:space="preserve">12.8158416748047</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">12.8900289535522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0940446853638</t>
+    <t xml:space="preserve">13.0940456390381</t>
   </si>
   <si>
     <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3351516723633</t>
+    <t xml:space="preserve">13.3351526260376</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569496154785</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">12.3150777816772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4634532928467</t>
+    <t xml:space="preserve">12.463451385498</t>
   </si>
   <si>
     <t xml:space="preserve">12.4263582229614</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">11.8514080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2950029373169</t>
+    <t xml:space="preserve">11.7772207260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2950038909912</t>
   </si>
   <si>
     <t xml:space="preserve">11.0168008804321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090989112854</t>
+    <t xml:space="preserve">11.0909872055054</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353479385376</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">11.3135499954224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2764549255371</t>
+    <t xml:space="preserve">11.1280832290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2764568328857</t>
   </si>
   <si>
     <t xml:space="preserve">11.2208156585693</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">11.3691892623901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177581787109</t>
+    <t xml:space="preserve">11.1095342636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177391052246</t>
   </si>
   <si>
     <t xml:space="preserve">9.40322875976562</t>
@@ -932,43 +932,43 @@
     <t xml:space="preserve">8.88391876220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55160427093506</t>
+    <t xml:space="preserve">9.55160331726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.71699810028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80973148345947</t>
+    <t xml:space="preserve">8.80973052978516</t>
   </si>
   <si>
     <t xml:space="preserve">8.20696067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24405574798584</t>
+    <t xml:space="preserve">8.24405479431152</t>
   </si>
   <si>
     <t xml:space="preserve">8.19768714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53153038024902</t>
+    <t xml:space="preserve">8.53152847290039</t>
   </si>
   <si>
     <t xml:space="preserve">8.43879508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64433765411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200517654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77416610717773</t>
+    <t xml:space="preserve">9.64433860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77416515350342</t>
   </si>
   <si>
     <t xml:space="preserve">10.2934761047363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2378349304199</t>
+    <t xml:space="preserve">10.2378358840942</t>
   </si>
   <si>
     <t xml:space="preserve">9.71852397918701</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">10.7015056610107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6844873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8699531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4819993972778</t>
+    <t xml:space="preserve">11.6844863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8699541091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4819984436035</t>
   </si>
   <si>
     <t xml:space="preserve">12.6118259429932</t>
@@ -1004,34 +1004,34 @@
     <t xml:space="preserve">13.650447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8930835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0414581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2439460754395</t>
+    <t xml:space="preserve">14.8930826187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0414571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2439441680908</t>
   </si>
   <si>
     <t xml:space="preserve">15.2825660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6148824691772</t>
+    <t xml:space="preserve">15.7462377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687986373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938474655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6148815155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.4665069580078</t>
@@ -1040,25 +1040,25 @@
     <t xml:space="preserve">14.0399303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">14.132664680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7988214492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8173694610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6689949035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0770225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3181324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076139450073</t>
+    <t xml:space="preserve">14.1326637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7988224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8173675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6689929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0770235061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3181343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076148986816</t>
   </si>
   <si>
     <t xml:space="preserve">14.9858160018921</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">14.5560483932495</t>
   </si>
   <si>
-    <t xml:space="preserve">14.79896068573</t>
+    <t xml:space="preserve">14.7989597320557</t>
   </si>
   <si>
     <t xml:space="preserve">14.8923902511597</t>
@@ -1079,7 +1079,10 @@
     <t xml:space="preserve">14.7615909576416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2660989761353</t>
+    <t xml:space="preserve">14.9858169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2661008834839</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287302017212</t>
@@ -1094,25 +1097,25 @@
     <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6121063232422</t>
+    <t xml:space="preserve">14.6121072769165</t>
   </si>
   <si>
     <t xml:space="preserve">15.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">14.911075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6494770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1353034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297609329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0231876373291</t>
+    <t xml:space="preserve">14.9110746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6494779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1353025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.929759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0231885910034</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
@@ -1121,28 +1124,28 @@
     <t xml:space="preserve">14.9484462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813079833984</t>
+    <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
     <t xml:space="preserve">15.5650682449341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1630077362061</t>
+    <t xml:space="preserve">16.1630058288574</t>
   </si>
   <si>
     <t xml:space="preserve">16.9664878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6765384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.723575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8730602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4336261749268</t>
+    <t xml:space="preserve">17.6765403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7235736846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8730583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4336242675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4149398803711</t>
@@ -1151,94 +1154,94 @@
     <t xml:space="preserve">17.3962535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7886543273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0128765106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8820781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2744770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3118495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6578540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5270538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9941940307617</t>
+    <t xml:space="preserve">17.7886524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0128784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8820762634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2744750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3118476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6578521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5270519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9941921234131</t>
   </si>
   <si>
     <t xml:space="preserve">18.6855583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1526966094971</t>
+    <t xml:space="preserve">19.1526947021484</t>
   </si>
   <si>
     <t xml:space="preserve">18.3305320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2184181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0315647125244</t>
+    <t xml:space="preserve">18.2184162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.031566619873</t>
   </si>
   <si>
     <t xml:space="preserve">17.3775691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9568214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4709968566895</t>
+    <t xml:space="preserve">17.9568195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4709987640381</t>
   </si>
   <si>
     <t xml:space="preserve">17.807336807251</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9291133880615</t>
+    <t xml:space="preserve">16.9291152954102</t>
   </si>
   <si>
     <t xml:space="preserve">16.667516708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266668319702</t>
+    <t xml:space="preserve">15.8266677856445</t>
   </si>
   <si>
     <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.957465171814</t>
+    <t xml:space="preserve">15.9574661254883</t>
   </si>
   <si>
     <t xml:space="preserve">15.378212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706108093262</t>
+    <t xml:space="preserve">15.7706089019775</t>
   </si>
   <si>
     <t xml:space="preserve">16.5367202758789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927791595459</t>
+    <t xml:space="preserve">16.5927772521973</t>
   </si>
   <si>
     <t xml:space="preserve">16.2938060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4246044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2751216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8543701171875</t>
+    <t xml:space="preserve">16.4246082305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2751197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8543720245361</t>
   </si>
   <si>
     <t xml:space="preserve">16.7048873901367</t>
@@ -1247,22 +1250,22 @@
     <t xml:space="preserve">16.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4993476867676</t>
+    <t xml:space="preserve">16.4993457794189</t>
   </si>
   <si>
     <t xml:space="preserve">16.3685474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3498611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862049102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6301460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114597320557</t>
+    <t xml:space="preserve">16.3498630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.63014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114616394043</t>
   </si>
   <si>
     <t xml:space="preserve">16.7609462738037</t>
@@ -1271,13 +1274,13 @@
     <t xml:space="preserve">16.8170013427734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7983169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434271812439</t>
+    <t xml:space="preserve">16.7983150482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7892961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4342708587646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671316146851</t>
@@ -1286,10 +1289,10 @@
     <t xml:space="preserve">14.6868476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5373640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.32151222229</t>
+    <t xml:space="preserve">14.5373630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3215141296387</t>
   </si>
   <si>
     <t xml:space="preserve">16.5180339813232</t>
@@ -1298,40 +1301,40 @@
     <t xml:space="preserve">15.6211252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8827238082886</t>
+    <t xml:space="preserve">15.8827228546143</t>
   </si>
   <si>
     <t xml:space="preserve">16.2377490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4806632995605</t>
+    <t xml:space="preserve">16.4806613922119</t>
   </si>
   <si>
     <t xml:space="preserve">16.8356876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4432926177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9477996826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0786018371582</t>
+    <t xml:space="preserve">16.4432888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9478015899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0785999298096</t>
   </si>
   <si>
     <t xml:space="preserve">16.648832321167</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9104290008545</t>
+    <t xml:space="preserve">16.9104309082031</t>
   </si>
   <si>
     <t xml:space="preserve">16.8917446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">17.900764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0876197814941</t>
+    <t xml:space="preserve">17.9007663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0876178741455</t>
   </si>
   <si>
     <t xml:space="preserve">18.5360736846924</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">16.574089050293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7422580718994</t>
+    <t xml:space="preserve">16.742259979248</t>
   </si>
   <si>
     <t xml:space="preserve">16.5554046630859</t>
@@ -1358,55 +1361,55 @@
     <t xml:space="preserve">17.0225429534912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.069580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8453540802002</t>
+    <t xml:space="preserve">16.0695819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8453531265259</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6024408340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0135250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9014091491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186777114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1636524200439</t>
+    <t xml:space="preserve">15.6024398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0135231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9014101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9761514663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3595275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
     <t xml:space="preserve">14.855019569397</t>
   </si>
   <si>
-    <t xml:space="preserve">15.50901222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6398105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6771802902222</t>
+    <t xml:space="preserve">15.5090131759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6398115158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6771812438965</t>
   </si>
   <si>
     <t xml:space="preserve">15.52769947052</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7145528793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716415405273</t>
+    <t xml:space="preserve">15.7145557403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716424942017</t>
   </si>
   <si>
     <t xml:space="preserve">15.452956199646</t>
@@ -1415,13 +1418,13 @@
     <t xml:space="preserve">15.6584968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8640403747559</t>
+    <t xml:space="preserve">15.8640394210815</t>
   </si>
   <si>
     <t xml:space="preserve">16.2190647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0972881317139</t>
+    <t xml:space="preserve">17.0972862243652</t>
   </si>
   <si>
     <t xml:space="preserve">17.1346569061279</t>
@@ -1430,7 +1433,7 @@
     <t xml:space="preserve">17.9381370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5831089019775</t>
+    <t xml:space="preserve">17.5831108093262</t>
   </si>
   <si>
     <t xml:space="preserve">17.7699642181396</t>
@@ -1454,16 +1457,16 @@
     <t xml:space="preserve">17.5644226074219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6017932891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7512817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7132663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8066921234131</t>
+    <t xml:space="preserve">17.6017951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.751277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.713264465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8066902160645</t>
   </si>
   <si>
     <t xml:space="preserve">19.4329814910889</t>
@@ -1478,34 +1481,34 @@
     <t xml:space="preserve">20.5541133880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4606876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2738304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1336860656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.946834564209</t>
+    <t xml:space="preserve">20.4606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.273832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1336879730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9468326568604</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6008281707764</t>
+    <t xml:space="preserve">20.600830078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.6475410461426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2081050872803</t>
+    <t xml:space="preserve">21.2081069946289</t>
   </si>
   <si>
     <t xml:space="preserve">21.5818214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">21.955530166626</t>
+    <t xml:space="preserve">21.9555320739746</t>
   </si>
   <si>
     <t xml:space="preserve">21.3015365600586</t>
@@ -1514,34 +1517,34 @@
     <t xml:space="preserve">20.8343982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0869750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7599754333496</t>
+    <t xml:space="preserve">20.0869770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7599773406982</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1994113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7350749969482</t>
+    <t xml:space="preserve">19.1994094848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7350769042969</t>
   </si>
   <si>
     <t xml:space="preserve">19.9700183868408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7820644378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4531497955322</t>
+    <t xml:space="preserve">19.7820663452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4531478881836</t>
   </si>
   <si>
     <t xml:space="preserve">19.5471248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001354217529</t>
+    <t xml:space="preserve">19.5001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">19.6880893707275</t>
@@ -1550,34 +1553,34 @@
     <t xml:space="preserve">19.030252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8422985076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1712169647217</t>
+    <t xml:space="preserve">18.8423004150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1712188720703</t>
   </si>
   <si>
     <t xml:space="preserve">19.0772399902344</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9362773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6410980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832649230957</t>
+    <t xml:space="preserve">18.936279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832668304443</t>
   </si>
   <si>
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290557861328</t>
+    <t xml:space="preserve">19.8290538787842</t>
   </si>
   <si>
     <t xml:space="preserve">19.2651920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4194068908691</t>
+    <t xml:space="preserve">18.4194049835205</t>
   </si>
   <si>
     <t xml:space="preserve">18.6261558532715</t>
@@ -1589,22 +1592,22 @@
     <t xml:space="preserve">18.7765159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5133819580078</t>
+    <t xml:space="preserve">18.5133800506592</t>
   </si>
   <si>
     <t xml:space="preserve">18.7953109741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6449508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639953613281</t>
+    <t xml:space="preserve">18.6449489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639934539795</t>
   </si>
   <si>
     <t xml:space="preserve">20.3929138183594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8158073425293</t>
+    <t xml:space="preserve">20.8158054351807</t>
   </si>
   <si>
     <t xml:space="preserve">21.2856903076172</t>
@@ -1613,25 +1616,25 @@
     <t xml:space="preserve">22.0844917297363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4603996276855</t>
+    <t xml:space="preserve">22.4603958129883</t>
   </si>
   <si>
     <t xml:space="preserve">22.9772701263428</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2122077941895</t>
+    <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
     <t xml:space="preserve">23.494140625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1652221679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0712413787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.58811378479</t>
+    <t xml:space="preserve">23.1652202606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0712432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5881156921387</t>
   </si>
   <si>
     <t xml:space="preserve">24.1989631652832</t>
@@ -1640,25 +1643,25 @@
     <t xml:space="preserve">23.7760677337646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7290802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0242557525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8363056182861</t>
+    <t xml:space="preserve">23.7290821075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0242576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8363018035889</t>
   </si>
   <si>
     <t xml:space="preserve">22.8832912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5411262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9302787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2591972351074</t>
+    <t xml:space="preserve">23.5411281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591953277588</t>
   </si>
   <si>
     <t xml:space="preserve">23.447151184082</t>
@@ -1670,7 +1673,7 @@
     <t xml:space="preserve">21.7555732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7085838317871</t>
+    <t xml:space="preserve">21.7085876464844</t>
   </si>
   <si>
     <t xml:space="preserve">22.1314792633057</t>
@@ -1694,7 +1697,7 @@
     <t xml:space="preserve">20.7688179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5808658599854</t>
+    <t xml:space="preserve">20.580867767334</t>
   </si>
   <si>
     <t xml:space="preserve">21.2387008666992</t>
@@ -1703,28 +1706,28 @@
     <t xml:space="preserve">21.8495483398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8098106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977645874023</t>
+    <t xml:space="preserve">24.8098087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977626800537</t>
   </si>
   <si>
     <t xml:space="preserve">24.4339046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3869152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4001636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6351051330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519756317139</t>
+    <t xml:space="preserve">24.3869171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4001617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.635103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519737243652</t>
   </si>
   <si>
     <t xml:space="preserve">23.8230590820312</t>
@@ -1733,22 +1736,22 @@
     <t xml:space="preserve">24.2929401397705</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9640235900879</t>
+    <t xml:space="preserve">23.9640216827393</t>
   </si>
   <si>
     <t xml:space="preserve">24.4808921813965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5616207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206581115723</t>
+    <t xml:space="preserve">25.5616245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
   </si>
   <si>
     <t xml:space="preserve">25.6555995941162</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3736724853516</t>
+    <t xml:space="preserve">25.3736705780029</t>
   </si>
   <si>
     <t xml:space="preserve">25.2796936035156</t>
@@ -1757,37 +1760,37 @@
     <t xml:space="preserve">23.3061847686768</t>
   </si>
   <si>
-    <t xml:space="preserve">22.554370880127</t>
+    <t xml:space="preserve">22.5543727874756</t>
   </si>
   <si>
     <t xml:space="preserve">22.2724437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1182346343994</t>
+    <t xml:space="preserve">23.118236541748</t>
   </si>
   <si>
     <t xml:space="preserve">24.2459506988525</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7158336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278797149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9170341491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0110111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8568019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6218566894531</t>
+    <t xml:space="preserve">24.7158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278835296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7628211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9170360565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0110092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8568000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6218585968018</t>
   </si>
   <si>
     <t xml:space="preserve">25.1857166290283</t>
@@ -1796,37 +1799,37 @@
     <t xml:space="preserve">25.138729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5206317901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1917133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266567230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4398994445801</t>
+    <t xml:space="preserve">21.5206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1917152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
   </si>
   <si>
     <t xml:space="preserve">21.8025608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8627967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326797485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3796653747559</t>
+    <t xml:space="preserve">20.8627948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3796672821045</t>
   </si>
   <si>
     <t xml:space="preserve">20.2519474029541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3459243774414</t>
+    <t xml:space="preserve">20.34592628479</t>
   </si>
   <si>
     <t xml:space="preserve">19.218204498291</t>
@@ -1835,10 +1838,10 @@
     <t xml:space="preserve">18.5697650909424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.674840927124</t>
+    <t xml:space="preserve">19.8760433197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6748447418213</t>
   </si>
   <si>
     <t xml:space="preserve">19.3591709136963</t>
@@ -1847,28 +1850,28 @@
     <t xml:space="preserve">18.2126579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3292751312256</t>
+    <t xml:space="preserve">17.3292770385742</t>
   </si>
   <si>
     <t xml:space="preserve">17.0473480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8218040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3066349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1938629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.663745880127</t>
+    <t xml:space="preserve">16.8218021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3066329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1938610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637439727783</t>
   </si>
   <si>
     <t xml:space="preserve">19.9230289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6615982055664</t>
+    <t xml:space="preserve">21.6615943908691</t>
   </si>
   <si>
     <t xml:space="preserve">21.990514755249</t>
@@ -1877,10 +1880,10 @@
     <t xml:space="preserve">22.3194332122803</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4736423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4868907928467</t>
+    <t xml:space="preserve">21.4736442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.486888885498</t>
   </si>
   <si>
     <t xml:space="preserve">20.2989368438721</t>
@@ -1892,7 +1895,7 @@
     <t xml:space="preserve">18.7389259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7013320922852</t>
+    <t xml:space="preserve">18.7013339996338</t>
   </si>
   <si>
     <t xml:space="preserve">21.8965358734131</t>
@@ -1901,34 +1904,34 @@
     <t xml:space="preserve">20.2049598693848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5338745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3254299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9683170318604</t>
+    <t xml:space="preserve">20.5338764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3254261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">17.8931369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2165031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977100372314</t>
+    <t xml:space="preserve">17.2165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977119445801</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9418792724609</t>
+    <t xml:space="preserve">16.9418773651123</t>
   </si>
   <si>
     <t xml:space="preserve">16.9039745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923091888428</t>
+    <t xml:space="preserve">16.3923072814941</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596530914307</t>
@@ -1940,7 +1943,7 @@
     <t xml:space="preserve">17.5293464660645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9652099609375</t>
+    <t xml:space="preserve">17.9652118682861</t>
   </si>
   <si>
     <t xml:space="preserve">17.813606262207</t>
@@ -1949,37 +1952,37 @@
     <t xml:space="preserve">18.2684230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2494735717773</t>
+    <t xml:space="preserve">18.2494716644287</t>
   </si>
   <si>
     <t xml:space="preserve">18.1736679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.950647354126</t>
+    <t xml:space="preserve">18.9506454467773</t>
   </si>
   <si>
     <t xml:space="preserve">18.6284866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5716342926025</t>
+    <t xml:space="preserve">18.5716323852539</t>
   </si>
   <si>
     <t xml:space="preserve">18.7800922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9462623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5905838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8507995605469</t>
+    <t xml:space="preserve">17.9462604522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5905818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8508014678955</t>
   </si>
   <si>
     <t xml:space="preserve">20.1824378967285</t>
@@ -1994,34 +1997,34 @@
     <t xml:space="preserve">20.9404621124268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8930854797363</t>
+    <t xml:space="preserve">20.893087387085</t>
   </si>
   <si>
     <t xml:space="preserve">21.0352153778076</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2771911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0775012969971</t>
+    <t xml:space="preserve">20.2771892547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0774993896484</t>
   </si>
   <si>
     <t xml:space="preserve">22.6933975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2670097351074</t>
+    <t xml:space="preserve">22.2670078277588</t>
   </si>
   <si>
     <t xml:space="preserve">22.4565143585205</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0301265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4616069793701</t>
+    <t xml:space="preserve">22.5986442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0301246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.6511116027832</t>
@@ -2033,79 +2036,79 @@
     <t xml:space="preserve">20.9878387451172</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7983341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4193210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6612949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9455528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2349052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5665397644043</t>
+    <t xml:space="preserve">20.7983322143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.419319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6612930297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9455547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2349033355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5665416717529</t>
   </si>
   <si>
     <t xml:space="preserve">20.0403079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7560482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1875286102295</t>
+    <t xml:space="preserve">19.756046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1875267028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.9980220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0453987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3631763458252</t>
+    <t xml:space="preserve">19.0453968048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3631744384766</t>
   </si>
   <si>
     <t xml:space="preserve">17.9273128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2305221557617</t>
+    <t xml:space="preserve">18.2305202484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.7188549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3821239471436</t>
+    <t xml:space="preserve">18.3821258544922</t>
   </si>
   <si>
     <t xml:space="preserve">17.7757053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7946548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357669830322</t>
+    <t xml:space="preserve">17.7946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357650756836</t>
   </si>
   <si>
     <t xml:space="preserve">19.0927772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.087682723999</t>
+    <t xml:space="preserve">20.0876846313477</t>
   </si>
   <si>
     <t xml:space="preserve">18.7990398406982</t>
@@ -2114,19 +2117,19 @@
     <t xml:space="preserve">18.1547183990479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2873725891113</t>
+    <t xml:space="preserve">18.28737449646</t>
   </si>
   <si>
     <t xml:space="preserve">18.5147819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0599632263184</t>
+    <t xml:space="preserve">18.059965133667</t>
   </si>
   <si>
     <t xml:space="preserve">18.2115707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">18.476879119873</t>
+    <t xml:space="preserve">18.4768772125244</t>
   </si>
   <si>
     <t xml:space="preserve">20.6562023162842</t>
@@ -2135,31 +2138,28 @@
     <t xml:space="preserve">20.6088275909424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5140743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5038890838623</t>
+    <t xml:space="preserve">20.5140762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5038928985596</t>
   </si>
   <si>
     <t xml:space="preserve">23.3092956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.162073135376</t>
+    <t xml:space="preserve">24.1620750427246</t>
   </si>
   <si>
     <t xml:space="preserve">24.7779693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3566722869873</t>
+    <t xml:space="preserve">23.3566703796387</t>
   </si>
   <si>
     <t xml:space="preserve">23.4040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6883068084717</t>
+    <t xml:space="preserve">23.6883087158203</t>
   </si>
   <si>
     <t xml:space="preserve">22.1248798370361</t>
@@ -2168,31 +2168,31 @@
     <t xml:space="preserve">22.8829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7881526947021</t>
+    <t xml:space="preserve">22.7881507873535</t>
   </si>
   <si>
     <t xml:space="preserve">23.0250339508057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1722564697266</t>
+    <t xml:space="preserve">22.1722545623779</t>
   </si>
   <si>
     <t xml:space="preserve">22.8355274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4514236450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3515777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.167163848877</t>
+    <t xml:space="preserve">23.4514217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3515796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1671657562256</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9827499389648</t>
+    <t xml:space="preserve">21.9827480316162</t>
   </si>
   <si>
     <t xml:space="preserve">22.5512676239014</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">21.7458667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6037368774414</t>
+    <t xml:space="preserve">21.6037349700928</t>
   </si>
   <si>
     <t xml:space="preserve">21.7932434082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6984882354736</t>
+    <t xml:space="preserve">21.6984901428223</t>
   </si>
   <si>
     <t xml:space="preserve">21.5563583374023</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">21.5089817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">23.49880027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6832160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9725666046143</t>
+    <t xml:space="preserve">23.4987983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6832141876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9725646972656</t>
   </si>
   <si>
     <t xml:space="preserve">24.2568264007568</t>
@@ -2264,31 +2264,31 @@
     <t xml:space="preserve">25.7255001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6358394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5359935760498</t>
+    <t xml:space="preserve">24.6358375549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5359954833984</t>
   </si>
   <si>
     <t xml:space="preserve">25.772876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3464870452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5935554504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5461769104004</t>
+    <t xml:space="preserve">25.3464889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5935535430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.546178817749</t>
   </si>
   <si>
     <t xml:space="preserve">23.1197872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9776554107666</t>
+    <t xml:space="preserve">23.2619152069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9776573181152</t>
   </si>
   <si>
     <t xml:space="preserve">23.2145404815674</t>
@@ -2303,28 +2303,28 @@
     <t xml:space="preserve">23.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7830581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3194751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6460227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.361759185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622310638428</t>
+    <t xml:space="preserve">23.7830600738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3194770812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6460208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3617630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622291564941</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4835300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3887748718262</t>
+    <t xml:space="preserve">26.483528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3887729644775</t>
   </si>
   <si>
     <t xml:space="preserve">26.6256561279297</t>
@@ -2333,25 +2333,25 @@
     <t xml:space="preserve">26.1992664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.820255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5309047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6730308532715</t>
+    <t xml:space="preserve">25.8202533721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5309028625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6730327606201</t>
   </si>
   <si>
     <t xml:space="preserve">26.3201923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7480125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6526489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843376159668</t>
+    <t xml:space="preserve">25.7480144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6526508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8433742523193</t>
   </si>
   <si>
     <t xml:space="preserve">25.6049690246582</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">25.891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0817832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5096035003662</t>
+    <t xml:space="preserve">26.0817813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5096054077148</t>
   </si>
   <si>
     <t xml:space="preserve">26.1294651031494</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">25.9387378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7956943511963</t>
+    <t xml:space="preserve">25.7956962585449</t>
   </si>
   <si>
     <t xml:space="preserve">25.12815284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.223518371582</t>
+    <t xml:space="preserve">25.2235164642334</t>
   </si>
   <si>
     <t xml:space="preserve">25.2711982727051</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">24.9851093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1758346557617</t>
+    <t xml:space="preserve">25.1758327484131</t>
   </si>
   <si>
     <t xml:space="preserve">24.5559749603271</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">24.6990203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9361133575439</t>
+    <t xml:space="preserve">23.9361152648926</t>
   </si>
   <si>
     <t xml:space="preserve">24.937427520752</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">24.8420639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5082931518555</t>
+    <t xml:space="preserve">24.5082912445068</t>
   </si>
   <si>
     <t xml:space="preserve">23.8884334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.222204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6977081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8407535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3175678253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.079158782959</t>
+    <t xml:space="preserve">24.2222061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6977062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8407516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.317569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0791606903076</t>
   </si>
   <si>
     <t xml:space="preserve">24.6513366699219</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">22.9824848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871212005615</t>
+    <t xml:space="preserve">22.8871231079102</t>
   </si>
   <si>
     <t xml:space="preserve">22.0288562774658</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">21.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1705875396729</t>
+    <t xml:space="preserve">21.1705894470215</t>
   </si>
   <si>
     <t xml:space="preserve">21.0752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9321804046631</t>
+    <t xml:space="preserve">20.9321784973145</t>
   </si>
   <si>
     <t xml:space="preserve">20.5984115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136310577393</t>
+    <t xml:space="preserve">21.3136329650879</t>
   </si>
   <si>
     <t xml:space="preserve">21.6474018096924</t>
@@ -2495,10 +2495,10 @@
     <t xml:space="preserve">20.8368167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.88450050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0739116668701</t>
+    <t xml:space="preserve">20.8844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0739135742188</t>
   </si>
   <si>
     <t xml:space="preserve">21.1229057312012</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">20.6460933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.939094543457</t>
+    <t xml:space="preserve">18.9390926361084</t>
   </si>
   <si>
     <t xml:space="preserve">19.4063720703125</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">18.6339321136475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5385684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5194969177246</t>
+    <t xml:space="preserve">18.5385704040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.519495010376</t>
   </si>
   <si>
     <t xml:space="preserve">18.0426826477051</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">17.6993732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8710269927979</t>
+    <t xml:space="preserve">17.8710289001465</t>
   </si>
   <si>
     <t xml:space="preserve">18.7674388885498</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">20.2169570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8355045318604</t>
+    <t xml:space="preserve">19.835506439209</t>
   </si>
   <si>
     <t xml:space="preserve">20.5030479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.789134979248</t>
+    <t xml:space="preserve">20.7891368865967</t>
   </si>
   <si>
     <t xml:space="preserve">21.7904472351074</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">19.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7894744873047</t>
+    <t xml:space="preserve">19.7894763946533</t>
   </si>
   <si>
     <t xml:space="preserve">20.5751628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9188995361328</t>
+    <t xml:space="preserve">20.9188976287842</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">22.6375885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">22.883113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7849044799805</t>
+    <t xml:space="preserve">22.8831157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7849063873291</t>
   </si>
   <si>
     <t xml:space="preserve">21.9010066986084</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">21.6554794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2268524169922</t>
+    <t xml:space="preserve">23.2268543243408</t>
   </si>
   <si>
     <t xml:space="preserve">24.0125408172607</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">22.6866931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340110778809</t>
+    <t xml:space="preserve">22.8340091705322</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5393772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1956405639648</t>
+    <t xml:space="preserve">22.539379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1956386566162</t>
   </si>
   <si>
     <t xml:space="preserve">22.4902725219727</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">22.4411659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7045860290527</t>
+    <t xml:space="preserve">21.7045879364014</t>
   </si>
   <si>
     <t xml:space="preserve">22.293851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8519039154053</t>
+    <t xml:space="preserve">21.8519020080566</t>
   </si>
   <si>
     <t xml:space="preserve">22.2447452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501132965088</t>
+    <t xml:space="preserve">21.9501152038574</t>
   </si>
   <si>
     <t xml:space="preserve">22.3429565429688</t>
@@ -2681,22 +2681,22 @@
     <t xml:space="preserve">21.6063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.017110824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4590587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1153202056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4099540710449</t>
+    <t xml:space="preserve">21.2135334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0171089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4590606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1153221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4099521636963</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403697967529</t>
@@ -2708,10 +2708,10 @@
     <t xml:space="preserve">19.6028747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3278865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9350414276123</t>
+    <t xml:space="preserve">19.3278846740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9350433349609</t>
   </si>
   <si>
     <t xml:space="preserve">18.954683303833</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">19.5046634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1823196411133</t>
+    <t xml:space="preserve">20.1823177337646</t>
   </si>
   <si>
     <t xml:space="preserve">20.1332130432129</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">19.985897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6912631988525</t>
+    <t xml:space="preserve">19.6912651062012</t>
   </si>
   <si>
     <t xml:space="preserve">19.5832328796387</t>
@@ -2759,16 +2759,16 @@
     <t xml:space="preserve">19.3671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7386207580566</t>
+    <t xml:space="preserve">18.738618850708</t>
   </si>
   <si>
     <t xml:space="preserve">18.4047031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1689987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2279243469238</t>
+    <t xml:space="preserve">18.1689968109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2279224395752</t>
   </si>
   <si>
     <t xml:space="preserve">18.0904293060303</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">18.1493549346924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7172298431396</t>
+    <t xml:space="preserve">17.717227935791</t>
   </si>
   <si>
     <t xml:space="preserve">18.6796951293945</t>
@@ -2789,22 +2789,22 @@
     <t xml:space="preserve">18.6404094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5029144287109</t>
+    <t xml:space="preserve">18.5029125213623</t>
   </si>
   <si>
     <t xml:space="preserve">18.8761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4225940704346</t>
+    <t xml:space="preserve">17.4225959777832</t>
   </si>
   <si>
     <t xml:space="preserve">18.2868518829346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2475662231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547607421875</t>
+    <t xml:space="preserve">18.2475643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547626495361</t>
   </si>
   <si>
     <t xml:space="preserve">18.4832706451416</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">17.9529342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1297130584717</t>
+    <t xml:space="preserve">18.129711151123</t>
   </si>
   <si>
     <t xml:space="preserve">17.5208072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2654571533203</t>
+    <t xml:space="preserve">17.2654590606689</t>
   </si>
   <si>
     <t xml:space="preserve">17.3243827819824</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">17.4618797302246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1083221435547</t>
+    <t xml:space="preserve">17.1083202362061</t>
   </si>
   <si>
     <t xml:space="preserve">17.2458152770996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7744026184082</t>
+    <t xml:space="preserve">16.7744045257568</t>
   </si>
   <si>
     <t xml:space="preserve">16.9904670715332</t>
@@ -3510,6 +3510,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.4500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8500003814697</t>
   </si>
 </sst>
 </file>
@@ -17334,7 +17337,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17360,7 +17363,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17412,7 +17415,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17438,7 +17441,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17464,7 +17467,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17490,7 +17493,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17516,7 +17519,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17542,7 +17545,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17568,7 +17571,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17594,7 +17597,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17620,7 +17623,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17646,7 +17649,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17672,7 +17675,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17698,7 +17701,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17724,7 +17727,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17750,7 +17753,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17776,7 +17779,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17802,7 +17805,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17828,7 +17831,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17854,7 +17857,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17880,7 +17883,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17906,7 +17909,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17958,7 +17961,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17984,7 +17987,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18010,7 +18013,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18036,7 +18039,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -18062,7 +18065,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18088,7 +18091,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18114,7 +18117,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18140,7 +18143,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18166,7 +18169,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18192,7 +18195,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18218,7 +18221,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18244,7 +18247,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18270,7 +18273,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18296,7 +18299,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18322,7 +18325,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18348,7 +18351,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18374,7 +18377,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18400,7 +18403,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18426,7 +18429,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18452,7 +18455,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18478,7 +18481,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18504,7 +18507,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18530,7 +18533,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18556,7 +18559,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18582,7 +18585,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18608,7 +18611,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18634,7 +18637,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18660,7 +18663,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18686,7 +18689,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18712,7 +18715,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18738,7 +18741,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18764,7 +18767,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18790,7 +18793,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18816,7 +18819,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18842,7 +18845,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18868,7 +18871,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18894,7 +18897,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18920,7 +18923,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18946,7 +18949,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18972,7 +18975,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18998,7 +19001,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19024,7 +19027,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -19050,7 +19053,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -19076,7 +19079,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19102,7 +19105,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19128,7 +19131,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19154,7 +19157,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19180,7 +19183,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19206,7 +19209,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19232,7 +19235,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19258,7 +19261,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19284,7 +19287,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19310,7 +19313,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19336,7 +19339,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19362,7 +19365,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19388,7 +19391,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19414,7 +19417,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19440,7 +19443,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19466,7 +19469,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19492,7 +19495,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19518,7 +19521,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19544,7 +19547,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19570,7 +19573,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19596,7 +19599,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19622,7 +19625,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19648,7 +19651,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19674,7 +19677,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19700,7 +19703,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19726,7 +19729,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19752,7 +19755,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19778,7 +19781,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19804,7 +19807,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19830,7 +19833,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19856,7 +19859,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19882,7 +19885,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19908,7 +19911,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19934,7 +19937,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19960,7 +19963,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19986,7 +19989,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20012,7 +20015,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -20038,7 +20041,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20064,7 +20067,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20090,7 +20093,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20116,7 +20119,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20142,7 +20145,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20168,7 +20171,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20194,7 +20197,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20220,7 +20223,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20246,7 +20249,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20272,7 +20275,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20298,7 +20301,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20324,7 +20327,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20350,7 +20353,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20376,7 +20379,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20402,7 +20405,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20428,7 +20431,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20454,7 +20457,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20480,7 +20483,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20506,7 +20509,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20532,7 +20535,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20558,7 +20561,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20584,7 +20587,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20610,7 +20613,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20636,7 +20639,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20662,7 +20665,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20688,7 +20691,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20714,7 +20717,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20740,7 +20743,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20766,7 +20769,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20792,7 +20795,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20818,7 +20821,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20844,7 +20847,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20870,7 +20873,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20896,7 +20899,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20922,7 +20925,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20948,7 +20951,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20974,7 +20977,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21000,7 +21003,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -21026,7 +21029,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21052,7 +21055,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21078,7 +21081,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21104,7 +21107,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21130,7 +21133,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21156,7 +21159,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21182,7 +21185,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21208,7 +21211,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21234,7 +21237,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21260,7 +21263,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21286,7 +21289,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21312,7 +21315,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21338,7 +21341,7 @@
         <v>17.6916809082031</v>
       </c>
       <c r="G673" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21364,7 +21367,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21390,7 +21393,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21416,7 +21419,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21442,7 +21445,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21468,7 +21471,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21494,7 +21497,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21520,7 +21523,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21546,7 +21549,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21572,7 +21575,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21598,7 +21601,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21624,7 +21627,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21650,7 +21653,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21676,7 +21679,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21702,7 +21705,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21728,7 +21731,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21754,7 +21757,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21780,7 +21783,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21806,7 +21809,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21832,7 +21835,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21858,7 +21861,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21884,7 +21887,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21910,7 +21913,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21962,7 +21965,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21988,7 +21991,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22014,7 +22017,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22040,7 +22043,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22066,7 +22069,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22092,7 +22095,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22118,7 +22121,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22144,7 +22147,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22170,7 +22173,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22196,7 +22199,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22222,7 +22225,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22248,7 +22251,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22274,7 +22277,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22300,7 +22303,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22326,7 +22329,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22352,7 +22355,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22378,7 +22381,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22404,7 +22407,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22430,7 +22433,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22456,7 +22459,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22482,7 +22485,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22508,7 +22511,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22534,7 +22537,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22560,7 +22563,7 @@
         <v>18.2742824554443</v>
       </c>
       <c r="G720" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22586,7 +22589,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22612,7 +22615,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22638,7 +22641,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22664,7 +22667,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22690,7 +22693,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22716,7 +22719,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22742,7 +22745,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22768,7 +22771,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22794,7 +22797,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22820,7 +22823,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22846,7 +22849,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22872,7 +22875,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22898,7 +22901,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22924,7 +22927,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22950,7 +22953,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22976,7 +22979,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23002,7 +23005,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23028,7 +23031,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23054,7 +23057,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23080,7 +23083,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23106,7 +23109,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G741" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23132,7 +23135,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23158,7 +23161,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23184,7 +23187,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23210,7 +23213,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23236,7 +23239,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23262,7 +23265,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23288,7 +23291,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23314,7 +23317,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23340,7 +23343,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23366,7 +23369,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23392,7 +23395,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23418,7 +23421,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23444,7 +23447,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23470,7 +23473,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23496,7 +23499,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23522,7 +23525,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23548,7 +23551,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23574,7 +23577,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23600,7 +23603,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23626,7 +23629,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23652,7 +23655,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23678,7 +23681,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G763" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23704,7 +23707,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23730,7 +23733,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23756,7 +23759,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23782,7 +23785,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23808,7 +23811,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G768" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23834,7 +23837,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23860,7 +23863,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23886,7 +23889,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23912,7 +23915,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23938,7 +23941,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23964,7 +23967,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23990,7 +23993,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24016,7 +24019,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24042,7 +24045,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24068,7 +24071,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24094,7 +24097,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24120,7 +24123,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24146,7 +24149,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24172,7 +24175,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24198,7 +24201,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24224,7 +24227,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24250,7 +24253,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24276,7 +24279,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24302,7 +24305,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24328,7 +24331,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24354,7 +24357,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24380,7 +24383,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24406,7 +24409,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24432,7 +24435,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24458,7 +24461,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24484,7 +24487,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24510,7 +24513,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24536,7 +24539,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24562,7 +24565,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24588,7 +24591,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24614,7 +24617,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G799" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24640,7 +24643,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24666,7 +24669,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24692,7 +24695,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24718,7 +24721,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24744,7 +24747,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24770,7 +24773,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24796,7 +24799,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24822,7 +24825,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24848,7 +24851,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24874,7 +24877,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24900,7 +24903,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24926,7 +24929,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24952,7 +24955,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24978,7 +24981,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25004,7 +25007,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25030,7 +25033,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25056,7 +25059,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25082,7 +25085,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25108,7 +25111,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25134,7 +25137,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25160,7 +25163,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25186,7 +25189,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25212,7 +25215,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25238,7 +25241,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25264,7 +25267,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25290,7 +25293,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25316,7 +25319,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25342,7 +25345,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25368,7 +25371,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25394,7 +25397,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25420,7 +25423,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25446,7 +25449,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25472,7 +25475,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25498,7 +25501,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25524,7 +25527,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25550,7 +25553,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25576,7 +25579,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25602,7 +25605,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25628,7 +25631,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25654,7 +25657,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25680,7 +25683,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25706,7 +25709,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25732,7 +25735,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25758,7 +25761,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G843" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25784,7 +25787,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25810,7 +25813,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25836,7 +25839,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25862,7 +25865,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G847" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25888,7 +25891,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25914,7 +25917,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25940,7 +25943,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25966,7 +25969,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25992,7 +25995,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26018,7 +26021,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26044,7 +26047,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26070,7 +26073,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26096,7 +26099,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26122,7 +26125,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26148,7 +26151,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26174,7 +26177,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26200,7 +26203,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26226,7 +26229,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26252,7 +26255,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26278,7 +26281,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26304,7 +26307,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26330,7 +26333,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26356,7 +26359,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26382,7 +26385,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26408,7 +26411,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26434,7 +26437,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26460,7 +26463,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26486,7 +26489,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G871" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26512,7 +26515,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26538,7 +26541,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G873" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26564,7 +26567,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26590,7 +26593,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26616,7 +26619,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26642,7 +26645,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26668,7 +26671,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26694,7 +26697,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26720,7 +26723,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26746,7 +26749,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26772,7 +26775,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26798,7 +26801,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26824,7 +26827,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26850,7 +26853,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26876,7 +26879,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26902,7 +26905,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26928,7 +26931,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26954,7 +26957,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26980,7 +26983,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27006,7 +27009,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27032,7 +27035,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27058,7 +27061,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27084,7 +27087,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G894" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27110,7 +27113,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27136,7 +27139,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27162,7 +27165,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27188,7 +27191,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27214,7 +27217,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27240,7 +27243,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27266,7 +27269,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27292,7 +27295,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27318,7 +27321,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27344,7 +27347,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27370,7 +27373,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27396,7 +27399,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27422,7 +27425,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27448,7 +27451,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27474,7 +27477,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27500,7 +27503,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27526,7 +27529,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27552,7 +27555,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G912" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27578,7 +27581,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27604,7 +27607,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27630,7 +27633,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27656,7 +27659,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27682,7 +27685,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27708,7 +27711,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27734,7 +27737,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27760,7 +27763,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27786,7 +27789,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27812,7 +27815,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27838,7 +27841,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27864,7 +27867,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27890,7 +27893,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27916,7 +27919,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27942,7 +27945,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27968,7 +27971,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27994,7 +27997,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28020,7 +28023,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28046,7 +28049,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28072,7 +28075,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G932" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28098,7 +28101,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28124,7 +28127,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28150,7 +28153,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28176,7 +28179,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28202,7 +28205,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28228,7 +28231,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28254,7 +28257,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28280,7 +28283,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28306,7 +28309,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28332,7 +28335,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28358,7 +28361,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28384,7 +28387,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28410,7 +28413,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28436,7 +28439,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28462,7 +28465,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28488,7 +28491,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28514,7 +28517,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28540,7 +28543,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28566,7 +28569,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28592,7 +28595,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28618,7 +28621,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28644,7 +28647,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28670,7 +28673,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28696,7 +28699,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28722,7 +28725,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28748,7 +28751,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28774,7 +28777,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28800,7 +28803,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28826,7 +28829,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28852,7 +28855,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28878,7 +28881,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28904,7 +28907,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28930,7 +28933,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28956,7 +28959,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28982,7 +28985,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29008,7 +29011,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29034,7 +29037,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29060,7 +29063,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29086,7 +29089,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29112,7 +29115,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29138,7 +29141,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29164,7 +29167,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29190,7 +29193,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29216,7 +29219,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29242,7 +29245,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29268,7 +29271,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29294,7 +29297,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29320,7 +29323,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29346,7 +29349,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G981" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29372,7 +29375,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29398,7 +29401,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29424,7 +29427,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29450,7 +29453,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29476,7 +29479,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29502,7 +29505,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G987" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29528,7 +29531,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29554,7 +29557,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29580,7 +29583,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29606,7 +29609,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29632,7 +29635,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29658,7 +29661,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G993" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29684,7 +29687,7 @@
         <v>19.3618068695068</v>
       </c>
       <c r="G994" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29710,7 +29713,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29736,7 +29739,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29762,7 +29765,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29788,7 +29791,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29814,7 +29817,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29840,7 +29843,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29866,7 +29869,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1001" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29892,7 +29895,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29918,7 +29921,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29944,7 +29947,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29970,7 +29973,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29996,7 +29999,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30022,7 +30025,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30048,7 +30051,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30074,7 +30077,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30100,7 +30103,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30126,7 +30129,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30152,7 +30155,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30178,7 +30181,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30204,7 +30207,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30230,7 +30233,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30256,7 +30259,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30282,7 +30285,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G1017" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30308,7 +30311,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30334,7 +30337,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30360,7 +30363,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30386,7 +30389,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30412,7 +30415,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30438,7 +30441,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30464,7 +30467,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30490,7 +30493,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30516,7 +30519,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30542,7 +30545,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30568,7 +30571,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30594,7 +30597,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30620,7 +30623,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1030" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30646,7 +30649,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1031" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30672,7 +30675,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30698,7 +30701,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30724,7 +30727,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30750,7 +30753,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30776,7 +30779,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30802,7 +30805,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30828,7 +30831,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30854,7 +30857,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G1039" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30880,7 +30883,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30906,7 +30909,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30932,7 +30935,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30958,7 +30961,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30984,7 +30987,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31010,7 +31013,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31036,7 +31039,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31062,7 +31065,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31088,7 +31091,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31114,7 +31117,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1049" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31140,7 +31143,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31166,7 +31169,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31192,7 +31195,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31218,7 +31221,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31244,7 +31247,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31270,7 +31273,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31296,7 +31299,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31322,7 +31325,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31348,7 +31351,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31374,7 +31377,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31400,7 +31403,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1060" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31426,7 +31429,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31452,7 +31455,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31478,7 +31481,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1063" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31504,7 +31507,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31530,7 +31533,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31556,7 +31559,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31582,7 +31585,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31608,7 +31611,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31634,7 +31637,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1069" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31660,7 +31663,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31686,7 +31689,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31712,7 +31715,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31738,7 +31741,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31764,7 +31767,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31790,7 +31793,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31816,7 +31819,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31842,7 +31845,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31868,7 +31871,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31894,7 +31897,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31920,7 +31923,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31946,7 +31949,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31972,7 +31975,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31998,7 +32001,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32024,7 +32027,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32050,7 +32053,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32076,7 +32079,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32102,7 +32105,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32128,7 +32131,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32154,7 +32157,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32180,7 +32183,7 @@
         <v>18.6821041107178</v>
       </c>
       <c r="G1090" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32206,7 +32209,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32232,7 +32235,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32258,7 +32261,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32284,7 +32287,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G1094" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32310,7 +32313,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32336,7 +32339,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32362,7 +32365,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32388,7 +32391,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32414,7 +32417,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32440,7 +32443,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32466,7 +32469,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32492,7 +32495,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32518,7 +32521,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32544,7 +32547,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32570,7 +32573,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32596,7 +32599,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32622,7 +32625,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32648,7 +32651,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32674,7 +32677,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32700,7 +32703,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32726,7 +32729,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G1111" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32752,7 +32755,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32778,7 +32781,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32804,7 +32807,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32830,7 +32833,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32856,7 +32859,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32882,7 +32885,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32908,7 +32911,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32934,7 +32937,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32960,7 +32963,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32986,7 +32989,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33012,7 +33015,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33038,7 +33041,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1123" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33064,7 +33067,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33090,7 +33093,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1125" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33116,7 +33119,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33142,7 +33145,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33168,7 +33171,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33194,7 +33197,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33220,7 +33223,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33246,7 +33249,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33272,7 +33275,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33298,7 +33301,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>714</v>
+        <v>548</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33324,7 +33327,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33376,7 +33379,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33402,7 +33405,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>714</v>
+        <v>548</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33428,7 +33431,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33480,7 +33483,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33740,7 +33743,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33922,7 +33925,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33948,7 +33951,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34000,7 +34003,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34026,7 +34029,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1161" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34052,7 +34055,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1162" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34182,7 +34185,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34416,7 +34419,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1176" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34442,7 +34445,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>714</v>
+        <v>548</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34494,7 +34497,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34520,7 +34523,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34624,7 +34627,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34676,7 +34679,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34754,7 +34757,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34962,7 +34965,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35404,7 +35407,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35456,7 +35459,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>714</v>
+        <v>548</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35976,7 +35979,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36002,7 +36005,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36054,7 +36057,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36106,7 +36109,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36262,7 +36265,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36314,7 +36317,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36574,7 +36577,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>714</v>
+        <v>548</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36600,7 +36603,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36626,7 +36629,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -52754,7 +52757,7 @@
     </row>
     <row r="1882">
       <c r="A1882" s="1" t="n">
-        <v>45964.6911342593</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1882" t="n">
         <v>40260</v>
@@ -52775,6 +52778,32 @@
         <v>1165</v>
       </c>
       <c r="H1882" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="1" t="n">
+        <v>45965.6911921296</v>
+      </c>
+      <c r="B1883" t="n">
+        <v>32820</v>
+      </c>
+      <c r="C1883" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="D1883" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="E1883" t="n">
+        <v>22.3500003814697</v>
+      </c>
+      <c r="F1883" t="n">
+        <v>21.8500003814697</v>
+      </c>
+      <c r="G1883" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H1883" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="1168">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125925064087</t>
+    <t xml:space="preserve">7.58125829696655</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099414825439</t>
+    <t xml:space="preserve">7.90288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099271774292</t>
   </si>
   <si>
     <t xml:space="preserve">7.71910047531128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68969202041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348175048828</t>
+    <t xml:space="preserve">7.68969249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348079681396</t>
   </si>
   <si>
     <t xml:space="preserve">7.96721315383911</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">7.67407035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.976402759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.302818775177</t>
+    <t xml:space="preserve">7.97640180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44433641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30281972885132</t>
   </si>
   <si>
     <t xml:space="preserve">7.52520275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46639108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206916809082</t>
+    <t xml:space="preserve">7.46639060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57206869125366</t>
   </si>
   <si>
     <t xml:space="preserve">7.4434175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52612209320068</t>
+    <t xml:space="preserve">7.52612161636353</t>
   </si>
   <si>
     <t xml:space="preserve">7.54450082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64742183685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180501937866</t>
+    <t xml:space="preserve">7.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8018045425415</t>
   </si>
   <si>
     <t xml:space="preserve">7.8569393157959</t>
@@ -104,61 +104,61 @@
     <t xml:space="preserve">7.92218542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00397109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86612939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01959228515625</t>
+    <t xml:space="preserve">8.00397205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86612844467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01959323883057</t>
   </si>
   <si>
     <t xml:space="preserve">7.81466865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76504707336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142755508423</t>
+    <t xml:space="preserve">7.7650465965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142612457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.69336891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74666690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910341262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56379890441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67315196990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7852635383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74850606918335</t>
+    <t xml:space="preserve">7.79261445999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74666786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56379842758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67315149307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78526401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74850559234619</t>
   </si>
   <si>
     <t xml:space="preserve">7.99478197097778</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06002616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11424446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30354499816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46344089508057</t>
+    <t xml:space="preserve">8.06002521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11424350738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46344184875488</t>
   </si>
   <si>
     <t xml:space="preserve">8.48641395568848</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">8.75382423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95966815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60128307342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28884315490723</t>
+    <t xml:space="preserve">8.95966911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60128116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28884124755859</t>
   </si>
   <si>
     <t xml:space="preserve">8.25208377838135</t>
@@ -182,46 +182,46 @@
     <t xml:space="preserve">8.46987342834473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3623571395874</t>
+    <t xml:space="preserve">8.36235809326172</t>
   </si>
   <si>
     <t xml:space="preserve">8.45425224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7115535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74831199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61598491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66560745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7942590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00561618804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86869335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11588954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14345645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09751224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680698394775</t>
+    <t xml:space="preserve">8.71155452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74831295013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6159839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66560935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79426002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86869430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11588859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14345741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09751129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.99091148376465</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">9.06167030334473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02399349212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76577091217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99367046356201</t>
+    <t xml:space="preserve">9.02399253845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76577186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99366855621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.04237365722656</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">8.90177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67112064361572</t>
+    <t xml:space="preserve">8.67112159729004</t>
   </si>
   <si>
     <t xml:space="preserve">8.50754928588867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98191452026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30630302429199</t>
+    <t xml:space="preserve">7.98191595077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30630207061768</t>
   </si>
   <si>
     <t xml:space="preserve">8.40830421447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54614543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59209251403809</t>
+    <t xml:space="preserve">8.54614734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59209442138672</t>
   </si>
   <si>
     <t xml:space="preserve">8.63803958892822</t>
@@ -278,16 +278,16 @@
     <t xml:space="preserve">8.02970027923584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75126218795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126703262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34214019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7749605178833</t>
+    <t xml:space="preserve">7.7512640953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126607894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34214115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77496147155762</t>
   </si>
   <si>
     <t xml:space="preserve">8.77771854400635</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">8.50571250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59944438934326</t>
+    <t xml:space="preserve">8.59944343566895</t>
   </si>
   <si>
     <t xml:space="preserve">8.70144653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57738876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39268207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34121990203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5608491897583</t>
+    <t xml:space="preserve">8.57739067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39268112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34122276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085014343262</t>
   </si>
   <si>
     <t xml:space="preserve">8.71982479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0545129776001</t>
+    <t xml:space="preserve">8.05451202392578</t>
   </si>
   <si>
     <t xml:space="preserve">8.04164791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08667469024658</t>
+    <t xml:space="preserve">8.0866756439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.18867683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.548903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33479118347168</t>
+    <t xml:space="preserve">8.54890155792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33478832244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.50938892364502</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">8.9210729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03869724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437191009521</t>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9743709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.01664257049561</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">8.85582828521729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30446338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27046394348145</t>
+    <t xml:space="preserve">8.30446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23370361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27046298980713</t>
   </si>
   <si>
     <t xml:space="preserve">8.33754634857178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20062255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40371036529541</t>
+    <t xml:space="preserve">8.20062351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40370941162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.27413940429688</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">8.35408687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22083854675293</t>
+    <t xml:space="preserve">8.22084045410156</t>
   </si>
   <si>
     <t xml:space="preserve">8.15283966064453</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48365688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70971584320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77128505706787</t>
+    <t xml:space="preserve">8.48365783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.709716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77128601074219</t>
   </si>
   <si>
     <t xml:space="preserve">8.72074413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10026550292969</t>
+    <t xml:space="preserve">9.10026741027832</t>
   </si>
   <si>
     <t xml:space="preserve">9.06534671783447</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">8.83469390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97712898254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05156230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23535060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2059440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36216449737549</t>
+    <t xml:space="preserve">8.97712802886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05156135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20594501495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36216354370117</t>
   </si>
   <si>
     <t xml:space="preserve">9.3952465057373</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">9.61027812957764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64887237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69482040405273</t>
+    <t xml:space="preserve">9.64887428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69482231140137</t>
   </si>
   <si>
     <t xml:space="preserve">9.59373760223389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64335918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989192962646</t>
+    <t xml:space="preserve">9.64336109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3198938369751</t>
   </si>
   <si>
     <t xml:space="preserve">9.6176290512085</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">9.46324729919434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33091926574707</t>
+    <t xml:space="preserve">9.33092021942139</t>
   </si>
   <si>
     <t xml:space="preserve">9.12875461578369</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">9.26291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14713191986084</t>
+    <t xml:space="preserve">9.14713382720947</t>
   </si>
   <si>
     <t xml:space="preserve">9.06075096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94128894805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37798023223877</t>
+    <t xml:space="preserve">8.94128799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37797927856445</t>
   </si>
   <si>
     <t xml:space="preserve">8.76025772094727</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">9.39157104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74076747894287</t>
+    <t xml:space="preserve">9.7407693862915</t>
   </si>
   <si>
     <t xml:space="preserve">9.46508598327637</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">9.53860092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75914764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68563270568848</t>
+    <t xml:space="preserve">9.75914669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68563175201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.90617656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532083511353</t>
+    <t xml:space="preserve">9.99807071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532073974609</t>
   </si>
   <si>
     <t xml:space="preserve">9.79590511322021</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">9.92455673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81428241729736</t>
+    <t xml:space="preserve">9.81428337097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.94293594360352</t>
@@ -569,121 +569,124 @@
     <t xml:space="preserve">10.0715866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1083431243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6672534942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77752494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83266067504883</t>
+    <t xml:space="preserve">10.108344078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66725254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77752685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83266162872314</t>
   </si>
   <si>
     <t xml:space="preserve">9.86941814422607</t>
   </si>
   <si>
+    <t xml:space="preserve">10.1451025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.163480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105115890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0348281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0164499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267223358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5126800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6045722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659707069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7332220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207849502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97969436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85103988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88544750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253875732422</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.1451015472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.163480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0348310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0164489746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267223358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.512677192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6045713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597080230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7332239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4759206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97969341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85104084014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821956634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.941086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99672698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.200740814209</t>
+    <t xml:space="preserve">9.99672603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">10.2192878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0894622802734</t>
+    <t xml:space="preserve">10.0894613265991</t>
   </si>
   <si>
     <t xml:space="preserve">9.90399265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0523672103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7370719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86690044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1636486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5531320571899</t>
+    <t xml:space="preserve">10.0523681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73707103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86689949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1636476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5531311035156</t>
   </si>
   <si>
     <t xml:space="preserve">10.4047574996948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4233045578003</t>
+    <t xml:space="preserve">10.423303604126</t>
   </si>
   <si>
     <t xml:space="preserve">10.3862104415894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3676633834839</t>
+    <t xml:space="preserve">10.3676624298096</t>
   </si>
   <si>
     <t xml:space="preserve">9.82980632781982</t>
@@ -692,16 +695,16 @@
     <t xml:space="preserve">10.3120241165161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.033821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81126022338867</t>
+    <t xml:space="preserve">10.0338220596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81125926971436</t>
   </si>
   <si>
     <t xml:space="preserve">10.070915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080074310303</t>
+    <t xml:space="preserve">10.1080083847046</t>
   </si>
   <si>
     <t xml:space="preserve">9.79271221160889</t>
@@ -710,34 +713,34 @@
     <t xml:space="preserve">10.2563829421997</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8498811721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4789428710938</t>
+    <t xml:space="preserve">10.8498802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4789438247681</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651763916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062852859497</t>
+    <t xml:space="preserve">11.1651754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062833786011</t>
   </si>
   <si>
     <t xml:space="preserve">11.5361108779907</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6288461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175647735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9626874923706</t>
+    <t xml:space="preserve">11.6288452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175657272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9626884460449</t>
   </si>
   <si>
     <t xml:space="preserve">12.1481561660767</t>
@@ -746,19 +749,19 @@
     <t xml:space="preserve">12.2408905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4449052810669</t>
+    <t xml:space="preserve">12.4449043273926</t>
   </si>
   <si>
     <t xml:space="preserve">12.593279838562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1852493286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5732069015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5917530059814</t>
+    <t xml:space="preserve">12.1852502822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5732049942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5917520523071</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401275634766</t>
@@ -767,16 +770,16 @@
     <t xml:space="preserve">11.4804716110229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.11106300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1667022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2223434448242</t>
+    <t xml:space="preserve">11.9255933761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1110620498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1667032241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2223424911499</t>
   </si>
   <si>
     <t xml:space="preserve">12.5190935134888</t>
@@ -788,25 +791,25 @@
     <t xml:space="preserve">12.982762336731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.26096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3536996841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5020723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0584783554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4649791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2053241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125917434692</t>
+    <t xml:space="preserve">13.2609643936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3536987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5020732879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584774017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2053251266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125907897949</t>
   </si>
   <si>
     <t xml:space="preserve">12.3892650604248</t>
@@ -818,22 +821,22 @@
     <t xml:space="preserve">12.2965307235718</t>
   </si>
   <si>
-    <t xml:space="preserve">12.407811164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2037973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2779836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5963354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9101037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4093399047852</t>
+    <t xml:space="preserve">12.4078121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2037963867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.277982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5963344573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.910101890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4093389511108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1682319641113</t>
@@ -842,16 +845,16 @@
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045593261719</t>
+    <t xml:space="preserve">12.7045602798462</t>
   </si>
   <si>
     <t xml:space="preserve">12.5561866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">12.370719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7787485122681</t>
+    <t xml:space="preserve">12.3707180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7787494659424</t>
   </si>
   <si>
     <t xml:space="preserve">12.8158416748047</t>
@@ -860,31 +863,31 @@
     <t xml:space="preserve">12.8900289535522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0940456390381</t>
+    <t xml:space="preserve">13.0940427780151</t>
   </si>
   <si>
     <t xml:space="preserve">13.075496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3351526260376</t>
+    <t xml:space="preserve">13.3351516723633</t>
   </si>
   <si>
     <t xml:space="preserve">13.0569496154785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6489200592041</t>
+    <t xml:space="preserve">12.6489191055298</t>
   </si>
   <si>
     <t xml:space="preserve">12.3150777816772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.463451385498</t>
+    <t xml:space="preserve">12.4634523391724</t>
   </si>
   <si>
     <t xml:space="preserve">12.4263582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514080047607</t>
+    <t xml:space="preserve">11.8514070510864</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772207260132</t>
@@ -893,10 +896,10 @@
     <t xml:space="preserve">11.2950038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0168008804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909872055054</t>
+    <t xml:space="preserve">11.0167999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0909881591797</t>
   </si>
   <si>
     <t xml:space="preserve">11.0353479385376</t>
@@ -911,55 +914,55 @@
     <t xml:space="preserve">11.1280832290649</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2764568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2208156585693</t>
+    <t xml:space="preserve">11.2764558792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2208166122437</t>
   </si>
   <si>
     <t xml:space="preserve">11.3691892623901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095342636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177391052246</t>
+    <t xml:space="preserve">11.1095352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177486419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.40322875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88391876220703</t>
+    <t xml:space="preserve">8.88391780853271</t>
   </si>
   <si>
     <t xml:space="preserve">9.55160331726074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71699810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80973052978516</t>
+    <t xml:space="preserve">8.71699714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80973243713379</t>
   </si>
   <si>
     <t xml:space="preserve">8.20696067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24405479431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19768714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53152847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43879508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64433860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200527191162</t>
+    <t xml:space="preserve">8.24405384063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19768619537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53152942657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.438796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64433765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200517654419</t>
   </si>
   <si>
     <t xml:space="preserve">9.77416515350342</t>
@@ -971,10 +974,10 @@
     <t xml:space="preserve">10.2378358840942</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71852397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152740478516</t>
+    <t xml:space="preserve">9.71852588653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152750015259</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015056610107</t>
@@ -983,16 +986,16 @@
     <t xml:space="preserve">11.6844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8699541091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4819984436035</t>
+    <t xml:space="preserve">11.8699550628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4819974899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.6118259429932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7586736679077</t>
+    <t xml:space="preserve">11.7586727142334</t>
   </si>
   <si>
     <t xml:space="preserve">13.7246341705322</t>
@@ -1001,19 +1004,19 @@
     <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.650447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930826187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0414571762085</t>
+    <t xml:space="preserve">13.6504487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0414581298828</t>
   </si>
   <si>
     <t xml:space="preserve">14.9301776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2439441680908</t>
+    <t xml:space="preserve">14.2439470291138</t>
   </si>
   <si>
     <t xml:space="preserve">15.2825660705566</t>
@@ -1025,13 +1028,13 @@
     <t xml:space="preserve">15.9687986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3938474655151</t>
+    <t xml:space="preserve">15.3938455581665</t>
   </si>
   <si>
     <t xml:space="preserve">14.9487228393555</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6148815155029</t>
+    <t xml:space="preserve">14.6148824691772</t>
   </si>
   <si>
     <t xml:space="preserve">14.4665069580078</t>
@@ -1046,76 +1049,73 @@
     <t xml:space="preserve">13.7988224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8173675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6689929962158</t>
+    <t xml:space="preserve">13.8173685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6689939498901</t>
   </si>
   <si>
     <t xml:space="preserve">14.0770235061646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3181343078613</t>
+    <t xml:space="preserve">14.3181324005127</t>
   </si>
   <si>
     <t xml:space="preserve">14.7076148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9858160018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5560483932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7989597320557</t>
+    <t xml:space="preserve">14.9858169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5560503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.79896068573</t>
   </si>
   <si>
     <t xml:space="preserve">14.8923902511597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7802762985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7615909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9858169555664</t>
+    <t xml:space="preserve">14.7802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7615900039673</t>
   </si>
   <si>
     <t xml:space="preserve">15.2661008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2287302017212</t>
+    <t xml:space="preserve">15.2287292480469</t>
   </si>
   <si>
     <t xml:space="preserve">15.4155855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3221578598022</t>
+    <t xml:space="preserve">15.3221569061279</t>
   </si>
   <si>
     <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6121072769165</t>
+    <t xml:space="preserve">14.6121053695679</t>
   </si>
   <si>
     <t xml:space="preserve">15.0792446136475</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9110746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6494779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1353025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.929759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0231885910034</t>
+    <t xml:space="preserve">14.911075592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6494770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1353015899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297609329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0231876373291</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">17.6765403747559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235736846924</t>
+    <t xml:space="preserve">16.723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8730583190918</t>
@@ -1154,28 +1154,28 @@
     <t xml:space="preserve">17.3962535858154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7886524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0128784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8820762634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2744750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3118476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6578521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5270519256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9941921234131</t>
+    <t xml:space="preserve">17.7886505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0128765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.882080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2744770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3118457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6578502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5270538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9941940307617</t>
   </si>
   <si>
     <t xml:space="preserve">18.6855583190918</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">18.3305320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2184162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.031566619873</t>
+    <t xml:space="preserve">18.2184200286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0315647125244</t>
   </si>
   <si>
     <t xml:space="preserve">17.3775691986084</t>
@@ -1202,52 +1202,52 @@
     <t xml:space="preserve">17.4709987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.807336807251</t>
+    <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9291152954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.667516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266677856445</t>
+    <t xml:space="preserve">16.6675148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266668319702</t>
   </si>
   <si>
     <t xml:space="preserve">16.4619750976562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9574661254883</t>
+    <t xml:space="preserve">15.9574642181396</t>
   </si>
   <si>
     <t xml:space="preserve">15.378212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5927772521973</t>
+    <t xml:space="preserve">15.7706098556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5367183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5927753448486</t>
   </si>
   <si>
     <t xml:space="preserve">16.2938060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4246082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2751197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8543720245361</t>
+    <t xml:space="preserve">16.4246063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2751235961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8543739318848</t>
   </si>
   <si>
     <t xml:space="preserve">16.7048873901367</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3311767578125</t>
+    <t xml:space="preserve">16.3311786651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.4993457794189</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">16.6862030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.63014793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6114616394043</t>
+    <t xml:space="preserve">16.6301460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6114597320557</t>
   </si>
   <si>
     <t xml:space="preserve">16.7609462738037</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">16.8170013427734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7983150482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7892961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4342708587646</t>
+    <t xml:space="preserve">16.798318862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7892951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.434271812439</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671316146851</t>
@@ -1289,34 +1289,34 @@
     <t xml:space="preserve">14.6868476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5373630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3215141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5180339813232</t>
+    <t xml:space="preserve">14.5373640060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3215103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.518030166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.6211252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8827228546143</t>
+    <t xml:space="preserve">15.8827238082886</t>
   </si>
   <si>
     <t xml:space="preserve">16.2377490997314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4806613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4432888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9478015899658</t>
+    <t xml:space="preserve">16.4806632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4432926177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9477996826172</t>
   </si>
   <si>
     <t xml:space="preserve">17.0785999298096</t>
@@ -1325,31 +1325,31 @@
     <t xml:space="preserve">16.648832321167</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9104309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8917446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9007663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0876178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5360736846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9194488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0502471923828</t>
+    <t xml:space="preserve">16.9104270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8917465209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9007625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0876216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5360717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9194507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0502510070801</t>
   </si>
   <si>
     <t xml:space="preserve">16.574089050293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.742259979248</t>
+    <t xml:space="preserve">16.7422580718994</t>
   </si>
   <si>
     <t xml:space="preserve">16.5554046630859</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">16.3124923706055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0225429534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0695819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8453531265259</t>
+    <t xml:space="preserve">17.0225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.069580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8453521728516</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519254684448</t>
@@ -1376,43 +1376,43 @@
     <t xml:space="preserve">16.0135231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9014101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761514663696</t>
+    <t xml:space="preserve">15.9014091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9761524200439</t>
   </si>
   <si>
     <t xml:space="preserve">15.3595275878906</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5186767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1636533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.855019569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5090131759644</t>
+    <t xml:space="preserve">14.5186786651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1636524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8550186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5090112686157</t>
   </si>
   <si>
     <t xml:space="preserve">15.6398115158081</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6771812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.52769947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145557403564</t>
+    <t xml:space="preserve">15.6771802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5276985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145547866821</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716424942017</t>
   </si>
   <si>
-    <t xml:space="preserve">15.452956199646</t>
+    <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
     <t xml:space="preserve">15.6584968566895</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">15.8640394210815</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2190647125244</t>
+    <t xml:space="preserve">16.2190628051758</t>
   </si>
   <si>
     <t xml:space="preserve">17.0972862243652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1346569061279</t>
+    <t xml:space="preserve">17.1346588134766</t>
   </si>
   <si>
     <t xml:space="preserve">17.9381370544434</t>
@@ -1442,67 +1442,67 @@
     <t xml:space="preserve">18.1249904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6391658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.480016708374</t>
+    <t xml:space="preserve">17.6391677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4800186157227</t>
   </si>
   <si>
     <t xml:space="preserve">18.0689334869385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1720275878906</t>
+    <t xml:space="preserve">17.1720294952393</t>
   </si>
   <si>
     <t xml:space="preserve">17.5644226074219</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.751277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.713264465332</t>
+    <t xml:space="preserve">17.6017932891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7132663726807</t>
   </si>
   <si>
     <t xml:space="preserve">19.8066902160645</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4329814910889</t>
+    <t xml:space="preserve">19.4329795837402</t>
   </si>
   <si>
     <t xml:space="preserve">19.5264072418213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9935455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5541133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4606857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.273832321167</t>
+    <t xml:space="preserve">19.9935436248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5541152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4606876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2738304138184</t>
   </si>
   <si>
     <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9468326568604</t>
+    <t xml:space="preserve">19.946834564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.600830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6475410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2081069946289</t>
+    <t xml:space="preserve">20.6008281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6475391387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2081089019775</t>
   </si>
   <si>
     <t xml:space="preserve">21.5818214416504</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">19.7599773406982</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1994094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7350769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9700183868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7820663452148</t>
+    <t xml:space="preserve">19.4796943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1994113922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7350749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9700164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7820644378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.4531478881836</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">19.5471248626709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6880893707275</t>
+    <t xml:space="preserve">19.5001354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6880912780762</t>
   </si>
   <si>
     <t xml:space="preserve">19.030252456665</t>
@@ -1556,25 +1556,25 @@
     <t xml:space="preserve">18.8423004150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1712188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0772399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.936279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6410999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832668304443</t>
+    <t xml:space="preserve">19.1712169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.077241897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9362754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6410980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832649230957</t>
   </si>
   <si>
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290538787842</t>
+    <t xml:space="preserve">19.8290557861328</t>
   </si>
   <si>
     <t xml:space="preserve">19.2651920318604</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">18.4194049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6261558532715</t>
+    <t xml:space="preserve">18.6261539459229</t>
   </si>
   <si>
     <t xml:space="preserve">18.4757919311523</t>
@@ -1592,64 +1592,64 @@
     <t xml:space="preserve">18.7765159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5133800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7953109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6449489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639934539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8158054351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2856903076172</t>
+    <t xml:space="preserve">18.5133819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7953128814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.644947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3929119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8158073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2856884002686</t>
   </si>
   <si>
     <t xml:space="preserve">22.0844917297363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4603958129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9772701263428</t>
+    <t xml:space="preserve">22.4603977203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9772682189941</t>
   </si>
   <si>
     <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1652202606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0712432861328</t>
+    <t xml:space="preserve">23.4941387176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1652221679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0712471008301</t>
   </si>
   <si>
     <t xml:space="preserve">23.5881156921387</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1989631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7760677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7290821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0242576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8363018035889</t>
+    <t xml:space="preserve">24.1989650726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7290802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0242557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8363037109375</t>
   </si>
   <si>
     <t xml:space="preserve">22.8832912445068</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">23.5411281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9302806854248</t>
+    <t xml:space="preserve">22.9302787780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.2591953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.447151184082</t>
+    <t xml:space="preserve">23.4471530914307</t>
   </si>
   <si>
     <t xml:space="preserve">23.870044708252</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">21.7555732727051</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7085876464844</t>
+    <t xml:space="preserve">21.7085857391357</t>
   </si>
   <si>
     <t xml:space="preserve">22.1314792633057</t>
@@ -1682,31 +1682,31 @@
     <t xml:space="preserve">21.9435272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5676193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567718505859</t>
+    <t xml:space="preserve">21.5676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.909782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567737579346</t>
   </si>
   <si>
     <t xml:space="preserve">20.7688179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.580867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2387008666992</t>
+    <t xml:space="preserve">20.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2387027740479</t>
   </si>
   <si>
     <t xml:space="preserve">21.8495483398438</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8098087310791</t>
+    <t xml:space="preserve">24.8098106384277</t>
   </si>
   <si>
     <t xml:space="preserve">24.6688442230225</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">23.4001617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">23.635103225708</t>
+    <t xml:space="preserve">23.6351013183594</t>
   </si>
   <si>
     <t xml:space="preserve">24.1519737243652</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">25.5616245269775</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4206600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6555995941162</t>
+    <t xml:space="preserve">25.4206619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6556015014648</t>
   </si>
   <si>
     <t xml:space="preserve">25.3736705780029</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">25.2796936035156</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3061847686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5543727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2724437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.118236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2459506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278835296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7628211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9170360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0110092163086</t>
+    <t xml:space="preserve">23.3061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2724456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1182327270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2459526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9170341491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0110111236572</t>
   </si>
   <si>
     <t xml:space="preserve">24.8568000793457</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">21.1917152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4266548156738</t>
+    <t xml:space="preserve">21.4266567230225</t>
   </si>
   <si>
     <t xml:space="preserve">20.4399013519287</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">21.8025608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8627948760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3796672821045</t>
+    <t xml:space="preserve">20.8627967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326797485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3796653747559</t>
   </si>
   <si>
     <t xml:space="preserve">20.2519474029541</t>
@@ -1832,31 +1832,31 @@
     <t xml:space="preserve">20.34592628479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6748447418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3591709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3292770385742</t>
+    <t xml:space="preserve">19.2182064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5697689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3591690063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3292751312256</t>
   </si>
   <si>
     <t xml:space="preserve">17.0473480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8218021392822</t>
+    <t xml:space="preserve">16.8218040466309</t>
   </si>
   <si>
     <t xml:space="preserve">18.3066329956055</t>
@@ -1868,28 +1868,28 @@
     <t xml:space="preserve">18.6637439727783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615943908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3194332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4736442565918</t>
+    <t xml:space="preserve">19.9230308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9905128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4736423492432</t>
   </si>
   <si>
     <t xml:space="preserve">20.486888885498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2989368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0170059204102</t>
+    <t xml:space="preserve">20.2989387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0170078277588</t>
   </si>
   <si>
     <t xml:space="preserve">18.7389259338379</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">18.7013339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8965358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049598693848</t>
+    <t xml:space="preserve">21.8965377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049617767334</t>
   </si>
   <si>
     <t xml:space="preserve">20.5338764190674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3254261016846</t>
+    <t xml:space="preserve">18.3254280090332</t>
   </si>
   <si>
     <t xml:space="preserve">17.9683151245117</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">17.8931369781494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2165069580078</t>
+    <t xml:space="preserve">17.2165031433105</t>
   </si>
   <si>
     <t xml:space="preserve">17.1977119445801</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">16.7713222503662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9418773651123</t>
+    <t xml:space="preserve">16.9418754577637</t>
   </si>
   <si>
     <t xml:space="preserve">16.9039745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3923072814941</t>
+    <t xml:space="preserve">16.3923091888428</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5293464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652118682861</t>
+    <t xml:space="preserve">16.8281726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5293445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652137756348</t>
   </si>
   <si>
     <t xml:space="preserve">17.813606262207</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">18.1736679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9506454467773</t>
+    <t xml:space="preserve">18.950647354126</t>
   </si>
   <si>
     <t xml:space="preserve">18.6284866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5716323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7800922393799</t>
+    <t xml:space="preserve">18.5716342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7800903320312</t>
   </si>
   <si>
     <t xml:space="preserve">17.9462604522705</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">18.4200286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5905818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8508014678955</t>
+    <t xml:space="preserve">18.5905838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8508033752441</t>
   </si>
   <si>
     <t xml:space="preserve">20.1824378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7509574890137</t>
+    <t xml:space="preserve">20.750955581665</t>
   </si>
   <si>
     <t xml:space="preserve">20.8457107543945</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">20.893087387085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0352153778076</t>
+    <t xml:space="preserve">21.0352172851562</t>
   </si>
   <si>
     <t xml:space="preserve">20.2771892547607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0774993896484</t>
+    <t xml:space="preserve">22.0775032043457</t>
   </si>
   <si>
     <t xml:space="preserve">22.6933975219727</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">22.2670078277588</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4565143585205</t>
+    <t xml:space="preserve">22.4565162658691</t>
   </si>
   <si>
     <t xml:space="preserve">22.5986442565918</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">21.6511116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4142284393311</t>
+    <t xml:space="preserve">21.4142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">20.9878387451172</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">20.419319152832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6612930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298126220703</t>
+    <t xml:space="preserve">19.6612949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298145294189</t>
   </si>
   <si>
     <t xml:space="preserve">19.9455547332764</t>
@@ -2054,34 +2054,34 @@
     <t xml:space="preserve">19.7086715698242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2349033355713</t>
+    <t xml:space="preserve">19.2349052429199</t>
   </si>
   <si>
     <t xml:space="preserve">19.5665416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0403079986572</t>
+    <t xml:space="preserve">20.0403060913086</t>
   </si>
   <si>
     <t xml:space="preserve">19.756046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1875267028809</t>
+    <t xml:space="preserve">19.1875286102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.9980220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0453968048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526828765869</t>
+    <t xml:space="preserve">19.0453987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526809692383</t>
   </si>
   <si>
     <t xml:space="preserve">18.3631744384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9273128509521</t>
+    <t xml:space="preserve">17.9273109436035</t>
   </si>
   <si>
     <t xml:space="preserve">18.2305202484131</t>
@@ -2096,43 +2096,43 @@
     <t xml:space="preserve">17.7757053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0876846313477</t>
+    <t xml:space="preserve">17.7946548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987316131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0927753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.087682723999</t>
   </si>
   <si>
     <t xml:space="preserve">18.7990398406982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1547183990479</t>
+    <t xml:space="preserve">18.1547164916992</t>
   </si>
   <si>
     <t xml:space="preserve">18.28737449646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5147819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.059965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4768772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6562023162842</t>
+    <t xml:space="preserve">18.5147800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0599632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2115688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.476879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6562042236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.6088275909424</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">20.5140762329102</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5038928985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3092956542969</t>
+    <t xml:space="preserve">22.5038909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3092937469482</t>
   </si>
   <si>
     <t xml:space="preserve">24.1620750427246</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">24.7779693603516</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3566703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4040470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6883087158203</t>
+    <t xml:space="preserve">23.3566722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4040489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6883068084717</t>
   </si>
   <si>
     <t xml:space="preserve">22.1248798370361</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">22.8829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7881507873535</t>
+    <t xml:space="preserve">22.7881526947021</t>
   </si>
   <si>
     <t xml:space="preserve">23.0250339508057</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">22.8355274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4514217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3515796661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1671657562256</t>
+    <t xml:space="preserve">23.4514236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3515777587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.167163848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">21.7932434082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6984901428223</t>
+    <t xml:space="preserve">21.6984882354736</t>
   </si>
   <si>
     <t xml:space="preserve">21.5563583374023</t>
@@ -2222,25 +2222,25 @@
     <t xml:space="preserve">21.5089817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4987983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6832141876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9725646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2568264007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0673179626465</t>
+    <t xml:space="preserve">23.49880027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6832160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9725666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2568244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0673217773438</t>
   </si>
   <si>
     <t xml:space="preserve">25.2991123199463</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9201011657715</t>
+    <t xml:space="preserve">24.9200992584229</t>
   </si>
   <si>
     <t xml:space="preserve">24.825345993042</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">24.5884628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.493709564209</t>
+    <t xml:space="preserve">24.4937076568604</t>
   </si>
   <si>
     <t xml:space="preserve">25.0148506164551</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">25.7255001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6358375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5359954833984</t>
+    <t xml:space="preserve">24.6358394622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5359935760498</t>
   </si>
   <si>
     <t xml:space="preserve">25.772876739502</t>
@@ -2276,28 +2276,28 @@
     <t xml:space="preserve">25.3464889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5935535430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.546178817749</t>
+    <t xml:space="preserve">23.5935516357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5461750030518</t>
   </si>
   <si>
     <t xml:space="preserve">23.1197872161865</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2619152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9776573181152</t>
+    <t xml:space="preserve">23.2619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.2145404815674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6409320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0199432373047</t>
+    <t xml:space="preserve">23.6409301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0199451446533</t>
   </si>
   <si>
     <t xml:space="preserve">23.8778133392334</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">23.7830600738525</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3194770812988</t>
+    <t xml:space="preserve">21.3194751739502</t>
   </si>
   <si>
     <t xml:space="preserve">22.6460208892822</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3617630004883</t>
+    <t xml:space="preserve">22.3617610931396</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5833721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.483528137207</t>
+    <t xml:space="preserve">25.5833740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4835262298584</t>
   </si>
   <si>
     <t xml:space="preserve">26.3887729644775</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">26.6256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1992664337158</t>
+    <t xml:space="preserve">26.1992683410645</t>
   </si>
   <si>
     <t xml:space="preserve">25.8202533721924</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5309028625488</t>
+    <t xml:space="preserve">26.5309047698975</t>
   </si>
   <si>
     <t xml:space="preserve">26.6730327606201</t>
@@ -3513,6 +3513,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.75</t>
   </si>
 </sst>
 </file>
@@ -10837,7 +10840,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10863,7 +10866,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10889,7 +10892,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10915,7 +10918,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10941,7 +10944,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10967,7 +10970,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10993,7 +10996,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -11019,7 +11022,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -11045,7 +11048,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -11071,7 +11074,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -11097,7 +11100,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -11123,7 +11126,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -11175,7 +11178,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -11253,7 +11256,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -11279,7 +11282,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -11305,7 +11308,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -11331,7 +11334,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -11357,7 +11360,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -11383,7 +11386,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -11409,7 +11412,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -11435,7 +11438,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -11461,7 +11464,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -11487,7 +11490,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -11513,7 +11516,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -11539,7 +11542,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -11565,7 +11568,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -11591,7 +11594,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11617,7 +11620,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11643,7 +11646,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11669,7 +11672,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11695,7 +11698,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11721,7 +11724,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11747,7 +11750,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11773,7 +11776,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11799,7 +11802,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11825,7 +11828,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11851,7 +11854,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11877,7 +11880,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11903,7 +11906,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11929,7 +11932,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11955,7 +11958,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11981,7 +11984,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -12007,7 +12010,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -12033,7 +12036,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -12059,7 +12062,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -12085,7 +12088,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -12111,7 +12114,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -12137,7 +12140,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -12163,7 +12166,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -12189,7 +12192,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -12215,7 +12218,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -12241,7 +12244,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -12267,7 +12270,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -12293,7 +12296,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -12319,7 +12322,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -12345,7 +12348,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -12371,7 +12374,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -12397,7 +12400,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -12423,7 +12426,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -12449,7 +12452,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -12475,7 +12478,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -12501,7 +12504,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -12527,7 +12530,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -12553,7 +12556,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -12579,7 +12582,7 @@
         <v>12.2929019927979</v>
       </c>
       <c r="G336" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12605,7 +12608,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12631,7 +12634,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12657,7 +12660,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12683,7 +12686,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12709,7 +12712,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12735,7 +12738,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12761,7 +12764,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12787,7 +12790,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12813,7 +12816,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12839,7 +12842,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12865,7 +12868,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12891,7 +12894,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12917,7 +12920,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12943,7 +12946,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12969,7 +12972,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12995,7 +12998,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -13021,7 +13024,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -13047,7 +13050,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -13073,7 +13076,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -13099,7 +13102,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -13125,7 +13128,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -13151,7 +13154,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -13177,7 +13180,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -13203,7 +13206,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -13229,7 +13232,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -13255,7 +13258,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -13281,7 +13284,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -13307,7 +13310,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -13333,7 +13336,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -13359,7 +13362,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -13385,7 +13388,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -13411,7 +13414,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -13437,7 +13440,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -13463,7 +13466,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -13489,7 +13492,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -13515,7 +13518,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -13541,7 +13544,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -13567,7 +13570,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -13593,7 +13596,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13619,7 +13622,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13645,7 +13648,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13671,7 +13674,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13697,7 +13700,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13723,7 +13726,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13749,7 +13752,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13775,7 +13778,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13801,7 +13804,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13827,7 +13830,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13853,7 +13856,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13879,7 +13882,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13905,7 +13908,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13931,7 +13934,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13957,7 +13960,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13983,7 +13986,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14009,7 +14012,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -14035,7 +14038,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -14061,7 +14064,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14087,7 +14090,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -14113,7 +14116,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14139,7 +14142,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14165,7 +14168,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14191,7 +14194,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14217,7 +14220,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14243,7 +14246,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14269,7 +14272,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14295,7 +14298,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14321,7 +14324,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14347,7 +14350,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14373,7 +14376,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14399,7 +14402,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14425,7 +14428,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14451,7 +14454,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14477,7 +14480,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14503,7 +14506,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14529,7 +14532,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14555,7 +14558,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14581,7 +14584,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14607,7 +14610,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14633,7 +14636,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14659,7 +14662,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14685,7 +14688,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14711,7 +14714,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14737,7 +14740,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14763,7 +14766,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14789,7 +14792,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14815,7 +14818,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14841,7 +14844,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14867,7 +14870,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14893,7 +14896,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14919,7 +14922,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14945,7 +14948,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14971,7 +14974,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14997,7 +15000,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -15023,7 +15026,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -15049,7 +15052,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -15075,7 +15078,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15101,7 +15104,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15127,7 +15130,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15153,7 +15156,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15179,7 +15182,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15205,7 +15208,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15231,7 +15234,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15257,7 +15260,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15283,7 +15286,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15309,7 +15312,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15335,7 +15338,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15361,7 +15364,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15387,7 +15390,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15413,7 +15416,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15439,7 +15442,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15465,7 +15468,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15517,7 +15520,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15543,7 +15546,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15569,7 +15572,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15595,7 +15598,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15621,7 +15624,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15647,7 +15650,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15673,7 +15676,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15699,7 +15702,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15725,7 +15728,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15751,7 +15754,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15777,7 +15780,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15803,7 +15806,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15829,7 +15832,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15855,7 +15858,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15881,7 +15884,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15907,7 +15910,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15933,7 +15936,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15959,7 +15962,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15985,7 +15988,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16011,7 +16014,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -16037,7 +16040,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -16063,7 +16066,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16089,7 +16092,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16115,7 +16118,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16141,7 +16144,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16167,7 +16170,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16193,7 +16196,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16219,7 +16222,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16245,7 +16248,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16271,7 +16274,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16297,7 +16300,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16323,7 +16326,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16349,7 +16352,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16375,7 +16378,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16401,7 +16404,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16427,7 +16430,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16453,7 +16456,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16479,7 +16482,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16505,7 +16508,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16531,7 +16534,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16557,7 +16560,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16583,7 +16586,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16609,7 +16612,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16635,7 +16638,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16661,7 +16664,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16687,7 +16690,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16713,7 +16716,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16739,7 +16742,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16765,7 +16768,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16791,7 +16794,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16817,7 +16820,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16843,7 +16846,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16869,7 +16872,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16895,7 +16898,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16921,7 +16924,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16947,7 +16950,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16973,7 +16976,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16999,7 +17002,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -17025,7 +17028,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -17051,7 +17054,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -17077,7 +17080,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17103,7 +17106,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17129,7 +17132,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17155,7 +17158,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17181,7 +17184,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17207,7 +17210,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17233,7 +17236,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17259,7 +17262,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17285,7 +17288,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17311,7 +17314,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17337,7 +17340,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17389,7 +17392,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17935,7 +17938,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -21939,7 +21942,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -52783,7 +52786,7 @@
     </row>
     <row r="1883">
       <c r="A1883" s="1" t="n">
-        <v>45965.6911921296</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1883" t="n">
         <v>32820</v>
@@ -52792,7 +52795,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="D1883" t="n">
-        <v>21.8999996185303</v>
+        <v>21.8500003814697</v>
       </c>
       <c r="E1883" t="n">
         <v>22.3500003814697</v>
@@ -52804,6 +52807,32 @@
         <v>1166</v>
       </c>
       <c r="H1883" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="1" t="n">
+        <v>45966.6912615741</v>
+      </c>
+      <c r="B1884" t="n">
+        <v>52881</v>
+      </c>
+      <c r="C1884" t="n">
+        <v>22.1499996185303</v>
+      </c>
+      <c r="D1884" t="n">
+        <v>21.5499992370605</v>
+      </c>
+      <c r="E1884" t="n">
+        <v>22.1499996185303</v>
+      </c>
+      <c r="F1884" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="G1884" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H1884" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125877380371</t>
+    <t xml:space="preserve">7.58125829696655</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288782119751</t>
+    <t xml:space="preserve">7.90288734436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.81099271774292</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71910047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68969249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348222732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721220016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67406988143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97640180587769</t>
+    <t xml:space="preserve">7.71909999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68969106674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348127365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721172332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67407083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97640228271484</t>
   </si>
   <si>
     <t xml:space="preserve">7.44433641433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30281972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46639060974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4434175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52612161636353</t>
+    <t xml:space="preserve">7.30281925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46639013290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57206869125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44341707229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52612113952637</t>
   </si>
   <si>
     <t xml:space="preserve">7.54450130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64742231369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180501937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85693979263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92218542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00397109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86612796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01959419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81466960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76504611968994</t>
+    <t xml:space="preserve">7.64742183685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80180358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8569393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92218589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00397205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86612939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01959323883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81466913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76504564285278</t>
   </si>
   <si>
     <t xml:space="preserve">7.85142707824707</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">7.69336843490601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79261493682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74666738510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88910293579102</t>
+    <t xml:space="preserve">7.79261445999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74666786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88910341262817</t>
   </si>
   <si>
     <t xml:space="preserve">7.56379842758179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67315149307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78526401519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74850511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478101730347</t>
+    <t xml:space="preserve">7.67315244674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7852635383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74850702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478054046631</t>
   </si>
   <si>
     <t xml:space="preserve">8.06002616882324</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">8.11424350738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30354404449463</t>
+    <t xml:space="preserve">8.30354690551758</t>
   </si>
   <si>
     <t xml:space="preserve">8.46343994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48641300201416</t>
+    <t xml:space="preserve">8.48641395568848</t>
   </si>
   <si>
     <t xml:space="preserve">8.75382518768311</t>
@@ -173,34 +173,34 @@
     <t xml:space="preserve">8.60128116607666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28884124755859</t>
+    <t xml:space="preserve">8.28884315490723</t>
   </si>
   <si>
     <t xml:space="preserve">8.25208473205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46987342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3623571395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45425128936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71155548095703</t>
+    <t xml:space="preserve">8.46987152099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36235809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45425224304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71155452728271</t>
   </si>
   <si>
     <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61598491668701</t>
+    <t xml:space="preserve">8.61598587036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.66560745239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7942590713501</t>
+    <t xml:space="preserve">8.79426002502441</t>
   </si>
   <si>
     <t xml:space="preserve">9.005615234375</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">8.86869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11589050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14345741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09751129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680793762207</t>
+    <t xml:space="preserve">9.11588764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14345645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680889129639</t>
   </si>
   <si>
     <t xml:space="preserve">8.99091243743896</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">9.06166934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02399349212646</t>
+    <t xml:space="preserve">9.02399444580078</t>
   </si>
   <si>
     <t xml:space="preserve">8.76577186584473</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">8.9936695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04237270355225</t>
+    <t xml:space="preserve">9.04237365722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.90177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98191452026367</t>
+    <t xml:space="preserve">8.67112064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50754833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98191595077515</t>
   </si>
   <si>
     <t xml:space="preserve">8.30630302429199</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">8.40830421447754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54614543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59209251403809</t>
+    <t xml:space="preserve">8.54614448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5920934677124</t>
   </si>
   <si>
     <t xml:space="preserve">8.63803958892822</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">8.02970123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75126266479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126607894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34214115142822</t>
+    <t xml:space="preserve">7.75126314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126417160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34214019775391</t>
   </si>
   <si>
     <t xml:space="preserve">8.7749605178833</t>
@@ -293,79 +293,79 @@
     <t xml:space="preserve">8.77771854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75474452972412</t>
+    <t xml:space="preserve">8.75474548339844</t>
   </si>
   <si>
     <t xml:space="preserve">8.50571250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59944534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70144653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57738971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3926830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34122276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71982479095459</t>
+    <t xml:space="preserve">8.59944343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70144748687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57739067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39268207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34122085571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5608491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71982669830322</t>
   </si>
   <si>
     <t xml:space="preserve">8.0545129776001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04164695739746</t>
+    <t xml:space="preserve">8.04164791107178</t>
   </si>
   <si>
     <t xml:space="preserve">8.0866756439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18867778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54890251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33479022979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50938892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92107391357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03869724273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437191009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15264701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84939575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07913017272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85582828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30446434020996</t>
+    <t xml:space="preserve">8.18867874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.548903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33479118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92107486724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0386962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9743709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664447784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1526460647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84939670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07913112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8558292388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30446338653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.23370552062988</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">8.27046394348145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33754539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20062255859375</t>
+    <t xml:space="preserve">8.33754634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20062351226807</t>
   </si>
   <si>
     <t xml:space="preserve">8.40370941162109</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">8.27413940429688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5001974105835</t>
+    <t xml:space="preserve">8.29803085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50019836425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.43587207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22451686859131</t>
+    <t xml:space="preserve">8.22451591491699</t>
   </si>
   <si>
     <t xml:space="preserve">8.35408782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22083854675293</t>
+    <t xml:space="preserve">8.22083950042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.15283870697021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39911460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42668437957764</t>
+    <t xml:space="preserve">8.39911556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.426682472229</t>
   </si>
   <si>
     <t xml:space="preserve">8.48365688323975</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">8.72074413299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.100266456604</t>
+    <t xml:space="preserve">9.10026550292969</t>
   </si>
   <si>
     <t xml:space="preserve">9.06534671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89810085296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469390869141</t>
+    <t xml:space="preserve">8.89809894561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469295501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.97712802886963</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">9.05156230926514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23535060882568</t>
+    <t xml:space="preserve">9.23534965515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.20594501495361</t>
@@ -452,70 +452,70 @@
     <t xml:space="preserve">9.36216354370117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3952465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027812957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6488733291626</t>
+    <t xml:space="preserve">9.39524745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
     <t xml:space="preserve">9.69482231140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59373760223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64336109161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31989192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61763000488281</t>
+    <t xml:space="preserve">9.59373664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64335918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31989288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6176290512085</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265384674072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5110330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28497409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46324634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3309211730957</t>
+    <t xml:space="preserve">9.51103210449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28497314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46324825286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33091926574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.12875461578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26291847229004</t>
+    <t xml:space="preserve">9.26291942596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.14713287353516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06075191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94128894805908</t>
+    <t xml:space="preserve">9.06075286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">8.37797927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76025772094727</t>
+    <t xml:space="preserve">8.76025676727295</t>
   </si>
   <si>
     <t xml:space="preserve">9.00653457641602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18940448760986</t>
+    <t xml:space="preserve">9.18940353393555</t>
   </si>
   <si>
     <t xml:space="preserve">8.96885776519775</t>
@@ -530,55 +530,55 @@
     <t xml:space="preserve">9.39157009124756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74076747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46508693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53860187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75914573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68563175201416</t>
+    <t xml:space="preserve">9.74076843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46508598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53860092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75914669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68563270568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.90617752075195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532083511353</t>
+    <t xml:space="preserve">9.99807071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532073974609</t>
   </si>
   <si>
     <t xml:space="preserve">9.7959041595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92455577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81428337097168</t>
+    <t xml:space="preserve">9.92455768585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81428241729736</t>
   </si>
   <si>
     <t xml:space="preserve">9.9429349899292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0715866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083421707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6672534942627</t>
+    <t xml:space="preserve">10.0715856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66725444793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.77752590179443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83266258239746</t>
+    <t xml:space="preserve">9.83266067504883</t>
   </si>
   <si>
     <t xml:space="preserve">9.86941909790039</t>
@@ -590,58 +590,58 @@
     <t xml:space="preserve">10.163480758667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3105096817017</t>
+    <t xml:space="preserve">10.3105115890503</t>
   </si>
   <si>
     <t xml:space="preserve">10.0348300933838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.016450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5126781463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6045722961426</t>
+    <t xml:space="preserve">10.0164499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5126791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6045713424683</t>
   </si>
   <si>
     <t xml:space="preserve">10.659707069397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7332229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4207849502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391632080078</t>
+    <t xml:space="preserve">10.7332239151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4207830429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4759197235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391622543335</t>
   </si>
   <si>
     <t xml:space="preserve">10.3288898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97969436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85104084014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821956634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.941086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92254066467285</t>
+    <t xml:space="preserve">9.97969341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85103988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821947097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8854455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92253875732422</t>
   </si>
   <si>
     <t xml:space="preserve">10.1451015472412</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">9.99672698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2007398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2192869186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0894613265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90399265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523681640625</t>
+    <t xml:space="preserve">10.2007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2192888259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0894603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90399169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523662567139</t>
   </si>
   <si>
     <t xml:space="preserve">9.7370719909668</t>
@@ -671,67 +671,67 @@
     <t xml:space="preserve">9.86689949035645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1636486053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5531320571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4047555923462</t>
+    <t xml:space="preserve">10.1636476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5531311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4047574996948</t>
   </si>
   <si>
     <t xml:space="preserve">10.423303604126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3862104415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3676643371582</t>
+    <t xml:space="preserve">10.3862113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3676633834839</t>
   </si>
   <si>
     <t xml:space="preserve">9.82980632781982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3120231628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0338201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81125926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0709161758423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1080083847046</t>
+    <t xml:space="preserve">10.3120222091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.033821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81126022338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.070915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.79271221160889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2563829421997</t>
+    <t xml:space="preserve">10.2563819885254</t>
   </si>
   <si>
     <t xml:space="preserve">10.8498802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789438247681</t>
+    <t xml:space="preserve">10.4789447784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.0554218292236</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1651773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.536111831665</t>
+    <t xml:space="preserve">11.1651763916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6102991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062833786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5361108779907</t>
   </si>
   <si>
     <t xml:space="preserve">11.6288452148438</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">11.9626884460449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1481561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2408895492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4449052810669</t>
+    <t xml:space="preserve">12.1481552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2408905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4449043273926</t>
   </si>
   <si>
     <t xml:space="preserve">12.5932788848877</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">12.1852493286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.573205947876</t>
+    <t xml:space="preserve">11.5732049942017</t>
   </si>
   <si>
     <t xml:space="preserve">11.5917520523071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7401275634766</t>
+    <t xml:space="preserve">11.7401266098022</t>
   </si>
   <si>
     <t xml:space="preserve">11.4804716110229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925594329834</t>
+    <t xml:space="preserve">11.9255933761597</t>
   </si>
   <si>
     <t xml:space="preserve">12.11106300354</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">12.1667032241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2223424911499</t>
+    <t xml:space="preserve">12.2223434448242</t>
   </si>
   <si>
     <t xml:space="preserve">12.5190935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.686014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827613830566</t>
+    <t xml:space="preserve">12.6860132217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9827632904053</t>
   </si>
   <si>
     <t xml:space="preserve">13.2609643936157</t>
@@ -797,55 +797,55 @@
     <t xml:space="preserve">13.3536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5020723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0584774017334</t>
+    <t xml:space="preserve">13.5020713806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584764480591</t>
   </si>
   <si>
     <t xml:space="preserve">13.4649791717529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053241729736</t>
+    <t xml:space="preserve">13.2053251266479</t>
   </si>
   <si>
     <t xml:space="preserve">13.1125917434692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3892641067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3521728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2965297698975</t>
+    <t xml:space="preserve">12.3892650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3521709442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2965316772461</t>
   </si>
   <si>
     <t xml:space="preserve">12.407811164856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2037973403931</t>
+    <t xml:space="preserve">12.2037963867188</t>
   </si>
   <si>
     <t xml:space="preserve">12.2779836654663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5963354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9101037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4093389511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1682300567627</t>
+    <t xml:space="preserve">14.5963363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9101028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4093379974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.168231010437</t>
   </si>
   <si>
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045593261719</t>
+    <t xml:space="preserve">12.7045602798462</t>
   </si>
   <si>
     <t xml:space="preserve">12.5561866760254</t>
@@ -860,34 +860,34 @@
     <t xml:space="preserve">12.8158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8900279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940446853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0754957199097</t>
+    <t xml:space="preserve">12.8900289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0754976272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.3351516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569486618042</t>
+    <t xml:space="preserve">13.0569496154785</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3150787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.463451385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4263572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514060974121</t>
+    <t xml:space="preserve">12.3150777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4634523391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4263591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514089584351</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772216796875</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">11.2950038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0167999267578</t>
+    <t xml:space="preserve">11.0168018341064</t>
   </si>
   <si>
     <t xml:space="preserve">11.090989112854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0353479385376</t>
+    <t xml:space="preserve">11.0353488922119</t>
   </si>
   <si>
     <t xml:space="preserve">10.7571449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3135499954224</t>
+    <t xml:space="preserve">11.313549041748</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280822753906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2764577865601</t>
+    <t xml:space="preserve">11.2764558792114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2208156585693</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">11.3691902160645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1095342636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40322875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88391876220703</t>
+    <t xml:space="preserve">11.1095352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40322971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88391780853271</t>
   </si>
   <si>
     <t xml:space="preserve">9.55160427093506</t>
@@ -941,67 +941,67 @@
     <t xml:space="preserve">8.71699810028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80973052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20695972442627</t>
+    <t xml:space="preserve">8.80973148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20696067810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.24405479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19768619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53152942657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43879508972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64433860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7200536727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77416515350342</t>
+    <t xml:space="preserve">8.19768714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53153038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.438796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64433765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7200527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77416610717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2934770584106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2378368377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71852397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0152730941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7015056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6844863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8699531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4819984436035</t>
+    <t xml:space="preserve">10.2378358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71852493286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0152750015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7015047073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6844882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8699541091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4819993972778</t>
   </si>
   <si>
     <t xml:space="preserve">12.6118249893188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7586736679077</t>
+    <t xml:space="preserve">11.758674621582</t>
   </si>
   <si>
     <t xml:space="preserve">13.7246351242065</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4835262298584</t>
+    <t xml:space="preserve">13.4835252761841</t>
   </si>
   <si>
     <t xml:space="preserve">13.650447845459</t>
@@ -1013,28 +1013,28 @@
     <t xml:space="preserve">15.0414581298828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9301776885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2439451217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.282567024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462377548218</t>
+    <t xml:space="preserve">14.9301767349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2439441680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462358474731</t>
   </si>
   <si>
     <t xml:space="preserve">15.9687986373901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3938465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6148815155029</t>
+    <t xml:space="preserve">15.3938455581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6148824691772</t>
   </si>
   <si>
     <t xml:space="preserve">14.4665079116821</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">14.1326637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7988214492798</t>
+    <t xml:space="preserve">13.7988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">13.8173685073853</t>
@@ -1058,34 +1058,31 @@
     <t xml:space="preserve">14.0770235061646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.318133354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9858160018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5560483932495</t>
+    <t xml:space="preserve">14.3181314468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076139450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9858169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5560493469238</t>
   </si>
   <si>
     <t xml:space="preserve">14.79896068573</t>
   </si>
   <si>
-    <t xml:space="preserve">14.892391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7802762985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7615909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9858169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2661008834839</t>
+    <t xml:space="preserve">14.8923892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7615900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2660999298096</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287302017212</t>
@@ -1097,16 +1094,16 @@
     <t xml:space="preserve">15.3221578598022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0045013427734</t>
+    <t xml:space="preserve">15.0045022964478</t>
   </si>
   <si>
     <t xml:space="preserve">14.6121063232422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0792446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9110746383667</t>
+    <t xml:space="preserve">15.0792455673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.911075592041</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494770050049</t>
@@ -1127,16 +1124,16 @@
     <t xml:space="preserve">14.9484462738037</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4813070297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5650682449341</t>
+    <t xml:space="preserve">14.4813079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5650691986084</t>
   </si>
   <si>
     <t xml:space="preserve">16.1630058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9664897918701</t>
+    <t xml:space="preserve">16.9664878845215</t>
   </si>
   <si>
     <t xml:space="preserve">17.6765384674072</t>
@@ -1148,7 +1145,7 @@
     <t xml:space="preserve">16.8730583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4336223602295</t>
+    <t xml:space="preserve">17.4336242675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4149398803711</t>
@@ -1160,10 +1157,10 @@
     <t xml:space="preserve">17.7886524200439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0128765106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8820781707764</t>
+    <t xml:space="preserve">18.0128746032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8820762634277</t>
   </si>
   <si>
     <t xml:space="preserve">18.2744750976562</t>
@@ -1178,16 +1175,16 @@
     <t xml:space="preserve">17.5270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9941940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6855602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1526947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3305320739746</t>
+    <t xml:space="preserve">17.9941921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6855583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1526966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.330530166626</t>
   </si>
   <si>
     <t xml:space="preserve">18.2184181213379</t>
@@ -1202,76 +1199,76 @@
     <t xml:space="preserve">17.9568214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4709949493408</t>
+    <t xml:space="preserve">17.4709968566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9291172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.667516708374</t>
+    <t xml:space="preserve">16.9291152954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6675186157227</t>
   </si>
   <si>
     <t xml:space="preserve">15.8266658782959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4619750976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9574642181396</t>
+    <t xml:space="preserve">16.4619770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.957465171814</t>
   </si>
   <si>
     <t xml:space="preserve">15.378212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5367183685303</t>
+    <t xml:space="preserve">15.7706108093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5367221832275</t>
   </si>
   <si>
     <t xml:space="preserve">16.5927772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2938060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4246063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2751235961914</t>
+    <t xml:space="preserve">16.2938041687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4246044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2751216888428</t>
   </si>
   <si>
     <t xml:space="preserve">16.8543720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7048873901367</t>
+    <t xml:space="preserve">16.7048892974854</t>
   </si>
   <si>
     <t xml:space="preserve">16.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4993457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3685474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3498630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6862030029297</t>
+    <t xml:space="preserve">16.4993476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3685455322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3498611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6862049102783</t>
   </si>
   <si>
     <t xml:space="preserve">16.63014793396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6114597320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7609462738037</t>
+    <t xml:space="preserve">16.6114616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7609481811523</t>
   </si>
   <si>
     <t xml:space="preserve">16.8170013427734</t>
@@ -1283,100 +1280,100 @@
     <t xml:space="preserve">15.7892942428589</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4342708587646</t>
+    <t xml:space="preserve">15.434271812439</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6868486404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5373630523682</t>
+    <t xml:space="preserve">14.6868476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5373640060425</t>
   </si>
   <si>
     <t xml:space="preserve">17.32151222229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5180320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6211261749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8827228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377490997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4806613922119</t>
+    <t xml:space="preserve">16.5180339813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6211252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8827219009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4806652069092</t>
   </si>
   <si>
     <t xml:space="preserve">16.8356895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4432888031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9478015899658</t>
+    <t xml:space="preserve">16.4432907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9477996826172</t>
   </si>
   <si>
     <t xml:space="preserve">17.0785999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6488304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9104290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8917446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9007663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0876178741455</t>
+    <t xml:space="preserve">16.648832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9104270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8917465209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9007625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0876197814941</t>
   </si>
   <si>
     <t xml:space="preserve">18.5360736846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9194507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0502471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.574089050293</t>
+    <t xml:space="preserve">17.9194488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0502490997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5740909576416</t>
   </si>
   <si>
     <t xml:space="preserve">16.742259979248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5554046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3124942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0225429534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0695819854736</t>
+    <t xml:space="preserve">16.5554065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3124923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.069580078125</t>
   </si>
   <si>
     <t xml:space="preserve">15.8453531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7519245147705</t>
+    <t xml:space="preserve">15.7519254684448</t>
   </si>
   <si>
     <t xml:space="preserve">15.6024408340454</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0135250091553</t>
+    <t xml:space="preserve">16.0135231018066</t>
   </si>
   <si>
     <t xml:space="preserve">15.9014101028442</t>
@@ -1385,31 +1382,31 @@
     <t xml:space="preserve">15.9761514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3595275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1636524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.855019569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.50901222229</t>
+    <t xml:space="preserve">15.3595285415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186786651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1636533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8550186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5090112686157</t>
   </si>
   <si>
     <t xml:space="preserve">15.6398115158081</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6771821975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.52769947052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7145538330078</t>
+    <t xml:space="preserve">15.6771812438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5276985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7145519256592</t>
   </si>
   <si>
     <t xml:space="preserve">15.4716415405273</t>
@@ -1418,22 +1415,22 @@
     <t xml:space="preserve">15.4529552459717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6584987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8640394210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2190647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0972862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1346588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9381370544434</t>
+    <t xml:space="preserve">15.6584978103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8640384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2190628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0972881317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1346569061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9381351470947</t>
   </si>
   <si>
     <t xml:space="preserve">17.5831108093262</t>
@@ -1445,7 +1442,7 @@
     <t xml:space="preserve">18.1249904632568</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6391639709473</t>
+    <t xml:space="preserve">17.6391658782959</t>
   </si>
   <si>
     <t xml:space="preserve">18.480016708374</t>
@@ -1454,19 +1451,19 @@
     <t xml:space="preserve">18.0689334869385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1720294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5644226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6017932891846</t>
+    <t xml:space="preserve">17.1720275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5644245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">17.7512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7132663726807</t>
+    <t xml:space="preserve">19.713264465332</t>
   </si>
   <si>
     <t xml:space="preserve">19.8066902160645</t>
@@ -1475,7 +1472,7 @@
     <t xml:space="preserve">19.4329814910889</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5264072418213</t>
+    <t xml:space="preserve">19.5264053344727</t>
   </si>
   <si>
     <t xml:space="preserve">19.9935455322266</t>
@@ -1487,31 +1484,31 @@
     <t xml:space="preserve">20.4606876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.273832321167</t>
+    <t xml:space="preserve">20.2738304138184</t>
   </si>
   <si>
     <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.946834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2271156311035</t>
+    <t xml:space="preserve">19.9468326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
     <t xml:space="preserve">20.6008281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6475410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2081069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5818195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9555320739746</t>
+    <t xml:space="preserve">20.6475429534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2081089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5818176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.955530166626</t>
   </si>
   <si>
     <t xml:space="preserve">21.3015365600586</t>
@@ -1520,13 +1517,13 @@
     <t xml:space="preserve">20.8343982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0869770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7599773406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4796924591064</t>
+    <t xml:space="preserve">20.0869731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7599754333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4796943664551</t>
   </si>
   <si>
     <t xml:space="preserve">19.1994113922119</t>
@@ -1535,64 +1532,64 @@
     <t xml:space="preserve">19.7350769042969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9700164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7820663452148</t>
+    <t xml:space="preserve">19.9700183868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7820644378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.4531478881836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5471248626709</t>
+    <t xml:space="preserve">19.5471229553223</t>
   </si>
   <si>
     <t xml:space="preserve">19.5001354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6880912780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0302543640137</t>
+    <t xml:space="preserve">19.6880874633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.030252456665</t>
   </si>
   <si>
     <t xml:space="preserve">18.8423004150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1712188720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0772399902344</t>
+    <t xml:space="preserve">19.1712169647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.077241897583</t>
   </si>
   <si>
     <t xml:space="preserve">18.9362773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832668304443</t>
+    <t xml:space="preserve">19.6410980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832649230957</t>
   </si>
   <si>
     <t xml:space="preserve">20.1579704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8290557861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.265193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4194049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6261539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4757900238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765159606934</t>
+    <t xml:space="preserve">19.8290538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2651920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4194068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6261558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.475793838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.776517868042</t>
   </si>
   <si>
     <t xml:space="preserve">18.5133819580078</t>
@@ -1619,7 +1616,7 @@
     <t xml:space="preserve">22.0844917297363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4603958129883</t>
+    <t xml:space="preserve">22.4603977203369</t>
   </si>
   <si>
     <t xml:space="preserve">22.9772682189941</t>
@@ -1631,28 +1628,28 @@
     <t xml:space="preserve">23.4941387176514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1652202606201</t>
+    <t xml:space="preserve">23.1652221679688</t>
   </si>
   <si>
     <t xml:space="preserve">23.0712451934814</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5881156921387</t>
+    <t xml:space="preserve">23.58811378479</t>
   </si>
   <si>
     <t xml:space="preserve">24.1989631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7760677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7290821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0242576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8363018035889</t>
+    <t xml:space="preserve">23.7760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7290782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0242557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8363037109375</t>
   </si>
   <si>
     <t xml:space="preserve">22.8832912445068</t>
@@ -1661,529 +1658,532 @@
     <t xml:space="preserve">23.5411281585693</t>
   </si>
   <si>
+    <t xml:space="preserve">22.9302787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8700428009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7085857391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1314792633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9435272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9097843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7688179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2387008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8495502471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8098087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4339046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3869171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4001636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.635103225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9640216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4808940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5616226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6555995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3736705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.554370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1182346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2459526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9170341491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0110111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8568019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6218585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1857166290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1387271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1917152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266567230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.802562713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8627948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3796653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2519493103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3459243774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2182064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.569766998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3591709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3292770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0473480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3066349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1938591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4736423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.486888885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2989368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0170078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7389278411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7013339996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8965377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5338764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3254280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9683170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8931369781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2165050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9418792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9039745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3923091888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5293464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.813606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2494735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5716342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7800922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5905838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8507995605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9404621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8930854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0775012969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6933975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4565143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0301265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4616069793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6511116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4142284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9878387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7983341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4193210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6612949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9455528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2349052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5665397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0403079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7560482025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9980220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0453987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3631763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9273128509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2305221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7188549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3821239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7946548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.087682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7990398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1547183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2873725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5147819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0599632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2115707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.476879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6562023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6088275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5140743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5038890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3092956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.162073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7779693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3566722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4040470123291</t>
+  </si>
+  <si>
     <t xml:space="preserve">22.9302806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2591953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.447151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8700466156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7085857391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1314792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9435253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7688179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.580867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2387027740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8495483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8098087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3869171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4001617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.635103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230590820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2929382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9640216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4808921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5616245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6555995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3736705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2796936035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061847686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5543727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2724456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1182346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2459526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7628211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9170341491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0110092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8568000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6218585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1857147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.138729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1917152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4399013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8025608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8627967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3796672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2519474029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.34592628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.218204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760433197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6748447418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3591709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3292770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0473480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3066329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1938610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6637420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615943908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3194313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4736442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4868907928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2989387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0170059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7389259338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7013339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8965377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5338764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3254280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9683151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2165050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713203430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9418773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9039745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3923072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5293464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.813606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2494716644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.950647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7800903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5905818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8508014678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7509574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8457107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.893087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2771892547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0775012969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6933975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2670078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4565162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0301246643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6511116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4142303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9878387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7983322143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.419319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6612949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9455547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2349033355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5665416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0403079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.756046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9980220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0453987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3631744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9273109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2305202484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7188549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3821258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7946548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987297058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0927753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0876846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7990398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1547164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.28737449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5147819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0599632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.476879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6562042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6088275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5140762329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5038909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3092937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1620750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7779693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3566703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4040470123291</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.6883068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1248779296875</t>
+    <t xml:space="preserve">22.1248798370361</t>
   </si>
   <si>
     <t xml:space="preserve">22.8829040527344</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7881507873535</t>
+    <t xml:space="preserve">22.7881526947021</t>
   </si>
   <si>
     <t xml:space="preserve">23.0250339508057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1722545623779</t>
+    <t xml:space="preserve">22.1722564697266</t>
   </si>
   <si>
     <t xml:space="preserve">22.8355274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4514217376709</t>
+    <t xml:space="preserve">23.4514236450195</t>
   </si>
   <si>
     <t xml:space="preserve">24.3515777587891</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">22.4091377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9827480316162</t>
+    <t xml:space="preserve">21.9827499389648</t>
   </si>
   <si>
     <t xml:space="preserve">22.5512676239014</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">21.7458667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6037349700928</t>
+    <t xml:space="preserve">21.6037368774414</t>
   </si>
   <si>
     <t xml:space="preserve">21.7932434082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6984901428223</t>
+    <t xml:space="preserve">21.6984882354736</t>
   </si>
   <si>
     <t xml:space="preserve">21.5563583374023</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">21.5089817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4987983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6832141876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9725646972656</t>
+    <t xml:space="preserve">23.49880027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6832160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9725666046143</t>
   </si>
   <si>
     <t xml:space="preserve">24.2568264007568</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0673198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2991104125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9200992584229</t>
+    <t xml:space="preserve">24.0673179626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2991123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9201011657715</t>
   </si>
   <si>
     <t xml:space="preserve">24.825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7305908203125</t>
+    <t xml:space="preserve">24.7305927276611</t>
   </si>
   <si>
     <t xml:space="preserve">24.3989562988281</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">24.5884628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4937076568604</t>
+    <t xml:space="preserve">24.493709564209</t>
   </si>
   <si>
     <t xml:space="preserve">25.0148506164551</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">25.7255001068115</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6358375549316</t>
+    <t xml:space="preserve">24.6358394622803</t>
   </si>
   <si>
     <t xml:space="preserve">25.5359935760498</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">25.772876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3464889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5935535430908</t>
+    <t xml:space="preserve">25.3464870452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5935554504395</t>
   </si>
   <si>
     <t xml:space="preserve">23.5461769104004</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">23.2619171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9776573181152</t>
+    <t xml:space="preserve">22.9776554107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.2145404815674</t>
@@ -2306,28 +2306,28 @@
     <t xml:space="preserve">23.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7830600738525</t>
+    <t xml:space="preserve">23.7830581665039</t>
   </si>
   <si>
     <t xml:space="preserve">21.3194751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6460208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3617630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622291564941</t>
+    <t xml:space="preserve">22.6460227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.361759185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622310638428</t>
   </si>
   <si>
     <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4835262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3887729644775</t>
+    <t xml:space="preserve">26.4835300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3887748718262</t>
   </si>
   <si>
     <t xml:space="preserve">26.6256561279297</t>
@@ -2336,25 +2336,25 @@
     <t xml:space="preserve">26.1992664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8202533721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5309028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6730327606201</t>
+    <t xml:space="preserve">25.820255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5309047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6730308532715</t>
   </si>
   <si>
     <t xml:space="preserve">26.3201923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7480144500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6526508331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8433742523193</t>
+    <t xml:space="preserve">25.7480125427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6526489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.843376159668</t>
   </si>
   <si>
     <t xml:space="preserve">25.6049690246582</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">25.891056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0817813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5096054077148</t>
+    <t xml:space="preserve">26.0817832946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5096035003662</t>
   </si>
   <si>
     <t xml:space="preserve">26.1294651031494</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">25.9387378692627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7956962585449</t>
+    <t xml:space="preserve">25.7956943511963</t>
   </si>
   <si>
     <t xml:space="preserve">25.12815284729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2235164642334</t>
+    <t xml:space="preserve">25.223518371582</t>
   </si>
   <si>
     <t xml:space="preserve">25.2711982727051</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">24.9851093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1758327484131</t>
+    <t xml:space="preserve">25.1758346557617</t>
   </si>
   <si>
     <t xml:space="preserve">24.5559749603271</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">24.6990203857422</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9361152648926</t>
+    <t xml:space="preserve">23.9361133575439</t>
   </si>
   <si>
     <t xml:space="preserve">24.937427520752</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">24.8420639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5082912445068</t>
+    <t xml:space="preserve">24.5082931518555</t>
   </si>
   <si>
     <t xml:space="preserve">23.8884334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2222061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6977062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8407516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.317569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0791606903076</t>
+    <t xml:space="preserve">24.222204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6977081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8407535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3175678253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.079158782959</t>
   </si>
   <si>
     <t xml:space="preserve">24.6513366699219</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">22.9824848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8871231079102</t>
+    <t xml:space="preserve">22.8871212005615</t>
   </si>
   <si>
     <t xml:space="preserve">22.0288562774658</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">21.9334926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1705894470215</t>
+    <t xml:space="preserve">21.1705875396729</t>
   </si>
   <si>
     <t xml:space="preserve">21.0752239227295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9321784973145</t>
+    <t xml:space="preserve">20.9321804046631</t>
   </si>
   <si>
     <t xml:space="preserve">20.5984115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3136329650879</t>
+    <t xml:space="preserve">21.3136310577393</t>
   </si>
   <si>
     <t xml:space="preserve">21.6474018096924</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">20.8368167877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0739135742188</t>
+    <t xml:space="preserve">20.88450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0739116668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.1229057312012</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">20.6460933685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9390926361084</t>
+    <t xml:space="preserve">18.939094543457</t>
   </si>
   <si>
     <t xml:space="preserve">19.4063720703125</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">18.6339321136475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5385704040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.519495010376</t>
+    <t xml:space="preserve">18.5385684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5194969177246</t>
   </si>
   <si>
     <t xml:space="preserve">18.0426826477051</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.6993732452393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8710289001465</t>
+    <t xml:space="preserve">17.8710269927979</t>
   </si>
   <si>
     <t xml:space="preserve">18.7674388885498</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">20.2169570922852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.835506439209</t>
+    <t xml:space="preserve">19.8355045318604</t>
   </si>
   <si>
     <t xml:space="preserve">20.5030479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7891368865967</t>
+    <t xml:space="preserve">20.789134979248</t>
   </si>
   <si>
     <t xml:space="preserve">21.7904472351074</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">19.9367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7894763946533</t>
+    <t xml:space="preserve">19.7894744873047</t>
   </si>
   <si>
     <t xml:space="preserve">20.5751628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9188976287842</t>
+    <t xml:space="preserve">20.9188995361328</t>
   </si>
   <si>
     <t xml:space="preserve">22.0974292755127</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">22.6375885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8831157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7849063873291</t>
+    <t xml:space="preserve">22.883113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7849044799805</t>
   </si>
   <si>
     <t xml:space="preserve">21.9010066986084</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">21.6554794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2268543243408</t>
+    <t xml:space="preserve">23.2268524169922</t>
   </si>
   <si>
     <t xml:space="preserve">24.0125408172607</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">22.6866931915283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8340091705322</t>
+    <t xml:space="preserve">22.8340110778809</t>
   </si>
   <si>
     <t xml:space="preserve">22.7357997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.539379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1956386566162</t>
+    <t xml:space="preserve">22.5393772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1956405639648</t>
   </si>
   <si>
     <t xml:space="preserve">22.4902725219727</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">22.4411659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7045879364014</t>
+    <t xml:space="preserve">21.7045860290527</t>
   </si>
   <si>
     <t xml:space="preserve">22.293851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8519020080566</t>
+    <t xml:space="preserve">21.8519039154053</t>
   </si>
   <si>
     <t xml:space="preserve">22.2447452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9501152038574</t>
+    <t xml:space="preserve">21.9501132965088</t>
   </si>
   <si>
     <t xml:space="preserve">22.3429565429688</t>
@@ -2684,22 +2684,22 @@
     <t xml:space="preserve">21.6063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2135334014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0171089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4590606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1153221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4099521636963</t>
+    <t xml:space="preserve">21.2135314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.017110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4590587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1153202056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4099540710449</t>
   </si>
   <si>
     <t xml:space="preserve">19.7403697967529</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">19.6028747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3278846740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9350433349609</t>
+    <t xml:space="preserve">19.3278865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9350414276123</t>
   </si>
   <si>
     <t xml:space="preserve">18.954683303833</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">19.5046634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1823177337646</t>
+    <t xml:space="preserve">20.1823196411133</t>
   </si>
   <si>
     <t xml:space="preserve">20.1332130432129</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">19.985897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6912651062012</t>
+    <t xml:space="preserve">19.6912631988525</t>
   </si>
   <si>
     <t xml:space="preserve">19.5832328796387</t>
@@ -2762,16 +2762,16 @@
     <t xml:space="preserve">19.3671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.738618850708</t>
+    <t xml:space="preserve">18.7386207580566</t>
   </si>
   <si>
     <t xml:space="preserve">18.4047031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1689968109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2279224395752</t>
+    <t xml:space="preserve">18.1689987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2279243469238</t>
   </si>
   <si>
     <t xml:space="preserve">18.0904293060303</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">18.1493549346924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.717227935791</t>
+    <t xml:space="preserve">17.7172298431396</t>
   </si>
   <si>
     <t xml:space="preserve">18.6796951293945</t>
@@ -2792,22 +2792,22 @@
     <t xml:space="preserve">18.6404094696045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5029125213623</t>
+    <t xml:space="preserve">18.5029144287109</t>
   </si>
   <si>
     <t xml:space="preserve">18.8761138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4225959777832</t>
+    <t xml:space="preserve">17.4225940704346</t>
   </si>
   <si>
     <t xml:space="preserve">18.2868518829346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7547626495361</t>
+    <t xml:space="preserve">18.2475662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7547607421875</t>
   </si>
   <si>
     <t xml:space="preserve">18.4832706451416</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">17.9529342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">18.129711151123</t>
+    <t xml:space="preserve">18.1297130584717</t>
   </si>
   <si>
     <t xml:space="preserve">17.5208072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2654590606689</t>
+    <t xml:space="preserve">17.2654571533203</t>
   </si>
   <si>
     <t xml:space="preserve">17.3243827819824</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">17.4618797302246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1083202362061</t>
+    <t xml:space="preserve">17.1083221435547</t>
   </si>
   <si>
     <t xml:space="preserve">17.2458152770996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7744045257568</t>
+    <t xml:space="preserve">16.7744026184082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9904670715332</t>
@@ -17343,7 +17343,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17369,7 +17369,7 @@
         <v>15.8661937713623</v>
       </c>
       <c r="G520" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17421,7 +17421,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G522" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17447,7 +17447,7 @@
         <v>16.0215549468994</v>
       </c>
       <c r="G523" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17473,7 +17473,7 @@
         <v>15.9244537353516</v>
       </c>
       <c r="G524" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17499,7 +17499,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G525" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17525,7 +17525,7 @@
         <v>15.1864919662476</v>
       </c>
       <c r="G526" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17551,7 +17551,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G527" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17577,7 +17577,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G528" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17603,7 +17603,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G529" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17629,7 +17629,7 @@
         <v>15.2253322601318</v>
       </c>
       <c r="G530" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17655,7 +17655,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G531" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17681,7 +17681,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G532" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17707,7 +17707,7 @@
         <v>15.613733291626</v>
       </c>
       <c r="G533" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17733,7 +17733,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G534" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17759,7 +17759,7 @@
         <v>15.8273544311523</v>
       </c>
       <c r="G535" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17785,7 +17785,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G536" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17811,7 +17811,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G537" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17837,7 +17837,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G538" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17863,7 +17863,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G539" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17889,7 +17889,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G540" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17915,7 +17915,7 @@
         <v>15.0505514144897</v>
       </c>
       <c r="G541" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17967,7 +17967,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G543" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17993,7 +17993,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G544" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -18019,7 +18019,7 @@
         <v>16.1769142150879</v>
       </c>
       <c r="G545" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -18045,7 +18045,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G546" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -18071,7 +18071,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G547" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18097,7 +18097,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G548" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18123,7 +18123,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G549" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18149,7 +18149,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G550" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18175,7 +18175,7 @@
         <v>17.536319732666</v>
       </c>
       <c r="G551" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18201,7 +18201,7 @@
         <v>18.1189212799072</v>
       </c>
       <c r="G552" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18227,7 +18227,7 @@
         <v>18.0995025634766</v>
       </c>
       <c r="G553" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18253,7 +18253,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G554" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18279,7 +18279,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G555" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18305,7 +18305,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G556" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18331,7 +18331,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G557" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18357,7 +18357,7 @@
         <v>18.9928245544434</v>
       </c>
       <c r="G558" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18383,7 +18383,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G559" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18409,7 +18409,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G560" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18435,7 +18435,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G561" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18461,7 +18461,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G562" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18487,7 +18487,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G563" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18513,7 +18513,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G564" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18539,7 +18539,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G565" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18565,7 +18565,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G566" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18591,7 +18591,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G567" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18617,7 +18617,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G568" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18643,7 +18643,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G569" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18669,7 +18669,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G570" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18695,7 +18695,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G571" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18721,7 +18721,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G572" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18747,7 +18747,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G573" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18773,7 +18773,7 @@
         <v>17.5945796966553</v>
       </c>
       <c r="G574" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18799,7 +18799,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G575" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18825,7 +18825,7 @@
         <v>16.4487953186035</v>
       </c>
       <c r="G576" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18851,7 +18851,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G577" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18877,7 +18877,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G578" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18903,7 +18903,7 @@
         <v>15.9827136993408</v>
       </c>
       <c r="G579" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18929,7 +18929,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G580" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18955,7 +18955,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G581" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18981,7 +18981,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G582" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -19007,7 +19007,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G583" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -19033,7 +19033,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G584" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -19059,7 +19059,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G585" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -19085,7 +19085,7 @@
         <v>17.5168991088867</v>
       </c>
       <c r="G586" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19111,7 +19111,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G587" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19137,7 +19137,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G588" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19163,7 +19163,7 @@
         <v>17.1479187011719</v>
       </c>
       <c r="G589" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19189,7 +19189,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G590" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19215,7 +19215,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G591" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19241,7 +19241,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G592" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19267,7 +19267,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G593" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19293,7 +19293,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G594" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19319,7 +19319,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G595" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19345,7 +19345,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G596" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19371,7 +19371,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G597" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19397,7 +19397,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G598" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19423,7 +19423,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G599" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19449,7 +19449,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G600" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19475,7 +19475,7 @@
         <v>17.4586391448975</v>
       </c>
       <c r="G601" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19501,7 +19501,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G602" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19527,7 +19527,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G603" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19553,7 +19553,7 @@
         <v>16.0409755706787</v>
       </c>
       <c r="G604" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19579,7 +19579,7 @@
         <v>15.5554733276367</v>
       </c>
       <c r="G605" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19605,7 +19605,7 @@
         <v>15.2641716003418</v>
       </c>
       <c r="G606" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19631,7 +19631,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G607" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19657,7 +19657,7 @@
         <v>15.5360527038574</v>
       </c>
       <c r="G608" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19683,7 +19683,7 @@
         <v>16.4099559783936</v>
       </c>
       <c r="G609" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19709,7 +19709,7 @@
         <v>15.6719932556152</v>
       </c>
       <c r="G610" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19735,7 +19735,7 @@
         <v>15.108811378479</v>
       </c>
       <c r="G611" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19761,7 +19761,7 @@
         <v>18.0024013519287</v>
       </c>
       <c r="G612" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19787,7 +19787,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G613" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19813,7 +19813,7 @@
         <v>17.1673374176025</v>
       </c>
       <c r="G614" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19839,7 +19839,7 @@
         <v>16.5847358703613</v>
       </c>
       <c r="G615" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19865,7 +19865,7 @@
         <v>16.2351741790771</v>
       </c>
       <c r="G616" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19891,7 +19891,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G617" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19917,7 +19917,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G618" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19943,7 +19943,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G619" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19969,7 +19969,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G620" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19995,7 +19995,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G621" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -20021,7 +20021,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G622" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -20047,7 +20047,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G623" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -20073,7 +20073,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G624" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20099,7 +20099,7 @@
         <v>17.6334209442139</v>
       </c>
       <c r="G625" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20125,7 +20125,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G626" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20151,7 +20151,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G627" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20177,7 +20177,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G628" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20203,7 +20203,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G629" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20229,7 +20229,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G630" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20255,7 +20255,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G631" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20281,7 +20281,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G632" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20307,7 +20307,7 @@
         <v>17.4974803924561</v>
       </c>
       <c r="G633" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20333,7 +20333,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G634" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20359,7 +20359,7 @@
         <v>17.7499408721924</v>
       </c>
       <c r="G635" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20385,7 +20385,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G636" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20411,7 +20411,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G637" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20437,7 +20437,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G638" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20463,7 +20463,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G639" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20489,7 +20489,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G640" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20515,7 +20515,7 @@
         <v>17.5557403564453</v>
       </c>
       <c r="G641" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20541,7 +20541,7 @@
         <v>17.1090774536133</v>
       </c>
       <c r="G642" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20567,7 +20567,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G643" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20593,7 +20593,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G644" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20619,7 +20619,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G645" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20645,7 +20645,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G646" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20671,7 +20671,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G647" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20697,7 +20697,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G648" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20723,7 +20723,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G649" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20749,7 +20749,7 @@
         <v>18.7597846984863</v>
       </c>
       <c r="G650" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20775,7 +20775,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G651" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20801,7 +20801,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G652" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20827,7 +20827,7 @@
         <v>17.303279876709</v>
       </c>
       <c r="G653" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20853,7 +20853,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G654" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20879,7 +20879,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G655" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20905,7 +20905,7 @@
         <v>17.4003791809082</v>
       </c>
       <c r="G656" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20931,7 +20931,7 @@
         <v>17.4780597686768</v>
       </c>
       <c r="G657" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20957,7 +20957,7 @@
         <v>17.2255992889404</v>
       </c>
       <c r="G658" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20983,7 +20983,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G659" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21009,7 +21009,7 @@
         <v>17.2644386291504</v>
       </c>
       <c r="G660" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -21035,7 +21035,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G661" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21061,7 +21061,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G662" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21087,7 +21087,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G663" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21113,7 +21113,7 @@
         <v>17.1284980773926</v>
       </c>
       <c r="G664" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21139,7 +21139,7 @@
         <v>16.9731388092041</v>
       </c>
       <c r="G665" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21165,7 +21165,7 @@
         <v>17.2838592529297</v>
       </c>
       <c r="G666" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21191,7 +21191,7 @@
         <v>17.0896587371826</v>
       </c>
       <c r="G667" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21217,7 +21217,7 @@
         <v>16.9148788452148</v>
       </c>
       <c r="G668" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21243,7 +21243,7 @@
         <v>16.5070552825928</v>
       </c>
       <c r="G669" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21269,7 +21269,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G670" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21295,7 +21295,7 @@
         <v>17.0119781494141</v>
       </c>
       <c r="G671" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21321,7 +21321,7 @@
         <v>17.575159072876</v>
       </c>
       <c r="G672" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21347,7 +21347,7 @@
         <v>17.6916809082031</v>
       </c>
       <c r="G673" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21373,7 +21373,7 @@
         <v>17.0702381134033</v>
       </c>
       <c r="G674" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21399,7 +21399,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G675" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21425,7 +21425,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G676" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21451,7 +21451,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G677" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21477,7 +21477,7 @@
         <v>16.9537181854248</v>
       </c>
       <c r="G678" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21503,7 +21503,7 @@
         <v>17.2061786651611</v>
       </c>
       <c r="G679" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21529,7 +21529,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G680" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21555,7 +21555,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G681" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21581,7 +21581,7 @@
         <v>16.7012577056885</v>
       </c>
       <c r="G682" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21607,7 +21607,7 @@
         <v>16.4682159423828</v>
       </c>
       <c r="G683" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21633,7 +21633,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G684" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21659,7 +21659,7 @@
         <v>16.8760375976562</v>
       </c>
       <c r="G685" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21685,7 +21685,7 @@
         <v>16.3711166381836</v>
       </c>
       <c r="G686" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21711,7 +21711,7 @@
         <v>16.2157554626465</v>
       </c>
       <c r="G687" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21737,7 +21737,7 @@
         <v>16.9342975616455</v>
       </c>
       <c r="G688" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21763,7 +21763,7 @@
         <v>16.6429977416992</v>
       </c>
       <c r="G689" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21789,7 +21789,7 @@
         <v>16.5264759063721</v>
       </c>
       <c r="G690" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21815,7 +21815,7 @@
         <v>16.6041564941406</v>
       </c>
       <c r="G691" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21841,7 +21841,7 @@
         <v>15.9632940292358</v>
       </c>
       <c r="G692" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21867,7 +21867,7 @@
         <v>15.5166330337524</v>
       </c>
       <c r="G693" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21893,7 +21893,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G694" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21919,7 +21919,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G695" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21971,7 +21971,7 @@
         <v>15.0893907546997</v>
       </c>
       <c r="G697" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21997,7 +21997,7 @@
         <v>15.4389533996582</v>
       </c>
       <c r="G698" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22023,7 +22023,7 @@
         <v>15.4972133636475</v>
       </c>
       <c r="G699" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22049,7 +22049,7 @@
         <v>15.7302541732788</v>
       </c>
       <c r="G700" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22075,7 +22075,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G701" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22101,7 +22101,7 @@
         <v>16.2545948028564</v>
       </c>
       <c r="G702" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22127,7 +22127,7 @@
         <v>16.2934341430664</v>
       </c>
       <c r="G703" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22153,7 +22153,7 @@
         <v>16.1380748748779</v>
       </c>
       <c r="G704" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22179,7 +22179,7 @@
         <v>16.332275390625</v>
       </c>
       <c r="G705" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22205,7 +22205,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G706" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22231,7 +22231,7 @@
         <v>16.0798149108887</v>
       </c>
       <c r="G707" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22257,7 +22257,7 @@
         <v>16.0603942871094</v>
       </c>
       <c r="G708" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22283,7 +22283,7 @@
         <v>16.3905353546143</v>
       </c>
       <c r="G709" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22309,7 +22309,7 @@
         <v>16.2740154266357</v>
       </c>
       <c r="G710" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22335,7 +22335,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G711" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22361,7 +22361,7 @@
         <v>16.856616973877</v>
       </c>
       <c r="G712" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22387,7 +22387,7 @@
         <v>16.9925575256348</v>
       </c>
       <c r="G713" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22413,7 +22413,7 @@
         <v>17.3421192169189</v>
       </c>
       <c r="G714" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22439,7 +22439,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G715" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22465,7 +22465,7 @@
         <v>17.8082008361816</v>
       </c>
       <c r="G716" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22491,7 +22491,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G717" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22517,7 +22517,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G718" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22543,7 +22543,7 @@
         <v>18.3519630432129</v>
       </c>
       <c r="G719" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22569,7 +22569,7 @@
         <v>18.2742824554443</v>
       </c>
       <c r="G720" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22595,7 +22595,7 @@
         <v>18.4684829711914</v>
       </c>
       <c r="G721" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22621,7 +22621,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G722" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22647,7 +22647,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G723" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22673,7 +22673,7 @@
         <v>18.3325424194336</v>
       </c>
       <c r="G724" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22699,7 +22699,7 @@
         <v>18.6432647705078</v>
       </c>
       <c r="G725" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22725,7 +22725,7 @@
         <v>19.2064456939697</v>
       </c>
       <c r="G726" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22751,7 +22751,7 @@
         <v>18.779203414917</v>
       </c>
       <c r="G727" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22777,7 +22777,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G728" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22803,7 +22803,7 @@
         <v>18.060661315918</v>
       </c>
       <c r="G729" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22829,7 +22829,7 @@
         <v>17.8470401763916</v>
       </c>
       <c r="G730" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22855,7 +22855,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G731" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22881,7 +22881,7 @@
         <v>18.0800819396973</v>
       </c>
       <c r="G732" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22907,7 +22907,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G733" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22933,7 +22933,7 @@
         <v>18.293701171875</v>
       </c>
       <c r="G734" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22959,7 +22959,7 @@
         <v>18.4490623474121</v>
       </c>
       <c r="G735" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22985,7 +22985,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G736" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23011,7 +23011,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G737" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23037,7 +23037,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G738" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23063,7 +23063,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G739" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23089,7 +23089,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G740" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23115,7 +23115,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G741" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23141,7 +23141,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G742" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23167,7 +23167,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G743" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23193,7 +23193,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G744" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23219,7 +23219,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G745" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23245,7 +23245,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G746" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23271,7 +23271,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G747" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23297,7 +23297,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G748" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23323,7 +23323,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G749" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23349,7 +23349,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G750" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23375,7 +23375,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G751" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23401,7 +23401,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G752" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23427,7 +23427,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G753" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23453,7 +23453,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G754" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23479,7 +23479,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G755" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23505,7 +23505,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G756" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23531,7 +23531,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G757" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23557,7 +23557,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G758" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23583,7 +23583,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G759" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23609,7 +23609,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G760" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23635,7 +23635,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G761" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23661,7 +23661,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G762" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23687,7 +23687,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G763" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23713,7 +23713,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G764" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23739,7 +23739,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G765" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23765,7 +23765,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G766" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23791,7 +23791,7 @@
         <v>19.9541187286377</v>
       </c>
       <c r="G767" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23817,7 +23817,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G768" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23843,7 +23843,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G769" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23869,7 +23869,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G770" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23895,7 +23895,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G771" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23921,7 +23921,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G772" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23947,7 +23947,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G773" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23973,7 +23973,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G774" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23999,7 +23999,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G775" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24025,7 +24025,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G776" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24051,7 +24051,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G777" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24077,7 +24077,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G778" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24103,7 +24103,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G779" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24129,7 +24129,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G780" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24155,7 +24155,7 @@
         <v>19.6142673492432</v>
       </c>
       <c r="G781" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24181,7 +24181,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G782" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24207,7 +24207,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G783" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24233,7 +24233,7 @@
         <v>20.4881706237793</v>
       </c>
       <c r="G784" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24259,7 +24259,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G785" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24285,7 +24285,7 @@
         <v>19.8084678649902</v>
       </c>
       <c r="G786" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24311,7 +24311,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G787" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24337,7 +24337,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G788" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24363,7 +24363,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G789" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24389,7 +24389,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G790" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24415,7 +24415,7 @@
         <v>19.4006462097168</v>
       </c>
       <c r="G791" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24441,7 +24441,7 @@
         <v>19.1287651062012</v>
       </c>
       <c r="G792" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24467,7 +24467,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G793" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24493,7 +24493,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G794" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24519,7 +24519,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G795" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24545,7 +24545,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G796" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24571,7 +24571,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G797" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24597,7 +24597,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G798" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24623,7 +24623,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G799" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24649,7 +24649,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G800" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24675,7 +24675,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G801" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24701,7 +24701,7 @@
         <v>20.8280200958252</v>
       </c>
       <c r="G802" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24727,7 +24727,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G803" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24753,7 +24753,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G804" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24779,7 +24779,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G805" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24805,7 +24805,7 @@
         <v>23.2069797515869</v>
       </c>
       <c r="G806" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24831,7 +24831,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G807" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24857,7 +24857,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G808" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24883,7 +24883,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G809" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24909,7 +24909,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G810" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24935,7 +24935,7 @@
         <v>23.8381309509277</v>
       </c>
       <c r="G811" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24961,7 +24961,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G812" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24987,7 +24987,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G813" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25013,7 +25013,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G814" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25039,7 +25039,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G815" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25065,7 +25065,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G816" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25091,7 +25091,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G817" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25117,7 +25117,7 @@
         <v>23.5953807830811</v>
       </c>
       <c r="G818" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25143,7 +25143,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G819" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25169,7 +25169,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G820" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25195,7 +25195,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G821" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25221,7 +25221,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G822" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25247,7 +25247,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G823" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25273,7 +25273,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G824" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25299,7 +25299,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G825" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25325,7 +25325,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G826" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25351,7 +25351,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G827" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25377,7 +25377,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G828" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25403,7 +25403,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G829" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25429,7 +25429,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G830" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25455,7 +25455,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G831" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25481,7 +25481,7 @@
         <v>24.2265338897705</v>
       </c>
       <c r="G832" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25507,7 +25507,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G833" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25533,7 +25533,7 @@
         <v>24.0323314666748</v>
       </c>
       <c r="G834" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25559,7 +25559,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G835" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25585,7 +25585,7 @@
         <v>25.0033359527588</v>
       </c>
       <c r="G836" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25611,7 +25611,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G837" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25637,7 +25637,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G838" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25663,7 +25663,7 @@
         <v>22.4787273406982</v>
       </c>
       <c r="G839" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25689,7 +25689,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G840" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25715,7 +25715,7 @@
         <v>22.8671283721924</v>
       </c>
       <c r="G841" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25741,7 +25741,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G842" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25767,7 +25767,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G843" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25793,7 +25793,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G844" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25819,7 +25819,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G845" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25845,7 +25845,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G846" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25871,7 +25871,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G847" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25897,7 +25897,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G848" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25923,7 +25923,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G849" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25949,7 +25949,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G850" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25975,7 +25975,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G851" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26001,7 +26001,7 @@
         <v>25.6344871520996</v>
       </c>
       <c r="G852" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26027,7 +26027,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G853" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26053,7 +26053,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G854" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26079,7 +26079,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G855" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26105,7 +26105,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G856" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26131,7 +26131,7 @@
         <v>25.1975364685059</v>
       </c>
       <c r="G857" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26157,7 +26157,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G858" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26183,7 +26183,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G859" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26209,7 +26209,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G860" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26235,7 +26235,7 @@
         <v>24.1779823303223</v>
       </c>
       <c r="G861" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26261,7 +26261,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G862" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26287,7 +26287,7 @@
         <v>24.3236331939697</v>
       </c>
       <c r="G863" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26313,7 +26313,7 @@
         <v>24.9547843933105</v>
       </c>
       <c r="G864" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26339,7 +26339,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G865" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26365,7 +26365,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G866" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26391,7 +26391,7 @@
         <v>25.100435256958</v>
       </c>
       <c r="G867" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26417,7 +26417,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G868" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26443,7 +26443,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G869" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26469,7 +26469,7 @@
         <v>25.2460861206055</v>
       </c>
       <c r="G870" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26495,7 +26495,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G871" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26521,7 +26521,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G872" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26547,7 +26547,7 @@
         <v>26.4112892150879</v>
       </c>
       <c r="G873" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26573,7 +26573,7 @@
         <v>26.2656402587891</v>
       </c>
       <c r="G874" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26599,7 +26599,7 @@
         <v>26.5083904266357</v>
       </c>
       <c r="G875" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26625,7 +26625,7 @@
         <v>26.2170906066895</v>
       </c>
       <c r="G876" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26651,7 +26651,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G877" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26677,7 +26677,7 @@
         <v>26.1199893951416</v>
       </c>
       <c r="G878" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26703,7 +26703,7 @@
         <v>24.5663833618164</v>
       </c>
       <c r="G879" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26729,7 +26729,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G880" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26755,7 +26755,7 @@
         <v>24.0808811187744</v>
       </c>
       <c r="G881" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26781,7 +26781,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G882" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26807,7 +26807,7 @@
         <v>23.3040790557861</v>
       </c>
       <c r="G883" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26833,7 +26833,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G884" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26859,7 +26859,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G885" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26885,7 +26885,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G886" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26911,7 +26911,7 @@
         <v>23.7410316467285</v>
       </c>
       <c r="G887" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26937,7 +26937,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G888" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26963,7 +26963,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G889" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26989,7 +26989,7 @@
         <v>24.6149349212646</v>
       </c>
       <c r="G890" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27015,7 +27015,7 @@
         <v>25.5373878479004</v>
       </c>
       <c r="G891" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27041,7 +27041,7 @@
         <v>25.4888362884521</v>
       </c>
       <c r="G892" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27067,7 +27067,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G893" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27093,7 +27093,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G894" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27119,7 +27119,7 @@
         <v>25.5859375</v>
       </c>
       <c r="G895" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27145,7 +27145,7 @@
         <v>25.3431873321533</v>
       </c>
       <c r="G896" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27171,7 +27171,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G897" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27197,7 +27197,7 @@
         <v>23.7895812988281</v>
       </c>
       <c r="G898" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27223,7 +27223,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G899" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27249,7 +27249,7 @@
         <v>24.7120342254639</v>
       </c>
       <c r="G900" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27275,7 +27275,7 @@
         <v>24.5178337097168</v>
       </c>
       <c r="G901" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27301,7 +27301,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G902" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27327,7 +27327,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G903" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27353,7 +27353,7 @@
         <v>25.6830387115479</v>
       </c>
       <c r="G904" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27379,7 +27379,7 @@
         <v>25.8286876678467</v>
       </c>
       <c r="G905" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27405,7 +27405,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G906" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27431,7 +27431,7 @@
         <v>25.4402866363525</v>
       </c>
       <c r="G907" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27457,7 +27457,7 @@
         <v>24.8091354370117</v>
       </c>
       <c r="G908" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27483,7 +27483,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G909" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27509,7 +27509,7 @@
         <v>24.6634845733643</v>
       </c>
       <c r="G910" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27535,7 +27535,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G911" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27561,7 +27561,7 @@
         <v>25.2946357727051</v>
       </c>
       <c r="G912" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27587,7 +27587,7 @@
         <v>26.0228881835938</v>
       </c>
       <c r="G913" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27613,7 +27613,7 @@
         <v>25.9743385314941</v>
       </c>
       <c r="G914" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27639,7 +27639,7 @@
         <v>25.0518856048584</v>
       </c>
       <c r="G915" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27665,7 +27665,7 @@
         <v>24.4207324981689</v>
       </c>
       <c r="G916" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27691,7 +27691,7 @@
         <v>23.6439304351807</v>
       </c>
       <c r="G917" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27717,7 +27717,7 @@
         <v>24.2750835418701</v>
       </c>
       <c r="G918" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27743,7 +27743,7 @@
         <v>24.3721828460693</v>
       </c>
       <c r="G919" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27769,7 +27769,7 @@
         <v>23.6924800872803</v>
       </c>
       <c r="G920" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27795,7 +27795,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G921" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27821,7 +27821,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G922" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27847,7 +27847,7 @@
         <v>22.1388759613037</v>
       </c>
       <c r="G923" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27873,7 +27873,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G924" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27899,7 +27899,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G925" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27925,7 +27925,7 @@
         <v>20.6338195800781</v>
       </c>
       <c r="G926" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27951,7 +27951,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G927" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27977,7 +27977,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G928" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28003,7 +28003,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G929" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28029,7 +28029,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G930" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28055,7 +28055,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G931" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28081,7 +28081,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G932" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28107,7 +28107,7 @@
         <v>22.0417747497559</v>
       </c>
       <c r="G933" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28133,7 +28133,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G934" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28159,7 +28159,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G935" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28185,7 +28185,7 @@
         <v>22.0903244018555</v>
       </c>
       <c r="G936" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28211,7 +28211,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G937" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28237,7 +28237,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G938" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28263,7 +28263,7 @@
         <v>21.896125793457</v>
       </c>
       <c r="G939" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28289,7 +28289,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G940" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28315,7 +28315,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G941" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28341,7 +28341,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G942" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28367,7 +28367,7 @@
         <v>19.8570175170898</v>
       </c>
       <c r="G943" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28393,7 +28393,7 @@
         <v>19.1870250701904</v>
       </c>
       <c r="G944" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28419,7 +28419,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G945" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28445,7 +28445,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G946" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28471,7 +28471,7 @@
         <v>20.0997695922852</v>
       </c>
       <c r="G947" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28497,7 +28497,7 @@
         <v>20.0026683807373</v>
       </c>
       <c r="G948" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28523,7 +28523,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G949" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28549,7 +28549,7 @@
         <v>17.9053001403809</v>
       </c>
       <c r="G950" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28575,7 +28575,7 @@
         <v>17.6140003204346</v>
       </c>
       <c r="G951" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28601,7 +28601,7 @@
         <v>17.3809585571289</v>
       </c>
       <c r="G952" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28627,7 +28627,7 @@
         <v>18.9151439666748</v>
       </c>
       <c r="G953" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28653,7 +28653,7 @@
         <v>18.7986240386963</v>
       </c>
       <c r="G954" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28679,7 +28679,7 @@
         <v>19.2841262817383</v>
       </c>
       <c r="G955" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28705,7 +28705,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G956" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28731,7 +28731,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G957" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28757,7 +28757,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G958" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28783,7 +28783,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G959" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28809,7 +28809,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G960" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28835,7 +28835,7 @@
         <v>21.6048240661621</v>
       </c>
       <c r="G961" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28861,7 +28861,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G962" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28887,7 +28887,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G963" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28913,7 +28913,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G964" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28939,7 +28939,7 @@
         <v>22.7214775085449</v>
       </c>
       <c r="G965" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28965,7 +28965,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G966" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28991,7 +28991,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G967" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29017,7 +29017,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G968" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29043,7 +29043,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G969" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29069,7 +29069,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G970" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29095,7 +29095,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G971" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29121,7 +29121,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G972" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29147,7 +29147,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G973" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29173,7 +29173,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G974" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29199,7 +29199,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G975" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29225,7 +29225,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G976" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29251,7 +29251,7 @@
         <v>20.9736728668213</v>
       </c>
       <c r="G977" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29277,7 +29277,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G978" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29303,7 +29303,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G979" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29329,7 +29329,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G980" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29355,7 +29355,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G981" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29381,7 +29381,7 @@
         <v>22.5272769927979</v>
       </c>
       <c r="G982" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29407,7 +29407,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G983" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29433,7 +29433,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G984" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29459,7 +29459,7 @@
         <v>22.3330764770508</v>
       </c>
       <c r="G985" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29485,7 +29485,7 @@
         <v>22.2359752655029</v>
       </c>
       <c r="G986" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29511,7 +29511,7 @@
         <v>22.2845268249512</v>
       </c>
       <c r="G987" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29537,7 +29537,7 @@
         <v>22.3816261291504</v>
       </c>
       <c r="G988" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29563,7 +29563,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G989" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29589,7 +29589,7 @@
         <v>22.6729278564453</v>
       </c>
       <c r="G990" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29615,7 +29615,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G991" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29641,7 +29641,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G992" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29667,7 +29667,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G993" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29693,7 +29693,7 @@
         <v>19.3618068695068</v>
       </c>
       <c r="G994" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29719,7 +29719,7 @@
         <v>19.3229656219482</v>
       </c>
       <c r="G995" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29745,7 +29745,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G996" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29771,7 +29771,7 @@
         <v>19.9055671691895</v>
       </c>
       <c r="G997" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29797,7 +29797,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G998" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29823,7 +29823,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G999" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29849,7 +29849,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1000" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29875,7 +29875,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1001" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29901,7 +29901,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1002" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29927,7 +29927,7 @@
         <v>20.2939682006836</v>
       </c>
       <c r="G1003" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29953,7 +29953,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1004" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29979,7 +29979,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1005" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30005,7 +30005,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1006" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30031,7 +30031,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1007" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30057,7 +30057,7 @@
         <v>21.8475742340088</v>
       </c>
       <c r="G1008" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30083,7 +30083,7 @@
         <v>22.4301776885986</v>
       </c>
       <c r="G1009" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30109,7 +30109,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1010" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30135,7 +30135,7 @@
         <v>21.6533737182617</v>
       </c>
       <c r="G1011" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30161,7 +30161,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1012" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30187,7 +30187,7 @@
         <v>20.8765716552734</v>
       </c>
       <c r="G1013" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30213,7 +30213,7 @@
         <v>21.0707721710205</v>
       </c>
       <c r="G1014" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30239,7 +30239,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1015" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30265,7 +30265,7 @@
         <v>21.2164211273193</v>
       </c>
       <c r="G1016" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30291,7 +30291,7 @@
         <v>20.3910694122314</v>
       </c>
       <c r="G1017" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30317,7 +30317,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1018" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30343,7 +30343,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1019" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30369,7 +30369,7 @@
         <v>18.5655822753906</v>
       </c>
       <c r="G1020" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30395,7 +30395,7 @@
         <v>18.4879035949707</v>
       </c>
       <c r="G1021" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30421,7 +30421,7 @@
         <v>17.7887802124023</v>
       </c>
       <c r="G1022" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30447,7 +30447,7 @@
         <v>17.7693614959717</v>
       </c>
       <c r="G1023" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30473,7 +30473,7 @@
         <v>17.1867599487305</v>
       </c>
       <c r="G1024" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30499,7 +30499,7 @@
         <v>17.3615398406982</v>
       </c>
       <c r="G1025" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30525,7 +30525,7 @@
         <v>17.3226985931396</v>
       </c>
       <c r="G1026" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30551,7 +30551,7 @@
         <v>16.7983570098877</v>
       </c>
       <c r="G1027" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30577,7 +30577,7 @@
         <v>16.6624164581299</v>
       </c>
       <c r="G1028" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30603,7 +30603,7 @@
         <v>17.2450199127197</v>
       </c>
       <c r="G1029" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30629,7 +30629,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1030" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30655,7 +30655,7 @@
         <v>17.9635601043701</v>
       </c>
       <c r="G1031" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30681,7 +30681,7 @@
         <v>18.4102230072021</v>
       </c>
       <c r="G1032" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30707,7 +30707,7 @@
         <v>18.254861831665</v>
       </c>
       <c r="G1033" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30733,7 +30733,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1034" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30759,7 +30759,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1035" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30785,7 +30785,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1036" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30811,7 +30811,7 @@
         <v>19.4200668334961</v>
       </c>
       <c r="G1037" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30837,7 +30837,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1038" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30863,7 +30863,7 @@
         <v>19.031665802002</v>
       </c>
       <c r="G1039" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30889,7 +30889,7 @@
         <v>19.2452869415283</v>
       </c>
       <c r="G1040" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30915,7 +30915,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1041" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30941,7 +30941,7 @@
         <v>18.3908023834229</v>
       </c>
       <c r="G1042" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30967,7 +30967,7 @@
         <v>18.8763046264648</v>
       </c>
       <c r="G1043" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30993,7 +30993,7 @@
         <v>19.0899257659912</v>
       </c>
       <c r="G1044" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31019,7 +31019,7 @@
         <v>19.0510845184326</v>
       </c>
       <c r="G1045" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31045,7 +31045,7 @@
         <v>19.225866317749</v>
       </c>
       <c r="G1046" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31071,7 +31071,7 @@
         <v>20.3425197601318</v>
       </c>
       <c r="G1047" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31097,7 +31097,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1048" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31123,7 +31123,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1049" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31149,7 +31149,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1050" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31175,7 +31175,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1051" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31201,7 +31201,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1052" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31227,7 +31227,7 @@
         <v>21.5562744140625</v>
       </c>
       <c r="G1053" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31253,7 +31253,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1054" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31279,7 +31279,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1055" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31305,7 +31305,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1056" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31331,7 +31331,7 @@
         <v>22.6243762969971</v>
       </c>
       <c r="G1057" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31357,7 +31357,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1058" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31383,7 +31383,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1059" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31409,7 +31409,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1060" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31435,7 +31435,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1061" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31461,7 +31461,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1062" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31487,7 +31487,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1063" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31513,7 +31513,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1064" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31539,7 +31539,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1065" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31565,7 +31565,7 @@
         <v>22.1874256134033</v>
       </c>
       <c r="G1066" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31591,7 +31591,7 @@
         <v>21.9446754455566</v>
       </c>
       <c r="G1067" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31617,7 +31617,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1068" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31643,7 +31643,7 @@
         <v>21.5077228546143</v>
       </c>
       <c r="G1069" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31669,7 +31669,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1070" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31695,7 +31695,7 @@
         <v>21.3135223388672</v>
       </c>
       <c r="G1071" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31721,7 +31721,7 @@
         <v>20.925121307373</v>
       </c>
       <c r="G1072" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31747,7 +31747,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1073" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31773,7 +31773,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1074" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31799,7 +31799,7 @@
         <v>20.7794704437256</v>
       </c>
       <c r="G1075" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31825,7 +31825,7 @@
         <v>20.1483192443848</v>
       </c>
       <c r="G1076" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31851,7 +31851,7 @@
         <v>20.730920791626</v>
       </c>
       <c r="G1077" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31877,7 +31877,7 @@
         <v>20.4396190643311</v>
       </c>
       <c r="G1078" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31903,7 +31903,7 @@
         <v>20.1968688964844</v>
       </c>
       <c r="G1079" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31929,7 +31929,7 @@
         <v>19.7113666534424</v>
       </c>
       <c r="G1080" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31955,7 +31955,7 @@
         <v>20.0512180328369</v>
       </c>
       <c r="G1081" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31981,7 +31981,7 @@
         <v>20.5367202758789</v>
       </c>
       <c r="G1082" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32007,7 +32007,7 @@
         <v>20.245418548584</v>
       </c>
       <c r="G1083" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32033,7 +32033,7 @@
         <v>19.6628170013428</v>
       </c>
       <c r="G1084" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32059,7 +32059,7 @@
         <v>19.4686164855957</v>
       </c>
       <c r="G1085" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32085,7 +32085,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1086" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32111,7 +32111,7 @@
         <v>19.0122451782227</v>
       </c>
       <c r="G1087" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32137,7 +32137,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1088" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32163,7 +32163,7 @@
         <v>18.3713836669922</v>
       </c>
       <c r="G1089" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32189,7 +32189,7 @@
         <v>18.6821041107178</v>
       </c>
       <c r="G1090" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32215,7 +32215,7 @@
         <v>18.1577625274658</v>
       </c>
       <c r="G1091" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32241,7 +32241,7 @@
         <v>18.8374633789062</v>
       </c>
       <c r="G1092" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32267,7 +32267,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1093" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32293,7 +32293,7 @@
         <v>18.2160224914551</v>
       </c>
       <c r="G1094" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32319,7 +32319,7 @@
         <v>18.2354412078857</v>
       </c>
       <c r="G1095" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32345,7 +32345,7 @@
         <v>17.4197998046875</v>
       </c>
       <c r="G1096" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32371,7 +32371,7 @@
         <v>18.5850028991699</v>
       </c>
       <c r="G1097" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32397,7 +32397,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1098" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32423,7 +32423,7 @@
         <v>20.5852699279785</v>
       </c>
       <c r="G1099" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32449,7 +32449,7 @@
         <v>19.5657176971436</v>
       </c>
       <c r="G1100" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32475,7 +32475,7 @@
         <v>19.264705657959</v>
       </c>
       <c r="G1101" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32501,7 +32501,7 @@
         <v>18.6044235229492</v>
       </c>
       <c r="G1102" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32527,7 +32527,7 @@
         <v>18.740364074707</v>
       </c>
       <c r="G1103" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32553,7 +32553,7 @@
         <v>18.9734058380127</v>
       </c>
       <c r="G1104" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32579,7 +32579,7 @@
         <v>18.6238422393799</v>
       </c>
       <c r="G1105" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32605,7 +32605,7 @@
         <v>18.7015247344971</v>
       </c>
       <c r="G1106" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32631,7 +32631,7 @@
         <v>18.5073223114014</v>
       </c>
       <c r="G1107" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32657,7 +32657,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1108" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32683,7 +32683,7 @@
         <v>18.8180446624756</v>
       </c>
       <c r="G1109" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32709,7 +32709,7 @@
         <v>18.7209434509277</v>
       </c>
       <c r="G1110" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32735,7 +32735,7 @@
         <v>18.6626834869385</v>
       </c>
       <c r="G1111" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32761,7 +32761,7 @@
         <v>18.9345645904541</v>
       </c>
       <c r="G1112" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32787,7 +32787,7 @@
         <v>19.5171661376953</v>
       </c>
       <c r="G1113" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32813,7 +32813,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1114" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32839,7 +32839,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1115" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32865,7 +32865,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1116" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32891,7 +32891,7 @@
         <v>21.4591732025146</v>
       </c>
       <c r="G1117" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32917,7 +32917,7 @@
         <v>21.410623550415</v>
       </c>
       <c r="G1118" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32943,7 +32943,7 @@
         <v>21.0222225189209</v>
       </c>
       <c r="G1119" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32969,7 +32969,7 @@
         <v>21.1678714752197</v>
       </c>
       <c r="G1120" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32995,7 +32995,7 @@
         <v>20.6823711395264</v>
       </c>
       <c r="G1121" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33021,7 +33021,7 @@
         <v>21.1193218231201</v>
       </c>
       <c r="G1122" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33047,7 +33047,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1123" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33073,7 +33073,7 @@
         <v>21.3620738983154</v>
       </c>
       <c r="G1124" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33099,7 +33099,7 @@
         <v>21.2649726867676</v>
       </c>
       <c r="G1125" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33125,7 +33125,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1126" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33151,7 +33151,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1127" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33177,7 +33177,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1128" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33203,7 +33203,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1129" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33229,7 +33229,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1130" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33255,7 +33255,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1131" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33281,7 +33281,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1132" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33307,7 +33307,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1133" t="s">
-        <v>549</v>
+        <v>715</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33333,7 +33333,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1134" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33385,7 +33385,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1136" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33411,7 +33411,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1137" t="s">
-        <v>549</v>
+        <v>715</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33437,7 +33437,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1138" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33489,7 +33489,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1140" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33749,7 +33749,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1150" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33931,7 +33931,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1157" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33957,7 +33957,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1158" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34009,7 +34009,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1160" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34035,7 +34035,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1161" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34061,7 +34061,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1162" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34191,7 +34191,7 @@
         <v>22.5758266448975</v>
       </c>
       <c r="G1167" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34425,7 +34425,7 @@
         <v>22.8185787200928</v>
       </c>
       <c r="G1176" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34451,7 +34451,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1177" t="s">
-        <v>549</v>
+        <v>715</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34503,7 +34503,7 @@
         <v>23.2555294036865</v>
       </c>
       <c r="G1179" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34529,7 +34529,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1180" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34633,7 +34633,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1184" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34685,7 +34685,7 @@
         <v>25.3917369842529</v>
       </c>
       <c r="G1186" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34763,7 +34763,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1189" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34971,7 +34971,7 @@
         <v>24.7605857849121</v>
       </c>
       <c r="G1197" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35413,7 +35413,7 @@
         <v>23.9352321624756</v>
       </c>
       <c r="G1214" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35465,7 +35465,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1216" t="s">
-        <v>549</v>
+        <v>715</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35985,7 +35985,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1236" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36011,7 +36011,7 @@
         <v>23.0613288879395</v>
       </c>
       <c r="G1237" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36063,7 +36063,7 @@
         <v>23.0127792358398</v>
       </c>
       <c r="G1239" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36115,7 +36115,7 @@
         <v>21.9932250976562</v>
       </c>
       <c r="G1241" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36271,7 +36271,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1247" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36323,7 +36323,7 @@
         <v>23.9837818145752</v>
       </c>
       <c r="G1249" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36583,7 +36583,7 @@
         <v>23.4982795715332</v>
       </c>
       <c r="G1259" t="s">
-        <v>549</v>
+        <v>715</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36609,7 +36609,7 @@
         <v>23.886682510376</v>
       </c>
       <c r="G1260" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36635,7 +36635,7 @@
         <v>23.1584281921387</v>
       </c>
       <c r="G1261" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -52815,19 +52815,19 @@
     </row>
     <row r="1884">
       <c r="A1884" s="1" t="n">
-        <v>45967.6912268518</v>
+        <v>45968.6911574074</v>
       </c>
       <c r="B1884" t="n">
-        <v>73369</v>
+        <v>121411</v>
       </c>
       <c r="C1884" t="n">
-        <v>22.0499992370605</v>
+        <v>21.5</v>
       </c>
       <c r="D1884" t="n">
-        <v>21.4500007629395</v>
+        <v>21.0499992370605</v>
       </c>
       <c r="E1884" t="n">
-        <v>22.0499992370605</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="F1884" t="n">
         <v>21.3999996185303</v>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="1170">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,136 +38,136 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58125829696655</t>
+    <t xml:space="preserve">7.58125877380371</t>
   </si>
   <si>
     <t xml:space="preserve">CRL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81099271774292</t>
+    <t xml:space="preserve">7.90288782119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81099319458008</t>
   </si>
   <si>
     <t xml:space="preserve">7.71909999847412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68969106674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348127365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721172332764</t>
+    <t xml:space="preserve">7.68969202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348079681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721220016479</t>
   </si>
   <si>
     <t xml:space="preserve">7.67407083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97640228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44433641433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30281925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520322799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46639013290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206869125366</t>
+    <t xml:space="preserve">7.97640180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44433689117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.302818775177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46639060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">7.44341707229614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52612113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54450130462646</t>
+    <t xml:space="preserve">7.52612209320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54450035095215</t>
   </si>
   <si>
     <t xml:space="preserve">7.64742183685303</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80180358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8569393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92218589782715</t>
+    <t xml:space="preserve">7.8018045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85694026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92218494415283</t>
   </si>
   <si>
     <t xml:space="preserve">8.00397205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86612939834595</t>
+    <t xml:space="preserve">7.86612892150879</t>
   </si>
   <si>
     <t xml:space="preserve">8.01959323883057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81466913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76504564285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336843490601</t>
+    <t xml:space="preserve">7.81466960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7650465965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142803192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336891174316</t>
   </si>
   <si>
     <t xml:space="preserve">7.79261445999146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74666786193848</t>
+    <t xml:space="preserve">7.74666833877563</t>
   </si>
   <si>
     <t xml:space="preserve">7.88910341262817</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56379842758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67315244674683</t>
+    <t xml:space="preserve">7.56379890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67315149307251</t>
   </si>
   <si>
     <t xml:space="preserve">7.7852635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74850702285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478054046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002616882324</t>
+    <t xml:space="preserve">7.74850606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9947829246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002712249756</t>
   </si>
   <si>
     <t xml:space="preserve">8.11424350738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30354690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46343994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48641395568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75382518768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9596700668335</t>
+    <t xml:space="preserve">8.30354499816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46344089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48641490936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75382614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95966815948486</t>
   </si>
   <si>
     <t xml:space="preserve">8.60128116607666</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">8.25208473205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46987152099609</t>
+    <t xml:space="preserve">8.46987247467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.36235809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45425224304199</t>
+    <t xml:space="preserve">8.45425128936768</t>
   </si>
   <si>
     <t xml:space="preserve">8.71155452728271</t>
@@ -200,28 +200,28 @@
     <t xml:space="preserve">8.66560745239258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79426002502441</t>
+    <t xml:space="preserve">8.7942590713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86869430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11588764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14345645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643436431885</t>
+    <t xml:space="preserve">8.86869335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11588954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14345741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643341064453</t>
   </si>
   <si>
     <t xml:space="preserve">9.09751033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11680889129639</t>
+    <t xml:space="preserve">9.11680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.99091243743896</t>
@@ -230,64 +230,64 @@
     <t xml:space="preserve">9.18572902679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06166934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02399444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76577186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9936695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04237365722656</t>
+    <t xml:space="preserve">9.06167030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02399349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76576995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99366855621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04237270355225</t>
   </si>
   <si>
     <t xml:space="preserve">8.90177536010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67112064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50754833221436</t>
+    <t xml:space="preserve">8.67112159729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50755023956299</t>
   </si>
   <si>
     <t xml:space="preserve">7.98191595077515</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30630302429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40830421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54614448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5920934677124</t>
+    <t xml:space="preserve">8.30630397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40830516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54614543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59209251403809</t>
   </si>
   <si>
     <t xml:space="preserve">8.63803958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75126314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92126417160034</t>
+    <t xml:space="preserve">8.80804347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75126266479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92126512527466</t>
   </si>
   <si>
     <t xml:space="preserve">8.34214019775391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7749605178833</t>
+    <t xml:space="preserve">8.77495956420898</t>
   </si>
   <si>
     <t xml:space="preserve">8.77771854400635</t>
@@ -296,97 +296,97 @@
     <t xml:space="preserve">8.75474548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50571250915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59944343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70144748687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57739067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39268207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34122085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5608491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71982669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0545129776001</t>
+    <t xml:space="preserve">8.50571060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59944629669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70144653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57738971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3926830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34122276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71982574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05451393127441</t>
   </si>
   <si>
     <t xml:space="preserve">8.04164791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0866756439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18867874145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.548903465271</t>
+    <t xml:space="preserve">8.08667659759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18867683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54890251159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.33479118347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92107486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0386962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9743709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1526460647583</t>
+    <t xml:space="preserve">8.50938701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92107391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03869819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97437191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15264701843262</t>
   </si>
   <si>
     <t xml:space="preserve">8.84939670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07913112640381</t>
+    <t xml:space="preserve">9.07912921905518</t>
   </si>
   <si>
     <t xml:space="preserve">8.8558292388916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30446338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27046394348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33754634857178</t>
+    <t xml:space="preserve">8.30446434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23370456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27046298980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33754730224609</t>
   </si>
   <si>
     <t xml:space="preserve">8.20062351226807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40370941162109</t>
+    <t xml:space="preserve">8.40371036529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.27413940429688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29803085327148</t>
+    <t xml:space="preserve">8.29803276062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.50019836425781</t>
@@ -398,19 +398,19 @@
     <t xml:space="preserve">8.22451591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35408782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22083950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15283870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39911556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.426682472229</t>
+    <t xml:space="preserve">8.35408687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22084045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15283966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39911651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
     <t xml:space="preserve">8.48365688323975</t>
@@ -419,22 +419,22 @@
     <t xml:space="preserve">8.70971584320068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77128505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72074413299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10026550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06534671783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89809894561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83469295501709</t>
+    <t xml:space="preserve">8.77128601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72074317932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.100266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06534767150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89809799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83469486236572</t>
   </si>
   <si>
     <t xml:space="preserve">8.97712802886963</t>
@@ -443,46 +443,46 @@
     <t xml:space="preserve">9.05156230926514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23534965515137</t>
+    <t xml:space="preserve">9.2353515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.20594501495361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36216354370117</t>
+    <t xml:space="preserve">9.36216449737549</t>
   </si>
   <si>
     <t xml:space="preserve">9.39524745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61027908325195</t>
+    <t xml:space="preserve">9.61027717590332</t>
   </si>
   <si>
     <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69482231140137</t>
+    <t xml:space="preserve">9.69482135772705</t>
   </si>
   <si>
     <t xml:space="preserve">9.59373664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64335918426514</t>
+    <t xml:space="preserve">9.64336204528809</t>
   </si>
   <si>
     <t xml:space="preserve">9.31989288330078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6176290512085</t>
+    <t xml:space="preserve">9.61763191223145</t>
   </si>
   <si>
     <t xml:space="preserve">9.49265384674072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51103210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28497314453125</t>
+    <t xml:space="preserve">9.5110330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28497409820557</t>
   </si>
   <si>
     <t xml:space="preserve">9.46324825286865</t>
@@ -491,43 +491,43 @@
     <t xml:space="preserve">9.33091926574707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12875461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26291942596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14713287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06075286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94129085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37797927856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76025676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00653457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18940353393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96885776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10669994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44670677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39157009124756</t>
+    <t xml:space="preserve">9.12875366210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26291847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14713382720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06075191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94128894805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37798023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76025867462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00653553009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18940448760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96885681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1067008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4467077255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39157104492188</t>
   </si>
   <si>
     <t xml:space="preserve">9.74076843261719</t>
@@ -545,40 +545,40 @@
     <t xml:space="preserve">9.68563270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90617752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99807071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7959041595459</t>
+    <t xml:space="preserve">9.90617656707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99807167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79590511322021</t>
   </si>
   <si>
     <t xml:space="preserve">9.92455768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81428241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9429349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0715856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66725444793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77752590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83266067504883</t>
+    <t xml:space="preserve">9.81428146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94293594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0715866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.108344078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66725254058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77752494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83266162872314</t>
   </si>
   <si>
     <t xml:space="preserve">9.86941909790039</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">10.163480758667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3105115890503</t>
+    <t xml:space="preserve">10.310510635376</t>
   </si>
   <si>
     <t xml:space="preserve">10.0348300933838</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">10.0164499282837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1267232894897</t>
+    <t xml:space="preserve">10.1267213821411</t>
   </si>
   <si>
     <t xml:space="preserve">10.5126791000366</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6045713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659707069397</t>
+    <t xml:space="preserve">10.6045722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597089767456</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332239151001</t>
@@ -617,58 +617,55 @@
     <t xml:space="preserve">10.4207830429077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4759197235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4391622543335</t>
+    <t xml:space="preserve">10.4759206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4391632080078</t>
   </si>
   <si>
     <t xml:space="preserve">10.3288898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97969341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85103988647461</t>
+    <t xml:space="preserve">9.97969245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85104084014893</t>
   </si>
   <si>
     <t xml:space="preserve">10.1821947097778</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8854455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92253875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1451015472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99672698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2007427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2192888259888</t>
+    <t xml:space="preserve">9.941086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88544654846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92254066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99672603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2007417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2192878723145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0894603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90399169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0523662567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7370719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86689949035645</t>
+    <t xml:space="preserve">9.90399360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0523672103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73707103729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86689853668213</t>
   </si>
   <si>
     <t xml:space="preserve">10.1636476516724</t>
@@ -677,25 +674,25 @@
     <t xml:space="preserve">10.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4047574996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3862113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3676633834839</t>
+    <t xml:space="preserve">10.4047565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4233026504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.386209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3676643371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.82980632781982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3120222091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.033821105957</t>
+    <t xml:space="preserve">10.3120231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0338220596313</t>
   </si>
   <si>
     <t xml:space="preserve">9.81126022338867</t>
@@ -704,10 +701,10 @@
     <t xml:space="preserve">10.070915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1080074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79271221160889</t>
+    <t xml:space="preserve">10.1080083847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79271125793457</t>
   </si>
   <si>
     <t xml:space="preserve">10.2563819885254</t>
@@ -716,43 +713,43 @@
     <t xml:space="preserve">10.8498802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4789447784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0554218292236</t>
+    <t xml:space="preserve">10.4789438247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0554227828979</t>
   </si>
   <si>
     <t xml:space="preserve">11.1651763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6102991104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062833786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5361108779907</t>
+    <t xml:space="preserve">11.6103000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062852859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.536111831665</t>
   </si>
   <si>
     <t xml:space="preserve">11.6288452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175657272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9626884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1481552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2408905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4449043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5932788848877</t>
+    <t xml:space="preserve">11.5175647735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9626874923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1481561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.240891456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4449052810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.593279838562</t>
   </si>
   <si>
     <t xml:space="preserve">12.1852493286133</t>
@@ -761,34 +758,34 @@
     <t xml:space="preserve">11.5732049942017</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5917520523071</t>
+    <t xml:space="preserve">11.5917530059814</t>
   </si>
   <si>
     <t xml:space="preserve">11.7401266098022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4804716110229</t>
+    <t xml:space="preserve">11.4804706573486</t>
   </si>
   <si>
     <t xml:space="preserve">11.9255933761597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.11106300354</t>
+    <t xml:space="preserve">12.1110620498657</t>
   </si>
   <si>
     <t xml:space="preserve">12.1667032241821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2223434448242</t>
+    <t xml:space="preserve">12.2223424911499</t>
   </si>
   <si>
     <t xml:space="preserve">12.5190935134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6860132217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9827632904053</t>
+    <t xml:space="preserve">12.686014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982762336731</t>
   </si>
   <si>
     <t xml:space="preserve">13.2609643936157</t>
@@ -797,46 +794,46 @@
     <t xml:space="preserve">13.3536987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5020713806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0584764480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4649791717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2053251266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1125917434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3892650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3521709442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2965316772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.407811164856</t>
+    <t xml:space="preserve">13.5020723342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0584783554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2053241729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1125907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3892641067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3521718978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2965307235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4078121185303</t>
   </si>
   <si>
     <t xml:space="preserve">12.2037963867188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2779836654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5963363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9101028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4093379974365</t>
+    <t xml:space="preserve">12.2779846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5963354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9101037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4093389511108</t>
   </si>
   <si>
     <t xml:space="preserve">13.168231010437</t>
@@ -845,7 +842,7 @@
     <t xml:space="preserve">12.8529348373413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7045602798462</t>
+    <t xml:space="preserve">12.7045612335205</t>
   </si>
   <si>
     <t xml:space="preserve">12.5561866760254</t>
@@ -854,28 +851,28 @@
     <t xml:space="preserve">12.3707189559937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7787475585938</t>
+    <t xml:space="preserve">12.7787485122681</t>
   </si>
   <si>
     <t xml:space="preserve">12.8158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8900289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0940437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0754976272583</t>
+    <t xml:space="preserve">12.8900299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0940446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0754957199097</t>
   </si>
   <si>
     <t xml:space="preserve">13.3351516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0569496154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489200592041</t>
+    <t xml:space="preserve">13.0569486618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489191055298</t>
   </si>
   <si>
     <t xml:space="preserve">12.3150777816772</t>
@@ -884,55 +881,55 @@
     <t xml:space="preserve">12.4634523391724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4263591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2950038909912</t>
+    <t xml:space="preserve">12.4263572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514070510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772197723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2950029373169</t>
   </si>
   <si>
     <t xml:space="preserve">11.0168018341064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090989112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0353488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7571449279785</t>
+    <t xml:space="preserve">11.0909881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0353479385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7571458816528</t>
   </si>
   <si>
     <t xml:space="preserve">11.313549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2764558792114</t>
+    <t xml:space="preserve">11.1280832290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2764568328857</t>
   </si>
   <si>
     <t xml:space="preserve">11.2208156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3691902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1095352172852</t>
+    <t xml:space="preserve">11.3691892623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1095333099365</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40322971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88391780853271</t>
+    <t xml:space="preserve">9.40322875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8839168548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.55160427093506</t>
@@ -956,7 +953,7 @@
     <t xml:space="preserve">8.53153038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.438796043396</t>
+    <t xml:space="preserve">8.43879508972168</t>
   </si>
   <si>
     <t xml:space="preserve">9.64433765411377</t>
@@ -968,7 +965,7 @@
     <t xml:space="preserve">9.77416610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2934770584106</t>
+    <t xml:space="preserve">10.2934761047363</t>
   </si>
   <si>
     <t xml:space="preserve">10.2378358840942</t>
@@ -983,7 +980,7 @@
     <t xml:space="preserve">10.7015047073364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6844882965088</t>
+    <t xml:space="preserve">11.6844873428345</t>
   </si>
   <si>
     <t xml:space="preserve">11.8699541091919</t>
@@ -992,16 +989,16 @@
     <t xml:space="preserve">12.4819993972778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6118249893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.758674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7246351242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4835252761841</t>
+    <t xml:space="preserve">12.6118259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7586727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7246341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4835262298584</t>
   </si>
   <si>
     <t xml:space="preserve">13.650447845459</t>
@@ -1010,31 +1007,31 @@
     <t xml:space="preserve">14.8930826187134</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0414581298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2439441680908</t>
+    <t xml:space="preserve">15.0414571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2439460754395</t>
   </si>
   <si>
     <t xml:space="preserve">15.2825660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9687986373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3938455581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9487228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6148824691772</t>
+    <t xml:space="preserve">15.7462368011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9687976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3938465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9487237930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6148815155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.4665079116821</t>
@@ -1055,43 +1052,46 @@
     <t xml:space="preserve">13.6689939498901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0770235061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3181314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076139450073</t>
+    <t xml:space="preserve">14.0770244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3181324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9858150482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5560493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7989616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.892388343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7802762985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7615900039673</t>
   </si>
   <si>
     <t xml:space="preserve">14.9858169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5560493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.79896068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8923892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7802753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7615900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2660999298096</t>
+    <t xml:space="preserve">15.2661008834839</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287302017212</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4155855178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3221578598022</t>
+    <t xml:space="preserve">15.415584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3221559524536</t>
   </si>
   <si>
     <t xml:space="preserve">15.0045022964478</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">14.6121063232422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0792455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.911075592041</t>
+    <t xml:space="preserve">15.0792446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9110765457153</t>
   </si>
   <si>
     <t xml:space="preserve">14.6494770050049</t>
@@ -1112,55 +1112,55 @@
     <t xml:space="preserve">15.1353025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.929759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0231876373291</t>
+    <t xml:space="preserve">14.9297609329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0231885910034</t>
   </si>
   <si>
     <t xml:space="preserve">15.3968992233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9484462738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4813079833984</t>
+    <t xml:space="preserve">14.9484453201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4813070297241</t>
   </si>
   <si>
     <t xml:space="preserve">15.5650691986084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1630058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9664878845215</t>
+    <t xml:space="preserve">16.1630077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9664859771729</t>
   </si>
   <si>
     <t xml:space="preserve">17.6765384674072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235736846924</t>
+    <t xml:space="preserve">16.723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.8730583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4336242675781</t>
+    <t xml:space="preserve">17.4336261749268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4149398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3962535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7886524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0128746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8820762634277</t>
+    <t xml:space="preserve">17.3962554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7886543273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0128784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.882080078125</t>
   </si>
   <si>
     <t xml:space="preserve">18.2744750976562</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">18.3118476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6578521728516</t>
+    <t xml:space="preserve">17.6578540802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.5270538330078</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">18.6855583190918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1526966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.330530166626</t>
+    <t xml:space="preserve">19.1526947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3305339813232</t>
   </si>
   <si>
     <t xml:space="preserve">18.2184181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0315647125244</t>
+    <t xml:space="preserve">18.0315628051758</t>
   </si>
   <si>
     <t xml:space="preserve">17.3775691986084</t>
@@ -1199,40 +1199,40 @@
     <t xml:space="preserve">17.9568214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4709968566895</t>
+    <t xml:space="preserve">17.4709987640381</t>
   </si>
   <si>
     <t xml:space="preserve">17.8073348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9291152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6675186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4619770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.957465171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.378212928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5367221832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2938041687012</t>
+    <t xml:space="preserve">16.9291172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.667516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4619750976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9574680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3782138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5367202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5927753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2938060760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.4246044158936</t>
@@ -1241,34 +1241,34 @@
     <t xml:space="preserve">16.2751216888428</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8543720245361</t>
+    <t xml:space="preserve">16.8543739318848</t>
   </si>
   <si>
     <t xml:space="preserve">16.7048892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3311767578125</t>
+    <t xml:space="preserve">16.3311786651611</t>
   </si>
   <si>
     <t xml:space="preserve">16.4993476867676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3685455322266</t>
+    <t xml:space="preserve">16.3685493469238</t>
   </si>
   <si>
     <t xml:space="preserve">16.3498611450195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6862049102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.63014793396</t>
+    <t xml:space="preserve">16.6862030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6301460266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.6114616394043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7609481811523</t>
+    <t xml:space="preserve">16.7609443664551</t>
   </si>
   <si>
     <t xml:space="preserve">16.8170013427734</t>
@@ -1277,58 +1277,58 @@
     <t xml:space="preserve">16.7983169555664</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7892942428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434271812439</t>
+    <t xml:space="preserve">15.7892961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4342708587646</t>
   </si>
   <si>
     <t xml:space="preserve">14.9671316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6868476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5373640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.32151222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5180339813232</t>
+    <t xml:space="preserve">14.6868467330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5373630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3215103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5180320739746</t>
   </si>
   <si>
     <t xml:space="preserve">15.6211252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8827219009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2377471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4806652069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356895446777</t>
+    <t xml:space="preserve">15.8827228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2377510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4806632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356876373291</t>
   </si>
   <si>
     <t xml:space="preserve">16.4432907104492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9477996826172</t>
+    <t xml:space="preserve">16.9478015899658</t>
   </si>
   <si>
     <t xml:space="preserve">17.0785999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.648832321167</t>
+    <t xml:space="preserve">16.6488342285156</t>
   </si>
   <si>
     <t xml:space="preserve">16.9104270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8917465209961</t>
+    <t xml:space="preserve">16.8917446136475</t>
   </si>
   <si>
     <t xml:space="preserve">17.9007625579834</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">18.0876197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5360736846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9194488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0502490997314</t>
+    <t xml:space="preserve">18.5360717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9194507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0502510070801</t>
   </si>
   <si>
     <t xml:space="preserve">16.5740909576416</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">16.742259979248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5554065704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3124923706055</t>
+    <t xml:space="preserve">16.5554027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3124904632568</t>
   </si>
   <si>
     <t xml:space="preserve">17.0225448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.069580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8453531265259</t>
+    <t xml:space="preserve">16.0695819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8453540802002</t>
   </si>
   <si>
     <t xml:space="preserve">15.7519254684448</t>
@@ -1376,46 +1376,46 @@
     <t xml:space="preserve">16.0135231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9014101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9761514663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3595285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5186786651611</t>
+    <t xml:space="preserve">15.9014081954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9761524200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3595275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5186777114868</t>
   </si>
   <si>
     <t xml:space="preserve">14.1636533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8550186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5090112686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6398115158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6771812438965</t>
+    <t xml:space="preserve">14.855019569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.50901222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6398105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6771802902222</t>
   </si>
   <si>
     <t xml:space="preserve">15.5276985168457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7145519256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4716415405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4529552459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6584978103638</t>
+    <t xml:space="preserve">15.7145557403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4716424942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4529571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6584968566895</t>
   </si>
   <si>
     <t xml:space="preserve">15.8640384674072</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">16.2190628051758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0972881317139</t>
+    <t xml:space="preserve">17.0972862243652</t>
   </si>
   <si>
     <t xml:space="preserve">17.1346569061279</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">17.9381351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5831108093262</t>
+    <t xml:space="preserve">17.5831089019775</t>
   </si>
   <si>
     <t xml:space="preserve">17.7699642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1249904632568</t>
+    <t xml:space="preserve">18.1249885559082</t>
   </si>
   <si>
     <t xml:space="preserve">17.6391658782959</t>
@@ -1466,61 +1466,61 @@
     <t xml:space="preserve">19.713264465332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8066902160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4329814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5264053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9935455322266</t>
+    <t xml:space="preserve">19.8066921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4329795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5264072418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9935474395752</t>
   </si>
   <si>
     <t xml:space="preserve">20.5541133880615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4606876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2738304138184</t>
+    <t xml:space="preserve">20.4606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2738285064697</t>
   </si>
   <si>
     <t xml:space="preserve">20.1336879730225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9468326568604</t>
+    <t xml:space="preserve">19.9468307495117</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271175384521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6008281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6475429534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2081089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5818176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.955530166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3015365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8343982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0869731903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7599754333496</t>
+    <t xml:space="preserve">20.6008262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6475410461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2081069946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5818195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9555320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3015384674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8343963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0869770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7599773406982</t>
   </si>
   <si>
     <t xml:space="preserve">19.4796943664551</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">19.1994113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7350769042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9700183868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7820644378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4531478881836</t>
+    <t xml:space="preserve">19.7350749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9700164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7820625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.453145980835</t>
   </si>
   <si>
     <t xml:space="preserve">19.5471229553223</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">19.5001354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6880874633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.030252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8423004150391</t>
+    <t xml:space="preserve">19.6880893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0302543640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8422985076904</t>
   </si>
   <si>
     <t xml:space="preserve">19.1712169647217</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">18.9362773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6410980224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9832649230957</t>
+    <t xml:space="preserve">19.6410999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9832668304443</t>
   </si>
   <si>
     <t xml:space="preserve">20.1579704284668</t>
@@ -1586,28 +1586,28 @@
     <t xml:space="preserve">18.6261558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">18.475793838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.776517868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5133819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7953128814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6449489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0639953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3929138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8158054351807</t>
+    <t xml:space="preserve">18.4757919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765140533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5133800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7953109741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.644947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0639934539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3929119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8158073425293</t>
   </si>
   <si>
     <t xml:space="preserve">21.2856903076172</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">23.2122097015381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4941387176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1652221679688</t>
+    <t xml:space="preserve">23.4941425323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1652240753174</t>
   </si>
   <si>
     <t xml:space="preserve">23.0712451934814</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">23.58811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1989631652832</t>
+    <t xml:space="preserve">24.1989650726318</t>
   </si>
   <si>
     <t xml:space="preserve">23.7760696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7290782928467</t>
+    <t xml:space="preserve">23.7290802001953</t>
   </si>
   <si>
     <t xml:space="preserve">23.0242557525635</t>
@@ -1652,517 +1652,517 @@
     <t xml:space="preserve">22.8363037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8832912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5411281585693</t>
+    <t xml:space="preserve">22.8832931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5411262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9302768707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2591953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4471530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.870044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7555732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7085857391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.131477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9435291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5676212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1447238922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.909782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9567718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7688179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5808658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2387027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8495502471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8098125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6688461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4339046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3869171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4001636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6351013183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1519737243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8230571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2929401397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9640216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4808921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5616226196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4206600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6555995941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3736705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.279691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3061847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5543746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2724456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1182346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2459506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5278835296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7628231048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9170322418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0110111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8568000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6218585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.138729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1917133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4266567230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4399013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8025608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8627948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3326778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3796653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2519474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.34592628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2182064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5697689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3591709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2126579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3292751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0473480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8218040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3066349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1938610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6637439727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9230308532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6615962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4736423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.486888885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2989387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0170078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7389259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7013359069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8965377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049617767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.533878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3254280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9683151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.893138885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2165069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1977100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9418773651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9039745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3923091888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.259651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5293464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9652118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.813606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2684230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2494716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1736679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.950647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6284866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5716342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7800922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9462623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5905838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7611389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8508014678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8457107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9404621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.893087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0775032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.693395614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4565143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0301246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4616069793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6511116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4142284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9878387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7983341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.419319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6612949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2298145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9455528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2349052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5665416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0403079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.756046295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9980220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0453987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5526809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3631763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9273109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2305221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7188549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3821239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7946548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9987297058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1357669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.087682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7990398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1547183990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2873725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5147800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0599632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2115688323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.476879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6562023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6088275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5140762329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5038909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3092937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.162073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7779693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3566722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4040489196777</t>
   </si>
   <si>
     <t xml:space="preserve">22.9302787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2591972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4471530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8700428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7555732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7085857391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1314792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5676212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1447238922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9567718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7688179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5808658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2387008666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8495502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8098087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6688442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9977626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4339046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3869171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4001636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.635103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1519737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8230571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2929401397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9640216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4808940887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5616226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4206600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6555995941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3736705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.279691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3061866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.554370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2724437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1182346343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2459526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5278816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7628231048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9170341491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0110111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8568019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6218585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1857166290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1387271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1917152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4266567230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4399013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.802562713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8627948760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3326778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3796653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2519493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3459243774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2182064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.569766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3591709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2126579284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3292770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0473480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8218002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3066349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1938591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6637439727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9230289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6615962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4736423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2989368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0170078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7389278411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7013339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8965377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5338764190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3254280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9683170318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2165050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1977100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713222503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9418792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9039745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3923091888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8281745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5293464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9652099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.813606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2684230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2494735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1736679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.950647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6284866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5716342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7800922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9462623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5905838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7611389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8507995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7509574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8457107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8930854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2771911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0775012969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6933975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2670097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4565143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0301265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4616069793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6511116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4142284393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9878387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7983341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4193210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6612949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2298145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9455528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2349052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5665397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0403079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7560482025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9980220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0453987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5526809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3631763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9273128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2305221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7188549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3821239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7946548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9987277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1357669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.087682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7990398406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1547183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2873725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5147819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0599632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2115707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.476879119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6562023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6088275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5140743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5038890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3092956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.162073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7779693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3566722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4040470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6883068084717</t>
+    <t xml:space="preserve">23.6883087158203</t>
   </si>
   <si>
     <t xml:space="preserve">22.1248798370361</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">22.7881526947021</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0250339508057</t>
+    <t xml:space="preserve">23.0250358581543</t>
   </si>
   <si>
     <t xml:space="preserve">22.1722564697266</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">23.4514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3515777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.167163848877</t>
+    <t xml:space="preserve">24.3515796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1671657562256</t>
   </si>
   <si>
     <t xml:space="preserve">22.4091377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9827499389648</t>
+    <t xml:space="preserve">21.9827480316162</t>
   </si>
   <si>
     <t xml:space="preserve">22.5512676239014</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">23.9725666046143</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2568264007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0673179626465</t>
+    <t xml:space="preserve">24.2568244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0673198699951</t>
   </si>
   <si>
     <t xml:space="preserve">25.2991123199463</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9201011657715</t>
+    <t xml:space="preserve">24.9200992584229</t>
   </si>
   <si>
     <t xml:space="preserve">24.825345993042</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">24.5884628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.493709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0148506164551</t>
+    <t xml:space="preserve">24.4937076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0148525238037</t>
   </si>
   <si>
     <t xml:space="preserve">25.7255001068115</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">25.3464870452881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5935554504395</t>
+    <t xml:space="preserve">23.5935535430908</t>
   </si>
   <si>
     <t xml:space="preserve">23.5461769104004</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">21.3194751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6460227966309</t>
+    <t xml:space="preserve">22.6460208892822</t>
   </si>
   <si>
     <t xml:space="preserve">22.361759185791</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">25.5833721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4835300445557</t>
+    <t xml:space="preserve">26.483528137207</t>
   </si>
   <si>
     <t xml:space="preserve">26.3887748718262</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">26.6256561279297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1992664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.820255279541</t>
+    <t xml:space="preserve">26.1992683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8202533721924</t>
   </si>
   <si>
     <t xml:space="preserve">26.5309047698975</t>
@@ -3516,6 +3516,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.8500003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.75</t>
   </si>
   <si>
     <t xml:space="preserve">21.3999996185303</t>
@@ -10843,7 +10846,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G269" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10869,7 +10872,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G270" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10895,7 +10898,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G271" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10921,7 +10924,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G272" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10947,7 +10950,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G273" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10973,7 +10976,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G274" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10999,7 +11002,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G275" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -11025,7 +11028,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G276" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -11051,7 +11054,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G277" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -11077,7 +11080,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G278" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -11103,7 +11106,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G279" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -11129,7 +11132,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G280" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -11181,7 +11184,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G282" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -11259,7 +11262,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G285" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -11285,7 +11288,7 @@
         <v>10.6421957015991</v>
       </c>
       <c r="G286" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -11311,7 +11314,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G287" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -11337,7 +11340,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G288" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -11363,7 +11366,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G289" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -11389,7 +11392,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G290" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -11415,7 +11418,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G291" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -11441,7 +11444,7 @@
         <v>10.8558168411255</v>
       </c>
       <c r="G292" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -11467,7 +11470,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G293" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -11493,7 +11496,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G294" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -11519,7 +11522,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G295" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -11545,7 +11548,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G296" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -11571,7 +11574,7 @@
         <v>10.5062561035156</v>
       </c>
       <c r="G297" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -11597,7 +11600,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G298" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11623,7 +11626,7 @@
         <v>10.3314752578735</v>
       </c>
       <c r="G299" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11649,7 +11652,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G300" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11675,7 +11678,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G301" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11701,7 +11704,7 @@
         <v>10.3703145980835</v>
       </c>
       <c r="G302" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11727,7 +11730,7 @@
         <v>10.5450963973999</v>
       </c>
       <c r="G303" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11753,7 +11756,7 @@
         <v>10.5839357376099</v>
       </c>
       <c r="G304" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11779,7 +11782,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G305" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11805,7 +11808,7 @@
         <v>10.253794670105</v>
       </c>
       <c r="G306" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11831,7 +11834,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G307" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11857,7 +11860,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G308" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11883,7 +11886,7 @@
         <v>10.467414855957</v>
       </c>
       <c r="G309" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11909,7 +11912,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G310" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11935,7 +11938,7 @@
         <v>10.7392959594727</v>
       </c>
       <c r="G311" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11961,7 +11964,7 @@
         <v>10.8752374649048</v>
       </c>
       <c r="G312" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11987,7 +11990,7 @@
         <v>11.0500173568726</v>
       </c>
       <c r="G313" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -12013,7 +12016,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G314" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -12039,7 +12042,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G315" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -12065,7 +12068,7 @@
         <v>10.7004556655884</v>
       </c>
       <c r="G316" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -12091,7 +12094,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G317" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -12117,7 +12120,7 @@
         <v>11.6908798217773</v>
       </c>
       <c r="G318" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -12143,7 +12146,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G319" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -12169,7 +12172,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G320" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -12195,7 +12198,7 @@
         <v>11.943341255188</v>
       </c>
       <c r="G321" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -12221,7 +12224,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G322" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -12247,7 +12250,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G323" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -12273,7 +12276,7 @@
         <v>12.0598611831665</v>
       </c>
       <c r="G324" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -12299,7 +12302,7 @@
         <v>12.15696144104</v>
       </c>
       <c r="G325" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -12325,7 +12328,7 @@
         <v>12.176381111145</v>
       </c>
       <c r="G326" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -12351,7 +12354,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G327" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -12377,7 +12380,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G328" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -12403,7 +12406,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G329" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -12429,7 +12432,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G330" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -12455,7 +12458,7 @@
         <v>13.0308637619019</v>
       </c>
       <c r="G331" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -12481,7 +12484,7 @@
         <v>13.186224937439</v>
       </c>
       <c r="G332" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -12507,7 +12510,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G333" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -12533,7 +12536,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G334" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -12559,7 +12562,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G335" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -12585,7 +12588,7 @@
         <v>12.2929019927979</v>
       </c>
       <c r="G336" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12611,7 +12614,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G337" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12637,7 +12640,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G338" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12663,7 +12666,7 @@
         <v>12.0210208892822</v>
       </c>
       <c r="G339" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12689,7 +12692,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G340" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12715,7 +12718,7 @@
         <v>12.0792808532715</v>
       </c>
       <c r="G341" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12741,7 +12744,7 @@
         <v>12.1375408172607</v>
       </c>
       <c r="G342" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12767,7 +12770,7 @@
         <v>12.1181211471558</v>
       </c>
       <c r="G343" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12793,7 +12796,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G344" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12819,7 +12822,7 @@
         <v>12.681303024292</v>
       </c>
       <c r="G345" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12845,7 +12848,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G346" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12871,7 +12874,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G347" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12897,7 +12900,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G348" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12923,7 +12926,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G349" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12949,7 +12952,7 @@
         <v>12.7978229522705</v>
       </c>
       <c r="G350" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12975,7 +12978,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G351" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -13001,7 +13004,7 @@
         <v>13.2833251953125</v>
       </c>
       <c r="G352" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -13027,7 +13030,7 @@
         <v>13.5940456390381</v>
       </c>
       <c r="G353" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -13053,7 +13056,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G354" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -13079,7 +13082,7 @@
         <v>13.9824476242065</v>
       </c>
       <c r="G355" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -13105,7 +13108,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G356" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -13131,7 +13134,7 @@
         <v>14.7204103469849</v>
       </c>
       <c r="G357" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -13157,7 +13160,7 @@
         <v>14.1378078460693</v>
       </c>
       <c r="G358" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -13183,7 +13186,7 @@
         <v>14.0989675521851</v>
       </c>
       <c r="G359" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -13209,7 +13212,7 @@
         <v>13.8270874023438</v>
       </c>
       <c r="G360" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -13235,7 +13238,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G361" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -13261,7 +13264,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G362" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -13287,7 +13290,7 @@
         <v>12.9726037979126</v>
       </c>
       <c r="G363" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -13313,7 +13316,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G364" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -13339,7 +13342,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G365" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -13365,7 +13368,7 @@
         <v>12.9920244216919</v>
       </c>
       <c r="G366" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -13391,7 +13394,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G367" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -13417,7 +13420,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G368" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -13443,7 +13446,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G369" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -13469,7 +13472,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -13495,7 +13498,7 @@
         <v>12.8560838699341</v>
       </c>
       <c r="G371" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -13521,7 +13524,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G372" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -13547,7 +13550,7 @@
         <v>15.2835922241211</v>
       </c>
       <c r="G373" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -13573,7 +13576,7 @@
         <v>14.5650501251221</v>
       </c>
       <c r="G374" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -13599,7 +13602,7 @@
         <v>14.0407075881958</v>
       </c>
       <c r="G375" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13625,7 +13628,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G376" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13651,7 +13654,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G377" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13677,7 +13680,7 @@
         <v>13.3027448654175</v>
       </c>
       <c r="G378" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13703,7 +13706,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G379" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13729,7 +13732,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G380" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13755,7 +13758,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G381" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13781,7 +13784,7 @@
         <v>12.9531841278076</v>
       </c>
       <c r="G382" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13807,7 +13810,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G383" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13833,7 +13836,7 @@
         <v>12.8755035400391</v>
       </c>
       <c r="G384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13859,7 +13862,7 @@
         <v>13.380425453186</v>
       </c>
       <c r="G385" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13885,7 +13888,7 @@
         <v>13.4192657470703</v>
       </c>
       <c r="G386" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13911,7 +13914,7 @@
         <v>13.4969463348389</v>
       </c>
       <c r="G387" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13937,7 +13940,7 @@
         <v>13.7105674743652</v>
       </c>
       <c r="G388" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13963,7 +13966,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G389" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13989,7 +13992,7 @@
         <v>13.6911468505859</v>
       </c>
       <c r="G390" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -14015,7 +14018,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G391" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -14041,7 +14044,7 @@
         <v>13.9630270004272</v>
       </c>
       <c r="G392" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -14067,7 +14070,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G393" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14093,7 +14096,7 @@
         <v>13.4581060409546</v>
       </c>
       <c r="G394" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -14119,7 +14122,7 @@
         <v>13.885347366333</v>
       </c>
       <c r="G395" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14145,7 +14148,7 @@
         <v>13.6717262268066</v>
       </c>
       <c r="G396" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14171,7 +14174,7 @@
         <v>13.2444849014282</v>
       </c>
       <c r="G397" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14197,7 +14200,7 @@
         <v>12.8949241638184</v>
       </c>
       <c r="G398" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14223,7 +14226,7 @@
         <v>12.7589826583862</v>
       </c>
       <c r="G399" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14249,7 +14252,7 @@
         <v>13.0502843856812</v>
       </c>
       <c r="G400" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14275,7 +14278,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G401" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14301,7 +14304,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G402" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14327,7 +14330,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G403" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14353,7 +14356,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G404" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14379,7 +14382,7 @@
         <v>12.8172435760498</v>
       </c>
       <c r="G405" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14405,7 +14408,7 @@
         <v>12.7201433181763</v>
       </c>
       <c r="G406" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14431,7 +14434,7 @@
         <v>12.7395629882812</v>
       </c>
       <c r="G407" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14457,7 +14460,7 @@
         <v>12.5259428024292</v>
       </c>
       <c r="G408" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14483,7 +14486,7 @@
         <v>12.4871015548706</v>
       </c>
       <c r="G409" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14509,7 +14512,7 @@
         <v>12.4094219207764</v>
       </c>
       <c r="G410" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14535,7 +14538,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G411" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14561,7 +14564,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G412" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14587,7 +14590,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G413" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14613,7 +14616,7 @@
         <v>11.6131992340088</v>
       </c>
       <c r="G414" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14639,7 +14642,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G415" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14665,7 +14668,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G416" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14691,7 +14694,7 @@
         <v>11.5549392700195</v>
       </c>
       <c r="G417" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14717,7 +14720,7 @@
         <v>11.2636375427246</v>
       </c>
       <c r="G418" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14743,7 +14746,7 @@
         <v>11.5355186462402</v>
       </c>
       <c r="G419" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14769,7 +14772,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G420" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14795,7 +14798,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G421" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14821,7 +14824,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G422" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14847,7 +14850,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G423" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14873,7 +14876,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G424" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14899,7 +14902,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G425" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14925,7 +14928,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G426" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14951,7 +14954,7 @@
         <v>11.8462400436401</v>
       </c>
       <c r="G427" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14977,7 +14980,7 @@
         <v>11.7491397857666</v>
       </c>
       <c r="G428" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -15003,7 +15006,7 @@
         <v>11.8073997497559</v>
       </c>
       <c r="G429" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -15029,7 +15032,7 @@
         <v>11.9045000076294</v>
       </c>
       <c r="G430" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -15055,7 +15058,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G431" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -15081,7 +15084,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G432" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15107,7 +15110,7 @@
         <v>10.972336769104</v>
       </c>
       <c r="G433" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15133,7 +15136,7 @@
         <v>11.3607387542725</v>
       </c>
       <c r="G434" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15159,7 +15162,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G435" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15185,7 +15188,7 @@
         <v>10.7975568771362</v>
       </c>
       <c r="G436" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15211,7 +15214,7 @@
         <v>10.5256757736206</v>
       </c>
       <c r="G437" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15237,7 +15240,7 @@
         <v>10.9140768051147</v>
       </c>
       <c r="G438" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15263,7 +15266,7 @@
         <v>10.8946571350098</v>
       </c>
       <c r="G439" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15289,7 +15292,7 @@
         <v>10.5645160675049</v>
       </c>
       <c r="G440" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15315,7 +15318,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G441" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15341,7 +15344,7 @@
         <v>10.1955347061157</v>
       </c>
       <c r="G442" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15367,7 +15370,7 @@
         <v>9.86539268493652</v>
       </c>
       <c r="G443" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15393,7 +15396,7 @@
         <v>9.84597301483154</v>
       </c>
       <c r="G444" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15419,7 +15422,7 @@
         <v>9.30221080780029</v>
       </c>
       <c r="G445" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15445,7 +15448,7 @@
         <v>10.0013341903687</v>
       </c>
       <c r="G446" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15471,7 +15474,7 @@
         <v>9.12743091583252</v>
       </c>
       <c r="G447" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15523,7 +15526,7 @@
         <v>9.22453117370605</v>
       </c>
       <c r="G449" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15549,7 +15552,7 @@
         <v>8.59337902069092</v>
       </c>
       <c r="G450" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15575,7 +15578,7 @@
         <v>8.6322193145752</v>
       </c>
       <c r="G451" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15601,7 +15604,7 @@
         <v>8.58366870880127</v>
       </c>
       <c r="G452" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15627,7 +15630,7 @@
         <v>8.93323040008545</v>
       </c>
       <c r="G453" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15653,7 +15656,7 @@
         <v>8.83613014221191</v>
       </c>
       <c r="G454" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15679,7 +15682,7 @@
         <v>10.0984344482422</v>
       </c>
       <c r="G455" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15705,7 +15708,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G456" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15731,7 +15734,7 @@
         <v>11.6326189041138</v>
       </c>
       <c r="G457" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15757,7 +15760,7 @@
         <v>11.2247982025146</v>
       </c>
       <c r="G458" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15783,7 +15786,7 @@
         <v>10.6227760314941</v>
       </c>
       <c r="G459" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15809,7 +15812,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G460" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15835,7 +15838,7 @@
         <v>10.234375</v>
       </c>
       <c r="G461" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15861,7 +15864,7 @@
         <v>10.6810359954834</v>
       </c>
       <c r="G462" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15887,7 +15890,7 @@
         <v>10.7781372070312</v>
       </c>
       <c r="G463" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15913,7 +15916,7 @@
         <v>10.7198762893677</v>
       </c>
       <c r="G464" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15939,7 +15942,7 @@
         <v>10.2926349639893</v>
       </c>
       <c r="G465" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15965,7 +15968,7 @@
         <v>10.2732152938843</v>
       </c>
       <c r="G466" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15991,7 +15994,7 @@
         <v>10.1761140823364</v>
       </c>
       <c r="G467" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -16017,7 +16020,7 @@
         <v>10.4868364334106</v>
       </c>
       <c r="G468" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -16043,7 +16046,7 @@
         <v>11.2053775787354</v>
       </c>
       <c r="G469" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -16069,7 +16072,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G470" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16095,7 +16098,7 @@
         <v>11.8268203735352</v>
       </c>
       <c r="G471" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16121,7 +16124,7 @@
         <v>11.6520395278931</v>
       </c>
       <c r="G472" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16147,7 +16150,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G473" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16173,7 +16176,7 @@
         <v>12.2346420288086</v>
       </c>
       <c r="G474" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16199,7 +16202,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G475" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16225,7 +16228,7 @@
         <v>13.0697040557861</v>
       </c>
       <c r="G476" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16251,7 +16254,7 @@
         <v>13.1473846435547</v>
       </c>
       <c r="G477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16277,7 +16280,7 @@
         <v>13.2056446075439</v>
       </c>
       <c r="G478" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16303,7 +16306,7 @@
         <v>13.0114440917969</v>
       </c>
       <c r="G479" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16329,7 +16332,7 @@
         <v>12.9337644577026</v>
       </c>
       <c r="G480" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16355,7 +16358,7 @@
         <v>12.6230430603027</v>
       </c>
       <c r="G481" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16381,7 +16384,7 @@
         <v>12.3123216629028</v>
       </c>
       <c r="G482" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16407,7 +16410,7 @@
         <v>12.4288415908813</v>
       </c>
       <c r="G483" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16433,7 +16436,7 @@
         <v>12.7784032821655</v>
       </c>
       <c r="G484" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16459,7 +16462,7 @@
         <v>12.3317422866821</v>
       </c>
       <c r="G485" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16485,7 +16488,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G486" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16511,7 +16514,7 @@
         <v>13.1085453033447</v>
       </c>
       <c r="G487" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16537,7 +16540,7 @@
         <v>13.7882471084595</v>
       </c>
       <c r="G488" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16563,7 +16566,7 @@
         <v>14.3708486557007</v>
       </c>
       <c r="G489" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16589,7 +16592,7 @@
         <v>14.1183881759644</v>
       </c>
       <c r="G490" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16615,7 +16618,7 @@
         <v>13.7299871444702</v>
       </c>
       <c r="G491" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16641,7 +16644,7 @@
         <v>14.2931690216064</v>
       </c>
       <c r="G492" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16667,7 +16670,7 @@
         <v>15.5943126678467</v>
       </c>
       <c r="G493" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16693,7 +16696,7 @@
         <v>15.7496738433838</v>
       </c>
       <c r="G494" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16719,7 +16722,7 @@
         <v>15.633152961731</v>
       </c>
       <c r="G495" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16745,7 +16748,7 @@
         <v>14.9146108627319</v>
       </c>
       <c r="G496" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16771,7 +16774,7 @@
         <v>16.0021343231201</v>
       </c>
       <c r="G497" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16797,7 +16800,7 @@
         <v>16.4876365661621</v>
       </c>
       <c r="G498" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16823,7 +16826,7 @@
         <v>16.7206764221191</v>
       </c>
       <c r="G499" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16849,7 +16852,7 @@
         <v>16.1186542510986</v>
       </c>
       <c r="G500" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16875,7 +16878,7 @@
         <v>15.6525726318359</v>
       </c>
       <c r="G501" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16901,7 +16904,7 @@
         <v>15.3030118942261</v>
       </c>
       <c r="G502" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16927,7 +16930,7 @@
         <v>15.1476516723633</v>
       </c>
       <c r="G503" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16953,7 +16956,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G504" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16979,7 +16982,7 @@
         <v>14.7009897232056</v>
       </c>
       <c r="G505" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -17005,7 +17008,7 @@
         <v>14.7980899810791</v>
       </c>
       <c r="G506" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -17031,7 +17034,7 @@
         <v>14.4485292434692</v>
       </c>
       <c r="G507" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -17057,7 +17060,7 @@
         <v>14.4679489135742</v>
       </c>
       <c r="G508" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -17083,7 +17086,7 @@
         <v>14.3125886917114</v>
       </c>
       <c r="G509" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17109,7 +17112,7 @@
         <v>14.7398300170898</v>
       </c>
       <c r="G510" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17135,7 +17138,7 @@
         <v>14.9922914505005</v>
       </c>
       <c r="G511" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17161,7 +17164,7 @@
         <v>15.4001121520996</v>
       </c>
       <c r="G512" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17187,7 +17190,7 @@
         <v>15.6914129257202</v>
       </c>
       <c r="G513" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17213,7 +17216,7 @@
         <v>15.128231048584</v>
       </c>
       <c r="G514" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17239,7 +17242,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G515" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17265,7 +17268,7 @@
         <v>15.4777927398682</v>
       </c>
       <c r="G516" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17291,7 +17294,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G517" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17317,7 +17320,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G518" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17343,7 +17346,7 @@
         <v>15.5748929977417</v>
       </c>
       <c r="G519" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17395,7 +17398,7 @@
         <v>15.3806915283203</v>
       </c>
       <c r="G521" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17941,7 +17944,7 @@
         <v>15.3612718582153</v>
       </c>
       <c r="G542" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -21945,7 +21948,7 @@
         <v>15.3418521881104</v>
       </c>
       <c r="G696" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -52815,27 +52818,105 @@
     </row>
     <row r="1884">
       <c r="A1884" s="1" t="n">
-        <v>45968.6911574074</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B1884" t="n">
-        <v>121411</v>
+        <v>52881</v>
       </c>
       <c r="C1884" t="n">
-        <v>21.5</v>
+        <v>22.1499996185303</v>
       </c>
       <c r="D1884" t="n">
-        <v>21.0499992370605</v>
+        <v>21.5499992370605</v>
       </c>
       <c r="E1884" t="n">
-        <v>21.3999996185303</v>
+        <v>22.1499996185303</v>
       </c>
       <c r="F1884" t="n">
-        <v>21.3999996185303</v>
+        <v>21.75</v>
       </c>
       <c r="G1884" t="s">
         <v>1168</v>
       </c>
       <c r="H1884" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1885" t="n">
+        <v>73369</v>
+      </c>
+      <c r="C1885" t="n">
+        <v>22.0499992370605</v>
+      </c>
+      <c r="D1885" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="E1885" t="n">
+        <v>22.0499992370605</v>
+      </c>
+      <c r="F1885" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G1885" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H1885" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1886" t="n">
+        <v>121411</v>
+      </c>
+      <c r="C1886" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D1886" t="n">
+        <v>21.0499992370605</v>
+      </c>
+      <c r="E1886" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F1886" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G1886" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H1886" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="1" t="n">
+        <v>45971.6913657407</v>
+      </c>
+      <c r="B1887" t="n">
+        <v>111922</v>
+      </c>
+      <c r="C1887" t="n">
+        <v>21.8500003814697</v>
+      </c>
+      <c r="D1887" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="E1887" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F1887" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G1887" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H1887" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CRL.MI.xlsx
+++ b/data/CRL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="1171">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">7.90288686752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81099224090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71910047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68969249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87348031997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96721315383911</t>
+    <t xml:space="preserve">7.81099319458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71909999847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68969202041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87348079681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96721363067627</t>
   </si>
   <si>
     <t xml:space="preserve">7.67407083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30281925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52520322799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46639060974121</t>
+    <t xml:space="preserve">7.97640180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44433641433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30281972885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46639108657837</t>
   </si>
   <si>
     <t xml:space="preserve">7.5720682144165</t>
@@ -86,88 +86,88 @@
     <t xml:space="preserve">7.4434175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52612161636353</t>
+    <t xml:space="preserve">7.52612209320068</t>
   </si>
   <si>
     <t xml:space="preserve">7.54450082778931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64742183685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85694026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92218494415283</t>
+    <t xml:space="preserve">7.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80180501937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85693979263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92218446731567</t>
   </si>
   <si>
     <t xml:space="preserve">8.00397109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86613035202026</t>
+    <t xml:space="preserve">7.86612987518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.01959228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81466865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76504564285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85142755508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69336891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79261541366577</t>
+    <t xml:space="preserve">7.81466960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76504802703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85142660140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69336843490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7926139831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74666833877563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88910293579102</t>
+    <t xml:space="preserve">7.88910388946533</t>
   </si>
   <si>
     <t xml:space="preserve">7.56379842758179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67315244674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78526306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74850606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99478054046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06002521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11424350738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30354499816895</t>
+    <t xml:space="preserve">7.67315196990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78526401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74850511550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99478149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06002712249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11424446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30354404449463</t>
   </si>
   <si>
     <t xml:space="preserve">8.46344089508057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48641395568848</t>
+    <t xml:space="preserve">8.48641300201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.75382518768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95966911315918</t>
+    <t xml:space="preserve">8.95966720581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.60128211975098</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">8.25208377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46987152099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36235809326172</t>
+    <t xml:space="preserve">8.46987342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3623571395874</t>
   </si>
   <si>
     <t xml:space="preserve">8.45425224304199</t>
@@ -191,52 +191,52 @@
     <t xml:space="preserve">8.7115535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74831295013428</t>
+    <t xml:space="preserve">8.74831199645996</t>
   </si>
   <si>
     <t xml:space="preserve">8.61598587036133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66560649871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79426002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.005615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86869335174561</t>
+    <t xml:space="preserve">8.66560840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7942590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00561618804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86869430541992</t>
   </si>
   <si>
     <t xml:space="preserve">9.11588954925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14345645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33643436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09750938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11680793762207</t>
+    <t xml:space="preserve">9.14345550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33643341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11680603027344</t>
   </si>
   <si>
     <t xml:space="preserve">8.99091243743896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18572807312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06167125701904</t>
+    <t xml:space="preserve">9.18572998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06167030334473</t>
   </si>
   <si>
     <t xml:space="preserve">9.02399349212646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76577186584473</t>
+    <t xml:space="preserve">8.76576995849609</t>
   </si>
   <si>
     <t xml:space="preserve">8.9936695098877</t>
@@ -245,46 +245,46 @@
     <t xml:space="preserve">9.04237365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90177536010742</t>
+    <t xml:space="preserve">8.90177440643311</t>
   </si>
   <si>
     <t xml:space="preserve">8.67112159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98191356658936</t>
+    <t xml:space="preserve">8.50754833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9819164276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.30630207061768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40830421447754</t>
+    <t xml:space="preserve">8.40830326080322</t>
   </si>
   <si>
     <t xml:space="preserve">8.54614543914795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59209156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63803958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80804252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02970027923584</t>
+    <t xml:space="preserve">8.59209251403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63803863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80804347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02970218658447</t>
   </si>
   <si>
     <t xml:space="preserve">7.75126314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92126369476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34214019775391</t>
+    <t xml:space="preserve">7.92126560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34214115142822</t>
   </si>
   <si>
     <t xml:space="preserve">8.77496147155762</t>
@@ -302,34 +302,34 @@
     <t xml:space="preserve">8.59944438934326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70144748687744</t>
+    <t xml:space="preserve">8.70144653320312</t>
   </si>
   <si>
     <t xml:space="preserve">8.57738971710205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3926830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34122276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5608491897583</t>
+    <t xml:space="preserve">8.39268207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34122180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085014343262</t>
   </si>
   <si>
     <t xml:space="preserve">8.71982479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05451202392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04164791107178</t>
+    <t xml:space="preserve">8.0545129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04164695739746</t>
   </si>
   <si>
     <t xml:space="preserve">8.0866756439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18867683410645</t>
+    <t xml:space="preserve">8.18867778778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.54890251159668</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">8.92107486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03869533538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97437191009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01664257049561</t>
+    <t xml:space="preserve">9.03869724273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9743709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01664447784424</t>
   </si>
   <si>
     <t xml:space="preserve">9.15264701843262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84939479827881</t>
+    <t xml:space="preserve">8.84939575195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.07913017272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8558292388916</t>
+    <t xml:space="preserve">8.85582828521729</t>
   </si>
   <si>
     <t xml:space="preserve">8.30446434020996</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">8.33754539489746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20062255859375</t>
+    <t xml:space="preserve">8.20062446594238</t>
   </si>
   <si>
     <t xml:space="preserve">8.40370941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27413845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2980318069458</t>
+    <t xml:space="preserve">8.27413940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29803276062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.50019836425781</t>
@@ -401,28 +401,28 @@
     <t xml:space="preserve">8.35408592224121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22083950042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15283870697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39911556243896</t>
+    <t xml:space="preserve">8.22084045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15283966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39911460876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.42668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48365783691406</t>
+    <t xml:space="preserve">8.48365688323975</t>
   </si>
   <si>
     <t xml:space="preserve">8.709716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77128505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72074317932129</t>
+    <t xml:space="preserve">8.77128601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72074413299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.100266456604</t>
@@ -437,34 +437,34 @@
     <t xml:space="preserve">8.83469390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97712898254395</t>
+    <t xml:space="preserve">8.97712802886963</t>
   </si>
   <si>
     <t xml:space="preserve">9.05156230926514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23534965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20594501495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36216354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39524745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61027908325195</t>
+    <t xml:space="preserve">9.2353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20594596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36216449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3952465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61027812957764</t>
   </si>
   <si>
     <t xml:space="preserve">9.64887428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69482135772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59373760223389</t>
+    <t xml:space="preserve">9.69482040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59373664855957</t>
   </si>
   <si>
     <t xml:space="preserve">9.64336013793945</t>
@@ -476,61 +476,61 @@
     <t xml:space="preserve">9.61763000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49265289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51103210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28497314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46324825286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3309211730957</t>
+    <t xml:space="preserve">9.49265480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5110330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28497505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46324729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33091926574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.12875366210938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26291942596436</t>
+    <t xml:space="preserve">9.26291847229004</t>
   </si>
   <si>
     <t xml:space="preserve">9.14713287353516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06075286865234</t>
+    <t xml:space="preserve">9.06075191497803</t>
   </si>
   <si>
     <t xml:space="preserve">8.9412899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37797832489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76025676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00653457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18940448760986</t>
+    <t xml:space="preserve">8.37797927856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76025867462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0065336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18940353393555</t>
   </si>
   <si>
     <t xml:space="preserve">8.96885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1067008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44670677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39157104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74076843261719</t>
+    <t xml:space="preserve">9.10669994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44670581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39157009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74076747894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.46508598327637</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">9.53859996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75914669036865</t>
+    <t xml:space="preserve">9.75914573669434</t>
   </si>
   <si>
     <t xml:space="preserve">9.68563270568848</t>
@@ -548,52 +548,52 @@
     <t xml:space="preserve">9.90617752075195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99807167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0532073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79590511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9245548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81428337097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9429349899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0715856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083431243896</t>
+    <t xml:space="preserve">9.99807071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0532083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79590606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92455768585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81428241729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94293594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0715866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.108344078064</t>
   </si>
   <si>
     <t xml:space="preserve">9.6672534942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83266162872314</t>
+    <t xml:space="preserve">9.77752494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83266258239746</t>
   </si>
   <si>
     <t xml:space="preserve">9.86942005157471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1451005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1634798049927</t>
+    <t xml:space="preserve">10.1451015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.163480758667</t>
   </si>
   <si>
     <t xml:space="preserve">10.310510635376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0348300933838</t>
+    <t xml:space="preserve">10.0348291397095</t>
   </si>
   <si>
     <t xml:space="preserve">10.0164499282837</t>
@@ -605,49 +605,49 @@
     <t xml:space="preserve">10.5126781463623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6045722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659707069397</t>
+    <t xml:space="preserve">10.6045713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597089767456</t>
   </si>
   <si>
     <t xml:space="preserve">10.7332229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4207820892334</t>
+    <t xml:space="preserve">10.4207849502563</t>
   </si>
   <si>
     <t xml:space="preserve">10.4759216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4391622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3288888931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97969245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85104179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94108772277832</t>
+    <t xml:space="preserve">10.4391613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3288908004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97969341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85103893280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.941086769104</t>
   </si>
   <si>
     <t xml:space="preserve">9.8854455947876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92253971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve"